--- a/Financial Analysis/BE.xlsx
+++ b/Financial Analysis/BE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C592E6F3-13B1-431E-B342-A53BD757DFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3405BCD-E2F6-4D6C-8C6A-9B54C676DC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FD927F57-917F-4496-A6AC-5E97F081D2C4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FD927F57-917F-4496-A6AC-5E97F081D2C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="102">
   <si>
     <t>BE</t>
   </si>
@@ -254,6 +254,84 @@
   </si>
   <si>
     <t>no idea what revenue is going to drive profits</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Restricted cash</t>
+  </si>
+  <si>
+    <t>A/R</t>
+  </si>
+  <si>
+    <t>Contract assets</t>
+  </si>
+  <si>
+    <t>Inventories</t>
+  </si>
+  <si>
+    <t>D/R</t>
+  </si>
+  <si>
+    <t>Prepaids</t>
+  </si>
+  <si>
+    <t>Current assets</t>
+  </si>
+  <si>
+    <t>PP&amp;E</t>
+  </si>
+  <si>
+    <t>Operating leases</t>
+  </si>
+  <si>
+    <t>ONCA</t>
+  </si>
+  <si>
+    <t>Non-current assets</t>
+  </si>
+  <si>
+    <t>Total assets</t>
+  </si>
+  <si>
+    <t>A/P</t>
+  </si>
+  <si>
+    <t>A/W</t>
+  </si>
+  <si>
+    <t>A/L</t>
+  </si>
+  <si>
+    <t>Recourse debt</t>
+  </si>
+  <si>
+    <t>Non-recourse debt</t>
+  </si>
+  <si>
+    <t>Current liabilities</t>
+  </si>
+  <si>
+    <t>ONCL</t>
+  </si>
+  <si>
+    <t>Non-current liablities</t>
+  </si>
+  <si>
+    <t>S/E</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
   </si>
 </sst>
 </file>
@@ -263,7 +341,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +371,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -314,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -332,6 +419,7 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -353,14 +441,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -377,7 +465,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8823960" y="7620"/>
+          <a:off x="10660380" y="7620"/>
           <a:ext cx="0" cy="9060180"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -403,14 +491,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -427,7 +515,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12496800" y="7620"/>
+          <a:off x="15521940" y="7620"/>
           <a:ext cx="0" cy="9608820"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -776,17 +864,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="7">
-        <v>24.61</v>
+        <v>70.709999999999994</v>
       </c>
       <c r="E3" s="3">
-        <v>45617</v>
+        <v>45927</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45617</v>
+        <v>45927</v>
       </c>
       <c r="G3" s="3">
-        <v>45694</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -794,7 +882,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -803,7 +895,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>5625.8459999999995</v>
+        <v>16546.14</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -811,8 +903,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>495.7+22.5+30.9</f>
-        <v>549.1</v>
+        <f>574.8</f>
+        <v>574.79999999999995</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -820,8 +915,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>20.9+114.1+390.5+1008.7+4.6</f>
-        <v>1538.8</v>
+        <f>219.8+1126.2</f>
+        <v>1346</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="I7" t="s">
         <v>75</v>
@@ -833,7 +931,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>-989.69999999999993</v>
+        <v>-771.2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -842,7 +940,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>6615.5459999999994</v>
+        <v>17317.34</v>
       </c>
     </row>
   </sheetData>
@@ -852,15 +950,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53B87E8-B0FD-46B4-8D96-88D1F839B6F5}">
-  <dimension ref="B2:EK48"/>
+  <dimension ref="B2:EO83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.44140625" customWidth="1"/>
-    <col min="35" max="35" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.44140625" customWidth="1"/>
+    <col min="39" max="39" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:35" x14ac:dyDescent="0.3">
       <c r="C2" s="5" t="s">
         <v>38</v>
       </c>
@@ -897,56 +995,68 @@
       <c r="N2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="P2">
+      <c r="O2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="T2">
         <v>2020</v>
       </c>
-      <c r="Q2">
+      <c r="U2">
         <v>2021</v>
       </c>
-      <c r="R2">
+      <c r="V2">
         <v>2022</v>
       </c>
-      <c r="S2">
+      <c r="W2">
         <v>2023</v>
       </c>
-      <c r="T2">
+      <c r="X2">
         <v>2024</v>
       </c>
-      <c r="U2">
+      <c r="Y2">
         <v>2025</v>
       </c>
-      <c r="V2">
+      <c r="Z2">
         <v>2026</v>
       </c>
-      <c r="W2">
+      <c r="AA2">
         <v>2027</v>
       </c>
-      <c r="X2">
+      <c r="AB2">
         <v>2028</v>
       </c>
-      <c r="Y2">
+      <c r="AC2">
         <v>2029</v>
       </c>
-      <c r="Z2">
+      <c r="AD2">
         <v>2030</v>
       </c>
-      <c r="AA2">
+      <c r="AE2">
         <v>2031</v>
       </c>
-      <c r="AB2">
+      <c r="AF2">
         <v>2032</v>
       </c>
-      <c r="AC2">
+      <c r="AG2">
         <v>2033</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2034</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -975,72 +1085,85 @@
         <v>233.8</v>
       </c>
       <c r="N3" s="4">
-        <f>J3*0.95</f>
-        <v>248.71</v>
+        <v>471.7</v>
+      </c>
+      <c r="O3" s="4">
+        <v>211.9</v>
       </c>
       <c r="P3" s="4">
+        <v>296.60000000000002</v>
+      </c>
+      <c r="Q3" s="4">
+        <f>M3*1.3</f>
+        <v>303.94</v>
+      </c>
+      <c r="R3" s="4">
+        <f>N3*1.05</f>
+        <v>495.28500000000003</v>
+      </c>
+      <c r="T3" s="4">
         <v>518.6</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="U3" s="4">
         <v>663.5</v>
       </c>
-      <c r="R3" s="4">
+      <c r="V3" s="4">
         <v>880.7</v>
       </c>
-      <c r="S3" s="4">
+      <c r="W3" s="4">
         <f>SUM(G3:J3)</f>
         <v>975.2</v>
       </c>
-      <c r="T3" s="4">
+      <c r="X3" s="4">
         <f>SUM(K3:N3)</f>
-        <v>862.21</v>
-      </c>
-      <c r="U3" s="4">
-        <f>T3*1.02</f>
-        <v>879.45420000000001</v>
-      </c>
-      <c r="V3" s="4">
-        <f>U3*1.05</f>
-        <v>923.42691000000002</v>
-      </c>
-      <c r="W3" s="4">
-        <f>V3*1.1</f>
-        <v>1015.7696010000001</v>
-      </c>
-      <c r="X3" s="4">
-        <f>W3*1.1</f>
-        <v>1117.3465611000001</v>
+        <v>1085.2</v>
       </c>
       <c r="Y3" s="4">
-        <f>X3*1.1</f>
-        <v>1229.0812172100002</v>
+        <f>SUM(O3:R3)</f>
+        <v>1307.7250000000001</v>
       </c>
       <c r="Z3" s="4">
-        <f>Y3*1.08</f>
-        <v>1327.4077145868002</v>
+        <f>Y3*1.14</f>
+        <v>1490.8064999999999</v>
       </c>
       <c r="AA3" s="4">
-        <f>Z3*1.05</f>
-        <v>1393.7781003161404</v>
+        <f>Z3*1.1</f>
+        <v>1639.88715</v>
       </c>
       <c r="AB3" s="4">
-        <f>AA3*1.04</f>
-        <v>1449.5292243287861</v>
+        <f>AA3*1.1</f>
+        <v>1803.8758650000002</v>
       </c>
       <c r="AC3" s="4">
-        <f t="shared" ref="Y3:AE3" si="0">AB3*1.03</f>
-        <v>1493.0151010586496</v>
+        <f>AB3*1.1</f>
+        <v>1984.2634515000004</v>
       </c>
       <c r="AD3" s="4">
+        <f>AC3*1.08</f>
+        <v>2143.0045276200008</v>
+      </c>
+      <c r="AE3" s="4">
+        <f>AD3*1.05</f>
+        <v>2250.154754001001</v>
+      </c>
+      <c r="AF3" s="4">
+        <f>AE3*1.04</f>
+        <v>2340.1609441610412</v>
+      </c>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AI3" si="0">AF3*1.03</f>
+        <v>2410.3657724858726</v>
+      </c>
+      <c r="AH3" s="4">
         <f t="shared" si="0"/>
-        <v>1537.8055540904093</v>
-      </c>
-      <c r="AE3" s="4">
+        <v>2482.6767456604489</v>
+      </c>
+      <c r="AI3" s="4">
         <f t="shared" si="0"/>
-        <v>1583.9397207131217</v>
-      </c>
-    </row>
-    <row r="4" spans="2:31" x14ac:dyDescent="0.3">
+        <v>2557.1570480302626</v>
+      </c>
+    </row>
+    <row r="4" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -1069,71 +1192,85 @@
         <v>32.1</v>
       </c>
       <c r="N4" s="4">
-        <f>J4*1.5</f>
-        <v>39</v>
+        <v>36.1</v>
+      </c>
+      <c r="O4" s="4">
+        <v>33.700000000000003</v>
       </c>
       <c r="P4" s="4">
+        <v>37.4</v>
+      </c>
+      <c r="Q4" s="4">
+        <f t="shared" ref="Q4" si="1">M4*1.05</f>
+        <v>33.705000000000005</v>
+      </c>
+      <c r="R4" s="4">
+        <f>N4*1.05</f>
+        <v>37.905000000000001</v>
+      </c>
+      <c r="T4" s="4">
         <v>101.9</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="U4" s="4">
         <v>96.1</v>
       </c>
-      <c r="R4" s="4">
+      <c r="V4" s="4">
         <v>92.1</v>
       </c>
-      <c r="S4" s="4">
+      <c r="W4" s="4">
         <f>SUM(G4:J4)</f>
         <v>92.6</v>
       </c>
-      <c r="T4" s="4">
+      <c r="X4" s="4">
         <f>SUM(K4:N4)</f>
-        <v>125.2</v>
-      </c>
-      <c r="U4" s="4">
-        <v>170</v>
-      </c>
-      <c r="V4" s="4">
-        <f>U4*1.25</f>
-        <v>212.5</v>
-      </c>
-      <c r="W4" s="4">
-        <f>V4*1.2</f>
-        <v>255</v>
-      </c>
-      <c r="X4" s="4">
-        <f>W4*1.15</f>
-        <v>293.25</v>
+        <v>122.30000000000001</v>
       </c>
       <c r="Y4" s="4">
-        <f>X4*1.08</f>
-        <v>316.71000000000004</v>
+        <f t="shared" ref="Y4:Y6" si="2">SUM(O4:R4)</f>
+        <v>142.71</v>
       </c>
       <c r="Z4" s="4">
-        <f>Y4*1.04</f>
-        <v>329.37840000000006</v>
+        <f>Y4*1.25</f>
+        <v>178.38750000000002</v>
       </c>
       <c r="AA4" s="4">
-        <f>Z4*1.03</f>
-        <v>339.25975200000005</v>
+        <f>Z4*1.2</f>
+        <v>214.06500000000003</v>
       </c>
       <c r="AB4" s="4">
-        <f t="shared" ref="AA4:AE4" si="1">AA4*1.02</f>
-        <v>346.04494704000007</v>
+        <f>AA4*1.15</f>
+        <v>246.17475000000002</v>
       </c>
       <c r="AC4" s="4">
-        <f t="shared" si="1"/>
-        <v>352.96584598080005</v>
+        <f>AB4*1.08</f>
+        <v>265.86873000000003</v>
       </c>
       <c r="AD4" s="4">
-        <f t="shared" si="1"/>
-        <v>360.02516290041603</v>
+        <f>AC4*1.05</f>
+        <v>279.16216650000007</v>
       </c>
       <c r="AE4" s="4">
-        <f t="shared" si="1"/>
-        <v>367.22566615842436</v>
-      </c>
-    </row>
-    <row r="5" spans="2:31" x14ac:dyDescent="0.3">
+        <f>AD4*1.04</f>
+        <v>290.3286531600001</v>
+      </c>
+      <c r="AF4" s="4">
+        <f>AE4*1.03</f>
+        <v>299.03851275480014</v>
+      </c>
+      <c r="AG4" s="4">
+        <f t="shared" ref="AG4:AI4" si="3">AF4*1.02</f>
+        <v>305.01928300989613</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="3"/>
+        <v>311.11966867009403</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="3"/>
+        <v>317.3420620434959</v>
+      </c>
+    </row>
+    <row r="5" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -1162,72 +1299,85 @@
         <v>50.8</v>
       </c>
       <c r="N5" s="4">
-        <f>J5*1.07</f>
-        <v>56.282000000000004</v>
+        <v>53.8</v>
+      </c>
+      <c r="O5" s="4">
+        <v>53.5</v>
       </c>
       <c r="P5" s="4">
+        <v>54.4</v>
+      </c>
+      <c r="Q5" s="4">
+        <f t="shared" ref="Q5:R5" si="4">M5*1.02</f>
+        <v>51.815999999999995</v>
+      </c>
+      <c r="R5" s="4">
+        <f t="shared" si="4"/>
+        <v>54.875999999999998</v>
+      </c>
+      <c r="T5" s="4">
         <v>109.6</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="U5" s="4">
         <v>144.19999999999999</v>
       </c>
-      <c r="R5" s="4">
+      <c r="V5" s="4">
         <v>151</v>
       </c>
-      <c r="S5" s="4">
+      <c r="W5" s="4">
         <f>SUM(G5:J5)</f>
         <v>183.1</v>
       </c>
-      <c r="T5" s="4">
+      <c r="X5" s="4">
         <f>SUM(K5:N5)</f>
-        <v>215.982</v>
-      </c>
-      <c r="U5" s="4">
-        <f>T5*1.14</f>
-        <v>246.21947999999998</v>
-      </c>
-      <c r="V5" s="4">
-        <f>U5*1.1</f>
-        <v>270.84142800000001</v>
-      </c>
-      <c r="W5" s="4">
-        <f>V5*1.07</f>
-        <v>289.80032796</v>
-      </c>
-      <c r="X5" s="4">
-        <f>W5*1.04</f>
-        <v>301.39234107840002</v>
+        <v>213.5</v>
       </c>
       <c r="Y5" s="4">
-        <f>X5*1.03</f>
-        <v>310.43411131075203</v>
+        <f t="shared" si="2"/>
+        <v>214.59200000000001</v>
       </c>
       <c r="Z5" s="4">
-        <f>Y5*1.02</f>
-        <v>316.64279353696708</v>
+        <f>Y5*1.1</f>
+        <v>236.05120000000002</v>
       </c>
       <c r="AA5" s="4">
-        <f t="shared" ref="AA5:AE5" si="2">Z5*1.02</f>
-        <v>322.97564940770644</v>
+        <f>Z5*1.07</f>
+        <v>252.57478400000005</v>
       </c>
       <c r="AB5" s="4">
-        <f t="shared" si="2"/>
-        <v>329.43516239586057</v>
+        <f>AA5*1.04</f>
+        <v>262.67777536000006</v>
       </c>
       <c r="AC5" s="4">
-        <f t="shared" si="2"/>
-        <v>336.02386564377781</v>
+        <f>AB5*1.03</f>
+        <v>270.55810862080006</v>
       </c>
       <c r="AD5" s="4">
-        <f t="shared" si="2"/>
-        <v>342.74434295665338</v>
+        <f>AC5*1.02</f>
+        <v>275.96927079321608</v>
       </c>
       <c r="AE5" s="4">
-        <f t="shared" si="2"/>
-        <v>349.59922981578643</v>
-      </c>
-    </row>
-    <row r="6" spans="2:31" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AE5:AI5" si="5">AD5*1.02</f>
+        <v>281.48865620908043</v>
+      </c>
+      <c r="AF5" s="4">
+        <f t="shared" si="5"/>
+        <v>287.11842933326204</v>
+      </c>
+      <c r="AG5" s="4">
+        <f t="shared" si="5"/>
+        <v>292.86079791992728</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="5"/>
+        <v>298.71801387832585</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="5"/>
+        <v>304.69237415589237</v>
+      </c>
+    </row>
+    <row r="6" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>14</v>
       </c>
@@ -1256,177 +1406,206 @@
         <v>13.8</v>
       </c>
       <c r="N6" s="4">
-        <f>J6*0.85</f>
-        <v>14.025</v>
+        <v>10.8</v>
+      </c>
+      <c r="O6" s="4">
+        <v>27</v>
       </c>
       <c r="P6" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="Q6" s="4">
+        <f t="shared" ref="Q6:R6" si="6">M6*1.9</f>
+        <v>26.22</v>
+      </c>
+      <c r="R6" s="4">
+        <f t="shared" si="6"/>
+        <v>20.52</v>
+      </c>
+      <c r="T6" s="4">
         <v>64.099999999999994</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="U6" s="4">
         <v>68.400000000000006</v>
       </c>
-      <c r="R6" s="4">
+      <c r="V6" s="4">
         <v>75.400000000000006</v>
       </c>
-      <c r="S6" s="4">
+      <c r="W6" s="4">
         <f>SUM(G6:J6)</f>
         <v>82.4</v>
       </c>
-      <c r="T6" s="4">
+      <c r="X6" s="4">
         <f>SUM(K6:N6)</f>
-        <v>56.024999999999999</v>
-      </c>
-      <c r="U6" s="4">
-        <f>T6*1.2</f>
-        <v>67.22999999999999</v>
-      </c>
-      <c r="V6" s="4">
-        <f t="shared" ref="V6:AE6" si="3">U6*1.2</f>
-        <v>80.675999999999988</v>
-      </c>
-      <c r="W6" s="4">
-        <f>V6*1.05</f>
-        <v>84.709799999999987</v>
-      </c>
-      <c r="X6" s="4">
-        <f t="shared" ref="X6:AE6" si="4">W6*1.05</f>
-        <v>88.945289999999986</v>
+        <v>52.8</v>
       </c>
       <c r="Y6" s="4">
-        <f t="shared" si="4"/>
-        <v>93.392554499999989</v>
+        <f t="shared" si="2"/>
+        <v>86.539999999999992</v>
       </c>
       <c r="Z6" s="4">
-        <f t="shared" si="4"/>
-        <v>98.062182224999987</v>
+        <f t="shared" ref="Z6" si="7">Y6*1.2</f>
+        <v>103.84799999999998</v>
       </c>
       <c r="AA6" s="4">
-        <f t="shared" si="4"/>
-        <v>102.96529133624999</v>
+        <f>Z6*1.05</f>
+        <v>109.04039999999999</v>
       </c>
       <c r="AB6" s="4">
-        <f t="shared" si="4"/>
-        <v>108.11355590306249</v>
+        <f t="shared" ref="AB6:AI6" si="8">AA6*1.05</f>
+        <v>114.49242</v>
       </c>
       <c r="AC6" s="4">
-        <f t="shared" si="4"/>
-        <v>113.51923369821561</v>
+        <f t="shared" si="8"/>
+        <v>120.21704099999999</v>
       </c>
       <c r="AD6" s="4">
-        <f t="shared" si="4"/>
-        <v>119.1951953831264</v>
+        <f t="shared" si="8"/>
+        <v>126.22789305000001</v>
       </c>
       <c r="AE6" s="4">
-        <f t="shared" si="4"/>
-        <v>125.15495515228272</v>
-      </c>
-    </row>
-    <row r="7" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>132.53928770250002</v>
+      </c>
+      <c r="AF6" s="4">
+        <f t="shared" si="8"/>
+        <v>139.16625208762503</v>
+      </c>
+      <c r="AG6" s="4">
+        <f t="shared" si="8"/>
+        <v>146.12456469200629</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="8"/>
+        <v>153.43079292660661</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="8"/>
+        <v>161.10233257293694</v>
+      </c>
+    </row>
+    <row r="7" spans="2:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="8">
-        <f>SUM(F3:F6)</f>
+        <f t="shared" ref="F7:O7" si="9">SUM(F3:F6)</f>
         <v>462.49999999999994</v>
       </c>
       <c r="G7" s="8">
-        <f>SUM(G3:G6)</f>
+        <f t="shared" si="9"/>
         <v>275.2</v>
       </c>
       <c r="H7" s="8">
-        <f>SUM(H3:H6)</f>
+        <f t="shared" si="9"/>
         <v>301</v>
       </c>
       <c r="I7" s="8">
-        <f>SUM(I3:I6)</f>
+        <f t="shared" si="9"/>
         <v>400.2</v>
       </c>
       <c r="J7" s="8">
-        <f>SUM(J3:J6)</f>
+        <f t="shared" si="9"/>
         <v>356.90000000000003</v>
       </c>
       <c r="K7" s="8">
-        <f>SUM(K3:K6)</f>
+        <f t="shared" si="9"/>
         <v>235.20000000000002</v>
       </c>
       <c r="L7" s="8">
-        <f>SUM(L3:L6)</f>
+        <f t="shared" si="9"/>
         <v>335.7</v>
       </c>
       <c r="M7" s="8">
-        <f>SUM(M3:M6)</f>
+        <f t="shared" si="9"/>
         <v>330.50000000000006</v>
       </c>
       <c r="N7" s="8">
-        <f>SUM(N3:N6)</f>
-        <v>358.017</v>
+        <f t="shared" si="9"/>
+        <v>572.4</v>
+      </c>
+      <c r="O7" s="8">
+        <f t="shared" si="9"/>
+        <v>326.10000000000002</v>
       </c>
       <c r="P7" s="8">
-        <f>SUM(P3:P6)</f>
-        <v>794.2</v>
+        <f t="shared" ref="P7" si="10">SUM(P3:P6)</f>
+        <v>401.2</v>
       </c>
       <c r="Q7" s="8">
-        <f>SUM(Q3:Q6)</f>
-        <v>972.19999999999993</v>
+        <f t="shared" ref="Q7" si="11">SUM(Q3:Q6)</f>
+        <v>415.68099999999993</v>
       </c>
       <c r="R7" s="8">
-        <f>SUM(R3:R6)</f>
-        <v>1199.2000000000003</v>
-      </c>
-      <c r="S7" s="8">
-        <f>SUM(S3:S6)</f>
-        <v>1333.3</v>
+        <f t="shared" ref="R7" si="12">SUM(R3:R6)</f>
+        <v>608.58600000000001</v>
       </c>
       <c r="T7" s="8">
         <f>SUM(T3:T6)</f>
-        <v>1259.4170000000001</v>
+        <v>794.2</v>
       </c>
       <c r="U7" s="8">
-        <f t="shared" ref="U7:AE7" si="5">SUM(U3:U6)</f>
-        <v>1362.9036800000001</v>
+        <f>SUM(U3:U6)</f>
+        <v>972.19999999999993</v>
       </c>
       <c r="V7" s="8">
-        <f t="shared" si="5"/>
-        <v>1487.444338</v>
+        <f>SUM(V3:V6)</f>
+        <v>1199.2000000000003</v>
       </c>
       <c r="W7" s="8">
-        <f t="shared" si="5"/>
-        <v>1645.2797289600001</v>
+        <f>SUM(W3:W6)</f>
+        <v>1333.3</v>
       </c>
       <c r="X7" s="8">
-        <f t="shared" si="5"/>
-        <v>1800.9341921784001</v>
+        <f>SUM(X3:X6)</f>
+        <v>1473.8</v>
       </c>
       <c r="Y7" s="8">
-        <f t="shared" si="5"/>
-        <v>1949.6178830207523</v>
+        <f t="shared" ref="Y7:AI7" si="13">SUM(Y3:Y6)</f>
+        <v>1751.5670000000002</v>
       </c>
       <c r="Z7" s="8">
-        <f t="shared" si="5"/>
-        <v>2071.4910903487671</v>
+        <f t="shared" si="13"/>
+        <v>2009.0932</v>
       </c>
       <c r="AA7" s="8">
-        <f t="shared" si="5"/>
-        <v>2158.9787930600969</v>
+        <f t="shared" si="13"/>
+        <v>2215.5673339999998</v>
       </c>
       <c r="AB7" s="8">
-        <f t="shared" si="5"/>
-        <v>2233.1228896677094</v>
+        <f t="shared" si="13"/>
+        <v>2427.2208103600001</v>
       </c>
       <c r="AC7" s="8">
-        <f t="shared" si="5"/>
-        <v>2295.524046381443</v>
+        <f t="shared" si="13"/>
+        <v>2640.9073311208003</v>
       </c>
       <c r="AD7" s="8">
-        <f t="shared" si="5"/>
-        <v>2359.7702553306049</v>
+        <f t="shared" si="13"/>
+        <v>2824.3638579632175</v>
       </c>
       <c r="AE7" s="8">
-        <f t="shared" si="5"/>
-        <v>2425.9195718396154</v>
-      </c>
-    </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.3">
+        <f t="shared" si="13"/>
+        <v>2954.5113510725819</v>
+      </c>
+      <c r="AF7" s="8">
+        <f t="shared" si="13"/>
+        <v>3065.4841383367284</v>
+      </c>
+      <c r="AG7" s="8">
+        <f t="shared" si="13"/>
+        <v>3154.3704181077028</v>
+      </c>
+      <c r="AH7" s="8">
+        <f t="shared" si="13"/>
+        <v>3245.9452211354755</v>
+      </c>
+      <c r="AI7" s="8">
+        <f t="shared" si="13"/>
+        <v>3340.293816802588</v>
+      </c>
+    </row>
+    <row r="8" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -1455,72 +1634,85 @@
         <v>155.1</v>
       </c>
       <c r="N8" s="4">
-        <f>N3*0.61</f>
-        <v>151.7131</v>
+        <v>253.7</v>
+      </c>
+      <c r="O8" s="4">
+        <v>139.6</v>
       </c>
       <c r="P8" s="4">
+        <v>198.7</v>
+      </c>
+      <c r="Q8" s="4">
+        <f t="shared" ref="Q8" si="14">Q3*0.65</f>
+        <v>197.56100000000001</v>
+      </c>
+      <c r="R8" s="4">
+        <f>R3*0.55</f>
+        <v>272.40675000000005</v>
+      </c>
+      <c r="T8" s="4">
         <v>332.7</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="U8" s="4">
         <v>471.7</v>
       </c>
-      <c r="R8" s="4">
+      <c r="V8" s="4">
         <v>616.20000000000005</v>
       </c>
-      <c r="S8" s="4">
+      <c r="W8" s="4">
         <f>SUM(G8:J8)</f>
         <v>630.09999999999991</v>
       </c>
-      <c r="T8" s="4">
+      <c r="X8" s="4">
         <f>SUM(K8:N8)</f>
-        <v>583.91309999999999</v>
-      </c>
-      <c r="U8" s="4">
-        <f>U3*0.67</f>
-        <v>589.23431400000004</v>
-      </c>
-      <c r="V8" s="4">
-        <f t="shared" ref="V8:AE8" si="6">V3*0.67</f>
-        <v>618.69602970000005</v>
-      </c>
-      <c r="W8" s="4">
-        <f t="shared" si="6"/>
-        <v>680.56563267000013</v>
-      </c>
-      <c r="X8" s="4">
-        <f t="shared" si="6"/>
-        <v>748.62219593700013</v>
+        <v>685.90000000000009</v>
       </c>
       <c r="Y8" s="4">
-        <f t="shared" si="6"/>
-        <v>823.48441553070018</v>
+        <f t="shared" ref="Y8:Y11" si="15">SUM(O8:R8)</f>
+        <v>808.26774999999998</v>
       </c>
       <c r="Z8" s="4">
-        <f t="shared" si="6"/>
-        <v>889.36316877315619</v>
+        <f>Z3*0.6</f>
+        <v>894.48389999999995</v>
       </c>
       <c r="AA8" s="4">
-        <f t="shared" si="6"/>
-        <v>933.83132721181414</v>
+        <f t="shared" ref="AA8:AI8" si="16">AA3*0.6</f>
+        <v>983.93228999999997</v>
       </c>
       <c r="AB8" s="4">
-        <f t="shared" si="6"/>
-        <v>971.18458030028671</v>
+        <f t="shared" si="16"/>
+        <v>1082.325519</v>
       </c>
       <c r="AC8" s="4">
-        <f t="shared" si="6"/>
-        <v>1000.3201177092953</v>
+        <f t="shared" si="16"/>
+        <v>1190.5580709000003</v>
       </c>
       <c r="AD8" s="4">
-        <f t="shared" si="6"/>
-        <v>1030.3297212405744</v>
+        <f t="shared" si="16"/>
+        <v>1285.8027165720005</v>
       </c>
       <c r="AE8" s="4">
-        <f t="shared" si="6"/>
-        <v>1061.2396128777916</v>
-      </c>
-    </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>1350.0928524006006</v>
+      </c>
+      <c r="AF8" s="4">
+        <f t="shared" si="16"/>
+        <v>1404.0965664966247</v>
+      </c>
+      <c r="AG8" s="4">
+        <f t="shared" si="16"/>
+        <v>1446.2194634915236</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="16"/>
+        <v>1489.6060473962693</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="16"/>
+        <v>1534.2942288181575</v>
+      </c>
+    </row>
+    <row r="9" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -1549,72 +1741,85 @@
         <v>35.700000000000003</v>
       </c>
       <c r="N9" s="4">
-        <f>N4*0.9</f>
-        <v>35.1</v>
+        <v>34.1</v>
+      </c>
+      <c r="O9" s="4">
+        <v>33.299999999999997</v>
       </c>
       <c r="P9" s="4">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="Q9" s="4">
+        <f>Q4*0.92</f>
+        <v>31.008600000000005</v>
+      </c>
+      <c r="R9" s="4">
+        <f>R4*0.88</f>
+        <v>33.356400000000001</v>
+      </c>
+      <c r="T9" s="4">
         <v>116.5</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="U9" s="4">
         <v>110.2</v>
       </c>
-      <c r="R9" s="4">
+      <c r="V9" s="4">
         <v>104.1</v>
       </c>
-      <c r="S9" s="4">
+      <c r="W9" s="4">
         <f>SUM(G9:J9)</f>
         <v>105.80000000000001</v>
       </c>
-      <c r="T9" s="4">
+      <c r="X9" s="4">
         <f>SUM(K9:N9)</f>
-        <v>130.5</v>
-      </c>
-      <c r="U9" s="4">
-        <f>U4*0.98</f>
-        <v>166.6</v>
-      </c>
-      <c r="V9" s="4">
-        <f>V4*0.96</f>
-        <v>204</v>
-      </c>
-      <c r="W9" s="4">
-        <f>W4*0.95</f>
-        <v>242.25</v>
-      </c>
-      <c r="X9" s="4">
-        <f t="shared" ref="X9:AE9" si="7">X4*0.95</f>
-        <v>278.58749999999998</v>
+        <v>129.5</v>
       </c>
       <c r="Y9" s="4">
-        <f t="shared" si="7"/>
-        <v>300.87450000000001</v>
+        <f t="shared" si="15"/>
+        <v>135.86500000000001</v>
       </c>
       <c r="Z9" s="4">
-        <f t="shared" si="7"/>
-        <v>312.90948000000003</v>
+        <f>Z4*0.91</f>
+        <v>162.33262500000001</v>
       </c>
       <c r="AA9" s="4">
-        <f t="shared" si="7"/>
-        <v>322.29676440000003</v>
+        <f t="shared" ref="AA9:AI9" si="17">AA4*0.91</f>
+        <v>194.79915000000003</v>
       </c>
       <c r="AB9" s="4">
-        <f t="shared" si="7"/>
-        <v>328.74269968800007</v>
+        <f t="shared" si="17"/>
+        <v>224.01902250000003</v>
       </c>
       <c r="AC9" s="4">
-        <f t="shared" si="7"/>
-        <v>335.31755368176005</v>
+        <f t="shared" si="17"/>
+        <v>241.94054430000003</v>
       </c>
       <c r="AD9" s="4">
-        <f t="shared" si="7"/>
-        <v>342.02390475539522</v>
+        <f t="shared" si="17"/>
+        <v>254.03757151500008</v>
       </c>
       <c r="AE9" s="4">
-        <f t="shared" si="7"/>
-        <v>348.86438285050315</v>
-      </c>
-    </row>
-    <row r="10" spans="2:31" x14ac:dyDescent="0.3">
+        <f t="shared" si="17"/>
+        <v>264.19907437560011</v>
+      </c>
+      <c r="AF9" s="4">
+        <f t="shared" si="17"/>
+        <v>272.12504660686812</v>
+      </c>
+      <c r="AG9" s="4">
+        <f t="shared" si="17"/>
+        <v>277.56754753900549</v>
+      </c>
+      <c r="AH9" s="4">
+        <f t="shared" si="17"/>
+        <v>283.11889848978558</v>
+      </c>
+      <c r="AI9" s="4">
+        <f t="shared" si="17"/>
+        <v>288.78127645958131</v>
+      </c>
+    </row>
+    <row r="10" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -1643,72 +1848,85 @@
         <v>51.4</v>
       </c>
       <c r="N10" s="4">
-        <f>N5*1</f>
-        <v>56.282000000000004</v>
+        <v>54.7</v>
+      </c>
+      <c r="O10" s="4">
+        <v>52.9</v>
       </c>
       <c r="P10" s="4">
+        <v>49.4</v>
+      </c>
+      <c r="Q10" s="4">
+        <f>Q5*0.95</f>
+        <v>49.225199999999994</v>
+      </c>
+      <c r="R10" s="4">
+        <f>R5*0.97</f>
+        <v>53.229719999999993</v>
+      </c>
+      <c r="T10" s="4">
         <v>132.30000000000001</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="U10" s="4">
         <v>148.30000000000001</v>
       </c>
-      <c r="R10" s="4">
+      <c r="V10" s="4">
         <v>168.5</v>
       </c>
-      <c r="S10" s="4">
+      <c r="W10" s="4">
         <f>SUM(G10:J10)</f>
         <v>221</v>
       </c>
-      <c r="T10" s="4">
+      <c r="X10" s="4">
         <f>SUM(K10:N10)</f>
-        <v>216.58200000000002</v>
-      </c>
-      <c r="U10" s="4">
-        <f>U5*0.92</f>
-        <v>226.52192159999998</v>
-      </c>
-      <c r="V10" s="4">
-        <f>V5*0.87</f>
-        <v>235.63204236000001</v>
-      </c>
-      <c r="W10" s="4">
-        <f>W5*0.84</f>
-        <v>243.43227548639999</v>
-      </c>
-      <c r="X10" s="4">
-        <f>X5*0.83</f>
-        <v>250.15564309507201</v>
+        <v>215</v>
       </c>
       <c r="Y10" s="4">
-        <f t="shared" ref="Y10:AE10" si="8">Y5*0.83</f>
-        <v>257.66031238792419</v>
+        <f t="shared" si="15"/>
+        <v>204.75491999999997</v>
       </c>
       <c r="Z10" s="4">
-        <f t="shared" si="8"/>
-        <v>262.81351863568267</v>
+        <f>Z5*0.9</f>
+        <v>212.44608000000002</v>
       </c>
       <c r="AA10" s="4">
-        <f t="shared" si="8"/>
-        <v>268.06978900839636</v>
+        <f>AA5*0.85</f>
+        <v>214.68856640000004</v>
       </c>
       <c r="AB10" s="4">
-        <f t="shared" si="8"/>
-        <v>273.43118478856428</v>
+        <f>AB5*0.83</f>
+        <v>218.02255354880003</v>
       </c>
       <c r="AC10" s="4">
-        <f t="shared" si="8"/>
-        <v>278.89980848433555</v>
+        <f t="shared" ref="AC10:AI10" si="18">AC5*0.83</f>
+        <v>224.56323015526402</v>
       </c>
       <c r="AD10" s="4">
-        <f t="shared" si="8"/>
-        <v>284.47780465402229</v>
+        <f t="shared" si="18"/>
+        <v>229.05449475836934</v>
       </c>
       <c r="AE10" s="4">
-        <f t="shared" si="8"/>
-        <v>290.16736074710275</v>
-      </c>
-    </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>233.63558465353674</v>
+      </c>
+      <c r="AF10" s="4">
+        <f t="shared" si="18"/>
+        <v>238.30829634660748</v>
+      </c>
+      <c r="AG10" s="4">
+        <f t="shared" si="18"/>
+        <v>243.07446227353964</v>
+      </c>
+      <c r="AH10" s="4">
+        <f t="shared" si="18"/>
+        <v>247.93595151901044</v>
+      </c>
+      <c r="AI10" s="4">
+        <f t="shared" si="18"/>
+        <v>252.89467054939064</v>
+      </c>
+    </row>
+    <row r="11" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -1737,282 +1955,325 @@
         <v>9.5</v>
       </c>
       <c r="N11" s="4">
-        <f>N6*0.62</f>
-        <v>8.6955000000000009</v>
+        <v>10.6</v>
+      </c>
+      <c r="O11" s="4">
+        <v>11.6</v>
       </c>
       <c r="P11" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>13</v>
+      </c>
+      <c r="R11" s="4">
+        <v>14</v>
+      </c>
+      <c r="T11" s="4">
         <v>46.9</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="U11" s="4">
         <v>44.4</v>
       </c>
-      <c r="R11" s="4">
+      <c r="V11" s="4">
         <v>162.1</v>
       </c>
-      <c r="S11" s="4">
+      <c r="W11" s="4">
         <f>SUM(G11:J11)</f>
         <v>179</v>
       </c>
-      <c r="T11" s="4">
+      <c r="X11" s="4">
         <f>SUM(K11:N11)</f>
-        <v>36.9955</v>
-      </c>
-      <c r="U11" s="4">
-        <f t="shared" ref="U9:AE11" si="9">U6*0.66</f>
-        <v>44.371799999999993</v>
-      </c>
-      <c r="V11" s="4">
-        <f t="shared" si="9"/>
-        <v>53.246159999999996</v>
-      </c>
-      <c r="W11" s="4">
-        <f t="shared" si="9"/>
-        <v>55.908467999999992</v>
-      </c>
-      <c r="X11" s="4">
-        <f t="shared" si="9"/>
-        <v>58.703891399999996</v>
+        <v>38.9</v>
       </c>
       <c r="Y11" s="4">
-        <f t="shared" si="9"/>
-        <v>61.639085969999996</v>
+        <f t="shared" si="15"/>
+        <v>46.3</v>
       </c>
       <c r="Z11" s="4">
-        <f t="shared" si="9"/>
-        <v>64.721040268499991</v>
+        <f>Z6*0.56</f>
+        <v>58.154879999999999</v>
       </c>
       <c r="AA11" s="4">
-        <f t="shared" si="9"/>
-        <v>67.957092281925</v>
+        <f t="shared" ref="AA11:AI11" si="19">AA6*0.56</f>
+        <v>61.062624</v>
       </c>
       <c r="AB11" s="4">
-        <f t="shared" si="9"/>
-        <v>71.354946896021247</v>
+        <f t="shared" si="19"/>
+        <v>64.115755200000009</v>
       </c>
       <c r="AC11" s="4">
-        <f t="shared" si="9"/>
-        <v>74.92269424082231</v>
+        <f t="shared" si="19"/>
+        <v>67.321542960000002</v>
       </c>
       <c r="AD11" s="4">
-        <f t="shared" si="9"/>
-        <v>78.668828952863436</v>
+        <f t="shared" si="19"/>
+        <v>70.687620108000004</v>
       </c>
       <c r="AE11" s="4">
-        <f t="shared" si="9"/>
-        <v>82.602270400506598</v>
-      </c>
-    </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.3">
+        <f t="shared" si="19"/>
+        <v>74.222001113400012</v>
+      </c>
+      <c r="AF11" s="4">
+        <f t="shared" si="19"/>
+        <v>77.933101169070028</v>
+      </c>
+      <c r="AG11" s="4">
+        <f t="shared" si="19"/>
+        <v>81.829756227523532</v>
+      </c>
+      <c r="AH11" s="4">
+        <f t="shared" si="19"/>
+        <v>85.921244038899715</v>
+      </c>
+      <c r="AI11" s="4">
+        <f t="shared" si="19"/>
+        <v>90.217306240844692</v>
+      </c>
+    </row>
+    <row r="12" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="4">
-        <f>SUM(F8:F11)</f>
+        <f t="shared" ref="F12:O12" si="20">SUM(F8:F11)</f>
         <v>391.1</v>
       </c>
       <c r="G12" s="4">
-        <f>SUM(G8:G11)</f>
+        <f t="shared" si="20"/>
         <v>220.89999999999998</v>
       </c>
       <c r="H12" s="4">
-        <f>SUM(H8:H11)</f>
+        <f t="shared" si="20"/>
         <v>244.89999999999998</v>
       </c>
       <c r="I12" s="4">
-        <f>SUM(I8:I11)</f>
+        <f t="shared" si="20"/>
         <v>405.5</v>
       </c>
       <c r="J12" s="4">
-        <f>SUM(J8:J11)</f>
+        <f t="shared" si="20"/>
         <v>264.60000000000002</v>
       </c>
       <c r="K12" s="4">
-        <f>SUM(K8:K11)</f>
+        <f t="shared" si="20"/>
         <v>197.29999999999998</v>
       </c>
       <c r="L12" s="4">
-        <f>SUM(L8:L11)</f>
+        <f t="shared" si="20"/>
         <v>267.2</v>
       </c>
       <c r="M12" s="4">
-        <f>SUM(M8:M11)</f>
+        <f t="shared" si="20"/>
         <v>251.70000000000002</v>
       </c>
       <c r="N12" s="4">
-        <f>SUM(N8:N11)</f>
-        <v>251.79060000000001</v>
+        <f t="shared" si="20"/>
+        <v>353.1</v>
+      </c>
+      <c r="O12" s="4">
+        <f t="shared" si="20"/>
+        <v>237.39999999999998</v>
       </c>
       <c r="P12" s="4">
-        <f>SUM(P8:P11)</f>
-        <v>628.4</v>
+        <f t="shared" ref="P12" si="21">SUM(P8:P11)</f>
+        <v>293.99999999999994</v>
       </c>
       <c r="Q12" s="4">
-        <f>SUM(Q8:Q11)</f>
-        <v>774.6</v>
+        <f t="shared" ref="Q12" si="22">SUM(Q8:Q11)</f>
+        <v>290.79480000000001</v>
       </c>
       <c r="R12" s="4">
-        <f>SUM(R8:R11)</f>
-        <v>1050.9000000000001</v>
-      </c>
-      <c r="S12" s="4">
-        <f>SUM(S8:S11)</f>
-        <v>1135.8999999999999</v>
+        <f t="shared" ref="R12" si="23">SUM(R8:R11)</f>
+        <v>372.99287000000004</v>
       </c>
       <c r="T12" s="4">
         <f>SUM(T8:T11)</f>
-        <v>967.99059999999997</v>
+        <v>628.4</v>
       </c>
       <c r="U12" s="4">
-        <f t="shared" ref="U12:AE12" si="10">SUM(U8:U11)</f>
-        <v>1026.7280355999999</v>
+        <f>SUM(U8:U11)</f>
+        <v>774.6</v>
       </c>
       <c r="V12" s="4">
-        <f t="shared" si="10"/>
-        <v>1111.57423206</v>
+        <f>SUM(V8:V11)</f>
+        <v>1050.9000000000001</v>
       </c>
       <c r="W12" s="4">
-        <f t="shared" si="10"/>
-        <v>1222.1563761564003</v>
+        <f>SUM(W8:W11)</f>
+        <v>1135.8999999999999</v>
       </c>
       <c r="X12" s="4">
-        <f t="shared" si="10"/>
-        <v>1336.0692304320721</v>
+        <f>SUM(X8:X11)</f>
+        <v>1069.3000000000002</v>
       </c>
       <c r="Y12" s="4">
-        <f t="shared" si="10"/>
-        <v>1443.6583138886244</v>
+        <f t="shared" ref="Y12:AI12" si="24">SUM(Y8:Y11)</f>
+        <v>1195.18767</v>
       </c>
       <c r="Z12" s="4">
-        <f t="shared" si="10"/>
-        <v>1529.8072076773387</v>
+        <f t="shared" si="24"/>
+        <v>1327.4174849999999</v>
       </c>
       <c r="AA12" s="4">
-        <f t="shared" si="10"/>
-        <v>1592.1549729021356</v>
+        <f t="shared" si="24"/>
+        <v>1454.4826304000001</v>
       </c>
       <c r="AB12" s="4">
-        <f t="shared" si="10"/>
-        <v>1644.7134116728721</v>
+        <f t="shared" si="24"/>
+        <v>1588.4828502488001</v>
       </c>
       <c r="AC12" s="4">
-        <f t="shared" si="10"/>
-        <v>1689.4601741162132</v>
+        <f t="shared" si="24"/>
+        <v>1724.3833883152643</v>
       </c>
       <c r="AD12" s="4">
-        <f t="shared" si="10"/>
-        <v>1735.5002596028553</v>
+        <f t="shared" si="24"/>
+        <v>1839.5824029533699</v>
       </c>
       <c r="AE12" s="4">
-        <f t="shared" si="10"/>
-        <v>1782.8736268759039</v>
-      </c>
-    </row>
-    <row r="13" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="24"/>
+        <v>1922.1495125431375</v>
+      </c>
+      <c r="AF12" s="4">
+        <f t="shared" si="24"/>
+        <v>1992.4630106191703</v>
+      </c>
+      <c r="AG12" s="4">
+        <f t="shared" si="24"/>
+        <v>2048.6912295315924</v>
+      </c>
+      <c r="AH12" s="4">
+        <f t="shared" si="24"/>
+        <v>2106.5821414439652</v>
+      </c>
+      <c r="AI12" s="4">
+        <f t="shared" si="24"/>
+        <v>2166.1874820679741</v>
+      </c>
+    </row>
+    <row r="13" spans="2:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="8">
-        <f>F7-F12</f>
+        <f t="shared" ref="F13:O13" si="25">F7-F12</f>
         <v>71.39999999999992</v>
       </c>
       <c r="G13" s="8">
-        <f>G7-G12</f>
+        <f t="shared" si="25"/>
         <v>54.300000000000011</v>
       </c>
       <c r="H13" s="8">
-        <f>H7-H12</f>
+        <f t="shared" si="25"/>
         <v>56.100000000000023</v>
       </c>
       <c r="I13" s="8">
-        <f>I7-I12</f>
+        <f t="shared" si="25"/>
         <v>-5.3000000000000114</v>
       </c>
       <c r="J13" s="8">
-        <f>J7-J12</f>
+        <f t="shared" si="25"/>
         <v>92.300000000000011</v>
       </c>
       <c r="K13" s="8">
-        <f>K7-K12</f>
+        <f t="shared" si="25"/>
         <v>37.900000000000034</v>
       </c>
       <c r="L13" s="8">
-        <f>L7-L12</f>
+        <f t="shared" si="25"/>
         <v>68.5</v>
       </c>
       <c r="M13" s="8">
-        <f>M7-M12</f>
+        <f t="shared" si="25"/>
         <v>78.80000000000004</v>
       </c>
       <c r="N13" s="8">
-        <f>N7-N12</f>
-        <v>106.22639999999998</v>
+        <f t="shared" si="25"/>
+        <v>219.29999999999995</v>
+      </c>
+      <c r="O13" s="8">
+        <f t="shared" si="25"/>
+        <v>88.700000000000045</v>
       </c>
       <c r="P13" s="8">
-        <f>P7-P12</f>
-        <v>165.80000000000007</v>
+        <f t="shared" ref="P13" si="26">P7-P12</f>
+        <v>107.20000000000005</v>
       </c>
       <c r="Q13" s="8">
-        <f>Q7-Q12</f>
-        <v>197.59999999999991</v>
+        <f t="shared" ref="Q13" si="27">Q7-Q12</f>
+        <v>124.88619999999992</v>
       </c>
       <c r="R13" s="8">
-        <f>R7-R12</f>
-        <v>148.30000000000018</v>
-      </c>
-      <c r="S13" s="8">
-        <f>S7-S12</f>
-        <v>197.40000000000009</v>
+        <f t="shared" ref="R13" si="28">R7-R12</f>
+        <v>235.59312999999997</v>
       </c>
       <c r="T13" s="8">
         <f>T7-T12</f>
-        <v>291.42640000000017</v>
+        <v>165.80000000000007</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" ref="U13:AE13" si="11">U7-U12</f>
-        <v>336.17564440000024</v>
+        <f>U7-U12</f>
+        <v>197.59999999999991</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" si="11"/>
-        <v>375.87010594000003</v>
+        <f>V7-V12</f>
+        <v>148.30000000000018</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" si="11"/>
-        <v>423.1233528035998</v>
+        <f>W7-W12</f>
+        <v>197.40000000000009</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" si="11"/>
-        <v>464.86496174632794</v>
+        <f>X7-X12</f>
+        <v>404.49999999999977</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="11"/>
-        <v>505.95956913212785</v>
+        <f t="shared" ref="Y13:AI13" si="29">Y7-Y12</f>
+        <v>556.37933000000021</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" si="11"/>
-        <v>541.68388267142836</v>
+        <f t="shared" si="29"/>
+        <v>681.67571500000008</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" si="11"/>
-        <v>566.82382015796134</v>
+        <f t="shared" si="29"/>
+        <v>761.08470359999978</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="11"/>
-        <v>588.40947799483729</v>
+        <f t="shared" si="29"/>
+        <v>838.73796011119998</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="11"/>
-        <v>606.06387226522975</v>
+        <f t="shared" si="29"/>
+        <v>916.52394280553608</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="11"/>
-        <v>624.26999572774957</v>
+        <f t="shared" si="29"/>
+        <v>984.7814550098476</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="11"/>
-        <v>643.04594496371146</v>
-      </c>
-    </row>
-    <row r="14" spans="2:31" x14ac:dyDescent="0.3">
+        <f t="shared" si="29"/>
+        <v>1032.3618385294444</v>
+      </c>
+      <c r="AF13" s="8">
+        <f t="shared" si="29"/>
+        <v>1073.0211277175581</v>
+      </c>
+      <c r="AG13" s="8">
+        <f t="shared" si="29"/>
+        <v>1105.6791885761104</v>
+      </c>
+      <c r="AH13" s="8">
+        <f t="shared" si="29"/>
+        <v>1139.3630796915104</v>
+      </c>
+      <c r="AI13" s="8">
+        <f t="shared" si="29"/>
+        <v>1174.1063347346139</v>
+      </c>
+    </row>
+    <row r="14" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>22</v>
       </c>
@@ -2041,72 +2302,83 @@
         <v>36.299999999999997</v>
       </c>
       <c r="N14" s="4">
-        <f>J14*1.03</f>
-        <v>34.608000000000004</v>
+        <v>39.5</v>
+      </c>
+      <c r="O14" s="4">
+        <v>40.6</v>
       </c>
       <c r="P14" s="4">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>42</v>
+      </c>
+      <c r="R14" s="4">
+        <v>45</v>
+      </c>
+      <c r="T14" s="4">
         <v>83.6</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="U14" s="4">
         <v>103.4</v>
       </c>
-      <c r="R14" s="4">
+      <c r="V14" s="4">
         <v>150.6</v>
       </c>
-      <c r="S14" s="4">
+      <c r="W14" s="4">
         <f>SUM(G14:J14)</f>
         <v>155.9</v>
       </c>
-      <c r="T14" s="4">
+      <c r="X14" s="4">
         <f>SUM(K14:N14)</f>
-        <v>143.80799999999999</v>
-      </c>
-      <c r="U14" s="4">
-        <f>T14*1.05</f>
-        <v>150.9984</v>
-      </c>
-      <c r="V14" s="4">
-        <f>U14*1.04</f>
-        <v>157.03833600000002</v>
-      </c>
-      <c r="W14" s="4">
-        <f t="shared" ref="V14:AE16" si="12">V14*1.03</f>
-        <v>161.74948608000003</v>
-      </c>
-      <c r="X14" s="4">
-        <f t="shared" si="12"/>
-        <v>166.60197066240002</v>
+        <v>148.69999999999999</v>
       </c>
       <c r="Y14" s="4">
-        <f t="shared" si="12"/>
-        <v>171.60002978227203</v>
+        <f t="shared" ref="Y14:Y16" si="30">SUM(O14:R14)</f>
+        <v>168.4</v>
       </c>
       <c r="Z14" s="4">
-        <f t="shared" si="12"/>
-        <v>176.74803067574021</v>
+        <f>Y14*1.09</f>
+        <v>183.55600000000001</v>
       </c>
       <c r="AA14" s="4">
-        <f>Z14*1.02</f>
-        <v>180.28299128925502</v>
+        <f>Z14*1.06</f>
+        <v>194.56936000000002</v>
       </c>
       <c r="AB14" s="4">
-        <f t="shared" ref="AB14:AE14" si="13">AA14*1.02</f>
-        <v>183.88865111504012</v>
+        <f>AA14*1.03</f>
+        <v>200.40644080000001</v>
       </c>
       <c r="AC14" s="4">
-        <f t="shared" si="13"/>
-        <v>187.56642413734093</v>
+        <f t="shared" ref="AC14:AD16" si="31">AB14*1.03</f>
+        <v>206.41863402400003</v>
       </c>
       <c r="AD14" s="4">
-        <f t="shared" si="13"/>
-        <v>191.31775262008776</v>
+        <f t="shared" si="31"/>
+        <v>212.61119304472004</v>
       </c>
       <c r="AE14" s="4">
-        <f t="shared" si="13"/>
-        <v>195.14410767248953</v>
-      </c>
-    </row>
-    <row r="15" spans="2:31" x14ac:dyDescent="0.3">
+        <f>AD14*1.02</f>
+        <v>216.86341690561446</v>
+      </c>
+      <c r="AF14" s="4">
+        <f t="shared" ref="AF14:AI14" si="32">AE14*1.02</f>
+        <v>221.20068524372675</v>
+      </c>
+      <c r="AG14" s="4">
+        <f t="shared" si="32"/>
+        <v>225.62469894860129</v>
+      </c>
+      <c r="AH14" s="4">
+        <f t="shared" si="32"/>
+        <v>230.13719292757332</v>
+      </c>
+      <c r="AI14" s="4">
+        <f t="shared" si="32"/>
+        <v>234.73993678612479</v>
+      </c>
+    </row>
+    <row r="15" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>23</v>
       </c>
@@ -2135,72 +2407,83 @@
         <v>14.7</v>
       </c>
       <c r="N15" s="4">
-        <f>N7*0.05</f>
-        <v>17.900850000000002</v>
+        <v>21.8</v>
+      </c>
+      <c r="O15" s="4">
+        <v>22.3</v>
       </c>
       <c r="P15" s="4">
+        <v>24.1</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>23</v>
+      </c>
+      <c r="R15" s="4">
+        <v>24</v>
+      </c>
+      <c r="T15" s="4">
         <v>55.9</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="U15" s="4">
         <v>86.5</v>
       </c>
-      <c r="R15" s="4">
+      <c r="V15" s="4">
         <v>90.9</v>
       </c>
-      <c r="S15" s="4">
+      <c r="W15" s="4">
         <f>SUM(G15:J15)</f>
         <v>89.9</v>
       </c>
-      <c r="T15" s="4">
+      <c r="X15" s="4">
         <f>SUM(K15:N15)</f>
-        <v>64.100850000000008</v>
-      </c>
-      <c r="U15" s="4">
-        <f>U7*0.05</f>
-        <v>68.145184000000015</v>
-      </c>
-      <c r="V15" s="4">
-        <f>V7*0.06</f>
-        <v>89.24666028</v>
-      </c>
-      <c r="W15" s="4">
-        <f t="shared" ref="W15:AE15" si="14">W7*0.06</f>
-        <v>98.716783737599997</v>
-      </c>
-      <c r="X15" s="4">
-        <f t="shared" si="14"/>
-        <v>108.056051530704</v>
+        <v>68</v>
       </c>
       <c r="Y15" s="4">
-        <f t="shared" si="14"/>
-        <v>116.97707298124513</v>
+        <f t="shared" si="30"/>
+        <v>93.4</v>
       </c>
       <c r="Z15" s="4">
-        <f t="shared" si="14"/>
-        <v>124.28946542092602</v>
+        <f>Z7*0.05</f>
+        <v>100.45466</v>
       </c>
       <c r="AA15" s="4">
-        <f t="shared" si="14"/>
-        <v>129.53872758360581</v>
+        <f t="shared" ref="AA15:AI15" si="33">AA7*0.05</f>
+        <v>110.77836669999999</v>
       </c>
       <c r="AB15" s="4">
-        <f t="shared" si="14"/>
-        <v>133.98737338006256</v>
+        <f t="shared" si="33"/>
+        <v>121.36104051800001</v>
       </c>
       <c r="AC15" s="4">
-        <f t="shared" si="14"/>
-        <v>137.73144278288657</v>
+        <f t="shared" si="33"/>
+        <v>132.04536655604002</v>
       </c>
       <c r="AD15" s="4">
-        <f t="shared" si="14"/>
-        <v>141.5862153198363</v>
+        <f t="shared" si="33"/>
+        <v>141.21819289816088</v>
       </c>
       <c r="AE15" s="4">
-        <f t="shared" si="14"/>
-        <v>145.55517431037691</v>
-      </c>
-    </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.3">
+        <f t="shared" si="33"/>
+        <v>147.72556755362911</v>
+      </c>
+      <c r="AF15" s="4">
+        <f t="shared" si="33"/>
+        <v>153.27420691683642</v>
+      </c>
+      <c r="AG15" s="4">
+        <f t="shared" si="33"/>
+        <v>157.71852090538516</v>
+      </c>
+      <c r="AH15" s="4">
+        <f t="shared" si="33"/>
+        <v>162.29726105677378</v>
+      </c>
+      <c r="AI15" s="4">
+        <f t="shared" si="33"/>
+        <v>167.01469084012942</v>
+      </c>
+    </row>
+    <row r="16" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>24</v>
       </c>
@@ -2229,282 +2512,325 @@
         <v>37.4</v>
       </c>
       <c r="N16" s="4">
-        <f>J16*1.02</f>
-        <v>30.497999999999998</v>
+        <v>53.3</v>
+      </c>
+      <c r="O16" s="4">
+        <v>44.9</v>
       </c>
       <c r="P16" s="4">
+        <v>45.8</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>47</v>
+      </c>
+      <c r="R16" s="4">
+        <v>60</v>
+      </c>
+      <c r="T16" s="4">
         <v>107.1</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="U16" s="4">
         <v>122.2</v>
       </c>
-      <c r="R16" s="4">
+      <c r="V16" s="4">
         <v>167.7</v>
       </c>
-      <c r="S16" s="4">
+      <c r="W16" s="4">
         <f>SUM(G16:J16)</f>
         <v>160.9</v>
       </c>
-      <c r="T16" s="4">
+      <c r="X16" s="4">
         <f>SUM(K16:N16)</f>
-        <v>142.298</v>
-      </c>
-      <c r="U16" s="4">
-        <f>T16*1.05</f>
-        <v>149.41290000000001</v>
-      </c>
-      <c r="V16" s="4">
-        <f>U16*1.04</f>
-        <v>155.38941600000001</v>
-      </c>
-      <c r="W16" s="4">
-        <f t="shared" si="12"/>
-        <v>160.05109848000001</v>
-      </c>
-      <c r="X16" s="4">
-        <f t="shared" si="12"/>
-        <v>164.85263143440002</v>
+        <v>165.10000000000002</v>
       </c>
       <c r="Y16" s="4">
-        <f t="shared" si="12"/>
-        <v>169.79821037743204</v>
+        <f t="shared" si="30"/>
+        <v>197.7</v>
       </c>
       <c r="Z16" s="4">
-        <f>Y16*1.02</f>
-        <v>173.19417458498069</v>
+        <f>Y16*1.1</f>
+        <v>217.47</v>
       </c>
       <c r="AA16" s="4">
-        <f t="shared" ref="AA16:AE16" si="15">Z16*1.02</f>
-        <v>176.65805807668031</v>
+        <f>Z16*1.05</f>
+        <v>228.34350000000001</v>
       </c>
       <c r="AB16" s="4">
-        <f t="shared" si="15"/>
-        <v>180.1912192382139</v>
+        <f>AA16*1.04</f>
+        <v>237.47724000000002</v>
       </c>
       <c r="AC16" s="4">
-        <f t="shared" si="15"/>
-        <v>183.7950436229782</v>
+        <f t="shared" si="31"/>
+        <v>244.60155720000003</v>
       </c>
       <c r="AD16" s="4">
-        <f t="shared" si="15"/>
-        <v>187.47094449543778</v>
+        <f>AC16*1.02</f>
+        <v>249.49358834400005</v>
       </c>
       <c r="AE16" s="4">
-        <f t="shared" si="15"/>
-        <v>191.22036338534653</v>
-      </c>
-    </row>
-    <row r="17" spans="2:141" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AE16:AI16" si="34">AD16*1.02</f>
+        <v>254.48346011088006</v>
+      </c>
+      <c r="AF16" s="4">
+        <f t="shared" si="34"/>
+        <v>259.57312931309764</v>
+      </c>
+      <c r="AG16" s="4">
+        <f t="shared" si="34"/>
+        <v>264.76459189935957</v>
+      </c>
+      <c r="AH16" s="4">
+        <f t="shared" si="34"/>
+        <v>270.05988373734675</v>
+      </c>
+      <c r="AI16" s="4">
+        <f t="shared" si="34"/>
+        <v>275.46108141209368</v>
+      </c>
+    </row>
+    <row r="17" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="4">
-        <f>SUM(F14:F16)</f>
+        <f t="shared" ref="F17:O17" si="35">SUM(F14:F16)</f>
         <v>111.99999999999999</v>
       </c>
       <c r="G17" s="4">
-        <f>SUM(G14:G16)</f>
+        <f t="shared" si="35"/>
         <v>117.9</v>
       </c>
       <c r="H17" s="4">
-        <f>SUM(H14:H16)</f>
+        <f t="shared" si="35"/>
         <v>110.8</v>
       </c>
       <c r="I17" s="4">
-        <f>SUM(I14:I16)</f>
+        <f t="shared" si="35"/>
         <v>98.5</v>
       </c>
       <c r="J17" s="4">
-        <f>SUM(J14:J16)</f>
+        <f t="shared" si="35"/>
         <v>79.5</v>
       </c>
       <c r="K17" s="4">
-        <f>SUM(K14:K16)</f>
+        <f t="shared" si="35"/>
         <v>87.1</v>
       </c>
       <c r="L17" s="4">
-        <f>SUM(L14:L16)</f>
+        <f t="shared" si="35"/>
         <v>91.699999999999989</v>
       </c>
       <c r="M17" s="4">
-        <f>SUM(M14:M16)</f>
+        <f t="shared" si="35"/>
         <v>88.4</v>
       </c>
       <c r="N17" s="4">
-        <f>SUM(N14:N16)</f>
-        <v>83.006850000000014</v>
+        <f t="shared" si="35"/>
+        <v>114.6</v>
+      </c>
+      <c r="O17" s="4">
+        <f t="shared" si="35"/>
+        <v>107.80000000000001</v>
       </c>
       <c r="P17" s="4">
-        <f>SUM(P14:P16)</f>
-        <v>246.6</v>
+        <f t="shared" ref="P17" si="36">SUM(P14:P16)</f>
+        <v>110.7</v>
       </c>
       <c r="Q17" s="4">
-        <f>SUM(Q14:Q16)</f>
-        <v>312.10000000000002</v>
+        <f t="shared" ref="Q17" si="37">SUM(Q14:Q16)</f>
+        <v>112</v>
       </c>
       <c r="R17" s="4">
-        <f>SUM(R14:R16)</f>
-        <v>409.2</v>
-      </c>
-      <c r="S17" s="4">
-        <f>SUM(S14:S16)</f>
-        <v>406.70000000000005</v>
+        <f t="shared" ref="R17" si="38">SUM(R14:R16)</f>
+        <v>129</v>
       </c>
       <c r="T17" s="4">
         <f>SUM(T14:T16)</f>
-        <v>350.20685000000003</v>
+        <v>246.6</v>
       </c>
       <c r="U17" s="4">
-        <f t="shared" ref="U17:AE17" si="16">SUM(U14:U16)</f>
-        <v>368.55648400000007</v>
+        <f>SUM(U14:U16)</f>
+        <v>312.10000000000002</v>
       </c>
       <c r="V17" s="4">
-        <f t="shared" si="16"/>
-        <v>401.67441228000007</v>
+        <f>SUM(V14:V16)</f>
+        <v>409.2</v>
       </c>
       <c r="W17" s="4">
-        <f t="shared" si="16"/>
-        <v>420.51736829760006</v>
+        <f>SUM(W14:W16)</f>
+        <v>406.70000000000005</v>
       </c>
       <c r="X17" s="4">
-        <f t="shared" si="16"/>
-        <v>439.51065362750398</v>
+        <f>SUM(X14:X16)</f>
+        <v>381.8</v>
       </c>
       <c r="Y17" s="4">
-        <f t="shared" si="16"/>
-        <v>458.37531314094917</v>
+        <f t="shared" ref="Y17:AI17" si="39">SUM(Y14:Y16)</f>
+        <v>459.5</v>
       </c>
       <c r="Z17" s="4">
-        <f t="shared" si="16"/>
-        <v>474.23167068164696</v>
+        <f t="shared" si="39"/>
+        <v>501.48066000000006</v>
       </c>
       <c r="AA17" s="4">
-        <f t="shared" si="16"/>
-        <v>486.47977694954113</v>
+        <f t="shared" si="39"/>
+        <v>533.69122670000002</v>
       </c>
       <c r="AB17" s="4">
-        <f t="shared" si="16"/>
-        <v>498.06724373331656</v>
+        <f t="shared" si="39"/>
+        <v>559.24472131800007</v>
       </c>
       <c r="AC17" s="4">
-        <f t="shared" si="16"/>
-        <v>509.09291054320573</v>
+        <f t="shared" si="39"/>
+        <v>583.06555778004008</v>
       </c>
       <c r="AD17" s="4">
-        <f t="shared" si="16"/>
-        <v>520.37491243536192</v>
+        <f t="shared" si="39"/>
+        <v>603.32297428688094</v>
       </c>
       <c r="AE17" s="4">
-        <f t="shared" si="16"/>
-        <v>531.91964536821297</v>
-      </c>
-    </row>
-    <row r="18" spans="2:141" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="39"/>
+        <v>619.07244457012359</v>
+      </c>
+      <c r="AF17" s="4">
+        <f t="shared" si="39"/>
+        <v>634.04802147366081</v>
+      </c>
+      <c r="AG17" s="4">
+        <f t="shared" si="39"/>
+        <v>648.10781175334603</v>
+      </c>
+      <c r="AH17" s="4">
+        <f t="shared" si="39"/>
+        <v>662.49433772169391</v>
+      </c>
+      <c r="AI17" s="4">
+        <f t="shared" si="39"/>
+        <v>677.21570903834788</v>
+      </c>
+    </row>
+    <row r="18" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="8">
-        <f>F13-F17</f>
+        <f t="shared" ref="F18:O18" si="40">F13-F17</f>
         <v>-40.600000000000065</v>
       </c>
       <c r="G18" s="8">
-        <f>G13-G17</f>
+        <f t="shared" si="40"/>
         <v>-63.599999999999994</v>
       </c>
       <c r="H18" s="8">
-        <f>H13-H17</f>
+        <f t="shared" si="40"/>
         <v>-54.699999999999974</v>
       </c>
       <c r="I18" s="8">
-        <f>I13-I17</f>
+        <f t="shared" si="40"/>
         <v>-103.80000000000001</v>
       </c>
       <c r="J18" s="8">
-        <f>J13-J17</f>
+        <f t="shared" si="40"/>
         <v>12.800000000000011</v>
       </c>
       <c r="K18" s="8">
-        <f>K13-K17</f>
+        <f t="shared" si="40"/>
         <v>-49.19999999999996</v>
       </c>
       <c r="L18" s="8">
-        <f>L13-L17</f>
+        <f t="shared" si="40"/>
         <v>-23.199999999999989</v>
       </c>
       <c r="M18" s="8">
-        <f>M13-M17</f>
+        <f t="shared" si="40"/>
         <v>-9.5999999999999659</v>
       </c>
       <c r="N18" s="8">
-        <f>N13-N17</f>
-        <v>23.21954999999997</v>
+        <f t="shared" si="40"/>
+        <v>104.69999999999996</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" si="40"/>
+        <v>-19.099999999999966</v>
       </c>
       <c r="P18" s="8">
-        <f>P13-P17</f>
-        <v>-80.799999999999926</v>
+        <f t="shared" ref="P18" si="41">P13-P17</f>
+        <v>-3.4999999999999574</v>
       </c>
       <c r="Q18" s="8">
-        <f>Q13-Q17</f>
-        <v>-114.50000000000011</v>
+        <f t="shared" ref="Q18" si="42">Q13-Q17</f>
+        <v>12.886199999999917</v>
       </c>
       <c r="R18" s="8">
-        <f>R13-R17</f>
-        <v>-260.89999999999981</v>
-      </c>
-      <c r="S18" s="8">
-        <f>S13-S17</f>
-        <v>-209.29999999999995</v>
+        <f t="shared" ref="R18" si="43">R13-R17</f>
+        <v>106.59312999999997</v>
       </c>
       <c r="T18" s="8">
         <f>T13-T17</f>
-        <v>-58.78044999999986</v>
+        <v>-80.799999999999926</v>
       </c>
       <c r="U18" s="8">
-        <f t="shared" ref="U18:AE18" si="17">U13-U17</f>
-        <v>-32.380839599999831</v>
+        <f>U13-U17</f>
+        <v>-114.50000000000011</v>
       </c>
       <c r="V18" s="8">
-        <f t="shared" si="17"/>
-        <v>-25.804306340000039</v>
+        <f>V13-V17</f>
+        <v>-260.89999999999981</v>
       </c>
       <c r="W18" s="8">
-        <f t="shared" si="17"/>
-        <v>2.6059845059997429</v>
+        <f>W13-W17</f>
+        <v>-209.29999999999995</v>
       </c>
       <c r="X18" s="8">
-        <f t="shared" si="17"/>
-        <v>25.354308118823951</v>
+        <f>X13-X17</f>
+        <v>22.699999999999761</v>
       </c>
       <c r="Y18" s="8">
-        <f t="shared" si="17"/>
-        <v>47.584255991178679</v>
+        <f t="shared" ref="Y18:AI18" si="44">Y13-Y17</f>
+        <v>96.879330000000209</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" si="17"/>
-        <v>67.452211989781404</v>
+        <f t="shared" si="44"/>
+        <v>180.19505500000002</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" si="17"/>
-        <v>80.344043208420203</v>
+        <f t="shared" si="44"/>
+        <v>227.39347689999977</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" si="17"/>
-        <v>90.34223426152073</v>
+        <f t="shared" si="44"/>
+        <v>279.49323879319991</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" si="17"/>
-        <v>96.970961722024015</v>
+        <f t="shared" si="44"/>
+        <v>333.458385025496</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="17"/>
-        <v>103.89508329238765</v>
+        <f t="shared" si="44"/>
+        <v>381.45848072296667</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="17"/>
-        <v>111.12629959549849</v>
-      </c>
-    </row>
-    <row r="19" spans="2:141" x14ac:dyDescent="0.3">
+        <f t="shared" si="44"/>
+        <v>413.28939395932082</v>
+      </c>
+      <c r="AF18" s="8">
+        <f t="shared" si="44"/>
+        <v>438.97310624389729</v>
+      </c>
+      <c r="AG18" s="8">
+        <f t="shared" si="44"/>
+        <v>457.57137682276436</v>
+      </c>
+      <c r="AH18" s="8">
+        <f t="shared" si="44"/>
+        <v>476.86874196981648</v>
+      </c>
+      <c r="AI18" s="8">
+        <f t="shared" si="44"/>
+        <v>496.89062569626606</v>
+      </c>
+    </row>
+    <row r="19" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>27</v>
       </c>
@@ -2533,71 +2859,83 @@
         <v>-6.5</v>
       </c>
       <c r="N19" s="4">
-        <v>-8</v>
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="O19" s="4">
+        <v>-8.6</v>
       </c>
       <c r="P19" s="4">
+        <v>-6.6</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>-10</v>
+      </c>
+      <c r="R19" s="4">
+        <v>-10</v>
+      </c>
+      <c r="T19" s="4">
         <v>-1.5</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="U19" s="4">
         <v>-0.3</v>
       </c>
-      <c r="R19" s="4">
+      <c r="V19" s="4">
         <v>-3.9</v>
       </c>
-      <c r="S19" s="4">
+      <c r="W19" s="4">
         <f>SUM(G19:J19)</f>
         <v>-19.899999999999999</v>
       </c>
-      <c r="T19" s="4">
+      <c r="X19" s="4">
         <f>SUM(K19:N19)</f>
-        <v>-28.4</v>
-      </c>
-      <c r="U19" s="4">
-        <f>T19*1.02</f>
-        <v>-28.968</v>
-      </c>
-      <c r="V19" s="4">
-        <f t="shared" ref="V19:AE19" si="18">U19*1.02</f>
-        <v>-29.547360000000001</v>
-      </c>
-      <c r="W19" s="4">
-        <f t="shared" si="18"/>
-        <v>-30.138307200000003</v>
-      </c>
-      <c r="X19" s="4">
-        <f t="shared" si="18"/>
-        <v>-30.741073344000004</v>
+        <v>-25.299999999999997</v>
       </c>
       <c r="Y19" s="4">
-        <f t="shared" si="18"/>
-        <v>-31.355894810880006</v>
+        <f t="shared" ref="Y19:Y23" si="45">SUM(O19:R19)</f>
+        <v>-35.200000000000003</v>
       </c>
       <c r="Z19" s="4">
-        <f t="shared" si="18"/>
-        <v>-31.983012707097608</v>
+        <f t="shared" ref="Z19:AI19" si="46">Y19*1.02</f>
+        <v>-35.904000000000003</v>
       </c>
       <c r="AA19" s="4">
-        <f t="shared" si="18"/>
-        <v>-32.622672961239559</v>
+        <f t="shared" si="46"/>
+        <v>-36.622080000000004</v>
       </c>
       <c r="AB19" s="4">
-        <f t="shared" si="18"/>
-        <v>-33.275126420464353</v>
+        <f t="shared" si="46"/>
+        <v>-37.354521600000005</v>
       </c>
       <c r="AC19" s="4">
-        <f t="shared" si="18"/>
-        <v>-33.940628948873638</v>
+        <f t="shared" si="46"/>
+        <v>-38.101612032000006</v>
       </c>
       <c r="AD19" s="4">
-        <f t="shared" si="18"/>
-        <v>-34.619441527851109</v>
+        <f t="shared" si="46"/>
+        <v>-38.863644272640009</v>
       </c>
       <c r="AE19" s="4">
-        <f t="shared" si="18"/>
-        <v>-35.31183035840813</v>
-      </c>
-    </row>
-    <row r="20" spans="2:141" x14ac:dyDescent="0.3">
+        <f t="shared" si="46"/>
+        <v>-39.640917158092812</v>
+      </c>
+      <c r="AF19" s="4">
+        <f t="shared" si="46"/>
+        <v>-40.433735501254667</v>
+      </c>
+      <c r="AG19" s="4">
+        <f t="shared" si="46"/>
+        <v>-41.242410211279761</v>
+      </c>
+      <c r="AH19" s="4">
+        <f t="shared" si="46"/>
+        <v>-42.067258415505357</v>
+      </c>
+      <c r="AI19" s="4">
+        <f t="shared" si="46"/>
+        <v>-42.908603583815463</v>
+      </c>
+    </row>
+    <row r="20" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>28</v>
       </c>
@@ -2626,72 +2964,84 @@
         <v>16.8</v>
       </c>
       <c r="N20" s="4">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="O20" s="4">
+        <v>14.4</v>
       </c>
       <c r="P20" s="4">
+        <v>14.4</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>15</v>
+      </c>
+      <c r="R20" s="4">
+        <v>15</v>
+      </c>
+      <c r="T20" s="4">
         <f>76.3+2.5</f>
         <v>78.8</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="U20" s="4">
         <v>69</v>
       </c>
-      <c r="R20" s="4">
+      <c r="V20" s="4">
         <v>53.5</v>
       </c>
-      <c r="S20" s="4">
+      <c r="W20" s="4">
         <f>SUM(G20:J20)</f>
         <v>108.3</v>
       </c>
-      <c r="T20" s="4">
+      <c r="X20" s="4">
         <f>SUM(K20:N20)</f>
-        <v>63.7</v>
-      </c>
-      <c r="U20" s="4">
-        <f>T20*1.02</f>
-        <v>64.974000000000004</v>
-      </c>
-      <c r="V20" s="4">
-        <f t="shared" ref="V20:AE20" si="19">U20*1.02</f>
-        <v>66.273480000000006</v>
-      </c>
-      <c r="W20" s="4">
-        <f t="shared" si="19"/>
-        <v>67.598949600000012</v>
-      </c>
-      <c r="X20" s="4">
-        <f t="shared" si="19"/>
-        <v>68.950928592000011</v>
+        <v>62.7</v>
       </c>
       <c r="Y20" s="4">
-        <f t="shared" si="19"/>
-        <v>70.329947163840018</v>
+        <f t="shared" si="45"/>
+        <v>58.8</v>
       </c>
       <c r="Z20" s="4">
-        <f t="shared" si="19"/>
-        <v>71.736546107116823</v>
+        <f t="shared" ref="Z20:AI20" si="47">Y20*1.02</f>
+        <v>59.975999999999999</v>
       </c>
       <c r="AA20" s="4">
-        <f t="shared" si="19"/>
-        <v>73.171277029259159</v>
+        <f t="shared" si="47"/>
+        <v>61.175519999999999</v>
       </c>
       <c r="AB20" s="4">
-        <f t="shared" si="19"/>
-        <v>74.634702569844336</v>
+        <f t="shared" si="47"/>
+        <v>62.399030400000001</v>
       </c>
       <c r="AC20" s="4">
-        <f t="shared" si="19"/>
-        <v>76.127396621241218</v>
+        <f t="shared" si="47"/>
+        <v>63.647011008</v>
       </c>
       <c r="AD20" s="4">
-        <f t="shared" si="19"/>
-        <v>77.649944553666046</v>
+        <f t="shared" si="47"/>
+        <v>64.919951228160002</v>
       </c>
       <c r="AE20" s="4">
-        <f t="shared" si="19"/>
-        <v>79.202943444739361</v>
-      </c>
-    </row>
-    <row r="21" spans="2:141" x14ac:dyDescent="0.3">
+        <f t="shared" si="47"/>
+        <v>66.218350252723198</v>
+      </c>
+      <c r="AF20" s="4">
+        <f t="shared" si="47"/>
+        <v>67.542717257777667</v>
+      </c>
+      <c r="AG20" s="4">
+        <f t="shared" si="47"/>
+        <v>68.893571602933221</v>
+      </c>
+      <c r="AH20" s="4">
+        <f t="shared" si="47"/>
+        <v>70.27144303499189</v>
+      </c>
+      <c r="AI20" s="4">
+        <f t="shared" si="47"/>
+        <v>71.676871895691733</v>
+      </c>
+    </row>
+    <row r="21" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>29</v>
       </c>
@@ -2720,10 +3070,13 @@
         <v>-5.8</v>
       </c>
       <c r="N21" s="4">
-        <v>0</v>
+        <v>-12.2</v>
+      </c>
+      <c r="O21" s="4">
+        <v>-2</v>
       </c>
       <c r="P21" s="4">
-        <v>12.9</v>
+        <v>-2.4</v>
       </c>
       <c r="Q21" s="4">
         <v>0</v>
@@ -2731,28 +3084,26 @@
       <c r="R21" s="4">
         <v>0</v>
       </c>
-      <c r="S21" s="4">
+      <c r="T21" s="4">
+        <v>12.9</v>
+      </c>
+      <c r="U21" s="4">
+        <v>0</v>
+      </c>
+      <c r="V21" s="4">
+        <v>0</v>
+      </c>
+      <c r="W21" s="4">
         <f>SUM(G21:J21)</f>
         <v>2.7</v>
       </c>
-      <c r="T21" s="4">
+      <c r="X21" s="4">
         <f>SUM(K21:N21)</f>
-        <v>-3.5999999999999996</v>
-      </c>
-      <c r="U21" s="4">
-        <v>0</v>
-      </c>
-      <c r="V21" s="4">
-        <v>0</v>
-      </c>
-      <c r="W21" s="4">
-        <v>0</v>
-      </c>
-      <c r="X21" s="4">
-        <v>0</v>
+        <v>-15.799999999999999</v>
       </c>
       <c r="Y21" s="4">
-        <v>0</v>
+        <f t="shared" si="45"/>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="Z21" s="4">
         <v>0</v>
@@ -2772,8 +3123,20 @@
       <c r="AE21" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:141" x14ac:dyDescent="0.3">
+      <c r="AF21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>30</v>
       </c>
@@ -2800,37 +3163,38 @@
       <c r="N22" s="4">
         <v>0</v>
       </c>
+      <c r="O22" s="4">
+        <v>0</v>
+      </c>
       <c r="P22" s="4">
-        <v>8.3000000000000007</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="Q22" s="4">
         <v>0</v>
       </c>
       <c r="R22" s="4">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="U22" s="4">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4">
         <v>9</v>
       </c>
-      <c r="S22" s="4">
+      <c r="W22" s="4">
         <f>SUM(G22:J22)</f>
         <v>4.3</v>
       </c>
-      <c r="T22" s="4">
+      <c r="X22" s="4">
         <f>SUM(K22:N22)</f>
         <v>27.2</v>
       </c>
-      <c r="U22" s="4">
-        <v>0</v>
-      </c>
-      <c r="V22" s="4">
-        <v>0</v>
-      </c>
-      <c r="W22" s="4">
-        <v>0</v>
-      </c>
-      <c r="X22" s="4">
-        <v>0</v>
-      </c>
       <c r="Y22" s="4">
-        <v>0</v>
+        <f t="shared" si="45"/>
+        <v>32.299999999999997</v>
       </c>
       <c r="Z22" s="4">
         <v>0</v>
@@ -2850,8 +3214,20 @@
       <c r="AE22" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:141" x14ac:dyDescent="0.3">
+      <c r="AF22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>31</v>
       </c>
@@ -2880,40 +3256,41 @@
         <v>0.4</v>
       </c>
       <c r="N23" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="O23" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P23" s="4">
+        <v>-0.1</v>
+      </c>
+      <c r="Q23" s="4">
         <v>0</v>
       </c>
-      <c r="P23" s="4">
+      <c r="R23" s="4">
+        <v>0</v>
+      </c>
+      <c r="T23" s="4">
         <v>-0.5</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="U23" s="4">
         <f>8.1+0.9</f>
         <v>9</v>
       </c>
-      <c r="R23" s="4">
+      <c r="V23" s="4">
         <f>-5-0.6</f>
         <v>-5.6</v>
       </c>
-      <c r="S23" s="4">
+      <c r="W23" s="4">
         <f>SUM(G23:J23)</f>
         <v>1.6</v>
       </c>
-      <c r="T23" s="4">
+      <c r="X23" s="4">
         <f>SUM(K23:N23)</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="U23" s="4">
-        <v>0</v>
-      </c>
-      <c r="V23" s="4">
-        <v>0</v>
-      </c>
-      <c r="W23" s="4">
-        <v>0</v>
-      </c>
-      <c r="X23" s="4">
-        <v>0</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="Y23" s="4">
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="Z23" s="4">
@@ -2934,218 +3311,262 @@
       <c r="AE23" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:141" x14ac:dyDescent="0.3">
+      <c r="AF23" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="4">
-        <f>SUM(F19:F23)</f>
+        <f t="shared" ref="F24:O24" si="48">SUM(F19:F23)</f>
         <v>10.1</v>
       </c>
       <c r="G24" s="4">
-        <f>SUM(G19:G23)</f>
+        <f t="shared" si="48"/>
         <v>10.9</v>
       </c>
       <c r="H24" s="4">
-        <f>SUM(H19:H23)</f>
+        <f t="shared" si="48"/>
         <v>14.399999999999999</v>
       </c>
       <c r="I24" s="4">
-        <f>SUM(I19:I23)</f>
+        <f t="shared" si="48"/>
         <v>63.7</v>
       </c>
       <c r="J24" s="4">
-        <f>SUM(J19:J23)</f>
+        <f t="shared" si="48"/>
         <v>8</v>
       </c>
       <c r="K24" s="4">
-        <f>SUM(K19:K23)</f>
+        <f t="shared" si="48"/>
         <v>7.9999999999999991</v>
       </c>
       <c r="L24" s="4">
-        <f>SUM(L19:L23)</f>
+        <f t="shared" si="48"/>
         <v>37.300000000000004</v>
       </c>
       <c r="M24" s="4">
-        <f>SUM(M19:M23)</f>
+        <f t="shared" si="48"/>
         <v>4.9000000000000012</v>
       </c>
       <c r="N24" s="4">
-        <f>SUM(N19:N23)</f>
-        <v>9</v>
+        <f t="shared" si="48"/>
+        <v>-0.69999999999999962</v>
+      </c>
+      <c r="O24" s="4">
+        <f t="shared" si="48"/>
+        <v>3.9000000000000008</v>
       </c>
       <c r="P24" s="4">
-        <f>SUM(P19:P23)</f>
+        <f t="shared" ref="P24" si="49">SUM(P19:P23)</f>
+        <v>37.599999999999994</v>
+      </c>
+      <c r="Q24" s="4">
+        <f t="shared" ref="Q24" si="50">SUM(Q19:Q23)</f>
+        <v>5</v>
+      </c>
+      <c r="R24" s="4">
+        <f t="shared" ref="R24" si="51">SUM(R19:R23)</f>
+        <v>5</v>
+      </c>
+      <c r="T24" s="4">
+        <f t="shared" ref="T24:Y24" si="52">SUM(T19:T23)</f>
         <v>98</v>
       </c>
-      <c r="Q24" s="4">
-        <f>SUM(Q19:Q23)</f>
+      <c r="U24" s="4">
+        <f t="shared" si="52"/>
         <v>77.7</v>
       </c>
-      <c r="R24" s="4">
-        <f>SUM(R19:R23)</f>
+      <c r="V24" s="4">
+        <f t="shared" si="52"/>
         <v>53</v>
       </c>
-      <c r="S24" s="4">
-        <f>SUM(S19:S23)</f>
+      <c r="W24" s="4">
+        <f t="shared" si="52"/>
         <v>97</v>
       </c>
-      <c r="T24" s="4">
-        <f>SUM(T19:T23)</f>
-        <v>59.2</v>
-      </c>
-      <c r="U24" s="4">
-        <f>SUM(U19:U23)</f>
-        <v>36.006</v>
-      </c>
-      <c r="V24" s="4">
-        <f t="shared" ref="V24:AE24" si="20">SUM(V19:V23)</f>
-        <v>36.726120000000009</v>
-      </c>
-      <c r="W24" s="4">
-        <f t="shared" si="20"/>
-        <v>37.460642400000012</v>
-      </c>
       <c r="X24" s="4">
-        <f t="shared" si="20"/>
-        <v>38.209855248000011</v>
+        <f t="shared" si="52"/>
+        <v>49.500000000000014</v>
       </c>
       <c r="Y24" s="4">
-        <f t="shared" si="20"/>
-        <v>38.974052352960015</v>
+        <f t="shared" si="52"/>
+        <v>51.499999999999993</v>
       </c>
       <c r="Z24" s="4">
-        <f t="shared" si="20"/>
-        <v>39.753533400019215</v>
+        <f t="shared" ref="Z24:AI24" si="53">SUM(Z19:Z23)</f>
+        <v>24.071999999999996</v>
       </c>
       <c r="AA24" s="4">
-        <f t="shared" si="20"/>
-        <v>40.5486040680196</v>
+        <f t="shared" si="53"/>
+        <v>24.553439999999995</v>
       </c>
       <c r="AB24" s="4">
-        <f t="shared" si="20"/>
-        <v>41.359576149379983</v>
+        <f t="shared" si="53"/>
+        <v>25.044508799999996</v>
       </c>
       <c r="AC24" s="4">
-        <f t="shared" si="20"/>
-        <v>42.18676767236758</v>
+        <f t="shared" si="53"/>
+        <v>25.545398975999994</v>
       </c>
       <c r="AD24" s="4">
-        <f t="shared" si="20"/>
-        <v>43.030503025814937</v>
+        <f t="shared" si="53"/>
+        <v>26.056306955519993</v>
       </c>
       <c r="AE24" s="4">
-        <f t="shared" si="20"/>
-        <v>43.891113086331231</v>
-      </c>
-    </row>
-    <row r="25" spans="2:141" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="53"/>
+        <v>26.577433094630386</v>
+      </c>
+      <c r="AF24" s="4">
+        <f t="shared" si="53"/>
+        <v>27.108981756523001</v>
+      </c>
+      <c r="AG24" s="4">
+        <f t="shared" si="53"/>
+        <v>27.65116139165346</v>
+      </c>
+      <c r="AH24" s="4">
+        <f t="shared" si="53"/>
+        <v>28.204184619486533</v>
+      </c>
+      <c r="AI24" s="4">
+        <f t="shared" si="53"/>
+        <v>28.76826831187627</v>
+      </c>
+    </row>
+    <row r="25" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F25" s="8">
-        <f>F18-F24</f>
+        <f t="shared" ref="F25:O25" si="54">F18-F24</f>
         <v>-50.700000000000067</v>
       </c>
       <c r="G25" s="8">
-        <f>G18-G24</f>
+        <f t="shared" si="54"/>
         <v>-74.5</v>
       </c>
       <c r="H25" s="8">
-        <f>H18-H24</f>
+        <f t="shared" si="54"/>
         <v>-69.099999999999966</v>
       </c>
       <c r="I25" s="8">
-        <f>I18-I24</f>
+        <f t="shared" si="54"/>
         <v>-167.5</v>
       </c>
       <c r="J25" s="8">
-        <f>J18-J24</f>
+        <f t="shared" si="54"/>
         <v>4.8000000000000114</v>
       </c>
       <c r="K25" s="8">
-        <f>K18-K24</f>
+        <f t="shared" si="54"/>
         <v>-57.19999999999996</v>
       </c>
       <c r="L25" s="8">
-        <f>L18-L24</f>
+        <f t="shared" si="54"/>
         <v>-60.499999999999993</v>
       </c>
       <c r="M25" s="8">
-        <f>M18-M24</f>
+        <f t="shared" si="54"/>
         <v>-14.499999999999968</v>
       </c>
       <c r="N25" s="8">
-        <f>N18-N24</f>
-        <v>14.21954999999997</v>
+        <f t="shared" si="54"/>
+        <v>105.39999999999996</v>
+      </c>
+      <c r="O25" s="8">
+        <f t="shared" si="54"/>
+        <v>-22.999999999999968</v>
       </c>
       <c r="P25" s="8">
-        <f>P18-P24</f>
+        <f t="shared" ref="P25" si="55">P18-P24</f>
+        <v>-41.099999999999952</v>
+      </c>
+      <c r="Q25" s="8">
+        <f t="shared" ref="Q25" si="56">Q18-Q24</f>
+        <v>7.8861999999999171</v>
+      </c>
+      <c r="R25" s="8">
+        <f t="shared" ref="R25" si="57">R18-R24</f>
+        <v>101.59312999999997</v>
+      </c>
+      <c r="T25" s="8">
+        <f t="shared" ref="T25:Y25" si="58">T18-T24</f>
         <v>-178.79999999999993</v>
       </c>
-      <c r="Q25" s="8">
-        <f>Q18-Q24</f>
+      <c r="U25" s="8">
+        <f t="shared" si="58"/>
         <v>-192.2000000000001</v>
       </c>
-      <c r="R25" s="8">
-        <f>R18-R24</f>
+      <c r="V25" s="8">
+        <f t="shared" si="58"/>
         <v>-313.89999999999981</v>
       </c>
-      <c r="S25" s="8">
-        <f>S18-S24</f>
+      <c r="W25" s="8">
+        <f t="shared" si="58"/>
         <v>-306.29999999999995</v>
       </c>
-      <c r="T25" s="8">
-        <f>T18-T24</f>
-        <v>-117.98044999999986</v>
-      </c>
-      <c r="U25" s="8">
-        <f>U18-U24</f>
-        <v>-68.386839599999831</v>
-      </c>
-      <c r="V25" s="8">
-        <f t="shared" ref="V25:AE25" si="21">V18-V24</f>
-        <v>-62.530426340000048</v>
-      </c>
-      <c r="W25" s="8">
-        <f t="shared" si="21"/>
-        <v>-34.854657894000269</v>
-      </c>
       <c r="X25" s="8">
-        <f t="shared" si="21"/>
-        <v>-12.85554712917606</v>
+        <f t="shared" si="58"/>
+        <v>-26.800000000000253</v>
       </c>
       <c r="Y25" s="8">
-        <f t="shared" si="21"/>
-        <v>8.610203638218664</v>
+        <f t="shared" si="58"/>
+        <v>45.379330000000216</v>
       </c>
       <c r="Z25" s="8">
-        <f t="shared" si="21"/>
-        <v>27.698678589762189</v>
+        <f t="shared" ref="Z25:AI25" si="59">Z18-Z24</f>
+        <v>156.12305500000002</v>
       </c>
       <c r="AA25" s="8">
-        <f t="shared" si="21"/>
-        <v>39.795439140400603</v>
+        <f t="shared" si="59"/>
+        <v>202.84003689999977</v>
       </c>
       <c r="AB25" s="8">
-        <f t="shared" si="21"/>
-        <v>48.982658112140747</v>
+        <f t="shared" si="59"/>
+        <v>254.44872999319992</v>
       </c>
       <c r="AC25" s="8">
-        <f t="shared" si="21"/>
-        <v>54.784194049656435</v>
+        <f t="shared" si="59"/>
+        <v>307.912986049496</v>
       </c>
       <c r="AD25" s="8">
-        <f t="shared" si="21"/>
-        <v>60.864580266572716</v>
+        <f t="shared" si="59"/>
+        <v>355.4021737674467</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" si="21"/>
-        <v>67.235186509167264</v>
-      </c>
-    </row>
-    <row r="26" spans="2:141" x14ac:dyDescent="0.3">
+        <f t="shared" si="59"/>
+        <v>386.71196086469041</v>
+      </c>
+      <c r="AF25" s="8">
+        <f t="shared" si="59"/>
+        <v>411.86412448737428</v>
+      </c>
+      <c r="AG25" s="8">
+        <f t="shared" si="59"/>
+        <v>429.92021543111093</v>
+      </c>
+      <c r="AH25" s="8">
+        <f t="shared" si="59"/>
+        <v>448.66455735032997</v>
+      </c>
+      <c r="AI25" s="8">
+        <f t="shared" si="59"/>
+        <v>468.12235738438977</v>
+      </c>
+    </row>
+    <row r="26" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>34</v>
       </c>
@@ -3174,71 +3595,83 @@
         <v>0.1</v>
       </c>
       <c r="N26" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="O26" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="P26" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="4">
         <v>0</v>
       </c>
-      <c r="P26" s="4">
+      <c r="R26" s="4">
+        <v>0</v>
+      </c>
+      <c r="T26" s="4">
         <v>0.3</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="U26" s="4">
         <v>1</v>
       </c>
-      <c r="R26" s="4">
+      <c r="V26" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="S26" s="4">
+      <c r="W26" s="4">
         <f>SUM(G26:J26)</f>
         <v>1.9000000000000001</v>
       </c>
-      <c r="T26" s="4">
+      <c r="X26" s="4">
         <f>SUM(K26:N26)</f>
-        <v>0.5</v>
-      </c>
-      <c r="U26" s="4">
-        <f>U25*0.05</f>
-        <v>-3.4193419799999916</v>
-      </c>
-      <c r="V26" s="4">
-        <f t="shared" ref="V26:AE26" si="22">V25*0.05</f>
-        <v>-3.1265213170000026</v>
-      </c>
-      <c r="W26" s="4">
-        <f t="shared" si="22"/>
-        <v>-1.7427328947000136</v>
-      </c>
-      <c r="X26" s="4">
-        <f t="shared" si="22"/>
-        <v>-0.64277735645880307</v>
+        <v>0.9</v>
       </c>
       <c r="Y26" s="4">
-        <f t="shared" si="22"/>
-        <v>0.43051018191093321</v>
+        <f t="shared" ref="Y26:Y27" si="60">SUM(O26:R26)</f>
+        <v>1.4</v>
       </c>
       <c r="Z26" s="4">
-        <f t="shared" si="22"/>
-        <v>1.3849339294881096</v>
+        <f t="shared" ref="Z26:AI26" si="61">Z25*0.05</f>
+        <v>7.8061527500000016</v>
       </c>
       <c r="AA26" s="4">
-        <f t="shared" si="22"/>
-        <v>1.9897719570200303</v>
+        <f t="shared" si="61"/>
+        <v>10.142001844999989</v>
       </c>
       <c r="AB26" s="4">
-        <f t="shared" si="22"/>
-        <v>2.4491329056070374</v>
+        <f t="shared" si="61"/>
+        <v>12.722436499659997</v>
       </c>
       <c r="AC26" s="4">
-        <f t="shared" si="22"/>
-        <v>2.7392097024828219</v>
+        <f t="shared" si="61"/>
+        <v>15.395649302474801</v>
       </c>
       <c r="AD26" s="4">
-        <f t="shared" si="22"/>
-        <v>3.0432290133286362</v>
+        <f t="shared" si="61"/>
+        <v>17.770108688372336</v>
       </c>
       <c r="AE26" s="4">
-        <f t="shared" si="22"/>
-        <v>3.3617593254583635</v>
-      </c>
-    </row>
-    <row r="27" spans="2:141" x14ac:dyDescent="0.3">
+        <f t="shared" si="61"/>
+        <v>19.335598043234523</v>
+      </c>
+      <c r="AF26" s="4">
+        <f t="shared" si="61"/>
+        <v>20.593206224368714</v>
+      </c>
+      <c r="AG26" s="4">
+        <f t="shared" si="61"/>
+        <v>21.496010771555547</v>
+      </c>
+      <c r="AH26" s="4">
+        <f t="shared" si="61"/>
+        <v>22.4332278675165</v>
+      </c>
+      <c r="AI26" s="4">
+        <f t="shared" si="61"/>
+        <v>23.406117869219489</v>
+      </c>
+    </row>
+    <row r="27" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>35</v>
       </c>
@@ -3267,617 +3700,645 @@
         <v>0.1</v>
       </c>
       <c r="N27" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="O27" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="P27" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="Q27" s="4">
         <v>0</v>
       </c>
-      <c r="P27" s="4">
+      <c r="R27" s="4">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4">
         <v>-21.5</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="U27" s="4">
         <v>-28.9</v>
       </c>
-      <c r="R27" s="4">
+      <c r="V27" s="4">
         <f>-13.4-0.3</f>
         <v>-13.700000000000001</v>
       </c>
-      <c r="S27" s="4">
+      <c r="W27" s="4">
         <f>SUM(G27:J27)</f>
         <v>-5.9</v>
       </c>
-      <c r="T27" s="4">
+      <c r="X27" s="4">
         <f>SUM(K27:N27)</f>
-        <v>1.7000000000000002</v>
-      </c>
-      <c r="U27" s="4">
-        <f>U25*0.02</f>
-        <v>-1.3677367919999968</v>
-      </c>
-      <c r="V27" s="4">
-        <f t="shared" ref="V27:AE27" si="23">V25*0.02</f>
-        <v>-1.2506085268000009</v>
-      </c>
-      <c r="W27" s="4">
-        <f t="shared" si="23"/>
-        <v>-0.69709315788000537</v>
-      </c>
-      <c r="X27" s="4">
-        <f t="shared" si="23"/>
-        <v>-0.25711094258352118</v>
+        <v>2.1</v>
       </c>
       <c r="Y27" s="4">
-        <f t="shared" si="23"/>
-        <v>0.17220407276437327</v>
+        <f t="shared" si="60"/>
+        <v>0.8</v>
       </c>
       <c r="Z27" s="4">
-        <f t="shared" si="23"/>
-        <v>0.55397357179524376</v>
+        <f t="shared" ref="Z27:AI27" si="62">Z25*0.02</f>
+        <v>3.1224611000000007</v>
       </c>
       <c r="AA27" s="4">
-        <f t="shared" si="23"/>
-        <v>0.79590878280801203</v>
+        <f t="shared" si="62"/>
+        <v>4.0568007379999953</v>
       </c>
       <c r="AB27" s="4">
-        <f t="shared" si="23"/>
-        <v>0.97965316224281496</v>
+        <f t="shared" si="62"/>
+        <v>5.0889745998639988</v>
       </c>
       <c r="AC27" s="4">
-        <f t="shared" si="23"/>
-        <v>1.0956838809931286</v>
+        <f t="shared" si="62"/>
+        <v>6.1582597209899204</v>
       </c>
       <c r="AD27" s="4">
-        <f t="shared" si="23"/>
-        <v>1.2172916053314544</v>
+        <f t="shared" si="62"/>
+        <v>7.1080434753489339</v>
       </c>
       <c r="AE27" s="4">
-        <f t="shared" si="23"/>
-        <v>1.3447037301833453</v>
-      </c>
-    </row>
-    <row r="28" spans="2:141" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="62"/>
+        <v>7.7342392172938084</v>
+      </c>
+      <c r="AF27" s="4">
+        <f t="shared" si="62"/>
+        <v>8.2372824897474857</v>
+      </c>
+      <c r="AG27" s="4">
+        <f t="shared" si="62"/>
+        <v>8.5984043086222197</v>
+      </c>
+      <c r="AH27" s="4">
+        <f t="shared" si="62"/>
+        <v>8.9732911470066004</v>
+      </c>
+      <c r="AI27" s="4">
+        <f t="shared" si="62"/>
+        <v>9.3624471476877957</v>
+      </c>
+    </row>
+    <row r="28" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F28" s="8">
-        <f>F25-F26-F27</f>
+        <f t="shared" ref="F28:O28" si="63">F25-F26-F27</f>
         <v>-47.100000000000065</v>
       </c>
       <c r="G28" s="8">
-        <f>G25-G26-G27</f>
+        <f t="shared" si="63"/>
         <v>-71.399999999999991</v>
       </c>
       <c r="H28" s="8">
-        <f>H25-H26-H27</f>
+        <f t="shared" si="63"/>
         <v>-66.299999999999969</v>
       </c>
       <c r="I28" s="8">
-        <f>I25-I26-I27</f>
+        <f t="shared" si="63"/>
         <v>-169</v>
       </c>
       <c r="J28" s="8">
-        <f>J25-J26-J27</f>
+        <f t="shared" si="63"/>
         <v>4.4000000000000119</v>
       </c>
       <c r="K28" s="8">
-        <f>K25-K26-K27</f>
+        <f t="shared" si="63"/>
         <v>-57.69999999999996</v>
       </c>
       <c r="L28" s="8">
-        <f>L25-L26-L27</f>
+        <f t="shared" si="63"/>
         <v>-61.999999999999993</v>
       </c>
       <c r="M28" s="8">
-        <f>M25-M26-M27</f>
+        <f t="shared" si="63"/>
         <v>-14.699999999999967</v>
       </c>
       <c r="N28" s="8">
-        <f>N25-N26-N27</f>
-        <v>14.21954999999997</v>
+        <f t="shared" si="63"/>
+        <v>104.59999999999995</v>
+      </c>
+      <c r="O28" s="8">
+        <f t="shared" si="63"/>
+        <v>-23.799999999999965</v>
       </c>
       <c r="P28" s="8">
-        <f>P25-P26-P27</f>
+        <f t="shared" ref="P28" si="64">P25-P26-P27</f>
+        <v>-42.49999999999995</v>
+      </c>
+      <c r="Q28" s="8">
+        <f t="shared" ref="Q28" si="65">Q25-Q26-Q27</f>
+        <v>7.8861999999999171</v>
+      </c>
+      <c r="R28" s="8">
+        <f t="shared" ref="R28" si="66">R25-R26-R27</f>
+        <v>101.59312999999997</v>
+      </c>
+      <c r="T28" s="8">
+        <f t="shared" ref="T28:Y28" si="67">T25-T26-T27</f>
         <v>-157.59999999999994</v>
       </c>
-      <c r="Q28" s="8">
-        <f>Q25-Q26-Q27</f>
+      <c r="U28" s="8">
+        <f t="shared" si="67"/>
         <v>-164.3000000000001</v>
       </c>
-      <c r="R28" s="8">
-        <f>R25-R26-R27</f>
+      <c r="V28" s="8">
+        <f t="shared" si="67"/>
         <v>-301.29999999999984</v>
       </c>
-      <c r="S28" s="8">
-        <f>S25-S26-S27</f>
+      <c r="W28" s="8">
+        <f t="shared" si="67"/>
         <v>-302.29999999999995</v>
       </c>
-      <c r="T28" s="8">
-        <f>T25-T26-T27</f>
-        <v>-120.18044999999987</v>
-      </c>
-      <c r="U28" s="8">
-        <f>U25-U26-U27</f>
-        <v>-63.599760827999852</v>
-      </c>
-      <c r="V28" s="8">
-        <f t="shared" ref="V28:AE28" si="24">V25-V26-V27</f>
-        <v>-58.153296496200042</v>
-      </c>
-      <c r="W28" s="8">
-        <f t="shared" si="24"/>
-        <v>-32.414831841420252</v>
-      </c>
       <c r="X28" s="8">
-        <f t="shared" si="24"/>
-        <v>-11.955658830133736</v>
+        <f t="shared" si="67"/>
+        <v>-29.800000000000253</v>
       </c>
       <c r="Y28" s="8">
-        <f t="shared" si="24"/>
-        <v>8.0074893835433585</v>
+        <f t="shared" si="67"/>
+        <v>43.17933000000022</v>
       </c>
       <c r="Z28" s="8">
-        <f t="shared" si="24"/>
-        <v>25.759771088478836</v>
+        <f t="shared" ref="Z28:AI28" si="68">Z25-Z26-Z27</f>
+        <v>145.19444115000002</v>
       </c>
       <c r="AA28" s="8">
-        <f t="shared" si="24"/>
-        <v>37.009758400572558</v>
+        <f t="shared" si="68"/>
+        <v>188.6412343169998</v>
       </c>
       <c r="AB28" s="8">
-        <f t="shared" si="24"/>
-        <v>45.553872044290898</v>
+        <f t="shared" si="68"/>
+        <v>236.63731889367591</v>
       </c>
       <c r="AC28" s="8">
-        <f t="shared" si="24"/>
-        <v>50.949300466180482</v>
+        <f t="shared" si="68"/>
+        <v>286.35907702603129</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="24"/>
-        <v>56.604059647912628</v>
+        <f t="shared" si="68"/>
+        <v>330.52402160372543</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" si="24"/>
-        <v>62.528723453525551</v>
-      </c>
-      <c r="AF28" s="1">
-        <f>AE28*(1+$AI$33)</f>
-        <v>61.903436218990294</v>
-      </c>
-      <c r="AG28" s="1">
-        <f t="shared" ref="AG28:CR28" si="25">AF28*(1+$AI$33)</f>
-        <v>61.284401856800393</v>
-      </c>
-      <c r="AH28" s="1">
-        <f t="shared" si="25"/>
-        <v>60.671557838232388</v>
-      </c>
-      <c r="AI28" s="1">
-        <f t="shared" si="25"/>
-        <v>60.064842259850067</v>
+        <f t="shared" si="68"/>
+        <v>359.64212360416207</v>
+      </c>
+      <c r="AF28" s="8">
+        <f t="shared" si="68"/>
+        <v>383.03363577325808</v>
+      </c>
+      <c r="AG28" s="8">
+        <f t="shared" si="68"/>
+        <v>399.82580035093315</v>
+      </c>
+      <c r="AH28" s="8">
+        <f t="shared" si="68"/>
+        <v>417.25803833580687</v>
+      </c>
+      <c r="AI28" s="8">
+        <f t="shared" si="68"/>
+        <v>435.35379236748247</v>
       </c>
       <c r="AJ28" s="1">
-        <f t="shared" si="25"/>
-        <v>59.464193837251564</v>
+        <f>AI28*(1+$AM$33)</f>
+        <v>431.00025444380765</v>
       </c>
       <c r="AK28" s="1">
-        <f t="shared" si="25"/>
-        <v>58.869551898879045</v>
+        <f t="shared" ref="AK28:CV28" si="69">AJ28*(1+$AM$33)</f>
+        <v>426.69025189936957</v>
       </c>
       <c r="AL28" s="1">
-        <f t="shared" si="25"/>
-        <v>58.280856379890253</v>
+        <f t="shared" si="69"/>
+        <v>422.4233493803759</v>
       </c>
       <c r="AM28" s="1">
-        <f t="shared" si="25"/>
-        <v>57.698047816091346</v>
+        <f t="shared" si="69"/>
+        <v>418.19911588657214</v>
       </c>
       <c r="AN28" s="1">
-        <f t="shared" si="25"/>
-        <v>57.121067337930434</v>
+        <f t="shared" si="69"/>
+        <v>414.0171247277064</v>
       </c>
       <c r="AO28" s="1">
-        <f t="shared" si="25"/>
-        <v>56.549856664551129</v>
+        <f t="shared" si="69"/>
+        <v>409.87695348042934</v>
       </c>
       <c r="AP28" s="1">
-        <f t="shared" si="25"/>
-        <v>55.98435809790562</v>
+        <f t="shared" si="69"/>
+        <v>405.77818394562502</v>
       </c>
       <c r="AQ28" s="1">
-        <f t="shared" si="25"/>
-        <v>55.424514516926564</v>
+        <f t="shared" si="69"/>
+        <v>401.72040210616876</v>
       </c>
       <c r="AR28" s="1">
-        <f t="shared" si="25"/>
-        <v>54.870269371757296</v>
+        <f t="shared" si="69"/>
+        <v>397.70319808510709</v>
       </c>
       <c r="AS28" s="1">
-        <f t="shared" si="25"/>
-        <v>54.321566678039723</v>
+        <f t="shared" si="69"/>
+        <v>393.72616610425604</v>
       </c>
       <c r="AT28" s="1">
-        <f t="shared" si="25"/>
-        <v>53.778351011259325</v>
+        <f t="shared" si="69"/>
+        <v>389.78890444321348</v>
       </c>
       <c r="AU28" s="1">
-        <f t="shared" si="25"/>
-        <v>53.240567501146728</v>
+        <f t="shared" si="69"/>
+        <v>385.89101539878135</v>
       </c>
       <c r="AV28" s="1">
-        <f t="shared" si="25"/>
-        <v>52.70816182613526</v>
+        <f t="shared" si="69"/>
+        <v>382.03210524479351</v>
       </c>
       <c r="AW28" s="1">
-        <f t="shared" si="25"/>
-        <v>52.181080207873904</v>
+        <f t="shared" si="69"/>
+        <v>378.21178419234559</v>
       </c>
       <c r="AX28" s="1">
-        <f t="shared" si="25"/>
-        <v>51.659269405795165</v>
+        <f t="shared" si="69"/>
+        <v>374.42966635042211</v>
       </c>
       <c r="AY28" s="1">
-        <f t="shared" si="25"/>
-        <v>51.142676711737209</v>
+        <f t="shared" si="69"/>
+        <v>370.68536968691791</v>
       </c>
       <c r="AZ28" s="1">
-        <f t="shared" si="25"/>
-        <v>50.631249944619839</v>
+        <f t="shared" si="69"/>
+        <v>366.97851599004872</v>
       </c>
       <c r="BA28" s="1">
-        <f t="shared" si="25"/>
-        <v>50.124937445173643</v>
+        <f t="shared" si="69"/>
+        <v>363.30873083014825</v>
       </c>
       <c r="BB28" s="1">
-        <f t="shared" si="25"/>
-        <v>49.623688070721904</v>
+        <f t="shared" si="69"/>
+        <v>359.67564352184678</v>
       </c>
       <c r="BC28" s="1">
-        <f t="shared" si="25"/>
-        <v>49.127451190014682</v>
+        <f t="shared" si="69"/>
+        <v>356.0788870866283</v>
       </c>
       <c r="BD28" s="1">
-        <f t="shared" si="25"/>
-        <v>48.636176678114538</v>
+        <f t="shared" si="69"/>
+        <v>352.518098215762</v>
       </c>
       <c r="BE28" s="1">
-        <f t="shared" si="25"/>
-        <v>48.149814911333394</v>
+        <f t="shared" si="69"/>
+        <v>348.99291723360437</v>
       </c>
       <c r="BF28" s="1">
-        <f t="shared" si="25"/>
-        <v>47.668316762220059</v>
+        <f t="shared" si="69"/>
+        <v>345.50298806126835</v>
       </c>
       <c r="BG28" s="1">
-        <f t="shared" si="25"/>
-        <v>47.19163359459786</v>
+        <f t="shared" si="69"/>
+        <v>342.04795818065566</v>
       </c>
       <c r="BH28" s="1">
-        <f t="shared" si="25"/>
-        <v>46.719717258651883</v>
+        <f t="shared" si="69"/>
+        <v>338.62747859884911</v>
       </c>
       <c r="BI28" s="1">
-        <f t="shared" si="25"/>
-        <v>46.252520086065367</v>
+        <f t="shared" si="69"/>
+        <v>335.24120381286059</v>
       </c>
       <c r="BJ28" s="1">
-        <f t="shared" si="25"/>
-        <v>45.789994885204713</v>
+        <f t="shared" si="69"/>
+        <v>331.888791774732</v>
       </c>
       <c r="BK28" s="1">
-        <f t="shared" si="25"/>
-        <v>45.332094936352668</v>
+        <f t="shared" si="69"/>
+        <v>328.56990385698469</v>
       </c>
       <c r="BL28" s="1">
-        <f t="shared" si="25"/>
-        <v>44.878773986989138</v>
+        <f t="shared" si="69"/>
+        <v>325.28420481841482</v>
       </c>
       <c r="BM28" s="1">
-        <f t="shared" si="25"/>
-        <v>44.429986247119245</v>
+        <f t="shared" si="69"/>
+        <v>322.03136277023066</v>
       </c>
       <c r="BN28" s="1">
-        <f t="shared" si="25"/>
-        <v>43.985686384648055</v>
+        <f t="shared" si="69"/>
+        <v>318.81104914252836</v>
       </c>
       <c r="BO28" s="1">
-        <f t="shared" si="25"/>
-        <v>43.545829520801576</v>
+        <f t="shared" si="69"/>
+        <v>315.62293865110308</v>
       </c>
       <c r="BP28" s="1">
-        <f t="shared" si="25"/>
-        <v>43.11037122559356</v>
+        <f t="shared" si="69"/>
+        <v>312.46670926459205</v>
       </c>
       <c r="BQ28" s="1">
-        <f t="shared" si="25"/>
-        <v>42.679267513337628</v>
+        <f t="shared" si="69"/>
+        <v>309.3420421719461</v>
       </c>
       <c r="BR28" s="1">
-        <f t="shared" si="25"/>
-        <v>42.25247483820425</v>
+        <f t="shared" si="69"/>
+        <v>306.24862175022662</v>
       </c>
       <c r="BS28" s="1">
-        <f t="shared" si="25"/>
-        <v>41.829950089822205</v>
+        <f t="shared" si="69"/>
+        <v>303.18613553272434</v>
       </c>
       <c r="BT28" s="1">
-        <f t="shared" si="25"/>
-        <v>41.411650588923983</v>
+        <f t="shared" si="69"/>
+        <v>300.1542741773971</v>
       </c>
       <c r="BU28" s="1">
-        <f t="shared" si="25"/>
-        <v>40.997534083034743</v>
+        <f t="shared" si="69"/>
+        <v>297.15273143562314</v>
       </c>
       <c r="BV28" s="1">
-        <f t="shared" si="25"/>
-        <v>40.587558742204394</v>
+        <f t="shared" si="69"/>
+        <v>294.18120412126689</v>
       </c>
       <c r="BW28" s="1">
-        <f t="shared" si="25"/>
-        <v>40.181683154782348</v>
+        <f t="shared" si="69"/>
+        <v>291.23939208005419</v>
       </c>
       <c r="BX28" s="1">
-        <f t="shared" si="25"/>
-        <v>39.779866323234522</v>
+        <f t="shared" si="69"/>
+        <v>288.32699815925366</v>
       </c>
       <c r="BY28" s="1">
-        <f t="shared" si="25"/>
-        <v>39.382067660002178</v>
+        <f t="shared" si="69"/>
+        <v>285.44372817766111</v>
       </c>
       <c r="BZ28" s="1">
-        <f t="shared" si="25"/>
-        <v>38.988246983402156</v>
+        <f t="shared" si="69"/>
+        <v>282.58929089588452</v>
       </c>
       <c r="CA28" s="1">
-        <f t="shared" si="25"/>
-        <v>38.598364513568136</v>
+        <f t="shared" si="69"/>
+        <v>279.76339798692567</v>
       </c>
       <c r="CB28" s="1">
-        <f t="shared" si="25"/>
-        <v>38.212380868432454</v>
+        <f t="shared" si="69"/>
+        <v>276.96576400705641</v>
       </c>
       <c r="CC28" s="1">
-        <f t="shared" si="25"/>
-        <v>37.830257059748128</v>
+        <f t="shared" si="69"/>
+        <v>274.19610636698582</v>
       </c>
       <c r="CD28" s="1">
-        <f t="shared" si="25"/>
-        <v>37.451954489150644</v>
+        <f t="shared" si="69"/>
+        <v>271.45414530331595</v>
       </c>
       <c r="CE28" s="1">
-        <f t="shared" si="25"/>
-        <v>37.077434944259139</v>
+        <f t="shared" si="69"/>
+        <v>268.73960385028278</v>
       </c>
       <c r="CF28" s="1">
-        <f t="shared" si="25"/>
-        <v>36.706660594816547</v>
+        <f t="shared" si="69"/>
+        <v>266.05220781177997</v>
       </c>
       <c r="CG28" s="1">
-        <f t="shared" si="25"/>
-        <v>36.33959398886838</v>
+        <f t="shared" si="69"/>
+        <v>263.39168573366214</v>
       </c>
       <c r="CH28" s="1">
-        <f t="shared" si="25"/>
-        <v>35.976198048979697</v>
+        <f t="shared" si="69"/>
+        <v>260.75776887632554</v>
       </c>
       <c r="CI28" s="1">
-        <f t="shared" si="25"/>
-        <v>35.616436068489897</v>
+        <f t="shared" si="69"/>
+        <v>258.15019118756226</v>
       </c>
       <c r="CJ28" s="1">
-        <f t="shared" si="25"/>
-        <v>35.260271707804996</v>
+        <f t="shared" si="69"/>
+        <v>255.56868927568664</v>
       </c>
       <c r="CK28" s="1">
-        <f t="shared" si="25"/>
-        <v>34.907668990726947</v>
+        <f t="shared" si="69"/>
+        <v>253.01300238292976</v>
       </c>
       <c r="CL28" s="1">
-        <f t="shared" si="25"/>
-        <v>34.558592300819676</v>
+        <f t="shared" si="69"/>
+        <v>250.48287235910047</v>
       </c>
       <c r="CM28" s="1">
-        <f t="shared" si="25"/>
-        <v>34.213006377811482</v>
+        <f t="shared" si="69"/>
+        <v>247.97804363550947</v>
       </c>
       <c r="CN28" s="1">
-        <f t="shared" si="25"/>
-        <v>33.870876314033367</v>
+        <f t="shared" si="69"/>
+        <v>245.49826319915437</v>
       </c>
       <c r="CO28" s="1">
-        <f t="shared" si="25"/>
-        <v>33.532167550893035</v>
+        <f t="shared" si="69"/>
+        <v>243.04328056716281</v>
       </c>
       <c r="CP28" s="1">
-        <f t="shared" si="25"/>
-        <v>33.196845875384106</v>
+        <f t="shared" si="69"/>
+        <v>240.61284776149117</v>
       </c>
       <c r="CQ28" s="1">
-        <f t="shared" si="25"/>
-        <v>32.864877416630264</v>
+        <f t="shared" si="69"/>
+        <v>238.20671928387625</v>
       </c>
       <c r="CR28" s="1">
-        <f t="shared" si="25"/>
-        <v>32.536228642463961</v>
+        <f t="shared" si="69"/>
+        <v>235.82465209103748</v>
       </c>
       <c r="CS28" s="1">
-        <f t="shared" ref="CS28:EK28" si="26">CR28*(1+$AI$33)</f>
-        <v>32.210866356039318</v>
+        <f t="shared" si="69"/>
+        <v>233.46640557012711</v>
       </c>
       <c r="CT28" s="1">
-        <f t="shared" si="26"/>
-        <v>31.888757692478926</v>
+        <f t="shared" si="69"/>
+        <v>231.13174151442584</v>
       </c>
       <c r="CU28" s="1">
-        <f t="shared" si="26"/>
-        <v>31.569870115554135</v>
+        <f t="shared" si="69"/>
+        <v>228.82042409928158</v>
       </c>
       <c r="CV28" s="1">
-        <f t="shared" si="26"/>
-        <v>31.254171414398595</v>
+        <f t="shared" si="69"/>
+        <v>226.53221985828876</v>
       </c>
       <c r="CW28" s="1">
-        <f t="shared" si="26"/>
-        <v>30.941629700254609</v>
+        <f t="shared" ref="CW28:EO28" si="70">CV28*(1+$AM$33)</f>
+        <v>224.26689765970588</v>
       </c>
       <c r="CX28" s="1">
-        <f t="shared" si="26"/>
-        <v>30.632213403252063</v>
+        <f t="shared" si="70"/>
+        <v>222.02422868310882</v>
       </c>
       <c r="CY28" s="1">
-        <f t="shared" si="26"/>
-        <v>30.325891269219543</v>
+        <f t="shared" si="70"/>
+        <v>219.80398639627774</v>
       </c>
       <c r="CZ28" s="1">
-        <f t="shared" si="26"/>
-        <v>30.022632356527346</v>
+        <f t="shared" si="70"/>
+        <v>217.60594653231496</v>
       </c>
       <c r="DA28" s="1">
-        <f t="shared" si="26"/>
-        <v>29.722406032962073</v>
+        <f t="shared" si="70"/>
+        <v>215.4298870669918</v>
       </c>
       <c r="DB28" s="1">
-        <f t="shared" si="26"/>
-        <v>29.425181972632451</v>
+        <f t="shared" si="70"/>
+        <v>213.27558819632188</v>
       </c>
       <c r="DC28" s="1">
-        <f t="shared" si="26"/>
-        <v>29.130930152906128</v>
+        <f t="shared" si="70"/>
+        <v>211.14283231435866</v>
       </c>
       <c r="DD28" s="1">
-        <f t="shared" si="26"/>
-        <v>28.839620851377067</v>
+        <f t="shared" si="70"/>
+        <v>209.03140399121506</v>
       </c>
       <c r="DE28" s="1">
-        <f t="shared" si="26"/>
-        <v>28.551224642863296</v>
+        <f t="shared" si="70"/>
+        <v>206.9410899513029</v>
       </c>
       <c r="DF28" s="1">
-        <f t="shared" si="26"/>
-        <v>28.265712396434662</v>
+        <f t="shared" si="70"/>
+        <v>204.87167905178987</v>
       </c>
       <c r="DG28" s="1">
-        <f t="shared" si="26"/>
-        <v>27.983055272470313</v>
+        <f t="shared" si="70"/>
+        <v>202.82296226127198</v>
       </c>
       <c r="DH28" s="1">
-        <f t="shared" si="26"/>
-        <v>27.703224719745609</v>
+        <f t="shared" si="70"/>
+        <v>200.79473263865927</v>
       </c>
       <c r="DI28" s="1">
-        <f t="shared" si="26"/>
-        <v>27.426192472548152</v>
+        <f t="shared" si="70"/>
+        <v>198.78678531227268</v>
       </c>
       <c r="DJ28" s="1">
-        <f t="shared" si="26"/>
-        <v>27.151930547822669</v>
+        <f t="shared" si="70"/>
+        <v>196.79891745914995</v>
       </c>
       <c r="DK28" s="1">
-        <f t="shared" si="26"/>
-        <v>26.880411242344444</v>
+        <f t="shared" si="70"/>
+        <v>194.83092828455844</v>
       </c>
       <c r="DL28" s="1">
-        <f t="shared" si="26"/>
-        <v>26.611607129920998</v>
+        <f t="shared" si="70"/>
+        <v>192.88261900171284</v>
       </c>
       <c r="DM28" s="1">
-        <f t="shared" si="26"/>
-        <v>26.345491058621789</v>
+        <f t="shared" si="70"/>
+        <v>190.95379281169571</v>
       </c>
       <c r="DN28" s="1">
-        <f t="shared" si="26"/>
-        <v>26.08203614803557</v>
+        <f t="shared" si="70"/>
+        <v>189.04425488357876</v>
       </c>
       <c r="DO28" s="1">
-        <f t="shared" si="26"/>
-        <v>25.821215786555214</v>
+        <f t="shared" si="70"/>
+        <v>187.15381233474298</v>
       </c>
       <c r="DP28" s="1">
-        <f t="shared" si="26"/>
-        <v>25.56300362868966</v>
+        <f t="shared" si="70"/>
+        <v>185.28227421139556</v>
       </c>
       <c r="DQ28" s="1">
-        <f t="shared" si="26"/>
-        <v>25.307373592402765</v>
+        <f t="shared" si="70"/>
+        <v>183.42945146928162</v>
       </c>
       <c r="DR28" s="1">
-        <f t="shared" si="26"/>
-        <v>25.054299856478739</v>
+        <f t="shared" si="70"/>
+        <v>181.59515695458879</v>
       </c>
       <c r="DS28" s="1">
-        <f t="shared" si="26"/>
-        <v>24.80375685791395</v>
+        <f t="shared" si="70"/>
+        <v>179.7792053850429</v>
       </c>
       <c r="DT28" s="1">
-        <f t="shared" si="26"/>
-        <v>24.55571928933481</v>
+        <f t="shared" si="70"/>
+        <v>177.98141333119247</v>
       </c>
       <c r="DU28" s="1">
-        <f t="shared" si="26"/>
-        <v>24.310162096441463</v>
+        <f t="shared" si="70"/>
+        <v>176.20159919788054</v>
       </c>
       <c r="DV28" s="1">
-        <f t="shared" si="26"/>
-        <v>24.067060475477049</v>
+        <f t="shared" si="70"/>
+        <v>174.43958320590173</v>
       </c>
       <c r="DW28" s="1">
-        <f t="shared" si="26"/>
-        <v>23.826389870722277</v>
+        <f t="shared" si="70"/>
+        <v>172.69518737384271</v>
       </c>
       <c r="DX28" s="1">
-        <f t="shared" si="26"/>
-        <v>23.588125972015053</v>
+        <f t="shared" si="70"/>
+        <v>170.9682355001043</v>
       </c>
       <c r="DY28" s="1">
-        <f t="shared" si="26"/>
-        <v>23.352244712294901</v>
+        <f t="shared" si="70"/>
+        <v>169.25855314510326</v>
       </c>
       <c r="DZ28" s="1">
-        <f t="shared" si="26"/>
-        <v>23.11872226517195</v>
+        <f t="shared" si="70"/>
+        <v>167.56596761365222</v>
       </c>
       <c r="EA28" s="1">
-        <f t="shared" si="26"/>
-        <v>22.887535042520231</v>
+        <f t="shared" si="70"/>
+        <v>165.8903079375157</v>
       </c>
       <c r="EB28" s="1">
-        <f t="shared" si="26"/>
-        <v>22.658659692095029</v>
+        <f t="shared" si="70"/>
+        <v>164.23140485814054</v>
       </c>
       <c r="EC28" s="1">
-        <f t="shared" si="26"/>
-        <v>22.432073095174079</v>
+        <f t="shared" si="70"/>
+        <v>162.58909080955914</v>
       </c>
       <c r="ED28" s="1">
-        <f t="shared" si="26"/>
-        <v>22.207752364222337</v>
+        <f t="shared" si="70"/>
+        <v>160.96319990146355</v>
       </c>
       <c r="EE28" s="1">
-        <f t="shared" si="26"/>
-        <v>21.985674840580113</v>
+        <f t="shared" si="70"/>
+        <v>159.35356790244893</v>
       </c>
       <c r="EF28" s="1">
-        <f t="shared" si="26"/>
-        <v>21.765818092174314</v>
+        <f t="shared" si="70"/>
+        <v>157.76003222342445</v>
       </c>
       <c r="EG28" s="1">
-        <f t="shared" si="26"/>
-        <v>21.548159911252572</v>
+        <f t="shared" si="70"/>
+        <v>156.1824319011902</v>
       </c>
       <c r="EH28" s="1">
-        <f t="shared" si="26"/>
-        <v>21.332678312140047</v>
+        <f t="shared" si="70"/>
+        <v>154.62060758217831</v>
       </c>
       <c r="EI28" s="1">
-        <f t="shared" si="26"/>
-        <v>21.119351529018648</v>
+        <f t="shared" si="70"/>
+        <v>153.07440150635654</v>
       </c>
       <c r="EJ28" s="1">
-        <f t="shared" si="26"/>
-        <v>20.90815801372846</v>
+        <f t="shared" si="70"/>
+        <v>151.54365749129298</v>
       </c>
       <c r="EK28" s="1">
-        <f t="shared" si="26"/>
-        <v>20.699076433591177</v>
-      </c>
-    </row>
-    <row r="29" spans="2:141" x14ac:dyDescent="0.3">
+        <f t="shared" si="70"/>
+        <v>150.02822091638004</v>
+      </c>
+      <c r="EL28" s="1">
+        <f t="shared" si="70"/>
+        <v>148.52793870721624</v>
+      </c>
+      <c r="EM28" s="1">
+        <f t="shared" si="70"/>
+        <v>147.04265932014408</v>
+      </c>
+      <c r="EN28" s="1">
+        <f t="shared" si="70"/>
+        <v>145.57223272694264</v>
+      </c>
+      <c r="EO28" s="1">
+        <f t="shared" si="70"/>
+        <v>144.11651039967322</v>
+      </c>
+    </row>
+    <row r="29" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>2</v>
       </c>
@@ -3906,19 +4367,23 @@
         <v>228.6</v>
       </c>
       <c r="N29" s="4">
-        <v>228.6</v>
+        <v>228.7</v>
+      </c>
+      <c r="O29" s="4">
+        <f>232.2</f>
+        <v>232.2</v>
       </c>
       <c r="P29" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
       </c>
       <c r="Q29" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
       </c>
       <c r="R29" s="4">
-        <v>228.6</v>
-      </c>
-      <c r="S29" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
       </c>
       <c r="T29" s="4">
         <v>228.6</v>
@@ -3936,146 +4401,185 @@
         <v>228.6</v>
       </c>
       <c r="Y29" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
       </c>
       <c r="Z29" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
       </c>
       <c r="AA29" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
       </c>
       <c r="AB29" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
       </c>
       <c r="AC29" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
       </c>
       <c r="AD29" s="4">
-        <v>228.6</v>
+        <f>234</f>
+        <v>234</v>
       </c>
       <c r="AE29" s="4">
-        <v>228.6</v>
-      </c>
-    </row>
-    <row r="30" spans="2:141" x14ac:dyDescent="0.3">
+        <f>234</f>
+        <v>234</v>
+      </c>
+      <c r="AF29" s="4">
+        <f>234</f>
+        <v>234</v>
+      </c>
+      <c r="AG29" s="4">
+        <f>234</f>
+        <v>234</v>
+      </c>
+      <c r="AH29" s="4">
+        <f>234</f>
+        <v>234</v>
+      </c>
+      <c r="AI29" s="4">
+        <f>234</f>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="F30" s="6">
-        <f>F28/F29</f>
+        <f t="shared" ref="F30:O30" si="71">F28/F29</f>
         <v>-0.20603674540682443</v>
       </c>
       <c r="G30" s="6">
-        <f>G28/G29</f>
+        <f t="shared" si="71"/>
         <v>-0.31233595800524933</v>
       </c>
       <c r="H30" s="6">
-        <f>H28/H29</f>
+        <f t="shared" si="71"/>
         <v>-0.29002624671916</v>
       </c>
       <c r="I30" s="6">
-        <f>I28/I29</f>
+        <f t="shared" si="71"/>
         <v>-0.73928258967629046</v>
       </c>
       <c r="J30" s="6">
-        <f>J28/J29</f>
+        <f t="shared" si="71"/>
         <v>1.9247594050743711E-2</v>
       </c>
       <c r="K30" s="6">
-        <f>K28/K29</f>
+        <f t="shared" si="71"/>
         <v>-0.2524059492563428</v>
       </c>
       <c r="L30" s="6">
-        <f>L28/L29</f>
+        <f t="shared" si="71"/>
         <v>-0.27121609798775148</v>
       </c>
       <c r="M30" s="6">
-        <f>M28/M29</f>
+        <f t="shared" si="71"/>
         <v>-6.4304461942257071E-2</v>
       </c>
       <c r="N30" s="6">
-        <f>N28/N29</f>
-        <v>6.2202755905511678E-2</v>
+        <f t="shared" si="71"/>
+        <v>0.45736773065150832</v>
+      </c>
+      <c r="O30" s="6">
+        <f t="shared" si="71"/>
+        <v>-0.10249784668389306</v>
       </c>
       <c r="P30" s="6">
-        <f>P28/P29</f>
+        <f t="shared" ref="P30" si="72">P28/P29</f>
+        <v>-0.18162393162393142</v>
+      </c>
+      <c r="Q30" s="6">
+        <f t="shared" ref="Q30" si="73">Q28/Q29</f>
+        <v>3.3701709401709044E-2</v>
+      </c>
+      <c r="R30" s="6">
+        <f t="shared" ref="R30" si="74">R28/R29</f>
+        <v>0.43415867521367513</v>
+      </c>
+      <c r="T30" s="6">
+        <f t="shared" ref="T30:Y30" si="75">T28/T29</f>
         <v>-0.68941382327209078</v>
       </c>
-      <c r="Q30" s="6">
-        <f>Q28/Q29</f>
+      <c r="U30" s="6">
+        <f t="shared" si="75"/>
         <v>-0.71872265966754201</v>
       </c>
-      <c r="R30" s="6">
-        <f>R28/R29</f>
+      <c r="V30" s="6">
+        <f t="shared" si="75"/>
         <v>-1.3180227471566048</v>
       </c>
-      <c r="S30" s="6">
-        <f>S28/S29</f>
+      <c r="W30" s="6">
+        <f t="shared" si="75"/>
         <v>-1.322397200349956</v>
       </c>
-      <c r="T30" s="6">
-        <f>T28/T29</f>
-        <v>-0.52572375328083931</v>
-      </c>
-      <c r="U30" s="6">
-        <f>U28/U29</f>
-        <v>-0.27821417685039307</v>
-      </c>
-      <c r="V30" s="6">
-        <f t="shared" ref="V30:AE30" si="27">V28/V29</f>
-        <v>-0.25438887356168</v>
-      </c>
-      <c r="W30" s="6">
-        <f t="shared" si="27"/>
-        <v>-0.14179716466063103</v>
-      </c>
       <c r="X30" s="6">
-        <f t="shared" si="27"/>
-        <v>-5.2299469948091586E-2</v>
+        <f t="shared" si="75"/>
+        <v>-0.13035870516185588</v>
       </c>
       <c r="Y30" s="6">
-        <f t="shared" si="27"/>
-        <v>3.5028387504564121E-2</v>
+        <f t="shared" si="75"/>
+        <v>0.18452705128205221</v>
       </c>
       <c r="Z30" s="6">
-        <f t="shared" si="27"/>
-        <v>0.11268491289798266</v>
+        <f t="shared" ref="Z30:AI30" si="76">Z28/Z29</f>
+        <v>0.62048906474358978</v>
       </c>
       <c r="AA30" s="6">
-        <f t="shared" si="27"/>
-        <v>0.16189745582052739</v>
+        <f t="shared" si="76"/>
+        <v>0.80615912101281961</v>
       </c>
       <c r="AB30" s="6">
-        <f t="shared" si="27"/>
-        <v>0.19927328103364347</v>
+        <f t="shared" si="76"/>
+        <v>1.0112705935627175</v>
       </c>
       <c r="AC30" s="6">
-        <f t="shared" si="27"/>
-        <v>0.22287533012327421</v>
+        <f t="shared" si="76"/>
+        <v>1.2237567394274842</v>
       </c>
       <c r="AD30" s="6">
-        <f t="shared" si="27"/>
-        <v>0.24761180948343234</v>
+        <f t="shared" si="76"/>
+        <v>1.4124958188193395</v>
       </c>
       <c r="AE30" s="6">
-        <f t="shared" si="27"/>
-        <v>0.27352897398742587</v>
-      </c>
-    </row>
-    <row r="32" spans="2:141" x14ac:dyDescent="0.3">
+        <f t="shared" si="76"/>
+        <v>1.5369321521545387</v>
+      </c>
+      <c r="AF30" s="6">
+        <f t="shared" si="76"/>
+        <v>1.6368958793728978</v>
+      </c>
+      <c r="AG30" s="6">
+        <f t="shared" si="76"/>
+        <v>1.7086572664569792</v>
+      </c>
+      <c r="AH30" s="6">
+        <f t="shared" si="76"/>
+        <v>1.7831540099820806</v>
+      </c>
+      <c r="AI30" s="6">
+        <f t="shared" si="76"/>
+        <v>1.8604862921687284</v>
+      </c>
+    </row>
+    <row r="32" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>51</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" ref="J32:L36" si="28">J3/F3-1</f>
+        <f t="shared" ref="J32:L36" si="77">J3/F3-1</f>
         <v>-0.27318156579677955</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>-0.20805369127516771</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>5.4028877503493389E-2</v>
       </c>
       <c r="M32" s="9">
@@ -4084,470 +4588,550 @@
       </c>
       <c r="N32" s="9">
         <f>N3/J3-1</f>
-        <v>-5.0000000000000044E-2</v>
-      </c>
-      <c r="P32" s="9"/>
+        <v>0.80175706646294875</v>
+      </c>
+      <c r="O32" s="9">
+        <f t="shared" ref="O32:R36" si="78">O3/K3-1</f>
+        <v>0.38135593220338992</v>
+      </c>
+      <c r="P32" s="9">
+        <f t="shared" si="78"/>
+        <v>0.31064958020327005</v>
+      </c>
       <c r="Q32" s="9">
-        <f>Q3/P3-1</f>
+        <f t="shared" si="78"/>
+        <v>0.29999999999999982</v>
+      </c>
+      <c r="R32" s="9">
+        <f t="shared" si="78"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9">
+        <f>U3/T3-1</f>
         <v>0.27940609332819122</v>
       </c>
-      <c r="R32" s="9">
-        <f t="shared" ref="R32:T32" si="29">R3/Q3-1</f>
+      <c r="V32" s="9">
+        <f t="shared" ref="V32:X32" si="79">V3/U3-1</f>
         <v>0.32735493594574239</v>
       </c>
-      <c r="S32" s="9">
-        <f t="shared" si="29"/>
+      <c r="W32" s="9">
+        <f t="shared" si="79"/>
         <v>0.10730101055978203</v>
       </c>
-      <c r="T32" s="9">
-        <f t="shared" si="29"/>
-        <v>-0.11586341263330602</v>
-      </c>
-      <c r="U32" s="9">
-        <f t="shared" ref="U32:AE32" si="30">U3/T3-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="V32" s="9">
-        <f t="shared" si="30"/>
+      <c r="X32" s="9">
+        <f t="shared" si="79"/>
+        <v>0.11279737489745689</v>
+      </c>
+      <c r="Y32" s="9">
+        <f t="shared" ref="Y32:AI32" si="80">Y3/X3-1</f>
+        <v>0.20505436785845932</v>
+      </c>
+      <c r="Z32" s="9">
+        <f t="shared" si="80"/>
+        <v>0.1399999999999999</v>
+      </c>
+      <c r="AA32" s="9">
+        <f t="shared" si="80"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AB32" s="9">
+        <f t="shared" si="80"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AC32" s="9">
+        <f t="shared" si="80"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AD32" s="9">
+        <f t="shared" si="80"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AE32" s="9">
+        <f t="shared" si="80"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="W32" s="9">
-        <f t="shared" si="30"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="X32" s="9">
-        <f t="shared" si="30"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="Y32" s="9">
-        <f t="shared" si="30"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="Z32" s="9">
-        <f t="shared" si="30"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AA32" s="9">
-        <f t="shared" si="30"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AB32" s="9">
-        <f t="shared" si="30"/>
+      <c r="AF32" s="9">
+        <f t="shared" si="80"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AC32" s="9">
-        <f t="shared" si="30"/>
+      <c r="AG32" s="9">
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD32" s="9">
-        <f t="shared" si="30"/>
+      <c r="AH32" s="9">
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AE32" s="9">
-        <f t="shared" si="30"/>
+      <c r="AI32" s="9">
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>52</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>-0.39814814814814814</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>-0.44390243902439019</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>0.7644628099173556</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" ref="M33:N36" si="31">M4/I4-1</f>
+        <f t="shared" ref="M33:N36" si="81">M4/I4-1</f>
         <v>0.46575342465753433</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="31"/>
-        <v>0.5</v>
-      </c>
-      <c r="P33" s="9"/>
+        <f t="shared" si="81"/>
+        <v>0.38846153846153841</v>
+      </c>
+      <c r="O33" s="9">
+        <f t="shared" si="78"/>
+        <v>1.9561403508771931</v>
+      </c>
+      <c r="P33" s="9">
+        <f t="shared" si="78"/>
+        <v>-0.12412177985948492</v>
+      </c>
       <c r="Q33" s="9">
-        <f t="shared" ref="Q33:T36" si="32">Q4/P4-1</f>
+        <f t="shared" si="78"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="78"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9">
+        <f t="shared" ref="U33:X36" si="82">U4/T4-1</f>
         <v>-5.6918547595682156E-2</v>
       </c>
-      <c r="R33" s="9">
-        <f t="shared" si="32"/>
+      <c r="V33" s="9">
+        <f t="shared" si="82"/>
         <v>-4.1623309053069768E-2</v>
       </c>
-      <c r="S33" s="9">
-        <f t="shared" si="32"/>
+      <c r="W33" s="9">
+        <f t="shared" si="82"/>
         <v>5.4288816503800241E-3</v>
       </c>
-      <c r="T33" s="9">
-        <f t="shared" si="32"/>
-        <v>0.35205183585313193</v>
-      </c>
-      <c r="U33" s="9">
-        <f t="shared" ref="U33:AE33" si="33">U4/T4-1</f>
-        <v>0.35782747603833864</v>
-      </c>
-      <c r="V33" s="9">
-        <f t="shared" si="33"/>
+      <c r="X33" s="9">
+        <f t="shared" si="82"/>
+        <v>0.32073434125269995</v>
+      </c>
+      <c r="Y33" s="9">
+        <f t="shared" ref="Y33:AI33" si="83">Y4/X4-1</f>
+        <v>0.16688470973017178</v>
+      </c>
+      <c r="Z33" s="9">
+        <f t="shared" si="83"/>
         <v>0.25</v>
       </c>
-      <c r="W33" s="9">
-        <f t="shared" si="33"/>
+      <c r="AA33" s="9">
+        <f t="shared" si="83"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="X33" s="9">
-        <f t="shared" si="33"/>
+      <c r="AB33" s="9">
+        <f t="shared" si="83"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="Y33" s="9">
-        <f t="shared" si="33"/>
+      <c r="AC33" s="9">
+        <f t="shared" si="83"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="Z33" s="9">
-        <f t="shared" si="33"/>
+      <c r="AD33" s="9">
+        <f t="shared" si="83"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AE33" s="9">
+        <f t="shared" si="83"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AA33" s="9">
-        <f t="shared" si="33"/>
+      <c r="AF33" s="9">
+        <f t="shared" si="83"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AB33" s="9">
-        <f t="shared" si="33"/>
+      <c r="AG33" s="9">
+        <f t="shared" si="83"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC33" s="9">
-        <f t="shared" si="33"/>
+      <c r="AH33" s="9">
+        <f t="shared" si="83"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD33" s="9">
-        <f t="shared" si="33"/>
+      <c r="AI33" s="9">
+        <f t="shared" si="83"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE33" s="9">
-        <f t="shared" si="33"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AH33" t="s">
+      <c r="AL33" t="s">
         <v>65</v>
       </c>
-      <c r="AI33" s="9">
+      <c r="AM33" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>53</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>0.31829573934837097</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>0.38574938574938566</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>0.24113475177304977</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="81"/>
         <v>6.9473684210526354E-2</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="81"/>
+        <v>2.281368821292773E-2</v>
+      </c>
+      <c r="O34" s="9">
+        <f t="shared" si="78"/>
+        <v>-5.1418439716311992E-2</v>
+      </c>
+      <c r="P34" s="9">
+        <f t="shared" si="78"/>
+        <v>3.6190476190476106E-2</v>
+      </c>
+      <c r="Q34" s="9">
+        <f t="shared" si="78"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" si="78"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9">
+        <f t="shared" si="82"/>
+        <v>0.31569343065693434</v>
+      </c>
+      <c r="V34" s="9">
+        <f t="shared" si="82"/>
+        <v>4.7156726768377233E-2</v>
+      </c>
+      <c r="W34" s="9">
+        <f t="shared" si="82"/>
+        <v>0.21258278145695364</v>
+      </c>
+      <c r="X34" s="9">
+        <f t="shared" si="82"/>
+        <v>0.16602949208083029</v>
+      </c>
+      <c r="Y34" s="9">
+        <f t="shared" ref="Y34:AI34" si="84">Y5/X5-1</f>
+        <v>5.1147540983607076E-3</v>
+      </c>
+      <c r="Z34" s="9">
+        <f t="shared" si="84"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AA34" s="9">
+        <f t="shared" si="84"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9">
-        <f t="shared" si="32"/>
-        <v>0.31569343065693434</v>
-      </c>
-      <c r="R34" s="9">
-        <f t="shared" si="32"/>
-        <v>4.7156726768377233E-2</v>
-      </c>
-      <c r="S34" s="9">
-        <f t="shared" si="32"/>
-        <v>0.21258278145695364</v>
-      </c>
-      <c r="T34" s="9">
-        <f t="shared" si="32"/>
-        <v>0.17958492626979794</v>
-      </c>
-      <c r="U34" s="9">
-        <f t="shared" ref="U34:AE34" si="34">U5/T5-1</f>
-        <v>0.1399999999999999</v>
-      </c>
-      <c r="V34" s="9">
-        <f t="shared" si="34"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="W34" s="9">
-        <f t="shared" si="34"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="X34" s="9">
-        <f t="shared" si="34"/>
+      <c r="AB34" s="9">
+        <f t="shared" si="84"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="Y34" s="9">
-        <f t="shared" si="34"/>
+      <c r="AC34" s="9">
+        <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="Z34" s="9">
-        <f t="shared" si="34"/>
+      <c r="AD34" s="9">
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA34" s="9">
-        <f t="shared" si="34"/>
+      <c r="AE34" s="9">
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB34" s="9">
-        <f t="shared" si="34"/>
+      <c r="AF34" s="9">
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC34" s="9">
-        <f t="shared" si="34"/>
+      <c r="AG34" s="9">
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD34" s="9">
-        <f t="shared" si="34"/>
+      <c r="AH34" s="9">
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE34" s="9">
-        <f t="shared" si="34"/>
+      <c r="AI34" s="9">
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH34" t="s">
+      <c r="AL34" t="s">
         <v>66</v>
       </c>
-      <c r="AI34" s="9">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AM34" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="35" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>54</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>-0.140625</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>-0.31034482758620696</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="77"/>
         <v>-0.28282828282828287</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="81"/>
         <v>-0.46511627906976738</v>
       </c>
       <c r="N35" s="9">
-        <f t="shared" si="31"/>
-        <v>-0.15000000000000002</v>
-      </c>
-      <c r="P35" s="9"/>
+        <f t="shared" si="81"/>
+        <v>-0.34545454545454546</v>
+      </c>
+      <c r="O35" s="9">
+        <f t="shared" si="78"/>
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="P35" s="9">
+        <f t="shared" si="78"/>
+        <v>-9.8591549295774517E-2</v>
+      </c>
       <c r="Q35" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="78"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="R35" s="9">
+        <f t="shared" si="78"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9">
+        <f t="shared" si="82"/>
         <v>6.708268330733258E-2</v>
       </c>
-      <c r="R35" s="9">
-        <f t="shared" si="32"/>
+      <c r="V35" s="9">
+        <f t="shared" si="82"/>
         <v>0.10233918128654973</v>
       </c>
-      <c r="S35" s="9">
-        <f t="shared" si="32"/>
+      <c r="W35" s="9">
+        <f t="shared" si="82"/>
         <v>9.2838196286472163E-2</v>
       </c>
-      <c r="T35" s="9">
-        <f t="shared" si="32"/>
-        <v>-0.32008495145631077</v>
-      </c>
-      <c r="U35" s="9">
-        <f t="shared" ref="U35:AE35" si="35">U6/T6-1</f>
+      <c r="X35" s="9">
+        <f t="shared" si="82"/>
+        <v>-0.35922330097087385</v>
+      </c>
+      <c r="Y35" s="9">
+        <f t="shared" ref="Y35:AI35" si="85">Y6/X6-1</f>
+        <v>0.63901515151515142</v>
+      </c>
+      <c r="Z35" s="9">
+        <f t="shared" si="85"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="V35" s="9">
-        <f t="shared" si="35"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="W35" s="9">
-        <f t="shared" si="35"/>
+      <c r="AA35" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="X35" s="9">
-        <f t="shared" si="35"/>
+      <c r="AB35" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="Y35" s="9">
-        <f t="shared" si="35"/>
+      <c r="AC35" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="Z35" s="9">
-        <f t="shared" si="35"/>
+      <c r="AD35" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AA35" s="9">
-        <f t="shared" si="35"/>
+      <c r="AE35" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AB35" s="9">
-        <f t="shared" si="35"/>
+      <c r="AF35" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC35" s="9">
-        <f t="shared" si="35"/>
+      <c r="AG35" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AD35" s="9">
-        <f t="shared" si="35"/>
+      <c r="AH35" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AE35" s="9">
-        <f t="shared" si="35"/>
+      <c r="AI35" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AH35" t="s">
+      <c r="AL35" t="s">
         <v>67</v>
       </c>
-      <c r="AI35" s="4">
-        <f>NPV(AI34,T28:EK28)</f>
-        <v>57.968666855227795</v>
-      </c>
-    </row>
-    <row r="36" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
+      <c r="AM35" s="4">
+        <f>NPV(AM34,Y28:EO28)</f>
+        <v>3446.5738933377929</v>
+      </c>
+    </row>
+    <row r="36" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J36" s="9">
-        <f t="shared" si="28"/>
+      <c r="J36" s="10">
+        <f t="shared" si="77"/>
         <v>-0.22832432432432415</v>
       </c>
-      <c r="K36" s="9">
-        <f t="shared" si="28"/>
+      <c r="K36" s="10">
+        <f t="shared" si="77"/>
         <v>-0.14534883720930225</v>
       </c>
-      <c r="L36" s="9">
-        <f t="shared" si="28"/>
+      <c r="L36" s="10">
+        <f t="shared" si="77"/>
         <v>0.11528239202657797</v>
       </c>
-      <c r="M36" s="9">
-        <f t="shared" si="31"/>
+      <c r="M36" s="10">
+        <f t="shared" si="81"/>
         <v>-0.17416291854072952</v>
       </c>
-      <c r="N36" s="9">
-        <f t="shared" si="31"/>
-        <v>3.1297282151863115E-3</v>
-      </c>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9">
-        <f t="shared" si="32"/>
+      <c r="N36" s="10">
+        <f t="shared" si="81"/>
+        <v>0.60381059120201708</v>
+      </c>
+      <c r="O36" s="10">
+        <f t="shared" si="78"/>
+        <v>0.38647959183673475</v>
+      </c>
+      <c r="P36" s="10">
+        <f t="shared" si="78"/>
+        <v>0.19511468573130775</v>
+      </c>
+      <c r="Q36" s="10">
+        <f t="shared" si="78"/>
+        <v>0.25773373676248057</v>
+      </c>
+      <c r="R36" s="10">
+        <f t="shared" si="78"/>
+        <v>6.3218029350104787E-2</v>
+      </c>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10">
+        <f t="shared" si="82"/>
         <v>0.2241249055653487</v>
       </c>
-      <c r="R36" s="9">
-        <f t="shared" si="32"/>
+      <c r="V36" s="10">
+        <f t="shared" si="82"/>
         <v>0.23349105122402825</v>
       </c>
-      <c r="S36" s="9">
-        <f t="shared" si="32"/>
+      <c r="W36" s="10">
+        <f t="shared" si="82"/>
         <v>0.1118245496997996</v>
       </c>
-      <c r="T36" s="9">
-        <f t="shared" si="32"/>
-        <v>-5.5413635340883394E-2</v>
-      </c>
-      <c r="U36" s="9">
-        <f t="shared" ref="U36:AE36" si="36">U7/T7-1</f>
-        <v>8.2170305784343034E-2</v>
-      </c>
-      <c r="V36" s="9">
-        <f t="shared" si="36"/>
-        <v>9.1378913878932266E-2</v>
-      </c>
-      <c r="W36" s="9">
-        <f t="shared" si="36"/>
-        <v>0.10611179654105496</v>
-      </c>
-      <c r="X36" s="9">
-        <f t="shared" si="36"/>
-        <v>9.4606686315153787E-2</v>
-      </c>
-      <c r="Y36" s="9">
-        <f t="shared" si="36"/>
-        <v>8.2559202600571036E-2</v>
-      </c>
-      <c r="Z36" s="9">
-        <f t="shared" si="36"/>
-        <v>6.2511330240356378E-2</v>
-      </c>
-      <c r="AA36" s="9">
-        <f t="shared" si="36"/>
-        <v>4.2234167995673033E-2</v>
-      </c>
-      <c r="AB36" s="9">
-        <f t="shared" si="36"/>
-        <v>3.4342206994318003E-2</v>
-      </c>
-      <c r="AC36" s="9">
-        <f t="shared" si="36"/>
-        <v>2.7943449508512685E-2</v>
-      </c>
-      <c r="AD36" s="9">
-        <f t="shared" si="36"/>
-        <v>2.7987600064759421E-2</v>
-      </c>
-      <c r="AE36" s="9">
-        <f t="shared" si="36"/>
-        <v>2.8032100311283559E-2</v>
-      </c>
-      <c r="AH36" t="s">
+      <c r="X36" s="10">
+        <f t="shared" si="82"/>
+        <v>0.10537763444086101</v>
+      </c>
+      <c r="Y36" s="10">
+        <f t="shared" ref="Y36:AI36" si="86">Y7/X7-1</f>
+        <v>0.18846994164744224</v>
+      </c>
+      <c r="Z36" s="10">
+        <f t="shared" si="86"/>
+        <v>0.14702617713167676</v>
+      </c>
+      <c r="AA36" s="10">
+        <f t="shared" si="86"/>
+        <v>0.10276981376473726</v>
+      </c>
+      <c r="AB36" s="10">
+        <f t="shared" si="86"/>
+        <v>9.5530148468961018E-2</v>
+      </c>
+      <c r="AC36" s="10">
+        <f t="shared" si="86"/>
+        <v>8.8037528291093903E-2</v>
+      </c>
+      <c r="AD36" s="10">
+        <f t="shared" si="86"/>
+        <v>6.9467233734611389E-2</v>
+      </c>
+      <c r="AE36" s="10">
+        <f t="shared" si="86"/>
+        <v>4.6080285563213419E-2</v>
+      </c>
+      <c r="AF36" s="10">
+        <f t="shared" si="86"/>
+        <v>3.7560453854360576E-2</v>
+      </c>
+      <c r="AG36" s="10">
+        <f t="shared" si="86"/>
+        <v>2.8995837446806227E-2</v>
+      </c>
+      <c r="AH36" s="10">
+        <f t="shared" si="86"/>
+        <v>2.9031087313679649E-2</v>
+      </c>
+      <c r="AI36" s="10">
+        <f t="shared" si="86"/>
+        <v>2.906660132548633E-2</v>
+      </c>
+      <c r="AL36" t="s">
         <v>68</v>
       </c>
-      <c r="AI36" s="4">
+      <c r="AM36" s="4">
         <f>Main!D8</f>
-        <v>-989.69999999999993</v>
-      </c>
-    </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.3">
+        <v>-771.2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>56</v>
       </c>
       <c r="F37" s="9">
-        <f t="shared" ref="F37:M40" si="37">(F3-F8)/F3</f>
+        <f t="shared" ref="F37:L40" si="87">(F3-F8)/F3</f>
         <v>0.38145474736257629</v>
       </c>
       <c r="G37" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.33092410944759937</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.32370749883558453</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.40065573770491797</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.3411000763941941</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.24511082138200788</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.28722934158197083</v>
       </c>
       <c r="M37" s="9">
@@ -4556,446 +5140,510 @@
       </c>
       <c r="N37" s="9">
         <f>(N3-N8)/N3</f>
-        <v>0.39</v>
+        <v>0.46215815136739452</v>
+      </c>
+      <c r="O37" s="9">
+        <f t="shared" ref="O37:R37" si="88">(O3-O8)/O3</f>
+        <v>0.34119867862199155</v>
       </c>
       <c r="P37" s="9">
-        <f>(P3-P8)/P3</f>
+        <f t="shared" si="88"/>
+        <v>0.3300741739716791</v>
+      </c>
+      <c r="Q37" s="9">
+        <f t="shared" si="88"/>
+        <v>0.35</v>
+      </c>
+      <c r="R37" s="9">
+        <f t="shared" si="88"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="T37" s="9">
+        <f>(T3-T8)/T3</f>
         <v>0.35846509834168921</v>
       </c>
-      <c r="Q37" s="9">
-        <f>(Q3-Q8)/Q3</f>
+      <c r="U37" s="9">
+        <f>(U3-U8)/U3</f>
         <v>0.28907309721175584</v>
       </c>
-      <c r="R37" s="9">
-        <f t="shared" ref="R37:T37" si="38">(R3-R8)/R3</f>
+      <c r="V37" s="9">
+        <f t="shared" ref="V37:X37" si="89">(V3-V8)/V3</f>
         <v>0.30032928352446914</v>
       </c>
-      <c r="S37" s="9">
-        <f t="shared" si="38"/>
+      <c r="W37" s="9">
+        <f t="shared" si="89"/>
         <v>0.35387612797374912</v>
       </c>
-      <c r="T37" s="9">
-        <f t="shared" si="38"/>
-        <v>0.32277159856647458</v>
-      </c>
-      <c r="U37" s="9">
-        <f t="shared" ref="U37:AE37" si="39">(U3-U8)/U3</f>
-        <v>0.32999999999999996</v>
-      </c>
-      <c r="V37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.32999999999999996</v>
-      </c>
-      <c r="W37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.3299999999999999</v>
-      </c>
       <c r="X37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.32999999999999996</v>
+        <f t="shared" si="89"/>
+        <v>0.36795060818282338</v>
       </c>
       <c r="Y37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.32999999999999996</v>
+        <f t="shared" ref="Y37:AI37" si="90">(Y3-Y8)/Y3</f>
+        <v>0.38192834885010235</v>
       </c>
       <c r="Z37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.32999999999999996</v>
+        <f t="shared" si="90"/>
+        <v>0.4</v>
       </c>
       <c r="AA37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.3299999999999999</v>
+        <f t="shared" si="90"/>
+        <v>0.4</v>
       </c>
       <c r="AB37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.32999999999999996</v>
+        <f t="shared" si="90"/>
+        <v>0.40000000000000008</v>
       </c>
       <c r="AC37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.32999999999999996</v>
+        <f t="shared" si="90"/>
+        <v>0.39999999999999997</v>
       </c>
       <c r="AD37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.3299999999999999</v>
+        <f t="shared" si="90"/>
+        <v>0.4</v>
       </c>
       <c r="AE37" s="9">
-        <f t="shared" si="39"/>
-        <v>0.32999999999999996</v>
-      </c>
-      <c r="AH37" t="s">
+        <f t="shared" si="90"/>
+        <v>0.4</v>
+      </c>
+      <c r="AF37" s="9">
+        <f t="shared" si="90"/>
+        <v>0.4</v>
+      </c>
+      <c r="AG37" s="9">
+        <f t="shared" si="90"/>
+        <v>0.4</v>
+      </c>
+      <c r="AH37" s="9">
+        <f t="shared" si="90"/>
+        <v>0.4</v>
+      </c>
+      <c r="AI37" s="9">
+        <f t="shared" si="90"/>
+        <v>0.4</v>
+      </c>
+      <c r="AL37" t="s">
         <v>69</v>
       </c>
-      <c r="AI37" s="4">
-        <f>AI35+AI36</f>
-        <v>-931.73133314477218</v>
-      </c>
-    </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AM37" s="4">
+        <f>AM35+AM36</f>
+        <v>2675.3738933377927</v>
+      </c>
+    </row>
+    <row r="38" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>57</v>
       </c>
       <c r="F38" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-7.175925925925912E-2</v>
       </c>
       <c r="G38" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-0.22439024390243908</v>
       </c>
       <c r="H38" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-0.11157024793388427</v>
       </c>
       <c r="I38" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-0.18264840182648404</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-7.3076923076923025E-2</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-0.35087719298245612</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-3.747072599531602E-2</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" ref="M38:N40" si="40">(M4-M9)/M4</f>
+        <f t="shared" ref="M38:N40" si="91">(M4-M9)/M4</f>
         <v>-0.11214953271028041</v>
       </c>
       <c r="N38" s="9">
-        <f t="shared" si="40"/>
-        <v>9.9999999999999964E-2</v>
+        <f t="shared" si="91"/>
+        <v>5.5401662049861494E-2</v>
+      </c>
+      <c r="O38" s="9">
+        <f t="shared" ref="O38:R38" si="92">(O4-O9)/O4</f>
+        <v>1.1869436201780582E-2</v>
       </c>
       <c r="P38" s="9">
-        <f t="shared" ref="P38" si="41">(P4-P9)/P4</f>
+        <f t="shared" si="92"/>
+        <v>-2.1390374331550915E-2</v>
+      </c>
+      <c r="Q38" s="9">
+        <f t="shared" si="92"/>
+        <v>0.08</v>
+      </c>
+      <c r="R38" s="9">
+        <f t="shared" si="92"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="T38" s="9">
+        <f t="shared" ref="T38" si="93">(T4-T9)/T4</f>
         <v>-0.1432777232580961</v>
       </c>
-      <c r="Q38" s="9">
-        <f t="shared" ref="Q38:T40" si="42">(Q4-Q9)/Q4</f>
+      <c r="U38" s="9">
+        <f t="shared" ref="U38:X40" si="94">(U4-U9)/U4</f>
         <v>-0.14672216441207087</v>
       </c>
-      <c r="R38" s="9">
-        <f t="shared" si="42"/>
+      <c r="V38" s="9">
+        <f t="shared" si="94"/>
         <v>-0.13029315960912052</v>
       </c>
-      <c r="S38" s="9">
-        <f t="shared" si="42"/>
+      <c r="W38" s="9">
+        <f t="shared" si="94"/>
         <v>-0.14254859611231122</v>
       </c>
-      <c r="T38" s="9">
-        <f t="shared" si="42"/>
-        <v>-4.2332268370607003E-2</v>
-      </c>
-      <c r="U38" s="9">
-        <f t="shared" ref="U38:AE38" si="43">(U4-U9)/U4</f>
-        <v>2.0000000000000035E-2</v>
-      </c>
-      <c r="V38" s="9">
-        <f t="shared" si="43"/>
-        <v>0.04</v>
-      </c>
-      <c r="W38" s="9">
-        <f t="shared" si="43"/>
-        <v>0.05</v>
-      </c>
       <c r="X38" s="9">
-        <f t="shared" si="43"/>
-        <v>5.0000000000000079E-2</v>
+        <f t="shared" si="94"/>
+        <v>-5.8871627146361308E-2</v>
       </c>
       <c r="Y38" s="9">
-        <f t="shared" si="43"/>
-        <v>5.0000000000000072E-2</v>
+        <f t="shared" ref="Y38:AI38" si="95">(Y4-Y9)/Y4</f>
+        <v>4.7964403335435488E-2</v>
       </c>
       <c r="Z38" s="9">
-        <f t="shared" si="43"/>
-        <v>5.0000000000000072E-2</v>
+        <f t="shared" si="95"/>
+        <v>9.0000000000000052E-2</v>
       </c>
       <c r="AA38" s="9">
-        <f t="shared" si="43"/>
-        <v>5.0000000000000051E-2</v>
+        <f t="shared" si="95"/>
+        <v>0.09</v>
       </c>
       <c r="AB38" s="9">
-        <f t="shared" si="43"/>
-        <v>4.9999999999999975E-2</v>
+        <f t="shared" si="95"/>
+        <v>8.9999999999999927E-2</v>
       </c>
       <c r="AC38" s="9">
-        <f t="shared" si="43"/>
-        <v>5.0000000000000017E-2</v>
+        <f t="shared" si="95"/>
+        <v>0.09</v>
       </c>
       <c r="AD38" s="9">
-        <f t="shared" si="43"/>
-        <v>5.0000000000000031E-2</v>
+        <f t="shared" si="95"/>
+        <v>8.9999999999999927E-2</v>
       </c>
       <c r="AE38" s="9">
-        <f t="shared" si="43"/>
-        <v>4.9999999999999982E-2</v>
-      </c>
-      <c r="AH38" t="s">
+        <f t="shared" si="95"/>
+        <v>8.9999999999999955E-2</v>
+      </c>
+      <c r="AF38" s="9">
+        <f t="shared" si="95"/>
+        <v>0.09</v>
+      </c>
+      <c r="AG38" s="9">
+        <f t="shared" si="95"/>
+        <v>8.9999999999999955E-2</v>
+      </c>
+      <c r="AH38" s="9">
+        <f t="shared" si="95"/>
+        <v>8.9999999999999955E-2</v>
+      </c>
+      <c r="AI38" s="9">
+        <f t="shared" si="95"/>
+        <v>8.9999999999999886E-2</v>
+      </c>
+      <c r="AL38" t="s">
         <v>70</v>
       </c>
-      <c r="AI38" s="7">
-        <f>AI37/AE29</f>
-        <v>-4.0758151056201761</v>
-      </c>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AM38" s="7">
+        <f>AM37/AI29</f>
+        <v>11.433221766400823</v>
+      </c>
+    </row>
+    <row r="39" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>58</v>
       </c>
       <c r="F39" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-9.7744360902255606E-2</v>
       </c>
       <c r="G39" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-0.25798525798525795</v>
       </c>
       <c r="H39" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-0.3546099290780142</v>
       </c>
       <c r="I39" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-0.20842105263157892</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-4.7528517110266157E-2</v>
       </c>
       <c r="K39" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-1.7730496453900962E-3</v>
       </c>
       <c r="L39" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>1.9047619047619319E-3</v>
       </c>
       <c r="M39" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="91"/>
         <v>-1.1811023622047273E-2</v>
       </c>
       <c r="N39" s="9">
-        <f t="shared" si="40"/>
-        <v>0</v>
+        <f t="shared" si="91"/>
+        <v>-1.6728624535316091E-2</v>
+      </c>
+      <c r="O39" s="9">
+        <f t="shared" ref="O39:R39" si="96">(O5-O10)/O5</f>
+        <v>1.1214953271028064E-2</v>
       </c>
       <c r="P39" s="9">
-        <f t="shared" ref="P39" si="44">(P5-P10)/P5</f>
+        <f t="shared" si="96"/>
+        <v>9.1911764705882359E-2</v>
+      </c>
+      <c r="Q39" s="9">
+        <f t="shared" si="96"/>
+        <v>5.0000000000000037E-2</v>
+      </c>
+      <c r="R39" s="9">
+        <f t="shared" si="96"/>
+        <v>3.0000000000000082E-2</v>
+      </c>
+      <c r="T39" s="9">
+        <f t="shared" ref="T39" si="97">(T5-T10)/T5</f>
         <v>-0.20711678832116806</v>
       </c>
-      <c r="Q39" s="9">
-        <f t="shared" si="42"/>
+      <c r="U39" s="9">
+        <f t="shared" si="94"/>
         <v>-2.8432732316227623E-2</v>
       </c>
-      <c r="R39" s="9">
-        <f t="shared" si="42"/>
+      <c r="V39" s="9">
+        <f t="shared" si="94"/>
         <v>-0.11589403973509933</v>
       </c>
-      <c r="S39" s="9">
-        <f t="shared" si="42"/>
+      <c r="W39" s="9">
+        <f t="shared" si="94"/>
         <v>-0.20699071545603498</v>
       </c>
-      <c r="T39" s="9">
-        <f t="shared" si="42"/>
-        <v>-2.7780092785510955E-3</v>
-      </c>
-      <c r="U39" s="9">
-        <f t="shared" ref="U39:AE39" si="45">(U5-U10)/U5</f>
-        <v>7.9999999999999974E-2</v>
-      </c>
-      <c r="V39" s="9">
-        <f t="shared" si="45"/>
-        <v>0.12999999999999998</v>
-      </c>
-      <c r="W39" s="9">
-        <f t="shared" si="45"/>
-        <v>0.16000000000000006</v>
-      </c>
       <c r="X39" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="94"/>
+        <v>-7.0257611241217799E-3</v>
+      </c>
+      <c r="Y39" s="9">
+        <f t="shared" ref="Y39:AI39" si="98">(Y5-Y10)/Y5</f>
+        <v>4.5840851476290086E-2</v>
+      </c>
+      <c r="Z39" s="9">
+        <f t="shared" si="98"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="AA39" s="9">
+        <f t="shared" si="98"/>
+        <v>0.15</v>
+      </c>
+      <c r="AB39" s="9">
+        <f t="shared" si="98"/>
         <v>0.17000000000000004</v>
       </c>
-      <c r="Y39" s="9">
-        <f t="shared" si="45"/>
-        <v>0.16999999999999998</v>
-      </c>
-      <c r="Z39" s="9">
-        <f t="shared" si="45"/>
+      <c r="AC39" s="9">
+        <f t="shared" si="98"/>
+        <v>0.1700000000000001</v>
+      </c>
+      <c r="AD39" s="9">
+        <f t="shared" si="98"/>
         <v>0.17</v>
       </c>
-      <c r="AA39" s="9">
-        <f t="shared" si="45"/>
-        <v>0.16999999999999998</v>
-      </c>
-      <c r="AB39" s="9">
-        <f t="shared" si="45"/>
-        <v>0.16999999999999998</v>
-      </c>
-      <c r="AC39" s="9">
-        <f t="shared" si="45"/>
+      <c r="AE39" s="9">
+        <f t="shared" si="98"/>
+        <v>0.17000000000000007</v>
+      </c>
+      <c r="AF39" s="9">
+        <f t="shared" si="98"/>
+        <v>0.17000000000000007</v>
+      </c>
+      <c r="AG39" s="9">
+        <f t="shared" si="98"/>
+        <v>0.17</v>
+      </c>
+      <c r="AH39" s="9">
+        <f t="shared" si="98"/>
+        <v>0.17000000000000004</v>
+      </c>
+      <c r="AI39" s="9">
+        <f t="shared" si="98"/>
         <v>0.1700000000000001</v>
       </c>
-      <c r="AD39" s="9">
-        <f t="shared" si="45"/>
-        <v>0.17000000000000004</v>
-      </c>
-      <c r="AE39" s="9">
-        <f t="shared" si="45"/>
-        <v>0.16999999999999996</v>
-      </c>
-      <c r="AH39" t="s">
+      <c r="AL39" t="s">
         <v>71</v>
       </c>
-      <c r="AI39" s="7">
+      <c r="AM39" s="7">
         <f>Main!D3</f>
-        <v>24.61</v>
-      </c>
-    </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.3">
+        <v>70.709999999999994</v>
+      </c>
+    </row>
+    <row r="40" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>59</v>
       </c>
       <c r="F40" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-3.072916666666667</v>
       </c>
       <c r="G40" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.26108374384236455</v>
       </c>
       <c r="H40" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.21717171717171721</v>
       </c>
       <c r="I40" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>-4.4031007751937983</v>
       </c>
       <c r="J40" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.44848484848484849</v>
       </c>
       <c r="K40" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.31428571428571433</v>
       </c>
       <c r="L40" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="87"/>
         <v>0.35211267605633806</v>
       </c>
       <c r="M40" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="91"/>
         <v>0.31159420289855078</v>
       </c>
       <c r="N40" s="9">
-        <f t="shared" si="40"/>
-        <v>0.37999999999999995</v>
+        <f t="shared" si="91"/>
+        <v>1.8518518518518615E-2</v>
+      </c>
+      <c r="O40" s="9">
+        <f t="shared" ref="O40:R40" si="99">(O6-O11)/O6</f>
+        <v>0.57037037037037042</v>
       </c>
       <c r="P40" s="9">
-        <f t="shared" ref="P40" si="46">(P6-P11)/P6</f>
+        <f t="shared" si="99"/>
+        <v>0.3984375</v>
+      </c>
+      <c r="Q40" s="9">
+        <f t="shared" si="99"/>
+        <v>0.50419527078565973</v>
+      </c>
+      <c r="R40" s="9">
+        <f t="shared" si="99"/>
+        <v>0.31773879142300193</v>
+      </c>
+      <c r="T40" s="9">
+        <f t="shared" ref="T40" si="100">(T6-T11)/T6</f>
         <v>0.26833073322932915</v>
       </c>
-      <c r="Q40" s="9">
-        <f t="shared" si="42"/>
+      <c r="U40" s="9">
+        <f t="shared" si="94"/>
         <v>0.35087719298245623</v>
       </c>
-      <c r="R40" s="9">
-        <f t="shared" si="42"/>
+      <c r="V40" s="9">
+        <f t="shared" si="94"/>
         <v>-1.1498673740053047</v>
       </c>
-      <c r="S40" s="9">
-        <f t="shared" si="42"/>
+      <c r="W40" s="9">
+        <f t="shared" si="94"/>
         <v>-1.1723300970873785</v>
       </c>
-      <c r="T40" s="9">
-        <f t="shared" si="42"/>
-        <v>0.33966086568496207</v>
-      </c>
-      <c r="U40" s="9">
-        <f t="shared" ref="U40:AE40" si="47">(U6-U11)/U6</f>
-        <v>0.34</v>
-      </c>
-      <c r="V40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="W40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.33999999999999997</v>
-      </c>
       <c r="X40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.33999999999999991</v>
+        <f t="shared" si="94"/>
+        <v>0.26325757575757575</v>
       </c>
       <c r="Y40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.33999999999999997</v>
+        <f t="shared" ref="Y40:AI40" si="101">(Y6-Y11)/Y6</f>
+        <v>0.46498728911486015</v>
       </c>
       <c r="Z40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.34</v>
+        <f t="shared" si="101"/>
+        <v>0.43999999999999995</v>
       </c>
       <c r="AA40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.33999999999999991</v>
+        <f t="shared" si="101"/>
+        <v>0.43999999999999995</v>
       </c>
       <c r="AB40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.33999999999999997</v>
+        <f t="shared" si="101"/>
+        <v>0.43999999999999989</v>
       </c>
       <c r="AC40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.33999999999999997</v>
+        <f t="shared" si="101"/>
+        <v>0.43999999999999995</v>
       </c>
       <c r="AD40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.33999999999999991</v>
+        <f t="shared" si="101"/>
+        <v>0.44</v>
       </c>
       <c r="AE40" s="9">
-        <f t="shared" si="47"/>
-        <v>0.34</v>
-      </c>
-      <c r="AH40" s="1" t="s">
+        <f t="shared" si="101"/>
+        <v>0.44</v>
+      </c>
+      <c r="AF40" s="9">
+        <f t="shared" si="101"/>
+        <v>0.43999999999999989</v>
+      </c>
+      <c r="AG40" s="9">
+        <f t="shared" si="101"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="AH40" s="9">
+        <f t="shared" si="101"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="AI40" s="9">
+        <f t="shared" si="101"/>
+        <v>0.44</v>
+      </c>
+      <c r="AL40" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AI40" s="10">
-        <f>AI38/AI39-1</f>
-        <v>-1.1656162172133351</v>
-      </c>
-    </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AM40" s="10">
+        <f>AM38/AM39-1</f>
+        <v>-0.83830827653230344</v>
+      </c>
+    </row>
+    <row r="41" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>50</v>
       </c>
       <c r="F41" s="9">
-        <f t="shared" ref="F41:M41" si="48">F13/F7</f>
+        <f t="shared" ref="F41:L41" si="102">F13/F7</f>
         <v>0.15437837837837823</v>
       </c>
       <c r="G41" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="102"/>
         <v>0.19731104651162795</v>
       </c>
       <c r="H41" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="102"/>
         <v>0.18637873754152831</v>
       </c>
       <c r="I41" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="102"/>
         <v>-1.3243378310844607E-2</v>
       </c>
       <c r="J41" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="102"/>
         <v>0.25861585878397308</v>
       </c>
       <c r="K41" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="102"/>
         <v>0.16113945578231306</v>
       </c>
       <c r="L41" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="102"/>
         <v>0.20405123622281801</v>
       </c>
       <c r="M41" s="9">
@@ -5004,80 +5652,96 @@
       </c>
       <c r="N41" s="9">
         <f>N13/N7</f>
-        <v>0.29670769823779314</v>
+        <v>0.38312368972746325</v>
+      </c>
+      <c r="O41" s="9">
+        <f t="shared" ref="O41:R41" si="103">O13/O7</f>
+        <v>0.27200245323520406</v>
       </c>
       <c r="P41" s="9">
-        <f>P13/P7</f>
+        <f t="shared" si="103"/>
+        <v>0.26719840478564322</v>
+      </c>
+      <c r="Q41" s="9">
+        <f t="shared" si="103"/>
+        <v>0.30043759517514618</v>
+      </c>
+      <c r="R41" s="9">
+        <f t="shared" si="103"/>
+        <v>0.38711559253745564</v>
+      </c>
+      <c r="T41" s="9">
+        <f>T13/T7</f>
         <v>0.2087635356333418</v>
       </c>
-      <c r="Q41" s="9">
-        <f>Q13/Q7</f>
+      <c r="U41" s="9">
+        <f>U13/U7</f>
         <v>0.20325036000822869</v>
       </c>
-      <c r="R41" s="9">
-        <f t="shared" ref="R41:T41" si="49">R13/R7</f>
+      <c r="V41" s="9">
+        <f t="shared" ref="V41:X41" si="104">V13/V7</f>
         <v>0.12366577718478998</v>
       </c>
-      <c r="S41" s="9">
-        <f t="shared" si="49"/>
+      <c r="W41" s="9">
+        <f t="shared" si="104"/>
         <v>0.14805370134253365</v>
       </c>
-      <c r="T41" s="9">
-        <f t="shared" si="49"/>
-        <v>0.23139786107381441</v>
-      </c>
-      <c r="U41" s="9">
-        <f t="shared" ref="U41:AE41" si="50">U13/U7</f>
-        <v>0.24666133735877813</v>
-      </c>
-      <c r="V41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.25269524131934273</v>
-      </c>
-      <c r="W41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.25717411170625731</v>
-      </c>
       <c r="X41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.25812434666700945</v>
+        <f t="shared" si="104"/>
+        <v>0.27446057809743507</v>
       </c>
       <c r="Y41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.25951730005071066</v>
+        <f t="shared" ref="Y41:AI41" si="105">Y13/Y7</f>
+        <v>0.3176466158588282</v>
       </c>
       <c r="Z41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.26149467173437257</v>
+        <f t="shared" si="105"/>
+        <v>0.33929521786246652</v>
       </c>
       <c r="AA41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.26254256039011653</v>
+        <f t="shared" si="105"/>
+        <v>0.3435168464169096</v>
       </c>
       <c r="AB41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.26349175888049453</v>
+        <f t="shared" si="105"/>
+        <v>0.34555486527276447</v>
       </c>
       <c r="AC41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.2640198316461117</v>
+        <f t="shared" si="105"/>
+        <v>0.34704888430014075</v>
       </c>
       <c r="AD41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.2645469381256732</v>
+        <f t="shared" si="105"/>
+        <v>0.34867372071529767</v>
       </c>
       <c r="AE41" s="9">
-        <f t="shared" si="50"/>
-        <v>0.26507306855028129</v>
-      </c>
-      <c r="AH41" t="s">
+        <f t="shared" si="105"/>
+        <v>0.34941880935900421</v>
+      </c>
+      <c r="AF41" s="9">
+        <f t="shared" si="105"/>
+        <v>0.35003316908361443</v>
+      </c>
+      <c r="AG41" s="9">
+        <f t="shared" si="105"/>
+        <v>0.35052293865962769</v>
+      </c>
+      <c r="AH41" s="9">
+        <f t="shared" si="105"/>
+        <v>0.35101118536219345</v>
+      </c>
+      <c r="AI41" s="9">
+        <f t="shared" si="105"/>
+        <v>0.35149792177817984</v>
+      </c>
+      <c r="AL41" t="s">
         <v>73</v>
       </c>
-      <c r="AI41" s="5" t="s">
+      <c r="AM41" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>60</v>
       </c>
@@ -5086,15 +5750,15 @@
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
       <c r="J42" s="9">
-        <f t="shared" ref="J42:L42" si="51">J14/F14-1</f>
+        <f t="shared" ref="J42:L42" si="106">J14/F14-1</f>
         <v>-0.12271540469973885</v>
       </c>
       <c r="K42" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="106"/>
         <v>-0.22319474835886222</v>
       </c>
       <c r="L42" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="106"/>
         <v>-9.8795180722891618E-2</v>
       </c>
       <c r="M42" s="9">
@@ -5103,100 +5767,116 @@
       </c>
       <c r="N42" s="9">
         <f>N14/J14-1</f>
+        <v>0.17559523809523814</v>
+      </c>
+      <c r="O42" s="9">
+        <f t="shared" ref="O42:R42" si="107">O14/K14-1</f>
+        <v>0.14366197183098595</v>
+      </c>
+      <c r="P42" s="9">
+        <f t="shared" si="107"/>
+        <v>9.0909090909090828E-2</v>
+      </c>
+      <c r="Q42" s="9">
+        <f t="shared" si="107"/>
+        <v>0.1570247933884299</v>
+      </c>
+      <c r="R42" s="9">
+        <f t="shared" si="107"/>
+        <v>0.139240506329114</v>
+      </c>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9">
+        <f>U14/T14-1</f>
+        <v>0.23684210526315796</v>
+      </c>
+      <c r="V42" s="9">
+        <f t="shared" ref="V42:X42" si="108">V14/U14-1</f>
+        <v>0.45647969052224369</v>
+      </c>
+      <c r="W42" s="9">
+        <f t="shared" si="108"/>
+        <v>3.5192563081009265E-2</v>
+      </c>
+      <c r="X42" s="9">
+        <f t="shared" si="108"/>
+        <v>-4.6183450930083469E-2</v>
+      </c>
+      <c r="Y42" s="9">
+        <f t="shared" ref="Y42:AI42" si="109">Y14/X14-1</f>
+        <v>0.13248150638870215</v>
+      </c>
+      <c r="Z42" s="9">
+        <f t="shared" si="109"/>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="AA42" s="9">
+        <f t="shared" si="109"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AB42" s="9">
+        <f t="shared" si="109"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9">
-        <f>Q14/P14-1</f>
-        <v>0.23684210526315796</v>
-      </c>
-      <c r="R42" s="9">
-        <f t="shared" ref="R42:T42" si="52">R14/Q14-1</f>
-        <v>0.45647969052224369</v>
-      </c>
-      <c r="S42" s="9">
-        <f t="shared" si="52"/>
-        <v>3.5192563081009265E-2</v>
-      </c>
-      <c r="T42" s="9">
-        <f t="shared" si="52"/>
-        <v>-7.7562540089801235E-2</v>
-      </c>
-      <c r="U42" s="9">
-        <f t="shared" ref="U42:AE42" si="53">U14/T14-1</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="V42" s="9">
-        <f t="shared" si="53"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="W42" s="9">
-        <f t="shared" si="53"/>
+      <c r="AC42" s="9">
+        <f t="shared" si="109"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="X42" s="9">
-        <f t="shared" si="53"/>
+      <c r="AD42" s="9">
+        <f t="shared" si="109"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="Y42" s="9">
-        <f t="shared" si="53"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="Z42" s="9">
-        <f t="shared" si="53"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AA42" s="9">
-        <f t="shared" si="53"/>
+      <c r="AE42" s="9">
+        <f t="shared" si="109"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB42" s="9">
-        <f t="shared" si="53"/>
+      <c r="AF42" s="9">
+        <f t="shared" si="109"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC42" s="9">
-        <f t="shared" si="53"/>
+      <c r="AG42" s="9">
+        <f t="shared" si="109"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD42" s="9">
-        <f t="shared" si="53"/>
+      <c r="AH42" s="9">
+        <f t="shared" si="109"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE42" s="9">
-        <f t="shared" si="53"/>
+      <c r="AI42" s="9">
+        <f t="shared" si="109"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>61</v>
       </c>
       <c r="F43" s="9">
-        <f t="shared" ref="F43:M43" si="54">F15/F7</f>
+        <f t="shared" ref="F43:L43" si="110">F15/F7</f>
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="G43" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="110"/>
         <v>9.8473837209302334E-2</v>
       </c>
       <c r="H43" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="110"/>
         <v>8.9036544850498348E-2</v>
       </c>
       <c r="I43" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="110"/>
         <v>4.9975012493753128E-2</v>
       </c>
       <c r="J43" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="110"/>
         <v>4.4830484729616135E-2</v>
       </c>
       <c r="K43" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="110"/>
         <v>5.7823129251700675E-2</v>
       </c>
       <c r="L43" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="110"/>
         <v>5.3321417932677986E-2</v>
       </c>
       <c r="M43" s="9">
@@ -5205,74 +5885,90 @@
       </c>
       <c r="N43" s="9">
         <f>N15/N7</f>
+        <v>3.8085255066387144E-2</v>
+      </c>
+      <c r="O43" s="9">
+        <f t="shared" ref="O43:R43" si="111">O15/O7</f>
+        <v>6.8383931309414281E-2</v>
+      </c>
+      <c r="P43" s="9">
+        <f t="shared" si="111"/>
+        <v>6.0069790628115662E-2</v>
+      </c>
+      <c r="Q43" s="9">
+        <f t="shared" si="111"/>
+        <v>5.5330890755170441E-2</v>
+      </c>
+      <c r="R43" s="9">
+        <f t="shared" si="111"/>
+        <v>3.9435675483826441E-2</v>
+      </c>
+      <c r="T43" s="9">
+        <f>T15/T7</f>
+        <v>7.0385293376983127E-2</v>
+      </c>
+      <c r="U43" s="9">
+        <f>U15/U7</f>
+        <v>8.8973462250565738E-2</v>
+      </c>
+      <c r="V43" s="9">
+        <f t="shared" ref="V43:X43" si="112">V15/V7</f>
+        <v>7.5800533689126065E-2</v>
+      </c>
+      <c r="W43" s="9">
+        <f t="shared" si="112"/>
+        <v>6.7426685667141689E-2</v>
+      </c>
+      <c r="X43" s="9">
+        <f t="shared" si="112"/>
+        <v>4.6139231917492196E-2</v>
+      </c>
+      <c r="Y43" s="9">
+        <f t="shared" ref="Y43:AI43" si="113">Y15/Y7</f>
+        <v>5.3323681023906021E-2</v>
+      </c>
+      <c r="Z43" s="9">
+        <f t="shared" si="113"/>
         <v>0.05</v>
       </c>
-      <c r="P43" s="9">
-        <f>P15/P7</f>
-        <v>7.0385293376983127E-2</v>
-      </c>
-      <c r="Q43" s="9">
-        <f>Q15/Q7</f>
-        <v>8.8973462250565738E-2</v>
-      </c>
-      <c r="R43" s="9">
-        <f t="shared" ref="R43:T43" si="55">R15/R7</f>
-        <v>7.5800533689126065E-2</v>
-      </c>
-      <c r="S43" s="9">
-        <f t="shared" si="55"/>
-        <v>6.7426685667141689E-2</v>
-      </c>
-      <c r="T43" s="9">
-        <f t="shared" si="55"/>
-        <v>5.0897240548603048E-2</v>
-      </c>
-      <c r="U43" s="9">
-        <f t="shared" ref="U43:AE43" si="56">U15/U7</f>
+      <c r="AA43" s="9">
+        <f t="shared" si="113"/>
+        <v>0.05</v>
+      </c>
+      <c r="AB43" s="9">
+        <f t="shared" si="113"/>
+        <v>0.05</v>
+      </c>
+      <c r="AC43" s="9">
+        <f t="shared" si="113"/>
+        <v>0.05</v>
+      </c>
+      <c r="AD43" s="9">
+        <f t="shared" si="113"/>
+        <v>0.05</v>
+      </c>
+      <c r="AE43" s="9">
+        <f t="shared" si="113"/>
+        <v>0.05</v>
+      </c>
+      <c r="AF43" s="9">
+        <f t="shared" si="113"/>
+        <v>0.05</v>
+      </c>
+      <c r="AG43" s="9">
+        <f t="shared" si="113"/>
         <v>5.000000000000001E-2</v>
       </c>
-      <c r="V43" s="9">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
-      <c r="W43" s="9">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
-      <c r="X43" s="9">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
-      <c r="Y43" s="9">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
-      <c r="Z43" s="9">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
-      <c r="AA43" s="9">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
-      <c r="AB43" s="9">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
-      <c r="AC43" s="9">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
-      <c r="AD43" s="9">
-        <f t="shared" si="56"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="AE43" s="9">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AH43" s="9">
+        <f t="shared" si="113"/>
+        <v>0.05</v>
+      </c>
+      <c r="AI43" s="9">
+        <f t="shared" si="113"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="44" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>62</v>
       </c>
@@ -5281,117 +5977,133 @@
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" s="9">
-        <f t="shared" ref="J44" si="57">J16/F16-1</f>
+        <f t="shared" ref="J44" si="114">J16/F16-1</f>
         <v>-0.37447698744769875</v>
       </c>
       <c r="K44" s="9">
-        <f t="shared" ref="K44" si="58">K16/G16-1</f>
+        <f t="shared" ref="K44" si="115">K16/G16-1</f>
         <v>-0.15742793791574283</v>
       </c>
       <c r="L44" s="9">
-        <f t="shared" ref="L44" si="59">L16/H16-1</f>
+        <f t="shared" ref="L44" si="116">L16/H16-1</f>
         <v>-0.14352941176470591</v>
       </c>
       <c r="M44" s="9">
-        <f t="shared" ref="M44:N44" si="60">M16/I16-1</f>
+        <f t="shared" ref="M44:N44" si="117">M16/I16-1</f>
         <v>-0.13824884792626724</v>
       </c>
       <c r="N44" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="117"/>
+        <v>0.78260869565217384</v>
+      </c>
+      <c r="O44" s="9">
+        <f t="shared" ref="O44" si="118">O16/K16-1</f>
+        <v>0.18157894736842106</v>
+      </c>
+      <c r="P44" s="9">
+        <f t="shared" ref="P44" si="119">P16/L16-1</f>
+        <v>0.25824175824175821</v>
+      </c>
+      <c r="Q44" s="9">
+        <f t="shared" ref="Q44" si="120">Q16/M16-1</f>
+        <v>0.25668449197860976</v>
+      </c>
+      <c r="R44" s="9">
+        <f t="shared" ref="R44" si="121">R16/N16-1</f>
+        <v>0.12570356472795496</v>
+      </c>
+      <c r="T44" s="9"/>
+      <c r="U44" s="9">
+        <f>U16/T16-1</f>
+        <v>0.14098972922502351</v>
+      </c>
+      <c r="V44" s="9">
+        <f t="shared" ref="V44:X44" si="122">V16/U16-1</f>
+        <v>0.37234042553191471</v>
+      </c>
+      <c r="W44" s="9">
+        <f t="shared" si="122"/>
+        <v>-4.054859868813343E-2</v>
+      </c>
+      <c r="X44" s="9">
+        <f t="shared" si="122"/>
+        <v>2.6103169670602888E-2</v>
+      </c>
+      <c r="Y44" s="9">
+        <f t="shared" ref="Y44:AI44" si="123">Y16/X16-1</f>
+        <v>0.19745608721986652</v>
+      </c>
+      <c r="Z44" s="9">
+        <f t="shared" si="123"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AA44" s="9">
+        <f t="shared" si="123"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AB44" s="9">
+        <f t="shared" si="123"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AC44" s="9">
+        <f t="shared" si="123"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD44" s="9">
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9">
-        <f>Q16/P16-1</f>
-        <v>0.14098972922502351</v>
-      </c>
-      <c r="R44" s="9">
-        <f t="shared" ref="R44:T44" si="61">R16/Q16-1</f>
-        <v>0.37234042553191471</v>
-      </c>
-      <c r="S44" s="9">
-        <f t="shared" si="61"/>
-        <v>-4.054859868813343E-2</v>
-      </c>
-      <c r="T44" s="9">
-        <f t="shared" si="61"/>
-        <v>-0.11561218147917962</v>
-      </c>
-      <c r="U44" s="9">
-        <f t="shared" ref="U44:AE44" si="62">U16/T16-1</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="V44" s="9">
-        <f t="shared" si="62"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="W44" s="9">
-        <f t="shared" si="62"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="X44" s="9">
-        <f t="shared" si="62"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="Y44" s="9">
-        <f t="shared" si="62"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="Z44" s="9">
-        <f t="shared" si="62"/>
+      <c r="AE44" s="9">
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA44" s="9">
-        <f t="shared" si="62"/>
+      <c r="AF44" s="9">
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB44" s="9">
-        <f t="shared" si="62"/>
+      <c r="AG44" s="9">
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC44" s="9">
-        <f t="shared" si="62"/>
+      <c r="AH44" s="9">
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD44" s="9">
-        <f t="shared" si="62"/>
+      <c r="AI44" s="9">
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE44" s="9">
-        <f t="shared" si="62"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>63</v>
       </c>
       <c r="F45" s="9">
-        <f t="shared" ref="F45:M45" si="63">F18/F7</f>
+        <f t="shared" ref="F45:L45" si="124">F18/F7</f>
         <v>-8.7783783783783931E-2</v>
       </c>
       <c r="G45" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="124"/>
         <v>-0.23110465116279069</v>
       </c>
       <c r="H45" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="124"/>
         <v>-0.18172757475083048</v>
       </c>
       <c r="I45" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="124"/>
         <v>-0.25937031484257872</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="124"/>
         <v>3.5864387783692941E-2</v>
       </c>
       <c r="K45" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="124"/>
         <v>-0.20918367346938757</v>
       </c>
       <c r="L45" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="124"/>
         <v>-6.9109323801012784E-2</v>
       </c>
       <c r="M45" s="9">
@@ -5400,103 +6112,119 @@
       </c>
       <c r="N45" s="9">
         <f>N18/N7</f>
-        <v>6.4855998458173691E-2</v>
+        <v>0.18291404612159323</v>
+      </c>
+      <c r="O45" s="9">
+        <f t="shared" ref="O45:R45" si="125">O18/O7</f>
+        <v>-5.8570990493713476E-2</v>
       </c>
       <c r="P45" s="9">
-        <f>P18/P7</f>
+        <f t="shared" si="125"/>
+        <v>-8.7238285144565237E-3</v>
+      </c>
+      <c r="Q45" s="9">
+        <f t="shared" si="125"/>
+        <v>3.100021410649012E-2</v>
+      </c>
+      <c r="R45" s="9">
+        <f t="shared" si="125"/>
+        <v>0.1751488368118885</v>
+      </c>
+      <c r="T45" s="9">
+        <f>T18/T7</f>
         <v>-0.10173759758247283</v>
       </c>
-      <c r="Q45" s="9">
-        <f>Q18/Q7</f>
+      <c r="U45" s="9">
+        <f>U18/U7</f>
         <v>-0.11777412055132701</v>
       </c>
-      <c r="R45" s="9">
-        <f t="shared" ref="R45:T45" si="64">R18/R7</f>
+      <c r="V45" s="9">
+        <f t="shared" ref="V45:X45" si="126">V18/V7</f>
         <v>-0.21756170780520326</v>
       </c>
-      <c r="S45" s="9">
-        <f t="shared" si="64"/>
+      <c r="W45" s="9">
+        <f t="shared" si="126"/>
         <v>-0.15697892447311179</v>
       </c>
-      <c r="T45" s="9">
-        <f t="shared" si="64"/>
-        <v>-4.6672746199233339E-2</v>
-      </c>
-      <c r="U45" s="9">
-        <f t="shared" ref="U45:AE45" si="65">U18/U7</f>
-        <v>-2.3758714629048348E-2</v>
-      </c>
-      <c r="V45" s="9">
-        <f t="shared" si="65"/>
-        <v>-1.7348081995926114E-2</v>
-      </c>
-      <c r="W45" s="9">
-        <f t="shared" si="65"/>
-        <v>1.5839157683216671E-3</v>
-      </c>
       <c r="X45" s="9">
-        <f t="shared" si="65"/>
-        <v>1.4078420093826705E-2</v>
+        <f t="shared" si="126"/>
+        <v>1.5402361243045028E-2</v>
       </c>
       <c r="Y45" s="9">
-        <f t="shared" si="65"/>
-        <v>2.4406965285654482E-2</v>
+        <f t="shared" ref="Y45:AI45" si="127">Y18/Y7</f>
+        <v>5.5310090907170664E-2</v>
       </c>
       <c r="Z45" s="9">
-        <f t="shared" si="65"/>
-        <v>3.2562154046448154E-2</v>
+        <f t="shared" si="127"/>
+        <v>8.9689744109432062E-2</v>
       </c>
       <c r="AA45" s="9">
-        <f t="shared" si="65"/>
-        <v>3.7213910329587825E-2</v>
+        <f t="shared" si="127"/>
+        <v>0.10263442388341323</v>
       </c>
       <c r="AB45" s="9">
-        <f t="shared" si="65"/>
-        <v>4.0455558751163814E-2</v>
+        <f t="shared" si="127"/>
+        <v>0.11514949014949574</v>
       </c>
       <c r="AC45" s="9">
-        <f t="shared" si="65"/>
-        <v>4.2243496370636811E-2</v>
+        <f t="shared" si="127"/>
+        <v>0.12626659826188463</v>
       </c>
       <c r="AD45" s="9">
-        <f t="shared" si="65"/>
-        <v>4.4027626442741101E-2</v>
+        <f t="shared" si="127"/>
+        <v>0.135059963909202</v>
       </c>
       <c r="AE45" s="9">
-        <f t="shared" si="65"/>
-        <v>4.5807907601499567E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.3">
+        <f t="shared" si="127"/>
+        <v>0.13988417875236242</v>
+      </c>
+      <c r="AF45" s="9">
+        <f t="shared" si="127"/>
+        <v>0.14319862261041594</v>
+      </c>
+      <c r="AG45" s="9">
+        <f t="shared" si="127"/>
+        <v>0.14505949402646884</v>
+      </c>
+      <c r="AH45" s="9">
+        <f t="shared" si="127"/>
+        <v>0.14691213482740209</v>
+      </c>
+      <c r="AI45" s="9">
+        <f t="shared" si="127"/>
+        <v>0.14875656243075708</v>
+      </c>
+    </row>
+    <row r="46" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>34</v>
       </c>
       <c r="F46" s="9">
-        <f t="shared" ref="F46:M46" si="66">F26/F25</f>
+        <f t="shared" ref="F46:L46" si="128">F26/F25</f>
         <v>7.1005917159763218E-2</v>
       </c>
       <c r="G46" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="128"/>
         <v>-4.0268456375838922E-3</v>
       </c>
       <c r="H46" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="128"/>
         <v>-2.8943560057887135E-3</v>
       </c>
       <c r="I46" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="128"/>
         <v>-3.582089552238806E-3</v>
       </c>
       <c r="J46" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="128"/>
         <v>0.16666666666666627</v>
       </c>
       <c r="K46" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="128"/>
         <v>8.7412587412587471E-3</v>
       </c>
       <c r="L46" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="128"/>
         <v>-1.4876033057851241E-2</v>
       </c>
       <c r="M46" s="9">
@@ -5505,103 +6233,119 @@
       </c>
       <c r="N46" s="9">
         <f>N26/N25</f>
+        <v>3.7950664136622405E-3</v>
+      </c>
+      <c r="O46" s="9">
+        <f t="shared" ref="O46:R46" si="129">O26/O25</f>
+        <v>-1.7391304347826111E-2</v>
+      </c>
+      <c r="P46" s="9">
+        <f t="shared" si="129"/>
+        <v>-2.4330900243309032E-2</v>
+      </c>
+      <c r="Q46" s="9">
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
-      <c r="P46" s="9">
-        <f>P26/P25</f>
+      <c r="R46" s="9">
+        <f t="shared" si="129"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="9">
+        <f>T26/T25</f>
         <v>-1.6778523489932892E-3</v>
       </c>
-      <c r="Q46" s="9">
-        <f>Q26/Q25</f>
+      <c r="U46" s="9">
+        <f>U26/U25</f>
         <v>-5.2029136316337123E-3</v>
       </c>
-      <c r="R46" s="9">
-        <f t="shared" ref="R46:T46" si="67">R26/R25</f>
+      <c r="V46" s="9">
+        <f t="shared" ref="V46:X46" si="130">V26/V25</f>
         <v>-3.5043007327174285E-3</v>
       </c>
-      <c r="S46" s="9">
-        <f t="shared" si="67"/>
+      <c r="W46" s="9">
+        <f t="shared" si="130"/>
         <v>-6.2030688867123745E-3</v>
       </c>
-      <c r="T46" s="9">
-        <f t="shared" si="67"/>
-        <v>-4.2379902772027109E-3</v>
-      </c>
-      <c r="U46" s="9">
-        <f t="shared" ref="U46:AE46" si="68">U26/U25</f>
+      <c r="X46" s="9">
+        <f t="shared" si="130"/>
+        <v>-3.3582089552238487E-2</v>
+      </c>
+      <c r="Y46" s="9">
+        <f t="shared" ref="Y46:AI46" si="131">Y26/Y25</f>
+        <v>3.0851050467250028E-2</v>
+      </c>
+      <c r="Z46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
-      <c r="V46" s="9">
-        <f t="shared" si="68"/>
+      <c r="AA46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
-      <c r="W46" s="9">
-        <f t="shared" si="68"/>
+      <c r="AB46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
-      <c r="X46" s="9">
-        <f t="shared" si="68"/>
-        <v>5.000000000000001E-2</v>
-      </c>
-      <c r="Y46" s="9">
-        <f t="shared" si="68"/>
+      <c r="AC46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
-      <c r="Z46" s="9">
-        <f t="shared" si="68"/>
+      <c r="AD46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
-      <c r="AA46" s="9">
-        <f t="shared" si="68"/>
+      <c r="AE46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
-      <c r="AB46" s="9">
-        <f t="shared" si="68"/>
+      <c r="AF46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
-      <c r="AC46" s="9">
-        <f t="shared" si="68"/>
+      <c r="AG46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
-      <c r="AD46" s="9">
-        <f t="shared" si="68"/>
+      <c r="AH46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
-      <c r="AE46" s="9">
-        <f t="shared" si="68"/>
+      <c r="AI46" s="9">
+        <f t="shared" si="131"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>35</v>
       </c>
       <c r="F47" s="9">
-        <f t="shared" ref="F47:M47" si="69">F27/F25</f>
+        <f t="shared" ref="F47:L47" si="132">F27/F25</f>
         <v>0</v>
       </c>
       <c r="G47" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="132"/>
         <v>4.5637583892617448E-2</v>
       </c>
       <c r="H47" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="132"/>
         <v>4.3415340086830699E-2</v>
       </c>
       <c r="I47" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="132"/>
         <v>-5.3731343283582094E-3</v>
       </c>
       <c r="J47" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="132"/>
         <v>-8.3333333333333134E-2</v>
       </c>
       <c r="K47" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="132"/>
         <v>-1.7482517482517494E-2</v>
       </c>
       <c r="L47" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="132"/>
         <v>-9.9173553719008271E-3</v>
       </c>
       <c r="M47" s="9">
@@ -5610,103 +6354,119 @@
       </c>
       <c r="N47" s="9">
         <f>N27/N25</f>
+        <v>3.7950664136622405E-3</v>
+      </c>
+      <c r="O47" s="9">
+        <f t="shared" ref="O47:R47" si="133">O27/O25</f>
+        <v>-1.7391304347826111E-2</v>
+      </c>
+      <c r="P47" s="9">
+        <f t="shared" si="133"/>
+        <v>-9.7323600973236134E-3</v>
+      </c>
+      <c r="Q47" s="9">
+        <f t="shared" si="133"/>
         <v>0</v>
       </c>
-      <c r="P47" s="9">
-        <f>P27/P25</f>
+      <c r="R47" s="9">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="9">
+        <f>T27/T25</f>
         <v>0.12024608501118574</v>
       </c>
-      <c r="Q47" s="9">
-        <f>Q27/Q25</f>
+      <c r="U47" s="9">
+        <f>U27/U25</f>
         <v>0.15036420395421426</v>
       </c>
-      <c r="R47" s="9">
-        <f t="shared" ref="R47:T47" si="70">R27/R25</f>
+      <c r="V47" s="9">
+        <f t="shared" ref="V47:X47" si="134">V27/V25</f>
         <v>4.3644472762026154E-2</v>
       </c>
-      <c r="S47" s="9">
-        <f t="shared" si="70"/>
+      <c r="W47" s="9">
+        <f t="shared" si="134"/>
         <v>1.9262161279791058E-2</v>
       </c>
-      <c r="T47" s="9">
-        <f t="shared" si="70"/>
-        <v>-1.440916694248922E-2</v>
-      </c>
-      <c r="U47" s="9">
-        <f t="shared" ref="U47:AE47" si="71">U27/U25</f>
+      <c r="X47" s="9">
+        <f t="shared" si="134"/>
+        <v>-7.8358208955223149E-2</v>
+      </c>
+      <c r="Y47" s="9">
+        <f t="shared" ref="Y47:AI47" si="135">Y27/Y25</f>
+        <v>1.7629171695571447E-2</v>
+      </c>
+      <c r="Z47" s="9">
+        <f t="shared" si="135"/>
         <v>0.02</v>
       </c>
-      <c r="V47" s="9">
-        <f t="shared" si="71"/>
+      <c r="AA47" s="9">
+        <f t="shared" si="135"/>
         <v>0.02</v>
       </c>
-      <c r="W47" s="9">
-        <f t="shared" si="71"/>
+      <c r="AB47" s="9">
+        <f t="shared" si="135"/>
         <v>0.02</v>
       </c>
-      <c r="X47" s="9">
-        <f t="shared" si="71"/>
+      <c r="AC47" s="9">
+        <f t="shared" si="135"/>
         <v>0.02</v>
       </c>
-      <c r="Y47" s="9">
-        <f t="shared" si="71"/>
+      <c r="AD47" s="9">
+        <f t="shared" si="135"/>
         <v>0.02</v>
       </c>
-      <c r="Z47" s="9">
-        <f t="shared" si="71"/>
+      <c r="AE47" s="9">
+        <f t="shared" si="135"/>
         <v>0.02</v>
       </c>
-      <c r="AA47" s="9">
-        <f t="shared" si="71"/>
+      <c r="AF47" s="9">
+        <f t="shared" si="135"/>
         <v>0.02</v>
       </c>
-      <c r="AB47" s="9">
-        <f t="shared" si="71"/>
+      <c r="AG47" s="9">
+        <f t="shared" si="135"/>
+        <v>2.0000000000000004E-2</v>
+      </c>
+      <c r="AH47" s="9">
+        <f t="shared" si="135"/>
         <v>0.02</v>
       </c>
-      <c r="AC47" s="9">
-        <f t="shared" si="71"/>
+      <c r="AI47" s="9">
+        <f t="shared" si="135"/>
         <v>0.02</v>
       </c>
-      <c r="AD47" s="9">
-        <f t="shared" si="71"/>
-        <v>0.02</v>
-      </c>
-      <c r="AE47" s="9">
-        <f t="shared" si="71"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>64</v>
       </c>
       <c r="F48" s="9">
-        <f t="shared" ref="F48:M48" si="72">F28/F7</f>
+        <f t="shared" ref="F48:L48" si="136">F28/F7</f>
         <v>-0.10183783783783799</v>
       </c>
       <c r="G48" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="136"/>
         <v>-0.25944767441860461</v>
       </c>
       <c r="H48" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="136"/>
         <v>-0.22026578073089689</v>
       </c>
       <c r="I48" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="136"/>
         <v>-0.42228885557221391</v>
       </c>
       <c r="J48" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="136"/>
         <v>1.2328383300644471E-2</v>
       </c>
       <c r="K48" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="136"/>
         <v>-0.24532312925170049</v>
       </c>
       <c r="L48" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="136"/>
         <v>-0.18468871015787905</v>
       </c>
       <c r="M48" s="9">
@@ -5715,71 +6475,357 @@
       </c>
       <c r="N48" s="9">
         <f>N28/N7</f>
-        <v>3.9717527379984664E-2</v>
+        <v>0.18273934311670154</v>
+      </c>
+      <c r="O48" s="9">
+        <f t="shared" ref="O48:R48" si="137">O28/O7</f>
+        <v>-7.2983747316773886E-2</v>
       </c>
       <c r="P48" s="9">
-        <f>P28/P7</f>
+        <f t="shared" si="137"/>
+        <v>-0.10593220338983039</v>
+      </c>
+      <c r="Q48" s="9">
+        <f t="shared" si="137"/>
+        <v>1.8971759594496547E-2</v>
+      </c>
+      <c r="R48" s="9">
+        <f t="shared" si="137"/>
+        <v>0.16693307108609132</v>
+      </c>
+      <c r="T48" s="9">
+        <f>T28/T7</f>
         <v>-0.19843868043314017</v>
       </c>
-      <c r="Q48" s="9">
-        <f>Q28/Q7</f>
+      <c r="U48" s="9">
+        <f>U28/U7</f>
         <v>-0.16899814852910935</v>
       </c>
-      <c r="R48" s="9">
-        <f t="shared" ref="R48:T48" si="73">R28/R7</f>
+      <c r="V48" s="9">
+        <f t="shared" ref="V48:X48" si="138">V28/V7</f>
         <v>-0.25125083388925934</v>
       </c>
-      <c r="S48" s="9">
-        <f t="shared" si="73"/>
+      <c r="W48" s="9">
+        <f t="shared" si="138"/>
         <v>-0.22673066826670665</v>
       </c>
-      <c r="T48" s="9">
-        <f t="shared" si="73"/>
-        <v>-9.5425462733947419E-2</v>
-      </c>
-      <c r="U48" s="9">
-        <f t="shared" ref="U48:AE48" si="74">U28/U7</f>
-        <v>-4.6664897718964149E-2</v>
-      </c>
-      <c r="V48" s="9">
-        <f t="shared" si="74"/>
-        <v>-3.9096116076781921E-2</v>
-      </c>
-      <c r="W48" s="9">
-        <f t="shared" si="74"/>
-        <v>-1.9701714712008295E-2</v>
-      </c>
       <c r="X48" s="9">
-        <f t="shared" si="74"/>
-        <v>-6.638587285453355E-3</v>
+        <f t="shared" si="138"/>
+        <v>-2.0219839869724695E-2</v>
       </c>
       <c r="Y48" s="9">
-        <f t="shared" si="74"/>
-        <v>4.1072096503015736E-3</v>
+        <f t="shared" ref="Y48:AI48" si="139">Y28/Y7</f>
+        <v>2.4651828905203291E-2</v>
       </c>
       <c r="Z48" s="9">
-        <f t="shared" si="74"/>
-        <v>1.2435376241054353E-2</v>
+        <f t="shared" si="139"/>
+        <v>7.2268643958378842E-2</v>
       </c>
       <c r="AA48" s="9">
-        <f t="shared" si="74"/>
-        <v>1.7142251938526736E-2</v>
+        <f t="shared" si="139"/>
+        <v>8.5143534760654588E-2</v>
       </c>
       <c r="AB48" s="9">
-        <f t="shared" si="74"/>
-        <v>2.0399178323352082E-2</v>
+        <f t="shared" si="139"/>
+        <v>9.7493115535120342E-2</v>
       </c>
       <c r="AC48" s="9">
-        <f t="shared" si="74"/>
-        <v>2.2195062842619566E-2</v>
+        <f t="shared" si="139"/>
+        <v>0.10843208076691603</v>
       </c>
       <c r="AD48" s="9">
-        <f t="shared" si="74"/>
-        <v>2.3987106168512313E-2</v>
+        <f t="shared" si="139"/>
+        <v>0.11702600593468929</v>
       </c>
       <c r="AE48" s="9">
-        <f t="shared" si="74"/>
-        <v>2.5775266492495039E-2</v>
+        <f t="shared" si="139"/>
+        <v>0.12172643150401183</v>
+      </c>
+      <c r="AF48" s="9">
+        <f t="shared" si="139"/>
+        <v>0.12495045431260481</v>
+      </c>
+      <c r="AG48" s="9">
+        <f t="shared" si="139"/>
+        <v>0.12675296409569661</v>
+      </c>
+      <c r="AH48" s="9">
+        <f t="shared" si="139"/>
+        <v>0.12854746765869463</v>
+      </c>
+      <c r="AI48" s="9">
+        <f t="shared" si="139"/>
+        <v>0.13033398145322853</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="P51" s="4">
+        <v>574.79999999999995</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>80</v>
+      </c>
+      <c r="P52" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>81</v>
+      </c>
+      <c r="P53" s="4">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>82</v>
+      </c>
+      <c r="P54" s="4">
+        <v>129.80000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>83</v>
+      </c>
+      <c r="P55" s="4">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>84</v>
+      </c>
+      <c r="P56" s="4">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>85</v>
+      </c>
+      <c r="P57" s="4">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P58" s="8">
+        <f>SUM(P51:P57)</f>
+        <v>1933.3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>87</v>
+      </c>
+      <c r="P59" s="4">
+        <v>402.9</v>
+      </c>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>88</v>
+      </c>
+      <c r="P60" s="4">
+        <v>117.3</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>80</v>
+      </c>
+      <c r="P61" s="4">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="P62" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>89</v>
+      </c>
+      <c r="P63" s="4">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P64" s="8">
+        <f>SUM(P59:P63)</f>
+        <v>597.19999999999993</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P65" s="11">
+        <f>P58+P64</f>
+        <v>2530.5</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>92</v>
+      </c>
+      <c r="P66" s="4">
+        <v>144.80000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>93</v>
+      </c>
+      <c r="P67" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>94</v>
+      </c>
+      <c r="P68" s="4">
+        <v>116.6</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>84</v>
+      </c>
+      <c r="P69" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="P70" s="4">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>5</v>
+      </c>
+      <c r="P71" s="4">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>95</v>
+      </c>
+      <c r="P72" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>96</v>
+      </c>
+      <c r="P73" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P74" s="8">
+        <f>SUM(P66:P73)</f>
+        <v>387.4</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>84</v>
+      </c>
+      <c r="P75" s="4">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>88</v>
+      </c>
+      <c r="P76" s="4">
+        <v>117.5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>5</v>
+      </c>
+      <c r="P77" s="4">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>95</v>
+      </c>
+      <c r="P78" s="4">
+        <v>1126.2</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>96</v>
+      </c>
+      <c r="P79" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>98</v>
+      </c>
+      <c r="P80" s="4">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="81" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P81" s="8">
+        <f>SUM(P75:P80)</f>
+        <v>1523.7</v>
+      </c>
+    </row>
+    <row r="82" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P82" s="8">
+        <v>619.4</v>
+      </c>
+    </row>
+    <row r="83" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="P83" s="11">
+        <f>P74+P81+P82</f>
+        <v>2530.5</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/BE.xlsx
+++ b/Financial Analysis/BE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3405BCD-E2F6-4D6C-8C6A-9B54C676DC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3C382E-3192-43A2-906C-26F11F31C0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FD927F57-917F-4496-A6AC-5E97F081D2C4}"/>
   </bookViews>
@@ -401,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -420,6 +420,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,13 +442,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -465,7 +466,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10660380" y="7620"/>
+          <a:off x="11269980" y="7620"/>
           <a:ext cx="0" cy="9060180"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -864,17 +865,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="7">
-        <v>70.709999999999994</v>
+        <v>132.12</v>
       </c>
       <c r="E3" s="3">
-        <v>45927</v>
+        <v>45959</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45927</v>
+        <v>45959</v>
       </c>
       <c r="G3" s="3">
-        <v>45960</v>
+        <v>46058</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -882,11 +883,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -895,7 +896,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>16546.14</v>
+        <v>31246.38</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -903,11 +904,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>574.8</f>
-        <v>574.79999999999995</v>
+        <f>595.1+8.5+5.9+23.5</f>
+        <v>633</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -915,8 +916,8 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>219.8+1126.2</f>
-        <v>1346</v>
+        <f>36.6+1.4+209.8+1128+2.8</f>
+        <v>1378.6</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>77</v>
@@ -931,7 +932,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>-771.2</v>
+        <v>-745.59999999999991</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -940,7 +941,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>17317.34</v>
+        <v>31991.98</v>
       </c>
     </row>
   </sheetData>
@@ -1094,12 +1095,11 @@
         <v>296.60000000000002</v>
       </c>
       <c r="Q3" s="4">
-        <f>M3*1.3</f>
-        <v>303.94</v>
+        <v>384.3</v>
       </c>
       <c r="R3" s="4">
-        <f>N3*1.05</f>
-        <v>495.28500000000003</v>
+        <f>N3*1.2</f>
+        <v>566.04</v>
       </c>
       <c r="T3" s="4">
         <v>518.6</v>
@@ -1120,47 +1120,47 @@
       </c>
       <c r="Y3" s="4">
         <f>SUM(O3:R3)</f>
-        <v>1307.7250000000001</v>
+        <v>1458.84</v>
       </c>
       <c r="Z3" s="4">
-        <f>Y3*1.14</f>
-        <v>1490.8064999999999</v>
+        <f>Y3*1.25</f>
+        <v>1823.55</v>
       </c>
       <c r="AA3" s="4">
-        <f>Z3*1.1</f>
-        <v>1639.88715</v>
+        <f>Z3*1.15</f>
+        <v>2097.0825</v>
       </c>
       <c r="AB3" s="4">
-        <f>AA3*1.1</f>
-        <v>1803.8758650000002</v>
+        <f>AA3*1.12</f>
+        <v>2348.7324000000003</v>
       </c>
       <c r="AC3" s="4">
         <f>AB3*1.1</f>
-        <v>1984.2634515000004</v>
+        <v>2583.6056400000007</v>
       </c>
       <c r="AD3" s="4">
-        <f>AC3*1.08</f>
-        <v>2143.0045276200008</v>
+        <f t="shared" ref="AD3:AI3" si="0">AC3*1.1</f>
+        <v>2841.9662040000012</v>
       </c>
       <c r="AE3" s="4">
-        <f>AD3*1.05</f>
-        <v>2250.154754001001</v>
+        <f t="shared" si="0"/>
+        <v>3126.1628244000017</v>
       </c>
       <c r="AF3" s="4">
-        <f>AE3*1.04</f>
-        <v>2340.1609441610412</v>
+        <f t="shared" si="0"/>
+        <v>3438.779106840002</v>
       </c>
       <c r="AG3" s="4">
-        <f t="shared" ref="AG3:AI3" si="0">AF3*1.03</f>
-        <v>2410.3657724858726</v>
+        <f t="shared" si="0"/>
+        <v>3782.6570175240026</v>
       </c>
       <c r="AH3" s="4">
         <f t="shared" si="0"/>
-        <v>2482.6767456604489</v>
+        <v>4160.9227192764029</v>
       </c>
       <c r="AI3" s="4">
         <f t="shared" si="0"/>
-        <v>2557.1570480302626</v>
+        <v>4577.0149912040433</v>
       </c>
     </row>
     <row r="4" spans="2:35" x14ac:dyDescent="0.3">
@@ -1201,12 +1201,11 @@
         <v>37.4</v>
       </c>
       <c r="Q4" s="4">
-        <f t="shared" ref="Q4" si="1">M4*1.05</f>
-        <v>33.705000000000005</v>
+        <v>65.8</v>
       </c>
       <c r="R4" s="4">
-        <f>N4*1.05</f>
-        <v>37.905000000000001</v>
+        <f>N4*2.2</f>
+        <v>79.420000000000016</v>
       </c>
       <c r="T4" s="4">
         <v>101.9</v>
@@ -1226,48 +1225,48 @@
         <v>122.30000000000001</v>
       </c>
       <c r="Y4" s="4">
-        <f t="shared" ref="Y4:Y6" si="2">SUM(O4:R4)</f>
-        <v>142.71</v>
+        <f t="shared" ref="Y4:Y6" si="1">SUM(O4:R4)</f>
+        <v>216.32</v>
       </c>
       <c r="Z4" s="4">
-        <f>Y4*1.25</f>
-        <v>178.38750000000002</v>
+        <f>Y4*1.5</f>
+        <v>324.48</v>
       </c>
       <c r="AA4" s="4">
-        <f>Z4*1.2</f>
-        <v>214.06500000000003</v>
+        <f>Z4*1.4</f>
+        <v>454.27199999999999</v>
       </c>
       <c r="AB4" s="4">
-        <f>AA4*1.15</f>
-        <v>246.17475000000002</v>
+        <f>AA4*1.3</f>
+        <v>590.55359999999996</v>
       </c>
       <c r="AC4" s="4">
-        <f>AB4*1.08</f>
-        <v>265.86873000000003</v>
+        <f>AB4*1.2</f>
+        <v>708.66431999999998</v>
       </c>
       <c r="AD4" s="4">
-        <f>AC4*1.05</f>
-        <v>279.16216650000007</v>
+        <f t="shared" ref="AD4:AI4" si="2">AC4*1.2</f>
+        <v>850.39718399999992</v>
       </c>
       <c r="AE4" s="4">
-        <f>AD4*1.04</f>
-        <v>290.3286531600001</v>
+        <f t="shared" si="2"/>
+        <v>1020.4766207999999</v>
       </c>
       <c r="AF4" s="4">
-        <f>AE4*1.03</f>
-        <v>299.03851275480014</v>
+        <f t="shared" si="2"/>
+        <v>1224.5719449599999</v>
       </c>
       <c r="AG4" s="4">
-        <f t="shared" ref="AG4:AI4" si="3">AF4*1.02</f>
-        <v>305.01928300989613</v>
+        <f t="shared" si="2"/>
+        <v>1469.4863339519998</v>
       </c>
       <c r="AH4" s="4">
-        <f t="shared" si="3"/>
-        <v>311.11966867009403</v>
+        <f t="shared" si="2"/>
+        <v>1763.3836007423997</v>
       </c>
       <c r="AI4" s="4">
-        <f t="shared" si="3"/>
-        <v>317.3420620434959</v>
+        <f t="shared" si="2"/>
+        <v>2116.0603208908797</v>
       </c>
     </row>
     <row r="5" spans="2:35" x14ac:dyDescent="0.3">
@@ -1308,12 +1307,11 @@
         <v>54.4</v>
       </c>
       <c r="Q5" s="4">
-        <f t="shared" ref="Q5:R5" si="4">M5*1.02</f>
-        <v>51.815999999999995</v>
+        <v>58.6</v>
       </c>
       <c r="R5" s="4">
-        <f t="shared" si="4"/>
-        <v>54.875999999999998</v>
+        <f>N5*1.2</f>
+        <v>64.559999999999988</v>
       </c>
       <c r="T5" s="4">
         <v>109.6</v>
@@ -1333,48 +1331,48 @@
         <v>213.5</v>
       </c>
       <c r="Y5" s="4">
-        <f t="shared" si="2"/>
-        <v>214.59200000000001</v>
+        <f t="shared" si="1"/>
+        <v>231.06</v>
       </c>
       <c r="Z5" s="4">
-        <f>Y5*1.1</f>
-        <v>236.05120000000002</v>
+        <f>Y5*1.07</f>
+        <v>247.23420000000002</v>
       </c>
       <c r="AA5" s="4">
-        <f>Z5*1.07</f>
-        <v>252.57478400000005</v>
+        <f>Z5*1.05</f>
+        <v>259.59591</v>
       </c>
       <c r="AB5" s="4">
         <f>AA5*1.04</f>
-        <v>262.67777536000006</v>
+        <v>269.97974640000001</v>
       </c>
       <c r="AC5" s="4">
         <f>AB5*1.03</f>
-        <v>270.55810862080006</v>
+        <v>278.07913879200004</v>
       </c>
       <c r="AD5" s="4">
         <f>AC5*1.02</f>
-        <v>275.96927079321608</v>
+        <v>283.64072156784005</v>
       </c>
       <c r="AE5" s="4">
-        <f t="shared" ref="AE5:AI5" si="5">AD5*1.02</f>
-        <v>281.48865620908043</v>
+        <f t="shared" ref="AE5:AI5" si="3">AD5*1.02</f>
+        <v>289.31353599919686</v>
       </c>
       <c r="AF5" s="4">
-        <f t="shared" si="5"/>
-        <v>287.11842933326204</v>
+        <f t="shared" si="3"/>
+        <v>295.09980671918078</v>
       </c>
       <c r="AG5" s="4">
-        <f t="shared" si="5"/>
-        <v>292.86079791992728</v>
+        <f t="shared" si="3"/>
+        <v>301.00180285356441</v>
       </c>
       <c r="AH5" s="4">
-        <f t="shared" si="5"/>
-        <v>298.71801387832585</v>
+        <f t="shared" si="3"/>
+        <v>307.02183891063572</v>
       </c>
       <c r="AI5" s="4">
-        <f t="shared" si="5"/>
-        <v>304.69237415589237</v>
+        <f t="shared" si="3"/>
+        <v>313.16227568884847</v>
       </c>
     </row>
     <row r="6" spans="2:35" x14ac:dyDescent="0.3">
@@ -1415,11 +1413,10 @@
         <v>12.8</v>
       </c>
       <c r="Q6" s="4">
-        <f t="shared" ref="Q6:R6" si="6">M6*1.9</f>
-        <v>26.22</v>
+        <v>10.4</v>
       </c>
       <c r="R6" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="Q6:R6" si="4">N6*1.9</f>
         <v>20.52</v>
       </c>
       <c r="T6" s="4">
@@ -1440,48 +1437,48 @@
         <v>52.8</v>
       </c>
       <c r="Y6" s="4">
-        <f t="shared" si="2"/>
-        <v>86.539999999999992</v>
+        <f t="shared" si="1"/>
+        <v>70.72</v>
       </c>
       <c r="Z6" s="4">
-        <f t="shared" ref="Z6" si="7">Y6*1.2</f>
-        <v>103.84799999999998</v>
+        <f>Y6*1.15</f>
+        <v>81.327999999999989</v>
       </c>
       <c r="AA6" s="4">
-        <f>Z6*1.05</f>
-        <v>109.04039999999999</v>
+        <f>Z6*1.08</f>
+        <v>87.834239999999994</v>
       </c>
       <c r="AB6" s="4">
-        <f t="shared" ref="AB6:AI6" si="8">AA6*1.05</f>
-        <v>114.49242</v>
+        <f t="shared" ref="AB6:AI6" si="5">AA6*1.05</f>
+        <v>92.225951999999992</v>
       </c>
       <c r="AC6" s="4">
-        <f t="shared" si="8"/>
-        <v>120.21704099999999</v>
+        <f t="shared" si="5"/>
+        <v>96.837249599999993</v>
       </c>
       <c r="AD6" s="4">
-        <f t="shared" si="8"/>
-        <v>126.22789305000001</v>
+        <f t="shared" si="5"/>
+        <v>101.67911208</v>
       </c>
       <c r="AE6" s="4">
-        <f t="shared" si="8"/>
-        <v>132.53928770250002</v>
+        <f t="shared" si="5"/>
+        <v>106.76306768400001</v>
       </c>
       <c r="AF6" s="4">
-        <f t="shared" si="8"/>
-        <v>139.16625208762503</v>
+        <f t="shared" si="5"/>
+        <v>112.1012210682</v>
       </c>
       <c r="AG6" s="4">
-        <f t="shared" si="8"/>
-        <v>146.12456469200629</v>
+        <f t="shared" si="5"/>
+        <v>117.70628212161002</v>
       </c>
       <c r="AH6" s="4">
-        <f t="shared" si="8"/>
-        <v>153.43079292660661</v>
+        <f t="shared" si="5"/>
+        <v>123.59159622769052</v>
       </c>
       <c r="AI6" s="4">
-        <f t="shared" si="8"/>
-        <v>161.10233257293694</v>
+        <f t="shared" si="5"/>
+        <v>129.77117603907504</v>
       </c>
     </row>
     <row r="7" spans="2:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1489,56 +1486,56 @@
         <v>15</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" ref="F7:O7" si="9">SUM(F3:F6)</f>
+        <f t="shared" ref="F7:O7" si="6">SUM(F3:F6)</f>
         <v>462.49999999999994</v>
       </c>
       <c r="G7" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>275.2</v>
       </c>
       <c r="H7" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>301</v>
       </c>
       <c r="I7" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>400.2</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>356.90000000000003</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>235.20000000000002</v>
       </c>
       <c r="L7" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>335.7</v>
       </c>
       <c r="M7" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>330.50000000000006</v>
       </c>
       <c r="N7" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>572.4</v>
       </c>
       <c r="O7" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>326.10000000000002</v>
       </c>
       <c r="P7" s="8">
-        <f t="shared" ref="P7" si="10">SUM(P3:P6)</f>
+        <f t="shared" ref="P7" si="7">SUM(P3:P6)</f>
         <v>401.2</v>
       </c>
       <c r="Q7" s="8">
-        <f t="shared" ref="Q7" si="11">SUM(Q3:Q6)</f>
-        <v>415.68099999999993</v>
+        <f t="shared" ref="Q7" si="8">SUM(Q3:Q6)</f>
+        <v>519.1</v>
       </c>
       <c r="R7" s="8">
-        <f t="shared" ref="R7" si="12">SUM(R3:R6)</f>
-        <v>608.58600000000001</v>
+        <f t="shared" ref="R7" si="9">SUM(R3:R6)</f>
+        <v>730.54</v>
       </c>
       <c r="T7" s="8">
         <f>SUM(T3:T6)</f>
@@ -1561,48 +1558,48 @@
         <v>1473.8</v>
       </c>
       <c r="Y7" s="8">
-        <f t="shared" ref="Y7:AI7" si="13">SUM(Y3:Y6)</f>
-        <v>1751.5670000000002</v>
+        <f t="shared" ref="Y7:AI7" si="10">SUM(Y3:Y6)</f>
+        <v>1976.9399999999998</v>
       </c>
       <c r="Z7" s="8">
-        <f t="shared" si="13"/>
-        <v>2009.0932</v>
+        <f t="shared" si="10"/>
+        <v>2476.5921999999996</v>
       </c>
       <c r="AA7" s="8">
-        <f t="shared" si="13"/>
-        <v>2215.5673339999998</v>
+        <f t="shared" si="10"/>
+        <v>2898.7846500000001</v>
       </c>
       <c r="AB7" s="8">
-        <f t="shared" si="13"/>
-        <v>2427.2208103600001</v>
+        <f t="shared" si="10"/>
+        <v>3301.4916983999997</v>
       </c>
       <c r="AC7" s="8">
-        <f t="shared" si="13"/>
-        <v>2640.9073311208003</v>
+        <f t="shared" si="10"/>
+        <v>3667.1863483920006</v>
       </c>
       <c r="AD7" s="8">
-        <f t="shared" si="13"/>
-        <v>2824.3638579632175</v>
+        <f t="shared" si="10"/>
+        <v>4077.683221647841</v>
       </c>
       <c r="AE7" s="8">
-        <f t="shared" si="13"/>
-        <v>2954.5113510725819</v>
+        <f t="shared" si="10"/>
+        <v>4542.7160488831978</v>
       </c>
       <c r="AF7" s="8">
-        <f t="shared" si="13"/>
-        <v>3065.4841383367284</v>
+        <f t="shared" si="10"/>
+        <v>5070.5520795873827</v>
       </c>
       <c r="AG7" s="8">
-        <f t="shared" si="13"/>
-        <v>3154.3704181077028</v>
+        <f t="shared" si="10"/>
+        <v>5670.8514364511775</v>
       </c>
       <c r="AH7" s="8">
-        <f t="shared" si="13"/>
-        <v>3245.9452211354755</v>
+        <f t="shared" si="10"/>
+        <v>6354.9197551571287</v>
       </c>
       <c r="AI7" s="8">
-        <f t="shared" si="13"/>
-        <v>3340.293816802588</v>
+        <f t="shared" si="10"/>
+        <v>7136.008763822846</v>
       </c>
     </row>
     <row r="8" spans="2:35" x14ac:dyDescent="0.3">
@@ -1643,12 +1640,11 @@
         <v>198.7</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" ref="Q8" si="14">Q3*0.65</f>
-        <v>197.56100000000001</v>
+        <v>249.8</v>
       </c>
       <c r="R8" s="4">
         <f>R3*0.55</f>
-        <v>272.40675000000005</v>
+        <v>311.322</v>
       </c>
       <c r="T8" s="4">
         <v>332.7</v>
@@ -1668,48 +1664,48 @@
         <v>685.90000000000009</v>
       </c>
       <c r="Y8" s="4">
-        <f t="shared" ref="Y8:Y11" si="15">SUM(O8:R8)</f>
-        <v>808.26774999999998</v>
+        <f t="shared" ref="Y8:Y11" si="11">SUM(O8:R8)</f>
+        <v>899.42199999999991</v>
       </c>
       <c r="Z8" s="4">
         <f>Z3*0.6</f>
-        <v>894.48389999999995</v>
+        <v>1094.1299999999999</v>
       </c>
       <c r="AA8" s="4">
-        <f t="shared" ref="AA8:AI8" si="16">AA3*0.6</f>
-        <v>983.93228999999997</v>
+        <f t="shared" ref="AA8:AI8" si="12">AA3*0.6</f>
+        <v>1258.2494999999999</v>
       </c>
       <c r="AB8" s="4">
-        <f t="shared" si="16"/>
-        <v>1082.325519</v>
+        <f t="shared" si="12"/>
+        <v>1409.2394400000001</v>
       </c>
       <c r="AC8" s="4">
-        <f t="shared" si="16"/>
-        <v>1190.5580709000003</v>
+        <f t="shared" si="12"/>
+        <v>1550.1633840000004</v>
       </c>
       <c r="AD8" s="4">
-        <f t="shared" si="16"/>
-        <v>1285.8027165720005</v>
+        <f t="shared" si="12"/>
+        <v>1705.1797224000006</v>
       </c>
       <c r="AE8" s="4">
-        <f t="shared" si="16"/>
-        <v>1350.0928524006006</v>
+        <f t="shared" si="12"/>
+        <v>1875.6976946400009</v>
       </c>
       <c r="AF8" s="4">
-        <f t="shared" si="16"/>
-        <v>1404.0965664966247</v>
+        <f t="shared" si="12"/>
+        <v>2063.2674641040012</v>
       </c>
       <c r="AG8" s="4">
-        <f t="shared" si="16"/>
-        <v>1446.2194634915236</v>
+        <f t="shared" si="12"/>
+        <v>2269.5942105144013</v>
       </c>
       <c r="AH8" s="4">
-        <f t="shared" si="16"/>
-        <v>1489.6060473962693</v>
+        <f t="shared" si="12"/>
+        <v>2496.5536315658414</v>
       </c>
       <c r="AI8" s="4">
-        <f t="shared" si="16"/>
-        <v>1534.2942288181575</v>
+        <f t="shared" si="12"/>
+        <v>2746.2089947224258</v>
       </c>
     </row>
     <row r="9" spans="2:35" x14ac:dyDescent="0.3">
@@ -1750,12 +1746,11 @@
         <v>38.200000000000003</v>
       </c>
       <c r="Q9" s="4">
-        <f>Q4*0.92</f>
-        <v>31.008600000000005</v>
+        <v>59.9</v>
       </c>
       <c r="R9" s="4">
         <f>R4*0.88</f>
-        <v>33.356400000000001</v>
+        <v>69.889600000000016</v>
       </c>
       <c r="T9" s="4">
         <v>116.5</v>
@@ -1775,48 +1770,48 @@
         <v>129.5</v>
       </c>
       <c r="Y9" s="4">
-        <f t="shared" si="15"/>
-        <v>135.86500000000001</v>
+        <f t="shared" si="11"/>
+        <v>201.28960000000001</v>
       </c>
       <c r="Z9" s="4">
         <f>Z4*0.91</f>
-        <v>162.33262500000001</v>
+        <v>295.27680000000004</v>
       </c>
       <c r="AA9" s="4">
-        <f t="shared" ref="AA9:AI9" si="17">AA4*0.91</f>
-        <v>194.79915000000003</v>
+        <f t="shared" ref="AA9:AI9" si="13">AA4*0.91</f>
+        <v>413.38751999999999</v>
       </c>
       <c r="AB9" s="4">
-        <f t="shared" si="17"/>
-        <v>224.01902250000003</v>
+        <f t="shared" si="13"/>
+        <v>537.40377599999999</v>
       </c>
       <c r="AC9" s="4">
-        <f t="shared" si="17"/>
-        <v>241.94054430000003</v>
+        <f t="shared" si="13"/>
+        <v>644.88453119999997</v>
       </c>
       <c r="AD9" s="4">
-        <f t="shared" si="17"/>
-        <v>254.03757151500008</v>
+        <f t="shared" si="13"/>
+        <v>773.86143743999992</v>
       </c>
       <c r="AE9" s="4">
-        <f t="shared" si="17"/>
-        <v>264.19907437560011</v>
+        <f t="shared" si="13"/>
+        <v>928.63372492799988</v>
       </c>
       <c r="AF9" s="4">
-        <f t="shared" si="17"/>
-        <v>272.12504660686812</v>
+        <f t="shared" si="13"/>
+        <v>1114.3604699135999</v>
       </c>
       <c r="AG9" s="4">
-        <f t="shared" si="17"/>
-        <v>277.56754753900549</v>
+        <f t="shared" si="13"/>
+        <v>1337.2325638963198</v>
       </c>
       <c r="AH9" s="4">
-        <f t="shared" si="17"/>
-        <v>283.11889848978558</v>
+        <f t="shared" si="13"/>
+        <v>1604.6790766755837</v>
       </c>
       <c r="AI9" s="4">
-        <f t="shared" si="17"/>
-        <v>288.78127645958131</v>
+        <f t="shared" si="13"/>
+        <v>1925.6148920107005</v>
       </c>
     </row>
     <row r="10" spans="2:35" x14ac:dyDescent="0.3">
@@ -1857,12 +1852,11 @@
         <v>49.4</v>
       </c>
       <c r="Q10" s="4">
-        <f>Q5*0.95</f>
-        <v>49.225199999999994</v>
+        <v>51.8</v>
       </c>
       <c r="R10" s="4">
-        <f>R5*0.97</f>
-        <v>53.229719999999993</v>
+        <f>R5*0.9</f>
+        <v>58.103999999999992</v>
       </c>
       <c r="T10" s="4">
         <v>132.30000000000001</v>
@@ -1882,48 +1876,48 @@
         <v>215</v>
       </c>
       <c r="Y10" s="4">
-        <f t="shared" si="15"/>
-        <v>204.75491999999997</v>
+        <f t="shared" si="11"/>
+        <v>212.20399999999998</v>
       </c>
       <c r="Z10" s="4">
         <f>Z5*0.9</f>
-        <v>212.44608000000002</v>
+        <v>222.51078000000001</v>
       </c>
       <c r="AA10" s="4">
         <f>AA5*0.85</f>
-        <v>214.68856640000004</v>
+        <v>220.65652349999999</v>
       </c>
       <c r="AB10" s="4">
         <f>AB5*0.83</f>
-        <v>218.02255354880003</v>
+        <v>224.08318951199999</v>
       </c>
       <c r="AC10" s="4">
-        <f t="shared" ref="AC10:AI10" si="18">AC5*0.83</f>
-        <v>224.56323015526402</v>
+        <f t="shared" ref="AC10:AI10" si="14">AC5*0.83</f>
+        <v>230.80568519736002</v>
       </c>
       <c r="AD10" s="4">
-        <f t="shared" si="18"/>
-        <v>229.05449475836934</v>
+        <f t="shared" si="14"/>
+        <v>235.42179890130723</v>
       </c>
       <c r="AE10" s="4">
-        <f t="shared" si="18"/>
-        <v>233.63558465353674</v>
+        <f t="shared" si="14"/>
+        <v>240.13023487933339</v>
       </c>
       <c r="AF10" s="4">
-        <f t="shared" si="18"/>
-        <v>238.30829634660748</v>
+        <f t="shared" si="14"/>
+        <v>244.93283957692003</v>
       </c>
       <c r="AG10" s="4">
-        <f t="shared" si="18"/>
-        <v>243.07446227353964</v>
+        <f t="shared" si="14"/>
+        <v>249.83149636845846</v>
       </c>
       <c r="AH10" s="4">
-        <f t="shared" si="18"/>
-        <v>247.93595151901044</v>
+        <f t="shared" si="14"/>
+        <v>254.82812629582764</v>
       </c>
       <c r="AI10" s="4">
-        <f t="shared" si="18"/>
-        <v>252.89467054939064</v>
+        <f t="shared" si="14"/>
+        <v>259.92468882174421</v>
       </c>
     </row>
     <row r="11" spans="2:35" x14ac:dyDescent="0.3">
@@ -1964,7 +1958,7 @@
         <v>7.7</v>
       </c>
       <c r="Q11" s="4">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="R11" s="4">
         <v>14</v>
@@ -1987,48 +1981,48 @@
         <v>38.9</v>
       </c>
       <c r="Y11" s="4">
-        <f t="shared" si="15"/>
-        <v>46.3</v>
+        <f t="shared" si="11"/>
+        <v>39.1</v>
       </c>
       <c r="Z11" s="4">
         <f>Z6*0.56</f>
-        <v>58.154879999999999</v>
+        <v>45.543679999999995</v>
       </c>
       <c r="AA11" s="4">
-        <f t="shared" ref="AA11:AI11" si="19">AA6*0.56</f>
-        <v>61.062624</v>
+        <f t="shared" ref="AA11:AI11" si="15">AA6*0.56</f>
+        <v>49.187174400000004</v>
       </c>
       <c r="AB11" s="4">
-        <f t="shared" si="19"/>
-        <v>64.115755200000009</v>
+        <f t="shared" si="15"/>
+        <v>51.646533120000001</v>
       </c>
       <c r="AC11" s="4">
-        <f t="shared" si="19"/>
-        <v>67.321542960000002</v>
+        <f t="shared" si="15"/>
+        <v>54.228859776</v>
       </c>
       <c r="AD11" s="4">
-        <f t="shared" si="19"/>
-        <v>70.687620108000004</v>
+        <f t="shared" si="15"/>
+        <v>56.940302764800002</v>
       </c>
       <c r="AE11" s="4">
-        <f t="shared" si="19"/>
-        <v>74.222001113400012</v>
+        <f t="shared" si="15"/>
+        <v>59.787317903040012</v>
       </c>
       <c r="AF11" s="4">
-        <f t="shared" si="19"/>
-        <v>77.933101169070028</v>
+        <f t="shared" si="15"/>
+        <v>62.77668379819201</v>
       </c>
       <c r="AG11" s="4">
-        <f t="shared" si="19"/>
-        <v>81.829756227523532</v>
+        <f t="shared" si="15"/>
+        <v>65.915517988101612</v>
       </c>
       <c r="AH11" s="4">
-        <f t="shared" si="19"/>
-        <v>85.921244038899715</v>
+        <f t="shared" si="15"/>
+        <v>69.211293887506699</v>
       </c>
       <c r="AI11" s="4">
-        <f t="shared" si="19"/>
-        <v>90.217306240844692</v>
+        <f t="shared" si="15"/>
+        <v>72.671858581882034</v>
       </c>
     </row>
     <row r="12" spans="2:35" x14ac:dyDescent="0.3">
@@ -2036,56 +2030,56 @@
         <v>20</v>
       </c>
       <c r="F12" s="4">
-        <f t="shared" ref="F12:O12" si="20">SUM(F8:F11)</f>
+        <f t="shared" ref="F12:O12" si="16">SUM(F8:F11)</f>
         <v>391.1</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>220.89999999999998</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>244.89999999999998</v>
       </c>
       <c r="I12" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>405.5</v>
       </c>
       <c r="J12" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>264.60000000000002</v>
       </c>
       <c r="K12" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>197.29999999999998</v>
       </c>
       <c r="L12" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>267.2</v>
       </c>
       <c r="M12" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>251.70000000000002</v>
       </c>
       <c r="N12" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>353.1</v>
       </c>
       <c r="O12" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>237.39999999999998</v>
       </c>
       <c r="P12" s="4">
-        <f t="shared" ref="P12" si="21">SUM(P8:P11)</f>
+        <f t="shared" ref="P12" si="17">SUM(P8:P11)</f>
         <v>293.99999999999994</v>
       </c>
       <c r="Q12" s="4">
-        <f t="shared" ref="Q12" si="22">SUM(Q8:Q11)</f>
-        <v>290.79480000000001</v>
+        <f t="shared" ref="Q12" si="18">SUM(Q8:Q11)</f>
+        <v>367.3</v>
       </c>
       <c r="R12" s="4">
-        <f t="shared" ref="R12" si="23">SUM(R8:R11)</f>
-        <v>372.99287000000004</v>
+        <f t="shared" ref="R12" si="19">SUM(R8:R11)</f>
+        <v>453.31560000000002</v>
       </c>
       <c r="T12" s="4">
         <f>SUM(T8:T11)</f>
@@ -2108,48 +2102,48 @@
         <v>1069.3000000000002</v>
       </c>
       <c r="Y12" s="4">
-        <f t="shared" ref="Y12:AI12" si="24">SUM(Y8:Y11)</f>
-        <v>1195.18767</v>
+        <f t="shared" ref="Y12:AI12" si="20">SUM(Y8:Y11)</f>
+        <v>1352.0155999999997</v>
       </c>
       <c r="Z12" s="4">
-        <f t="shared" si="24"/>
-        <v>1327.4174849999999</v>
+        <f t="shared" si="20"/>
+        <v>1657.46126</v>
       </c>
       <c r="AA12" s="4">
-        <f t="shared" si="24"/>
-        <v>1454.4826304000001</v>
+        <f t="shared" si="20"/>
+        <v>1941.4807178999999</v>
       </c>
       <c r="AB12" s="4">
-        <f t="shared" si="24"/>
-        <v>1588.4828502488001</v>
+        <f t="shared" si="20"/>
+        <v>2222.3729386320001</v>
       </c>
       <c r="AC12" s="4">
-        <f t="shared" si="24"/>
-        <v>1724.3833883152643</v>
+        <f t="shared" si="20"/>
+        <v>2480.0824601733602</v>
       </c>
       <c r="AD12" s="4">
-        <f t="shared" si="24"/>
-        <v>1839.5824029533699</v>
+        <f t="shared" si="20"/>
+        <v>2771.4032615061078</v>
       </c>
       <c r="AE12" s="4">
-        <f t="shared" si="24"/>
-        <v>1922.1495125431375</v>
+        <f t="shared" si="20"/>
+        <v>3104.2489723503741</v>
       </c>
       <c r="AF12" s="4">
-        <f t="shared" si="24"/>
-        <v>1992.4630106191703</v>
+        <f t="shared" si="20"/>
+        <v>3485.3374573927131</v>
       </c>
       <c r="AG12" s="4">
-        <f t="shared" si="24"/>
-        <v>2048.6912295315924</v>
+        <f t="shared" si="20"/>
+        <v>3922.5737887672813</v>
       </c>
       <c r="AH12" s="4">
-        <f t="shared" si="24"/>
-        <v>2106.5821414439652</v>
+        <f t="shared" si="20"/>
+        <v>4425.27212842476</v>
       </c>
       <c r="AI12" s="4">
-        <f t="shared" si="24"/>
-        <v>2166.1874820679741</v>
+        <f t="shared" si="20"/>
+        <v>5004.4204341367522</v>
       </c>
     </row>
     <row r="13" spans="2:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2157,56 +2151,56 @@
         <v>21</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" ref="F13:O13" si="25">F7-F12</f>
+        <f t="shared" ref="F13:O13" si="21">F7-F12</f>
         <v>71.39999999999992</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>54.300000000000011</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>56.100000000000023</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>-5.3000000000000114</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>92.300000000000011</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>37.900000000000034</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>68.5</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>78.80000000000004</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>219.29999999999995</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>88.700000000000045</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" ref="P13" si="26">P7-P12</f>
+        <f t="shared" ref="P13" si="22">P7-P12</f>
         <v>107.20000000000005</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" ref="Q13" si="27">Q7-Q12</f>
-        <v>124.88619999999992</v>
+        <f t="shared" ref="Q13" si="23">Q7-Q12</f>
+        <v>151.80000000000001</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" ref="R13" si="28">R7-R12</f>
-        <v>235.59312999999997</v>
+        <f t="shared" ref="R13" si="24">R7-R12</f>
+        <v>277.22439999999995</v>
       </c>
       <c r="T13" s="8">
         <f>T7-T12</f>
@@ -2229,48 +2223,48 @@
         <v>404.49999999999977</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" ref="Y13:AI13" si="29">Y7-Y12</f>
-        <v>556.37933000000021</v>
+        <f t="shared" ref="Y13:AI13" si="25">Y7-Y12</f>
+        <v>624.92440000000011</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" si="29"/>
-        <v>681.67571500000008</v>
+        <f t="shared" si="25"/>
+        <v>819.13093999999955</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" si="29"/>
-        <v>761.08470359999978</v>
+        <f t="shared" si="25"/>
+        <v>957.30393210000011</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="29"/>
-        <v>838.73796011119998</v>
+        <f t="shared" si="25"/>
+        <v>1079.1187597679996</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="29"/>
-        <v>916.52394280553608</v>
+        <f t="shared" si="25"/>
+        <v>1187.1038882186403</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="29"/>
-        <v>984.7814550098476</v>
+        <f t="shared" si="25"/>
+        <v>1306.2799601417332</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="29"/>
-        <v>1032.3618385294444</v>
+        <f t="shared" si="25"/>
+        <v>1438.4670765328237</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="29"/>
-        <v>1073.0211277175581</v>
+        <f t="shared" si="25"/>
+        <v>1585.2146221946696</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="29"/>
-        <v>1105.6791885761104</v>
+        <f t="shared" si="25"/>
+        <v>1748.2776476838962</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="29"/>
-        <v>1139.3630796915104</v>
+        <f t="shared" si="25"/>
+        <v>1929.6476267323687</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="29"/>
-        <v>1174.1063347346139</v>
+        <f t="shared" si="25"/>
+        <v>2131.5883296860939</v>
       </c>
     </row>
     <row r="14" spans="2:35" x14ac:dyDescent="0.3">
@@ -2311,10 +2305,10 @@
         <v>40.799999999999997</v>
       </c>
       <c r="Q14" s="4">
-        <v>42</v>
+        <v>48.7</v>
       </c>
       <c r="R14" s="4">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="T14" s="4">
         <v>83.6</v>
@@ -2334,48 +2328,48 @@
         <v>148.69999999999999</v>
       </c>
       <c r="Y14" s="4">
-        <f t="shared" ref="Y14:Y16" si="30">SUM(O14:R14)</f>
-        <v>168.4</v>
+        <f t="shared" ref="Y14:Y16" si="26">SUM(O14:R14)</f>
+        <v>184.10000000000002</v>
       </c>
       <c r="Z14" s="4">
         <f>Y14*1.09</f>
-        <v>183.55600000000001</v>
+        <v>200.66900000000004</v>
       </c>
       <c r="AA14" s="4">
         <f>Z14*1.06</f>
-        <v>194.56936000000002</v>
+        <v>212.70914000000005</v>
       </c>
       <c r="AB14" s="4">
         <f>AA14*1.03</f>
-        <v>200.40644080000001</v>
+        <v>219.09041420000005</v>
       </c>
       <c r="AC14" s="4">
-        <f t="shared" ref="AC14:AD16" si="31">AB14*1.03</f>
-        <v>206.41863402400003</v>
+        <f t="shared" ref="AC14:AD16" si="27">AB14*1.03</f>
+        <v>225.66312662600006</v>
       </c>
       <c r="AD14" s="4">
-        <f t="shared" si="31"/>
-        <v>212.61119304472004</v>
+        <f t="shared" si="27"/>
+        <v>232.43302042478007</v>
       </c>
       <c r="AE14" s="4">
         <f>AD14*1.02</f>
-        <v>216.86341690561446</v>
+        <v>237.08168083327567</v>
       </c>
       <c r="AF14" s="4">
-        <f t="shared" ref="AF14:AI14" si="32">AE14*1.02</f>
-        <v>221.20068524372675</v>
+        <f t="shared" ref="AF14:AI14" si="28">AE14*1.02</f>
+        <v>241.82331444994119</v>
       </c>
       <c r="AG14" s="4">
-        <f t="shared" si="32"/>
-        <v>225.62469894860129</v>
+        <f t="shared" si="28"/>
+        <v>246.65978073894001</v>
       </c>
       <c r="AH14" s="4">
-        <f t="shared" si="32"/>
-        <v>230.13719292757332</v>
+        <f t="shared" si="28"/>
+        <v>251.59297635371883</v>
       </c>
       <c r="AI14" s="4">
-        <f t="shared" si="32"/>
-        <v>234.73993678612479</v>
+        <f t="shared" si="28"/>
+        <v>256.62483588079323</v>
       </c>
     </row>
     <row r="15" spans="2:35" x14ac:dyDescent="0.3">
@@ -2416,10 +2410,10 @@
         <v>24.1</v>
       </c>
       <c r="Q15" s="4">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="R15" s="4">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="T15" s="4">
         <v>55.9</v>
@@ -2439,48 +2433,48 @@
         <v>68</v>
       </c>
       <c r="Y15" s="4">
-        <f t="shared" si="30"/>
-        <v>93.4</v>
+        <f t="shared" si="26"/>
+        <v>138.4</v>
       </c>
       <c r="Z15" s="4">
         <f>Z7*0.05</f>
-        <v>100.45466</v>
+        <v>123.82960999999999</v>
       </c>
       <c r="AA15" s="4">
-        <f t="shared" ref="AA15:AI15" si="33">AA7*0.05</f>
-        <v>110.77836669999999</v>
+        <f t="shared" ref="AA15:AI15" si="29">AA7*0.05</f>
+        <v>144.9392325</v>
       </c>
       <c r="AB15" s="4">
-        <f t="shared" si="33"/>
-        <v>121.36104051800001</v>
+        <f t="shared" si="29"/>
+        <v>165.07458492000001</v>
       </c>
       <c r="AC15" s="4">
-        <f t="shared" si="33"/>
-        <v>132.04536655604002</v>
+        <f t="shared" si="29"/>
+        <v>183.35931741960005</v>
       </c>
       <c r="AD15" s="4">
-        <f t="shared" si="33"/>
-        <v>141.21819289816088</v>
+        <f t="shared" si="29"/>
+        <v>203.88416108239207</v>
       </c>
       <c r="AE15" s="4">
-        <f t="shared" si="33"/>
-        <v>147.72556755362911</v>
+        <f t="shared" si="29"/>
+        <v>227.13580244415991</v>
       </c>
       <c r="AF15" s="4">
-        <f t="shared" si="33"/>
-        <v>153.27420691683642</v>
+        <f t="shared" si="29"/>
+        <v>253.52760397936913</v>
       </c>
       <c r="AG15" s="4">
-        <f t="shared" si="33"/>
-        <v>157.71852090538516</v>
+        <f t="shared" si="29"/>
+        <v>283.5425718225589</v>
       </c>
       <c r="AH15" s="4">
-        <f t="shared" si="33"/>
-        <v>162.29726105677378</v>
+        <f t="shared" si="29"/>
+        <v>317.74598775785648</v>
       </c>
       <c r="AI15" s="4">
-        <f t="shared" si="33"/>
-        <v>167.01469084012942</v>
+        <f t="shared" si="29"/>
+        <v>356.80043819114235</v>
       </c>
     </row>
     <row r="16" spans="2:35" x14ac:dyDescent="0.3">
@@ -2521,10 +2515,10 @@
         <v>45.8</v>
       </c>
       <c r="Q16" s="4">
-        <v>47</v>
+        <v>53.1</v>
       </c>
       <c r="R16" s="4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="T16" s="4">
         <v>107.1</v>
@@ -2544,48 +2538,48 @@
         <v>165.10000000000002</v>
       </c>
       <c r="Y16" s="4">
-        <f t="shared" si="30"/>
-        <v>197.7</v>
+        <f t="shared" si="26"/>
+        <v>213.79999999999998</v>
       </c>
       <c r="Z16" s="4">
         <f>Y16*1.1</f>
-        <v>217.47</v>
+        <v>235.18</v>
       </c>
       <c r="AA16" s="4">
         <f>Z16*1.05</f>
-        <v>228.34350000000001</v>
+        <v>246.93900000000002</v>
       </c>
       <c r="AB16" s="4">
         <f>AA16*1.04</f>
-        <v>237.47724000000002</v>
+        <v>256.81656000000004</v>
       </c>
       <c r="AC16" s="4">
-        <f t="shared" si="31"/>
-        <v>244.60155720000003</v>
+        <f t="shared" si="27"/>
+        <v>264.52105680000005</v>
       </c>
       <c r="AD16" s="4">
         <f>AC16*1.02</f>
-        <v>249.49358834400005</v>
+        <v>269.81147793600007</v>
       </c>
       <c r="AE16" s="4">
-        <f t="shared" ref="AE16:AI16" si="34">AD16*1.02</f>
-        <v>254.48346011088006</v>
+        <f t="shared" ref="AE16:AI16" si="30">AD16*1.02</f>
+        <v>275.20770749472007</v>
       </c>
       <c r="AF16" s="4">
-        <f t="shared" si="34"/>
-        <v>259.57312931309764</v>
+        <f t="shared" si="30"/>
+        <v>280.71186164461449</v>
       </c>
       <c r="AG16" s="4">
-        <f t="shared" si="34"/>
-        <v>264.76459189935957</v>
+        <f t="shared" si="30"/>
+        <v>286.32609887750681</v>
       </c>
       <c r="AH16" s="4">
-        <f t="shared" si="34"/>
-        <v>270.05988373734675</v>
+        <f t="shared" si="30"/>
+        <v>292.05262085505694</v>
       </c>
       <c r="AI16" s="4">
-        <f t="shared" si="34"/>
-        <v>275.46108141209368</v>
+        <f t="shared" si="30"/>
+        <v>297.89367327215808</v>
       </c>
     </row>
     <row r="17" spans="2:145" x14ac:dyDescent="0.3">
@@ -2593,56 +2587,56 @@
         <v>25</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" ref="F17:O17" si="35">SUM(F14:F16)</f>
+        <f t="shared" ref="F17:O17" si="31">SUM(F14:F16)</f>
         <v>111.99999999999999</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>117.9</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>110.8</v>
       </c>
       <c r="I17" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>98.5</v>
       </c>
       <c r="J17" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>79.5</v>
       </c>
       <c r="K17" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>87.1</v>
       </c>
       <c r="L17" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>91.699999999999989</v>
       </c>
       <c r="M17" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>88.4</v>
       </c>
       <c r="N17" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>114.6</v>
       </c>
       <c r="O17" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>107.80000000000001</v>
       </c>
       <c r="P17" s="4">
-        <f t="shared" ref="P17" si="36">SUM(P14:P16)</f>
+        <f t="shared" ref="P17" si="32">SUM(P14:P16)</f>
         <v>110.7</v>
       </c>
       <c r="Q17" s="4">
-        <f t="shared" ref="Q17" si="37">SUM(Q14:Q16)</f>
-        <v>112</v>
+        <f t="shared" ref="Q17" si="33">SUM(Q14:Q16)</f>
+        <v>143.80000000000001</v>
       </c>
       <c r="R17" s="4">
-        <f t="shared" ref="R17" si="38">SUM(R14:R16)</f>
-        <v>129</v>
+        <f t="shared" ref="R17" si="34">SUM(R14:R16)</f>
+        <v>174</v>
       </c>
       <c r="T17" s="4">
         <f>SUM(T14:T16)</f>
@@ -2665,48 +2659,48 @@
         <v>381.8</v>
       </c>
       <c r="Y17" s="4">
-        <f t="shared" ref="Y17:AI17" si="39">SUM(Y14:Y16)</f>
-        <v>459.5</v>
+        <f t="shared" ref="Y17:AI17" si="35">SUM(Y14:Y16)</f>
+        <v>536.29999999999995</v>
       </c>
       <c r="Z17" s="4">
-        <f t="shared" si="39"/>
-        <v>501.48066000000006</v>
+        <f t="shared" si="35"/>
+        <v>559.67861000000005</v>
       </c>
       <c r="AA17" s="4">
-        <f t="shared" si="39"/>
-        <v>533.69122670000002</v>
+        <f t="shared" si="35"/>
+        <v>604.58737250000013</v>
       </c>
       <c r="AB17" s="4">
-        <f t="shared" si="39"/>
-        <v>559.24472131800007</v>
+        <f t="shared" si="35"/>
+        <v>640.98155912000016</v>
       </c>
       <c r="AC17" s="4">
-        <f t="shared" si="39"/>
-        <v>583.06555778004008</v>
+        <f t="shared" si="35"/>
+        <v>673.54350084560019</v>
       </c>
       <c r="AD17" s="4">
-        <f t="shared" si="39"/>
-        <v>603.32297428688094</v>
+        <f t="shared" si="35"/>
+        <v>706.12865944317218</v>
       </c>
       <c r="AE17" s="4">
-        <f t="shared" si="39"/>
-        <v>619.07244457012359</v>
+        <f t="shared" si="35"/>
+        <v>739.4251907721557</v>
       </c>
       <c r="AF17" s="4">
-        <f t="shared" si="39"/>
-        <v>634.04802147366081</v>
+        <f t="shared" si="35"/>
+        <v>776.06278007392484</v>
       </c>
       <c r="AG17" s="4">
-        <f t="shared" si="39"/>
-        <v>648.10781175334603</v>
+        <f t="shared" si="35"/>
+        <v>816.52845143900572</v>
       </c>
       <c r="AH17" s="4">
-        <f t="shared" si="39"/>
-        <v>662.49433772169391</v>
+        <f t="shared" si="35"/>
+        <v>861.39158496663219</v>
       </c>
       <c r="AI17" s="4">
-        <f t="shared" si="39"/>
-        <v>677.21570903834788</v>
+        <f t="shared" si="35"/>
+        <v>911.31894734409366</v>
       </c>
     </row>
     <row r="18" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2714,56 +2708,56 @@
         <v>26</v>
       </c>
       <c r="F18" s="8">
-        <f t="shared" ref="F18:O18" si="40">F13-F17</f>
+        <f t="shared" ref="F18:O18" si="36">F13-F17</f>
         <v>-40.600000000000065</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>-63.599999999999994</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>-54.699999999999974</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>-103.80000000000001</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>12.800000000000011</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>-49.19999999999996</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>-23.199999999999989</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>-9.5999999999999659</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>104.69999999999996</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>-19.099999999999966</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" ref="P18" si="41">P13-P17</f>
+        <f t="shared" ref="P18" si="37">P13-P17</f>
         <v>-3.4999999999999574</v>
       </c>
       <c r="Q18" s="8">
-        <f t="shared" ref="Q18" si="42">Q13-Q17</f>
-        <v>12.886199999999917</v>
+        <f t="shared" ref="Q18" si="38">Q13-Q17</f>
+        <v>8</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" ref="R18" si="43">R13-R17</f>
-        <v>106.59312999999997</v>
+        <f t="shared" ref="R18" si="39">R13-R17</f>
+        <v>103.22439999999995</v>
       </c>
       <c r="T18" s="8">
         <f>T13-T17</f>
@@ -2786,48 +2780,48 @@
         <v>22.699999999999761</v>
       </c>
       <c r="Y18" s="8">
-        <f t="shared" ref="Y18:AI18" si="44">Y13-Y17</f>
-        <v>96.879330000000209</v>
+        <f t="shared" ref="Y18:AI18" si="40">Y13-Y17</f>
+        <v>88.624400000000151</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" si="44"/>
-        <v>180.19505500000002</v>
+        <f t="shared" si="40"/>
+        <v>259.45232999999951</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" si="44"/>
-        <v>227.39347689999977</v>
+        <f t="shared" si="40"/>
+        <v>352.71655959999998</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" si="44"/>
-        <v>279.49323879319991</v>
+        <f t="shared" si="40"/>
+        <v>438.13720064799941</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" si="44"/>
-        <v>333.458385025496</v>
+        <f t="shared" si="40"/>
+        <v>513.56038737304016</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="44"/>
-        <v>381.45848072296667</v>
+        <f t="shared" si="40"/>
+        <v>600.15130069856104</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="44"/>
-        <v>413.28939395932082</v>
+        <f t="shared" si="40"/>
+        <v>699.04188576066804</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" si="44"/>
-        <v>438.97310624389729</v>
+        <f t="shared" si="40"/>
+        <v>809.15184212074473</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" si="44"/>
-        <v>457.57137682276436</v>
+        <f t="shared" si="40"/>
+        <v>931.74919624489053</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="44"/>
-        <v>476.86874196981648</v>
+        <f t="shared" si="40"/>
+        <v>1068.2560417657364</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="44"/>
-        <v>496.89062569626606</v>
+        <f t="shared" si="40"/>
+        <v>1220.2693823420002</v>
       </c>
     </row>
     <row r="19" spans="2:145" x14ac:dyDescent="0.3">
@@ -2868,7 +2862,7 @@
         <v>-6.6</v>
       </c>
       <c r="Q19" s="4">
-        <v>-10</v>
+        <v>-5.3</v>
       </c>
       <c r="R19" s="4">
         <v>-10</v>
@@ -2891,48 +2885,48 @@
         <v>-25.299999999999997</v>
       </c>
       <c r="Y19" s="4">
-        <f t="shared" ref="Y19:Y23" si="45">SUM(O19:R19)</f>
-        <v>-35.200000000000003</v>
+        <f t="shared" ref="Y19:Y23" si="41">SUM(O19:R19)</f>
+        <v>-30.5</v>
       </c>
       <c r="Z19" s="4">
-        <f t="shared" ref="Z19:AI19" si="46">Y19*1.02</f>
-        <v>-35.904000000000003</v>
+        <f t="shared" ref="Z19:AI19" si="42">Y19*1.02</f>
+        <v>-31.11</v>
       </c>
       <c r="AA19" s="4">
-        <f t="shared" si="46"/>
-        <v>-36.622080000000004</v>
+        <f t="shared" si="42"/>
+        <v>-31.732199999999999</v>
       </c>
       <c r="AB19" s="4">
-        <f t="shared" si="46"/>
-        <v>-37.354521600000005</v>
+        <f t="shared" si="42"/>
+        <v>-32.366844</v>
       </c>
       <c r="AC19" s="4">
-        <f t="shared" si="46"/>
-        <v>-38.101612032000006</v>
+        <f t="shared" si="42"/>
+        <v>-33.014180879999998</v>
       </c>
       <c r="AD19" s="4">
-        <f t="shared" si="46"/>
-        <v>-38.863644272640009</v>
+        <f t="shared" si="42"/>
+        <v>-33.674464497599999</v>
       </c>
       <c r="AE19" s="4">
-        <f t="shared" si="46"/>
-        <v>-39.640917158092812</v>
+        <f t="shared" si="42"/>
+        <v>-34.347953787552001</v>
       </c>
       <c r="AF19" s="4">
-        <f t="shared" si="46"/>
-        <v>-40.433735501254667</v>
+        <f t="shared" si="42"/>
+        <v>-35.034912863303042</v>
       </c>
       <c r="AG19" s="4">
-        <f t="shared" si="46"/>
-        <v>-41.242410211279761</v>
+        <f t="shared" si="42"/>
+        <v>-35.735611120569104</v>
       </c>
       <c r="AH19" s="4">
-        <f t="shared" si="46"/>
-        <v>-42.067258415505357</v>
+        <f t="shared" si="42"/>
+        <v>-36.450323342980489</v>
       </c>
       <c r="AI19" s="4">
-        <f t="shared" si="46"/>
-        <v>-42.908603583815463</v>
+        <f t="shared" si="42"/>
+        <v>-37.179329809840098</v>
       </c>
     </row>
     <row r="20" spans="2:145" x14ac:dyDescent="0.3">
@@ -2973,7 +2967,7 @@
         <v>14.4</v>
       </c>
       <c r="Q20" s="4">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="R20" s="4">
         <v>15</v>
@@ -2997,48 +2991,48 @@
         <v>62.7</v>
       </c>
       <c r="Y20" s="4">
-        <f t="shared" si="45"/>
-        <v>58.8</v>
+        <f t="shared" si="41"/>
+        <v>58.2</v>
       </c>
       <c r="Z20" s="4">
-        <f t="shared" ref="Z20:AI20" si="47">Y20*1.02</f>
-        <v>59.975999999999999</v>
+        <f t="shared" ref="Z20:AI20" si="43">Y20*1.02</f>
+        <v>59.364000000000004</v>
       </c>
       <c r="AA20" s="4">
-        <f t="shared" si="47"/>
-        <v>61.175519999999999</v>
+        <f t="shared" si="43"/>
+        <v>60.551280000000006</v>
       </c>
       <c r="AB20" s="4">
-        <f t="shared" si="47"/>
-        <v>62.399030400000001</v>
+        <f t="shared" si="43"/>
+        <v>61.762305600000005</v>
       </c>
       <c r="AC20" s="4">
-        <f t="shared" si="47"/>
-        <v>63.647011008</v>
+        <f t="shared" si="43"/>
+        <v>62.997551712000003</v>
       </c>
       <c r="AD20" s="4">
-        <f t="shared" si="47"/>
-        <v>64.919951228160002</v>
+        <f t="shared" si="43"/>
+        <v>64.257502746240007</v>
       </c>
       <c r="AE20" s="4">
-        <f t="shared" si="47"/>
-        <v>66.218350252723198</v>
+        <f t="shared" si="43"/>
+        <v>65.542652801164806</v>
       </c>
       <c r="AF20" s="4">
-        <f t="shared" si="47"/>
-        <v>67.542717257777667</v>
+        <f t="shared" si="43"/>
+        <v>66.853505857188097</v>
       </c>
       <c r="AG20" s="4">
-        <f t="shared" si="47"/>
-        <v>68.893571602933221</v>
+        <f t="shared" si="43"/>
+        <v>68.190575974331864</v>
       </c>
       <c r="AH20" s="4">
-        <f t="shared" si="47"/>
-        <v>70.27144303499189</v>
+        <f t="shared" si="43"/>
+        <v>69.554387493818496</v>
       </c>
       <c r="AI20" s="4">
-        <f t="shared" si="47"/>
-        <v>71.676871895691733</v>
+        <f t="shared" si="43"/>
+        <v>70.945475243694872</v>
       </c>
     </row>
     <row r="21" spans="2:145" x14ac:dyDescent="0.3">
@@ -3079,7 +3073,7 @@
         <v>-2.4</v>
       </c>
       <c r="Q21" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R21" s="4">
         <v>0</v>
@@ -3102,8 +3096,8 @@
         <v>-15.799999999999999</v>
       </c>
       <c r="Y21" s="4">
-        <f t="shared" si="45"/>
-        <v>-4.4000000000000004</v>
+        <f t="shared" si="41"/>
+        <v>15.6</v>
       </c>
       <c r="Z21" s="4">
         <v>0</v>
@@ -3170,7 +3164,7 @@
         <v>32.299999999999997</v>
       </c>
       <c r="Q22" s="4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R22" s="4">
         <v>0</v>
@@ -3193,8 +3187,8 @@
         <v>27.2</v>
       </c>
       <c r="Y22" s="4">
-        <f t="shared" si="45"/>
-        <v>32.299999999999997</v>
+        <f t="shared" si="41"/>
+        <v>33.699999999999996</v>
       </c>
       <c r="Z22" s="4">
         <v>0</v>
@@ -3290,7 +3284,7 @@
         <v>0.70000000000000007</v>
       </c>
       <c r="Y23" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="Z23" s="4">
@@ -3329,120 +3323,120 @@
         <v>32</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" ref="F24:O24" si="48">SUM(F19:F23)</f>
+        <f t="shared" ref="F24:O24" si="44">SUM(F19:F23)</f>
         <v>10.1</v>
       </c>
       <c r="G24" s="4">
+        <f t="shared" si="44"/>
+        <v>10.9</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" si="44"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="44"/>
+        <v>63.7</v>
+      </c>
+      <c r="J24" s="4">
+        <f t="shared" si="44"/>
+        <v>8</v>
+      </c>
+      <c r="K24" s="4">
+        <f t="shared" si="44"/>
+        <v>7.9999999999999991</v>
+      </c>
+      <c r="L24" s="4">
+        <f t="shared" si="44"/>
+        <v>37.300000000000004</v>
+      </c>
+      <c r="M24" s="4">
+        <f t="shared" si="44"/>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="N24" s="4">
+        <f t="shared" si="44"/>
+        <v>-0.69999999999999962</v>
+      </c>
+      <c r="O24" s="4">
+        <f t="shared" si="44"/>
+        <v>3.9000000000000008</v>
+      </c>
+      <c r="P24" s="4">
+        <f t="shared" ref="P24" si="45">SUM(P19:P23)</f>
+        <v>37.599999999999994</v>
+      </c>
+      <c r="Q24" s="4">
+        <f t="shared" ref="Q24" si="46">SUM(Q19:Q23)</f>
+        <v>30.5</v>
+      </c>
+      <c r="R24" s="4">
+        <f t="shared" ref="R24" si="47">SUM(R19:R23)</f>
+        <v>5</v>
+      </c>
+      <c r="T24" s="4">
+        <f t="shared" ref="T24:Y24" si="48">SUM(T19:T23)</f>
+        <v>98</v>
+      </c>
+      <c r="U24" s="4">
         <f t="shared" si="48"/>
-        <v>10.9</v>
-      </c>
-      <c r="H24" s="4">
+        <v>77.7</v>
+      </c>
+      <c r="V24" s="4">
         <f t="shared" si="48"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="I24" s="4">
+        <v>53</v>
+      </c>
+      <c r="W24" s="4">
         <f t="shared" si="48"/>
-        <v>63.7</v>
-      </c>
-      <c r="J24" s="4">
+        <v>97</v>
+      </c>
+      <c r="X24" s="4">
         <f t="shared" si="48"/>
-        <v>8</v>
-      </c>
-      <c r="K24" s="4">
+        <v>49.500000000000014</v>
+      </c>
+      <c r="Y24" s="4">
         <f t="shared" si="48"/>
-        <v>7.9999999999999991</v>
-      </c>
-      <c r="L24" s="4">
-        <f t="shared" si="48"/>
-        <v>37.300000000000004</v>
-      </c>
-      <c r="M24" s="4">
-        <f t="shared" si="48"/>
-        <v>4.9000000000000012</v>
-      </c>
-      <c r="N24" s="4">
-        <f t="shared" si="48"/>
-        <v>-0.69999999999999962</v>
-      </c>
-      <c r="O24" s="4">
-        <f t="shared" si="48"/>
-        <v>3.9000000000000008</v>
-      </c>
-      <c r="P24" s="4">
-        <f t="shared" ref="P24" si="49">SUM(P19:P23)</f>
-        <v>37.599999999999994</v>
-      </c>
-      <c r="Q24" s="4">
-        <f t="shared" ref="Q24" si="50">SUM(Q19:Q23)</f>
-        <v>5</v>
-      </c>
-      <c r="R24" s="4">
-        <f t="shared" ref="R24" si="51">SUM(R19:R23)</f>
-        <v>5</v>
-      </c>
-      <c r="T24" s="4">
-        <f t="shared" ref="T24:Y24" si="52">SUM(T19:T23)</f>
-        <v>98</v>
-      </c>
-      <c r="U24" s="4">
-        <f t="shared" si="52"/>
-        <v>77.7</v>
-      </c>
-      <c r="V24" s="4">
-        <f t="shared" si="52"/>
-        <v>53</v>
-      </c>
-      <c r="W24" s="4">
-        <f t="shared" si="52"/>
-        <v>97</v>
-      </c>
-      <c r="X24" s="4">
-        <f t="shared" si="52"/>
-        <v>49.500000000000014</v>
-      </c>
-      <c r="Y24" s="4">
-        <f t="shared" si="52"/>
-        <v>51.499999999999993</v>
+        <v>77</v>
       </c>
       <c r="Z24" s="4">
-        <f t="shared" ref="Z24:AI24" si="53">SUM(Z19:Z23)</f>
-        <v>24.071999999999996</v>
+        <f t="shared" ref="Z24:AI24" si="49">SUM(Z19:Z23)</f>
+        <v>28.254000000000005</v>
       </c>
       <c r="AA24" s="4">
-        <f t="shared" si="53"/>
-        <v>24.553439999999995</v>
+        <f t="shared" si="49"/>
+        <v>28.819080000000007</v>
       </c>
       <c r="AB24" s="4">
-        <f t="shared" si="53"/>
-        <v>25.044508799999996</v>
+        <f t="shared" si="49"/>
+        <v>29.395461600000004</v>
       </c>
       <c r="AC24" s="4">
-        <f t="shared" si="53"/>
-        <v>25.545398975999994</v>
+        <f t="shared" si="49"/>
+        <v>29.983370832000006</v>
       </c>
       <c r="AD24" s="4">
-        <f t="shared" si="53"/>
-        <v>26.056306955519993</v>
+        <f t="shared" si="49"/>
+        <v>30.583038248640008</v>
       </c>
       <c r="AE24" s="4">
-        <f t="shared" si="53"/>
-        <v>26.577433094630386</v>
+        <f t="shared" si="49"/>
+        <v>31.194699013612805</v>
       </c>
       <c r="AF24" s="4">
-        <f t="shared" si="53"/>
-        <v>27.108981756523001</v>
+        <f t="shared" si="49"/>
+        <v>31.818592993885055</v>
       </c>
       <c r="AG24" s="4">
-        <f t="shared" si="53"/>
-        <v>27.65116139165346</v>
+        <f t="shared" si="49"/>
+        <v>32.45496485376276</v>
       </c>
       <c r="AH24" s="4">
-        <f t="shared" si="53"/>
-        <v>28.204184619486533</v>
+        <f t="shared" si="49"/>
+        <v>33.104064150838006</v>
       </c>
       <c r="AI24" s="4">
-        <f t="shared" si="53"/>
-        <v>28.76826831187627</v>
+        <f t="shared" si="49"/>
+        <v>33.766145433854774</v>
       </c>
     </row>
     <row r="25" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3450,120 +3444,120 @@
         <v>33</v>
       </c>
       <c r="F25" s="8">
-        <f t="shared" ref="F25:O25" si="54">F18-F24</f>
+        <f t="shared" ref="F25:O25" si="50">F18-F24</f>
         <v>-50.700000000000067</v>
       </c>
       <c r="G25" s="8">
+        <f t="shared" si="50"/>
+        <v>-74.5</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="50"/>
+        <v>-69.099999999999966</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="50"/>
+        <v>-167.5</v>
+      </c>
+      <c r="J25" s="8">
+        <f t="shared" si="50"/>
+        <v>4.8000000000000114</v>
+      </c>
+      <c r="K25" s="8">
+        <f t="shared" si="50"/>
+        <v>-57.19999999999996</v>
+      </c>
+      <c r="L25" s="8">
+        <f t="shared" si="50"/>
+        <v>-60.499999999999993</v>
+      </c>
+      <c r="M25" s="8">
+        <f t="shared" si="50"/>
+        <v>-14.499999999999968</v>
+      </c>
+      <c r="N25" s="8">
+        <f t="shared" si="50"/>
+        <v>105.39999999999996</v>
+      </c>
+      <c r="O25" s="8">
+        <f t="shared" si="50"/>
+        <v>-22.999999999999968</v>
+      </c>
+      <c r="P25" s="8">
+        <f t="shared" ref="P25" si="51">P18-P24</f>
+        <v>-41.099999999999952</v>
+      </c>
+      <c r="Q25" s="8">
+        <f t="shared" ref="Q25" si="52">Q18-Q24</f>
+        <v>-22.5</v>
+      </c>
+      <c r="R25" s="8">
+        <f t="shared" ref="R25" si="53">R18-R24</f>
+        <v>98.224399999999946</v>
+      </c>
+      <c r="T25" s="8">
+        <f t="shared" ref="T25:Y25" si="54">T18-T24</f>
+        <v>-178.79999999999993</v>
+      </c>
+      <c r="U25" s="8">
         <f t="shared" si="54"/>
-        <v>-74.5</v>
-      </c>
-      <c r="H25" s="8">
+        <v>-192.2000000000001</v>
+      </c>
+      <c r="V25" s="8">
         <f t="shared" si="54"/>
-        <v>-69.099999999999966</v>
-      </c>
-      <c r="I25" s="8">
+        <v>-313.89999999999981</v>
+      </c>
+      <c r="W25" s="8">
         <f t="shared" si="54"/>
-        <v>-167.5</v>
-      </c>
-      <c r="J25" s="8">
+        <v>-306.29999999999995</v>
+      </c>
+      <c r="X25" s="8">
         <f t="shared" si="54"/>
-        <v>4.8000000000000114</v>
-      </c>
-      <c r="K25" s="8">
+        <v>-26.800000000000253</v>
+      </c>
+      <c r="Y25" s="8">
         <f t="shared" si="54"/>
-        <v>-57.19999999999996</v>
-      </c>
-      <c r="L25" s="8">
-        <f t="shared" si="54"/>
-        <v>-60.499999999999993</v>
-      </c>
-      <c r="M25" s="8">
-        <f t="shared" si="54"/>
-        <v>-14.499999999999968</v>
-      </c>
-      <c r="N25" s="8">
-        <f t="shared" si="54"/>
-        <v>105.39999999999996</v>
-      </c>
-      <c r="O25" s="8">
-        <f t="shared" si="54"/>
-        <v>-22.999999999999968</v>
-      </c>
-      <c r="P25" s="8">
-        <f t="shared" ref="P25" si="55">P18-P24</f>
-        <v>-41.099999999999952</v>
-      </c>
-      <c r="Q25" s="8">
-        <f t="shared" ref="Q25" si="56">Q18-Q24</f>
-        <v>7.8861999999999171</v>
-      </c>
-      <c r="R25" s="8">
-        <f t="shared" ref="R25" si="57">R18-R24</f>
-        <v>101.59312999999997</v>
-      </c>
-      <c r="T25" s="8">
-        <f t="shared" ref="T25:Y25" si="58">T18-T24</f>
-        <v>-178.79999999999993</v>
-      </c>
-      <c r="U25" s="8">
-        <f t="shared" si="58"/>
-        <v>-192.2000000000001</v>
-      </c>
-      <c r="V25" s="8">
-        <f t="shared" si="58"/>
-        <v>-313.89999999999981</v>
-      </c>
-      <c r="W25" s="8">
-        <f t="shared" si="58"/>
-        <v>-306.29999999999995</v>
-      </c>
-      <c r="X25" s="8">
-        <f t="shared" si="58"/>
-        <v>-26.800000000000253</v>
-      </c>
-      <c r="Y25" s="8">
-        <f t="shared" si="58"/>
-        <v>45.379330000000216</v>
+        <v>11.624400000000151</v>
       </c>
       <c r="Z25" s="8">
-        <f t="shared" ref="Z25:AI25" si="59">Z18-Z24</f>
-        <v>156.12305500000002</v>
+        <f t="shared" ref="Z25:AI25" si="55">Z18-Z24</f>
+        <v>231.19832999999949</v>
       </c>
       <c r="AA25" s="8">
-        <f t="shared" si="59"/>
-        <v>202.84003689999977</v>
+        <f t="shared" si="55"/>
+        <v>323.8974796</v>
       </c>
       <c r="AB25" s="8">
-        <f t="shared" si="59"/>
-        <v>254.44872999319992</v>
+        <f t="shared" si="55"/>
+        <v>408.74173904799943</v>
       </c>
       <c r="AC25" s="8">
-        <f t="shared" si="59"/>
-        <v>307.912986049496</v>
+        <f t="shared" si="55"/>
+        <v>483.57701654104017</v>
       </c>
       <c r="AD25" s="8">
-        <f t="shared" si="59"/>
-        <v>355.4021737674467</v>
+        <f t="shared" si="55"/>
+        <v>569.56826244992101</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" si="59"/>
-        <v>386.71196086469041</v>
+        <f t="shared" si="55"/>
+        <v>667.84718674705528</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="59"/>
-        <v>411.86412448737428</v>
+        <f t="shared" si="55"/>
+        <v>777.33324912685964</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="59"/>
-        <v>429.92021543111093</v>
+        <f t="shared" si="55"/>
+        <v>899.29423139112782</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="59"/>
-        <v>448.66455735032997</v>
+        <f t="shared" si="55"/>
+        <v>1035.1519776148984</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" si="59"/>
-        <v>468.12235738438977</v>
+        <f t="shared" si="55"/>
+        <v>1186.5032369081455</v>
       </c>
     </row>
     <row r="26" spans="2:145" x14ac:dyDescent="0.3">
@@ -3604,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="Q26" s="4">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R26" s="4">
         <v>0</v>
@@ -3627,48 +3621,48 @@
         <v>0.9</v>
       </c>
       <c r="Y26" s="4">
-        <f t="shared" ref="Y26:Y27" si="60">SUM(O26:R26)</f>
-        <v>1.4</v>
+        <f t="shared" ref="Y26:Y27" si="56">SUM(O26:R26)</f>
+        <v>1.7</v>
       </c>
       <c r="Z26" s="4">
-        <f t="shared" ref="Z26:AI26" si="61">Z25*0.05</f>
-        <v>7.8061527500000016</v>
+        <f t="shared" ref="Z26:AI26" si="57">Z25*0.05</f>
+        <v>11.559916499999975</v>
       </c>
       <c r="AA26" s="4">
-        <f t="shared" si="61"/>
-        <v>10.142001844999989</v>
+        <f t="shared" si="57"/>
+        <v>16.194873980000001</v>
       </c>
       <c r="AB26" s="4">
-        <f t="shared" si="61"/>
-        <v>12.722436499659997</v>
+        <f t="shared" si="57"/>
+        <v>20.437086952399973</v>
       </c>
       <c r="AC26" s="4">
-        <f t="shared" si="61"/>
-        <v>15.395649302474801</v>
+        <f t="shared" si="57"/>
+        <v>24.17885082705201</v>
       </c>
       <c r="AD26" s="4">
-        <f t="shared" si="61"/>
-        <v>17.770108688372336</v>
+        <f t="shared" si="57"/>
+        <v>28.47841312249605</v>
       </c>
       <c r="AE26" s="4">
-        <f t="shared" si="61"/>
-        <v>19.335598043234523</v>
+        <f t="shared" si="57"/>
+        <v>33.392359337352765</v>
       </c>
       <c r="AF26" s="4">
-        <f t="shared" si="61"/>
-        <v>20.593206224368714</v>
+        <f t="shared" si="57"/>
+        <v>38.866662456342986</v>
       </c>
       <c r="AG26" s="4">
-        <f t="shared" si="61"/>
-        <v>21.496010771555547</v>
+        <f t="shared" si="57"/>
+        <v>44.964711569556393</v>
       </c>
       <c r="AH26" s="4">
-        <f t="shared" si="61"/>
-        <v>22.4332278675165</v>
+        <f t="shared" si="57"/>
+        <v>51.757598880744922</v>
       </c>
       <c r="AI26" s="4">
-        <f t="shared" si="61"/>
-        <v>23.406117869219489</v>
+        <f t="shared" si="57"/>
+        <v>59.32516184540728</v>
       </c>
     </row>
     <row r="27" spans="2:145" x14ac:dyDescent="0.3">
@@ -3709,7 +3703,7 @@
         <v>0.4</v>
       </c>
       <c r="Q27" s="4">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="R27" s="4">
         <v>0</v>
@@ -3733,48 +3727,48 @@
         <v>2.1</v>
       </c>
       <c r="Y27" s="4">
-        <f t="shared" si="60"/>
-        <v>0.8</v>
+        <f t="shared" si="56"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="Z27" s="4">
-        <f t="shared" ref="Z27:AI27" si="62">Z25*0.02</f>
-        <v>3.1224611000000007</v>
+        <f t="shared" ref="Z27:AI27" si="58">Z25*0.02</f>
+        <v>4.6239665999999895</v>
       </c>
       <c r="AA27" s="4">
-        <f t="shared" si="62"/>
-        <v>4.0568007379999953</v>
+        <f t="shared" si="58"/>
+        <v>6.4779495919999999</v>
       </c>
       <c r="AB27" s="4">
-        <f t="shared" si="62"/>
-        <v>5.0889745998639988</v>
+        <f t="shared" si="58"/>
+        <v>8.1748347809599888</v>
       </c>
       <c r="AC27" s="4">
-        <f t="shared" si="62"/>
-        <v>6.1582597209899204</v>
+        <f t="shared" si="58"/>
+        <v>9.6715403308208039</v>
       </c>
       <c r="AD27" s="4">
-        <f t="shared" si="62"/>
-        <v>7.1080434753489339</v>
+        <f t="shared" si="58"/>
+        <v>11.391365248998421</v>
       </c>
       <c r="AE27" s="4">
-        <f t="shared" si="62"/>
-        <v>7.7342392172938084</v>
+        <f t="shared" si="58"/>
+        <v>13.356943734941106</v>
       </c>
       <c r="AF27" s="4">
-        <f t="shared" si="62"/>
-        <v>8.2372824897474857</v>
+        <f t="shared" si="58"/>
+        <v>15.546664982537193</v>
       </c>
       <c r="AG27" s="4">
-        <f t="shared" si="62"/>
-        <v>8.5984043086222197</v>
+        <f t="shared" si="58"/>
+        <v>17.985884627822557</v>
       </c>
       <c r="AH27" s="4">
-        <f t="shared" si="62"/>
-        <v>8.9732911470066004</v>
+        <f t="shared" si="58"/>
+        <v>20.70303955229797</v>
       </c>
       <c r="AI27" s="4">
-        <f t="shared" si="62"/>
-        <v>9.3624471476877957</v>
+        <f t="shared" si="58"/>
+        <v>23.730064738162909</v>
       </c>
     </row>
     <row r="28" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3782,560 +3776,560 @@
         <v>36</v>
       </c>
       <c r="F28" s="8">
-        <f t="shared" ref="F28:O28" si="63">F25-F26-F27</f>
+        <f t="shared" ref="F28:O28" si="59">F25-F26-F27</f>
         <v>-47.100000000000065</v>
       </c>
       <c r="G28" s="8">
+        <f t="shared" si="59"/>
+        <v>-71.399999999999991</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="59"/>
+        <v>-66.299999999999969</v>
+      </c>
+      <c r="I28" s="8">
+        <f t="shared" si="59"/>
+        <v>-169</v>
+      </c>
+      <c r="J28" s="8">
+        <f t="shared" si="59"/>
+        <v>4.4000000000000119</v>
+      </c>
+      <c r="K28" s="8">
+        <f t="shared" si="59"/>
+        <v>-57.69999999999996</v>
+      </c>
+      <c r="L28" s="8">
+        <f t="shared" si="59"/>
+        <v>-61.999999999999993</v>
+      </c>
+      <c r="M28" s="8">
+        <f t="shared" si="59"/>
+        <v>-14.699999999999967</v>
+      </c>
+      <c r="N28" s="8">
+        <f t="shared" si="59"/>
+        <v>104.59999999999995</v>
+      </c>
+      <c r="O28" s="8">
+        <f t="shared" si="59"/>
+        <v>-23.799999999999965</v>
+      </c>
+      <c r="P28" s="8">
+        <f t="shared" ref="P28" si="60">P25-P26-P27</f>
+        <v>-42.49999999999995</v>
+      </c>
+      <c r="Q28" s="8">
+        <f t="shared" ref="Q28" si="61">Q25-Q26-Q27</f>
+        <v>-22.7</v>
+      </c>
+      <c r="R28" s="8">
+        <f t="shared" ref="R28" si="62">R25-R26-R27</f>
+        <v>98.224399999999946</v>
+      </c>
+      <c r="T28" s="8">
+        <f t="shared" ref="T28:Y28" si="63">T25-T26-T27</f>
+        <v>-157.59999999999994</v>
+      </c>
+      <c r="U28" s="8">
         <f t="shared" si="63"/>
-        <v>-71.399999999999991</v>
-      </c>
-      <c r="H28" s="8">
+        <v>-164.3000000000001</v>
+      </c>
+      <c r="V28" s="8">
         <f t="shared" si="63"/>
-        <v>-66.299999999999969</v>
-      </c>
-      <c r="I28" s="8">
+        <v>-301.29999999999984</v>
+      </c>
+      <c r="W28" s="8">
         <f t="shared" si="63"/>
-        <v>-169</v>
-      </c>
-      <c r="J28" s="8">
+        <v>-302.29999999999995</v>
+      </c>
+      <c r="X28" s="8">
         <f t="shared" si="63"/>
-        <v>4.4000000000000119</v>
-      </c>
-      <c r="K28" s="8">
+        <v>-29.800000000000253</v>
+      </c>
+      <c r="Y28" s="8">
         <f t="shared" si="63"/>
-        <v>-57.69999999999996</v>
-      </c>
-      <c r="L28" s="8">
-        <f t="shared" si="63"/>
-        <v>-61.999999999999993</v>
-      </c>
-      <c r="M28" s="8">
-        <f t="shared" si="63"/>
-        <v>-14.699999999999967</v>
-      </c>
-      <c r="N28" s="8">
-        <f t="shared" si="63"/>
-        <v>104.59999999999995</v>
-      </c>
-      <c r="O28" s="8">
-        <f t="shared" si="63"/>
-        <v>-23.799999999999965</v>
-      </c>
-      <c r="P28" s="8">
-        <f t="shared" ref="P28" si="64">P25-P26-P27</f>
-        <v>-42.49999999999995</v>
-      </c>
-      <c r="Q28" s="8">
-        <f t="shared" ref="Q28" si="65">Q25-Q26-Q27</f>
-        <v>7.8861999999999171</v>
-      </c>
-      <c r="R28" s="8">
-        <f t="shared" ref="R28" si="66">R25-R26-R27</f>
-        <v>101.59312999999997</v>
-      </c>
-      <c r="T28" s="8">
-        <f t="shared" ref="T28:Y28" si="67">T25-T26-T27</f>
-        <v>-157.59999999999994</v>
-      </c>
-      <c r="U28" s="8">
-        <f t="shared" si="67"/>
-        <v>-164.3000000000001</v>
-      </c>
-      <c r="V28" s="8">
-        <f t="shared" si="67"/>
-        <v>-301.29999999999984</v>
-      </c>
-      <c r="W28" s="8">
-        <f t="shared" si="67"/>
-        <v>-302.29999999999995</v>
-      </c>
-      <c r="X28" s="8">
-        <f t="shared" si="67"/>
-        <v>-29.800000000000253</v>
-      </c>
-      <c r="Y28" s="8">
-        <f t="shared" si="67"/>
-        <v>43.17933000000022</v>
+        <v>9.224400000000152</v>
       </c>
       <c r="Z28" s="8">
-        <f t="shared" ref="Z28:AI28" si="68">Z25-Z26-Z27</f>
-        <v>145.19444115000002</v>
+        <f t="shared" ref="Z28:AI28" si="64">Z25-Z26-Z27</f>
+        <v>215.01444689999951</v>
       </c>
       <c r="AA28" s="8">
-        <f t="shared" si="68"/>
-        <v>188.6412343169998</v>
+        <f t="shared" si="64"/>
+        <v>301.22465602799997</v>
       </c>
       <c r="AB28" s="8">
-        <f t="shared" si="68"/>
-        <v>236.63731889367591</v>
+        <f t="shared" si="64"/>
+        <v>380.12981731463947</v>
       </c>
       <c r="AC28" s="8">
-        <f t="shared" si="68"/>
-        <v>286.35907702603129</v>
+        <f t="shared" si="64"/>
+        <v>449.72662538316735</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="68"/>
-        <v>330.52402160372543</v>
+        <f t="shared" si="64"/>
+        <v>529.69848407842653</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" si="68"/>
-        <v>359.64212360416207</v>
+        <f t="shared" si="64"/>
+        <v>621.09788367476142</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="68"/>
-        <v>383.03363577325808</v>
+        <f t="shared" si="64"/>
+        <v>722.91992168797947</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="68"/>
-        <v>399.82580035093315</v>
+        <f t="shared" si="64"/>
+        <v>836.34363519374892</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="68"/>
-        <v>417.25803833580687</v>
+        <f t="shared" si="64"/>
+        <v>962.6913391818556</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" si="68"/>
-        <v>435.35379236748247</v>
+        <f t="shared" si="64"/>
+        <v>1103.4480103245753</v>
       </c>
       <c r="AJ28" s="1">
         <f>AI28*(1+$AM$33)</f>
-        <v>431.00025444380765</v>
+        <v>1092.4135302213294</v>
       </c>
       <c r="AK28" s="1">
-        <f t="shared" ref="AK28:CV28" si="69">AJ28*(1+$AM$33)</f>
-        <v>426.69025189936957</v>
+        <f t="shared" ref="AK28:CV28" si="65">AJ28*(1+$AM$33)</f>
+        <v>1081.4893949191162</v>
       </c>
       <c r="AL28" s="1">
-        <f t="shared" si="69"/>
-        <v>422.4233493803759</v>
+        <f t="shared" si="65"/>
+        <v>1070.674500969925</v>
       </c>
       <c r="AM28" s="1">
-        <f t="shared" si="69"/>
-        <v>418.19911588657214</v>
+        <f t="shared" si="65"/>
+        <v>1059.9677559602258</v>
       </c>
       <c r="AN28" s="1">
-        <f t="shared" si="69"/>
-        <v>414.0171247277064</v>
+        <f t="shared" si="65"/>
+        <v>1049.3680784006235</v>
       </c>
       <c r="AO28" s="1">
-        <f t="shared" si="69"/>
-        <v>409.87695348042934</v>
+        <f t="shared" si="65"/>
+        <v>1038.8743976166172</v>
       </c>
       <c r="AP28" s="1">
-        <f t="shared" si="69"/>
-        <v>405.77818394562502</v>
+        <f t="shared" si="65"/>
+        <v>1028.4856536404511</v>
       </c>
       <c r="AQ28" s="1">
-        <f t="shared" si="69"/>
-        <v>401.72040210616876</v>
+        <f t="shared" si="65"/>
+        <v>1018.2007971040466</v>
       </c>
       <c r="AR28" s="1">
-        <f t="shared" si="69"/>
-        <v>397.70319808510709</v>
+        <f t="shared" si="65"/>
+        <v>1008.0187891330062</v>
       </c>
       <c r="AS28" s="1">
-        <f t="shared" si="69"/>
-        <v>393.72616610425604</v>
+        <f t="shared" si="65"/>
+        <v>997.93860124167611</v>
       </c>
       <c r="AT28" s="1">
-        <f t="shared" si="69"/>
-        <v>389.78890444321348</v>
+        <f t="shared" si="65"/>
+        <v>987.95921522925937</v>
       </c>
       <c r="AU28" s="1">
-        <f t="shared" si="69"/>
-        <v>385.89101539878135</v>
+        <f t="shared" si="65"/>
+        <v>978.07962307696675</v>
       </c>
       <c r="AV28" s="1">
-        <f t="shared" si="69"/>
-        <v>382.03210524479351</v>
+        <f t="shared" si="65"/>
+        <v>968.29882684619713</v>
       </c>
       <c r="AW28" s="1">
-        <f t="shared" si="69"/>
-        <v>378.21178419234559</v>
+        <f t="shared" si="65"/>
+        <v>958.61583857773519</v>
       </c>
       <c r="AX28" s="1">
-        <f t="shared" si="69"/>
-        <v>374.42966635042211</v>
+        <f t="shared" si="65"/>
+        <v>949.02968019195782</v>
       </c>
       <c r="AY28" s="1">
-        <f t="shared" si="69"/>
-        <v>370.68536968691791</v>
+        <f t="shared" si="65"/>
+        <v>939.53938339003821</v>
       </c>
       <c r="AZ28" s="1">
-        <f t="shared" si="69"/>
-        <v>366.97851599004872</v>
+        <f t="shared" si="65"/>
+        <v>930.14398955613785</v>
       </c>
       <c r="BA28" s="1">
-        <f t="shared" si="69"/>
-        <v>363.30873083014825</v>
+        <f t="shared" si="65"/>
+        <v>920.84254966057642</v>
       </c>
       <c r="BB28" s="1">
-        <f t="shared" si="69"/>
-        <v>359.67564352184678</v>
+        <f t="shared" si="65"/>
+        <v>911.63412416397068</v>
       </c>
       <c r="BC28" s="1">
-        <f t="shared" si="69"/>
-        <v>356.0788870866283</v>
+        <f t="shared" si="65"/>
+        <v>902.51778292233098</v>
       </c>
       <c r="BD28" s="1">
-        <f t="shared" si="69"/>
-        <v>352.518098215762</v>
+        <f t="shared" si="65"/>
+        <v>893.49260509310761</v>
       </c>
       <c r="BE28" s="1">
-        <f t="shared" si="69"/>
-        <v>348.99291723360437</v>
+        <f t="shared" si="65"/>
+        <v>884.55767904217657</v>
       </c>
       <c r="BF28" s="1">
-        <f t="shared" si="69"/>
-        <v>345.50298806126835</v>
+        <f t="shared" si="65"/>
+        <v>875.7121022517548</v>
       </c>
       <c r="BG28" s="1">
-        <f t="shared" si="69"/>
-        <v>342.04795818065566</v>
+        <f t="shared" si="65"/>
+        <v>866.95498122923721</v>
       </c>
       <c r="BH28" s="1">
-        <f t="shared" si="69"/>
-        <v>338.62747859884911</v>
+        <f t="shared" si="65"/>
+        <v>858.28543141694479</v>
       </c>
       <c r="BI28" s="1">
-        <f t="shared" si="69"/>
-        <v>335.24120381286059</v>
+        <f t="shared" si="65"/>
+        <v>849.70257710277531</v>
       </c>
       <c r="BJ28" s="1">
-        <f t="shared" si="69"/>
-        <v>331.888791774732</v>
+        <f t="shared" si="65"/>
+        <v>841.20555133174753</v>
       </c>
       <c r="BK28" s="1">
-        <f t="shared" si="69"/>
-        <v>328.56990385698469</v>
+        <f t="shared" si="65"/>
+        <v>832.79349581843007</v>
       </c>
       <c r="BL28" s="1">
-        <f t="shared" si="69"/>
-        <v>325.28420481841482</v>
+        <f t="shared" si="65"/>
+        <v>824.46556086024577</v>
       </c>
       <c r="BM28" s="1">
-        <f t="shared" si="69"/>
-        <v>322.03136277023066</v>
+        <f t="shared" si="65"/>
+        <v>816.22090525164333</v>
       </c>
       <c r="BN28" s="1">
-        <f t="shared" si="69"/>
-        <v>318.81104914252836</v>
+        <f t="shared" si="65"/>
+        <v>808.05869619912687</v>
       </c>
       <c r="BO28" s="1">
-        <f t="shared" si="69"/>
-        <v>315.62293865110308</v>
+        <f t="shared" si="65"/>
+        <v>799.97810923713564</v>
       </c>
       <c r="BP28" s="1">
-        <f t="shared" si="69"/>
-        <v>312.46670926459205</v>
+        <f t="shared" si="65"/>
+        <v>791.9783281447643</v>
       </c>
       <c r="BQ28" s="1">
-        <f t="shared" si="69"/>
-        <v>309.3420421719461</v>
+        <f t="shared" si="65"/>
+        <v>784.05854486331668</v>
       </c>
       <c r="BR28" s="1">
-        <f t="shared" si="69"/>
-        <v>306.24862175022662</v>
+        <f t="shared" si="65"/>
+        <v>776.21795941468349</v>
       </c>
       <c r="BS28" s="1">
-        <f t="shared" si="69"/>
-        <v>303.18613553272434</v>
+        <f t="shared" si="65"/>
+        <v>768.45577982053669</v>
       </c>
       <c r="BT28" s="1">
-        <f t="shared" si="69"/>
-        <v>300.1542741773971</v>
+        <f t="shared" si="65"/>
+        <v>760.77122202233136</v>
       </c>
       <c r="BU28" s="1">
-        <f t="shared" si="69"/>
-        <v>297.15273143562314</v>
+        <f t="shared" si="65"/>
+        <v>753.16350980210802</v>
       </c>
       <c r="BV28" s="1">
-        <f t="shared" si="69"/>
-        <v>294.18120412126689</v>
+        <f t="shared" si="65"/>
+        <v>745.63187470408695</v>
       </c>
       <c r="BW28" s="1">
-        <f t="shared" si="69"/>
-        <v>291.23939208005419</v>
+        <f t="shared" si="65"/>
+        <v>738.17555595704607</v>
       </c>
       <c r="BX28" s="1">
-        <f t="shared" si="69"/>
-        <v>288.32699815925366</v>
+        <f t="shared" si="65"/>
+        <v>730.79380039747559</v>
       </c>
       <c r="BY28" s="1">
-        <f t="shared" si="69"/>
-        <v>285.44372817766111</v>
+        <f t="shared" si="65"/>
+        <v>723.48586239350084</v>
       </c>
       <c r="BZ28" s="1">
-        <f t="shared" si="69"/>
-        <v>282.58929089588452</v>
+        <f t="shared" si="65"/>
+        <v>716.25100376956584</v>
       </c>
       <c r="CA28" s="1">
-        <f t="shared" si="69"/>
-        <v>279.76339798692567</v>
+        <f t="shared" si="65"/>
+        <v>709.08849373187013</v>
       </c>
       <c r="CB28" s="1">
-        <f t="shared" si="69"/>
-        <v>276.96576400705641</v>
+        <f t="shared" si="65"/>
+        <v>701.99760879455141</v>
       </c>
       <c r="CC28" s="1">
-        <f t="shared" si="69"/>
-        <v>274.19610636698582</v>
+        <f t="shared" si="65"/>
+        <v>694.97763270660585</v>
       </c>
       <c r="CD28" s="1">
-        <f t="shared" si="69"/>
-        <v>271.45414530331595</v>
+        <f t="shared" si="65"/>
+        <v>688.0278563795398</v>
       </c>
       <c r="CE28" s="1">
-        <f t="shared" si="69"/>
-        <v>268.73960385028278</v>
+        <f t="shared" si="65"/>
+        <v>681.1475778157444</v>
       </c>
       <c r="CF28" s="1">
-        <f t="shared" si="69"/>
-        <v>266.05220781177997</v>
+        <f t="shared" si="65"/>
+        <v>674.3361020375869</v>
       </c>
       <c r="CG28" s="1">
-        <f t="shared" si="69"/>
-        <v>263.39168573366214</v>
+        <f t="shared" si="65"/>
+        <v>667.59274101721098</v>
       </c>
       <c r="CH28" s="1">
-        <f t="shared" si="69"/>
-        <v>260.75776887632554</v>
+        <f t="shared" si="65"/>
+        <v>660.91681360703888</v>
       </c>
       <c r="CI28" s="1">
-        <f t="shared" si="69"/>
-        <v>258.15019118756226</v>
+        <f t="shared" si="65"/>
+        <v>654.30764547096851</v>
       </c>
       <c r="CJ28" s="1">
-        <f t="shared" si="69"/>
-        <v>255.56868927568664</v>
+        <f t="shared" si="65"/>
+        <v>647.76456901625886</v>
       </c>
       <c r="CK28" s="1">
-        <f t="shared" si="69"/>
-        <v>253.01300238292976</v>
+        <f t="shared" si="65"/>
+        <v>641.28692332609626</v>
       </c>
       <c r="CL28" s="1">
-        <f t="shared" si="69"/>
-        <v>250.48287235910047</v>
+        <f t="shared" si="65"/>
+        <v>634.87405409283531</v>
       </c>
       <c r="CM28" s="1">
-        <f t="shared" si="69"/>
-        <v>247.97804363550947</v>
+        <f t="shared" si="65"/>
+        <v>628.52531355190695</v>
       </c>
       <c r="CN28" s="1">
-        <f t="shared" si="69"/>
-        <v>245.49826319915437</v>
+        <f t="shared" si="65"/>
+        <v>622.24006041638791</v>
       </c>
       <c r="CO28" s="1">
-        <f t="shared" si="69"/>
-        <v>243.04328056716281</v>
+        <f t="shared" si="65"/>
+        <v>616.017659812224</v>
       </c>
       <c r="CP28" s="1">
-        <f t="shared" si="69"/>
-        <v>240.61284776149117</v>
+        <f t="shared" si="65"/>
+        <v>609.85748321410176</v>
       </c>
       <c r="CQ28" s="1">
-        <f t="shared" si="69"/>
-        <v>238.20671928387625</v>
+        <f t="shared" si="65"/>
+        <v>603.75890838196074</v>
       </c>
       <c r="CR28" s="1">
-        <f t="shared" si="69"/>
-        <v>235.82465209103748</v>
+        <f t="shared" si="65"/>
+        <v>597.72131929814111</v>
       </c>
       <c r="CS28" s="1">
-        <f t="shared" si="69"/>
-        <v>233.46640557012711</v>
+        <f t="shared" si="65"/>
+        <v>591.74410610515974</v>
       </c>
       <c r="CT28" s="1">
-        <f t="shared" si="69"/>
-        <v>231.13174151442584</v>
+        <f t="shared" si="65"/>
+        <v>585.82666504410815</v>
       </c>
       <c r="CU28" s="1">
-        <f t="shared" si="69"/>
-        <v>228.82042409928158</v>
+        <f t="shared" si="65"/>
+        <v>579.96839839366703</v>
       </c>
       <c r="CV28" s="1">
-        <f t="shared" si="69"/>
-        <v>226.53221985828876</v>
+        <f t="shared" si="65"/>
+        <v>574.16871440973034</v>
       </c>
       <c r="CW28" s="1">
-        <f t="shared" ref="CW28:EO28" si="70">CV28*(1+$AM$33)</f>
-        <v>224.26689765970588</v>
+        <f t="shared" ref="CW28:EO28" si="66">CV28*(1+$AM$33)</f>
+        <v>568.427027265633</v>
       </c>
       <c r="CX28" s="1">
-        <f t="shared" si="70"/>
-        <v>222.02422868310882</v>
+        <f t="shared" si="66"/>
+        <v>562.74275699297664</v>
       </c>
       <c r="CY28" s="1">
-        <f t="shared" si="70"/>
-        <v>219.80398639627774</v>
+        <f t="shared" si="66"/>
+        <v>557.11532942304689</v>
       </c>
       <c r="CZ28" s="1">
-        <f t="shared" si="70"/>
-        <v>217.60594653231496</v>
+        <f t="shared" si="66"/>
+        <v>551.54417612881639</v>
       </c>
       <c r="DA28" s="1">
-        <f t="shared" si="70"/>
-        <v>215.4298870669918</v>
+        <f t="shared" si="66"/>
+        <v>546.02873436752827</v>
       </c>
       <c r="DB28" s="1">
-        <f t="shared" si="70"/>
-        <v>213.27558819632188</v>
+        <f t="shared" si="66"/>
+        <v>540.56844702385297</v>
       </c>
       <c r="DC28" s="1">
-        <f t="shared" si="70"/>
-        <v>211.14283231435866</v>
+        <f t="shared" si="66"/>
+        <v>535.16276255361447</v>
       </c>
       <c r="DD28" s="1">
-        <f t="shared" si="70"/>
-        <v>209.03140399121506</v>
+        <f t="shared" si="66"/>
+        <v>529.81113492807833</v>
       </c>
       <c r="DE28" s="1">
-        <f t="shared" si="70"/>
-        <v>206.9410899513029</v>
+        <f t="shared" si="66"/>
+        <v>524.51302357879752</v>
       </c>
       <c r="DF28" s="1">
-        <f t="shared" si="70"/>
-        <v>204.87167905178987</v>
+        <f t="shared" si="66"/>
+        <v>519.26789334300952</v>
       </c>
       <c r="DG28" s="1">
-        <f t="shared" si="70"/>
-        <v>202.82296226127198</v>
+        <f t="shared" si="66"/>
+        <v>514.07521440957942</v>
       </c>
       <c r="DH28" s="1">
-        <f t="shared" si="70"/>
-        <v>200.79473263865927</v>
+        <f t="shared" si="66"/>
+        <v>508.9344622654836</v>
       </c>
       <c r="DI28" s="1">
-        <f t="shared" si="70"/>
-        <v>198.78678531227268</v>
+        <f t="shared" si="66"/>
+        <v>503.84511764282877</v>
       </c>
       <c r="DJ28" s="1">
-        <f t="shared" si="70"/>
-        <v>196.79891745914995</v>
+        <f t="shared" si="66"/>
+        <v>498.80666646640049</v>
       </c>
       <c r="DK28" s="1">
-        <f t="shared" si="70"/>
-        <v>194.83092828455844</v>
+        <f t="shared" si="66"/>
+        <v>493.81859980173647</v>
       </c>
       <c r="DL28" s="1">
-        <f t="shared" si="70"/>
-        <v>192.88261900171284</v>
+        <f t="shared" si="66"/>
+        <v>488.88041380371908</v>
       </c>
       <c r="DM28" s="1">
-        <f t="shared" si="70"/>
-        <v>190.95379281169571</v>
+        <f t="shared" si="66"/>
+        <v>483.99160966568189</v>
       </c>
       <c r="DN28" s="1">
-        <f t="shared" si="70"/>
-        <v>189.04425488357876</v>
+        <f t="shared" si="66"/>
+        <v>479.15169356902504</v>
       </c>
       <c r="DO28" s="1">
-        <f t="shared" si="70"/>
-        <v>187.15381233474298</v>
+        <f t="shared" si="66"/>
+        <v>474.36017663333479</v>
       </c>
       <c r="DP28" s="1">
-        <f t="shared" si="70"/>
-        <v>185.28227421139556</v>
+        <f t="shared" si="66"/>
+        <v>469.61657486700142</v>
       </c>
       <c r="DQ28" s="1">
-        <f t="shared" si="70"/>
-        <v>183.42945146928162</v>
+        <f t="shared" si="66"/>
+        <v>464.92040911833141</v>
       </c>
       <c r="DR28" s="1">
-        <f t="shared" si="70"/>
-        <v>181.59515695458879</v>
+        <f t="shared" si="66"/>
+        <v>460.27120502714808</v>
       </c>
       <c r="DS28" s="1">
-        <f t="shared" si="70"/>
-        <v>179.7792053850429</v>
+        <f t="shared" si="66"/>
+        <v>455.66849297687662</v>
       </c>
       <c r="DT28" s="1">
-        <f t="shared" si="70"/>
-        <v>177.98141333119247</v>
+        <f t="shared" si="66"/>
+        <v>451.11180804710784</v>
       </c>
       <c r="DU28" s="1">
-        <f t="shared" si="70"/>
-        <v>176.20159919788054</v>
+        <f t="shared" si="66"/>
+        <v>446.60068996663676</v>
       </c>
       <c r="DV28" s="1">
-        <f t="shared" si="70"/>
-        <v>174.43958320590173</v>
+        <f t="shared" si="66"/>
+        <v>442.13468306697041</v>
       </c>
       <c r="DW28" s="1">
-        <f t="shared" si="70"/>
-        <v>172.69518737384271</v>
+        <f t="shared" si="66"/>
+        <v>437.71333623630068</v>
       </c>
       <c r="DX28" s="1">
-        <f t="shared" si="70"/>
-        <v>170.9682355001043</v>
+        <f t="shared" si="66"/>
+        <v>433.33620287393768</v>
       </c>
       <c r="DY28" s="1">
-        <f t="shared" si="70"/>
-        <v>169.25855314510326</v>
+        <f t="shared" si="66"/>
+        <v>429.00284084519831</v>
       </c>
       <c r="DZ28" s="1">
-        <f t="shared" si="70"/>
-        <v>167.56596761365222</v>
+        <f t="shared" si="66"/>
+        <v>424.71281243674633</v>
       </c>
       <c r="EA28" s="1">
-        <f t="shared" si="70"/>
-        <v>165.8903079375157</v>
+        <f t="shared" si="66"/>
+        <v>420.46568431237887</v>
       </c>
       <c r="EB28" s="1">
-        <f t="shared" si="70"/>
-        <v>164.23140485814054</v>
+        <f t="shared" si="66"/>
+        <v>416.26102746925505</v>
       </c>
       <c r="EC28" s="1">
-        <f t="shared" si="70"/>
-        <v>162.58909080955914</v>
+        <f t="shared" si="66"/>
+        <v>412.0984171945625</v>
       </c>
       <c r="ED28" s="1">
-        <f t="shared" si="70"/>
-        <v>160.96319990146355</v>
+        <f t="shared" si="66"/>
+        <v>407.97743302261688</v>
       </c>
       <c r="EE28" s="1">
-        <f t="shared" si="70"/>
-        <v>159.35356790244893</v>
+        <f t="shared" si="66"/>
+        <v>403.89765869239068</v>
       </c>
       <c r="EF28" s="1">
-        <f t="shared" si="70"/>
-        <v>157.76003222342445</v>
+        <f t="shared" si="66"/>
+        <v>399.85868210546676</v>
       </c>
       <c r="EG28" s="1">
-        <f t="shared" si="70"/>
-        <v>156.1824319011902</v>
+        <f t="shared" si="66"/>
+        <v>395.86009528441207</v>
       </c>
       <c r="EH28" s="1">
-        <f t="shared" si="70"/>
-        <v>154.62060758217831</v>
+        <f t="shared" si="66"/>
+        <v>391.90149433156796</v>
       </c>
       <c r="EI28" s="1">
-        <f t="shared" si="70"/>
-        <v>153.07440150635654</v>
+        <f t="shared" si="66"/>
+        <v>387.98247938825227</v>
       </c>
       <c r="EJ28" s="1">
-        <f t="shared" si="70"/>
-        <v>151.54365749129298</v>
+        <f t="shared" si="66"/>
+        <v>384.10265459436977</v>
       </c>
       <c r="EK28" s="1">
-        <f t="shared" si="70"/>
-        <v>150.02822091638004</v>
+        <f t="shared" si="66"/>
+        <v>380.26162804842608</v>
       </c>
       <c r="EL28" s="1">
-        <f t="shared" si="70"/>
-        <v>148.52793870721624</v>
+        <f t="shared" si="66"/>
+        <v>376.45901176794183</v>
       </c>
       <c r="EM28" s="1">
-        <f t="shared" si="70"/>
-        <v>147.04265932014408</v>
+        <f t="shared" si="66"/>
+        <v>372.69442165026243</v>
       </c>
       <c r="EN28" s="1">
-        <f t="shared" si="70"/>
-        <v>145.57223272694264</v>
+        <f t="shared" si="66"/>
+        <v>368.96747743375983</v>
       </c>
       <c r="EO28" s="1">
-        <f t="shared" si="70"/>
-        <v>144.11651039967322</v>
+        <f t="shared" si="66"/>
+        <v>365.27780265942221</v>
       </c>
     </row>
     <row r="29" spans="2:145" x14ac:dyDescent="0.3">
@@ -4378,12 +4372,12 @@
         <v>234</v>
       </c>
       <c r="Q29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="R29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="T29" s="4">
         <v>228.6</v>
@@ -4401,48 +4395,48 @@
         <v>228.6</v>
       </c>
       <c r="Y29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="Z29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="AA29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="AB29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="AC29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="AD29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="AE29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="AF29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="AG29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="AH29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
       <c r="AI29" s="4">
-        <f>234</f>
-        <v>234</v>
+        <f>236.5</f>
+        <v>236.5</v>
       </c>
     </row>
     <row r="30" spans="2:145" x14ac:dyDescent="0.3">
@@ -4450,120 +4444,120 @@
         <v>37</v>
       </c>
       <c r="F30" s="6">
-        <f t="shared" ref="F30:O30" si="71">F28/F29</f>
+        <f t="shared" ref="F30:O30" si="67">F28/F29</f>
         <v>-0.20603674540682443</v>
       </c>
       <c r="G30" s="6">
+        <f t="shared" si="67"/>
+        <v>-0.31233595800524933</v>
+      </c>
+      <c r="H30" s="6">
+        <f t="shared" si="67"/>
+        <v>-0.29002624671916</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="67"/>
+        <v>-0.73928258967629046</v>
+      </c>
+      <c r="J30" s="6">
+        <f t="shared" si="67"/>
+        <v>1.9247594050743711E-2</v>
+      </c>
+      <c r="K30" s="6">
+        <f t="shared" si="67"/>
+        <v>-0.2524059492563428</v>
+      </c>
+      <c r="L30" s="6">
+        <f t="shared" si="67"/>
+        <v>-0.27121609798775148</v>
+      </c>
+      <c r="M30" s="6">
+        <f t="shared" si="67"/>
+        <v>-6.4304461942257071E-2</v>
+      </c>
+      <c r="N30" s="6">
+        <f t="shared" si="67"/>
+        <v>0.45736773065150832</v>
+      </c>
+      <c r="O30" s="6">
+        <f t="shared" si="67"/>
+        <v>-0.10249784668389306</v>
+      </c>
+      <c r="P30" s="6">
+        <f t="shared" ref="P30" si="68">P28/P29</f>
+        <v>-0.18162393162393142</v>
+      </c>
+      <c r="Q30" s="6">
+        <f t="shared" ref="Q30" si="69">Q28/Q29</f>
+        <v>-9.5983086680761096E-2</v>
+      </c>
+      <c r="R30" s="6">
+        <f t="shared" ref="R30" si="70">R28/R29</f>
+        <v>0.41532515856236762</v>
+      </c>
+      <c r="T30" s="6">
+        <f t="shared" ref="T30:Y30" si="71">T28/T29</f>
+        <v>-0.68941382327209078</v>
+      </c>
+      <c r="U30" s="6">
         <f t="shared" si="71"/>
-        <v>-0.31233595800524933</v>
-      </c>
-      <c r="H30" s="6">
+        <v>-0.71872265966754201</v>
+      </c>
+      <c r="V30" s="6">
         <f t="shared" si="71"/>
-        <v>-0.29002624671916</v>
-      </c>
-      <c r="I30" s="6">
+        <v>-1.3180227471566048</v>
+      </c>
+      <c r="W30" s="6">
         <f t="shared" si="71"/>
-        <v>-0.73928258967629046</v>
-      </c>
-      <c r="J30" s="6">
+        <v>-1.322397200349956</v>
+      </c>
+      <c r="X30" s="6">
         <f t="shared" si="71"/>
-        <v>1.9247594050743711E-2</v>
-      </c>
-      <c r="K30" s="6">
+        <v>-0.13035870516185588</v>
+      </c>
+      <c r="Y30" s="6">
         <f t="shared" si="71"/>
-        <v>-0.2524059492563428</v>
-      </c>
-      <c r="L30" s="6">
-        <f t="shared" si="71"/>
-        <v>-0.27121609798775148</v>
-      </c>
-      <c r="M30" s="6">
-        <f t="shared" si="71"/>
-        <v>-6.4304461942257071E-2</v>
-      </c>
-      <c r="N30" s="6">
-        <f t="shared" si="71"/>
-        <v>0.45736773065150832</v>
-      </c>
-      <c r="O30" s="6">
-        <f t="shared" si="71"/>
-        <v>-0.10249784668389306</v>
-      </c>
-      <c r="P30" s="6">
-        <f t="shared" ref="P30" si="72">P28/P29</f>
-        <v>-0.18162393162393142</v>
-      </c>
-      <c r="Q30" s="6">
-        <f t="shared" ref="Q30" si="73">Q28/Q29</f>
-        <v>3.3701709401709044E-2</v>
-      </c>
-      <c r="R30" s="6">
-        <f t="shared" ref="R30" si="74">R28/R29</f>
-        <v>0.43415867521367513</v>
-      </c>
-      <c r="T30" s="6">
-        <f t="shared" ref="T30:Y30" si="75">T28/T29</f>
-        <v>-0.68941382327209078</v>
-      </c>
-      <c r="U30" s="6">
-        <f t="shared" si="75"/>
-        <v>-0.71872265966754201</v>
-      </c>
-      <c r="V30" s="6">
-        <f t="shared" si="75"/>
-        <v>-1.3180227471566048</v>
-      </c>
-      <c r="W30" s="6">
-        <f t="shared" si="75"/>
-        <v>-1.322397200349956</v>
-      </c>
-      <c r="X30" s="6">
-        <f t="shared" si="75"/>
-        <v>-0.13035870516185588</v>
-      </c>
-      <c r="Y30" s="6">
-        <f t="shared" si="75"/>
-        <v>0.18452705128205221</v>
+        <v>3.9003805496829393E-2</v>
       </c>
       <c r="Z30" s="6">
-        <f t="shared" ref="Z30:AI30" si="76">Z28/Z29</f>
-        <v>0.62048906474358978</v>
+        <f t="shared" ref="Z30:AI30" si="72">Z28/Z29</f>
+        <v>0.90915199534883517</v>
       </c>
       <c r="AA30" s="6">
-        <f t="shared" si="76"/>
-        <v>0.80615912101281961</v>
+        <f t="shared" si="72"/>
+        <v>1.2736771925073995</v>
       </c>
       <c r="AB30" s="6">
-        <f t="shared" si="76"/>
-        <v>1.0112705935627175</v>
+        <f t="shared" si="72"/>
+        <v>1.6073142381168688</v>
       </c>
       <c r="AC30" s="6">
-        <f t="shared" si="76"/>
-        <v>1.2237567394274842</v>
+        <f t="shared" si="72"/>
+        <v>1.9015924963347457</v>
       </c>
       <c r="AD30" s="6">
-        <f t="shared" si="76"/>
-        <v>1.4124958188193395</v>
+        <f t="shared" si="72"/>
+        <v>2.2397398903950383</v>
       </c>
       <c r="AE30" s="6">
-        <f t="shared" si="76"/>
-        <v>1.5369321521545387</v>
+        <f t="shared" si="72"/>
+        <v>2.6262066962992026</v>
       </c>
       <c r="AF30" s="6">
-        <f t="shared" si="76"/>
-        <v>1.6368958793728978</v>
+        <f t="shared" si="72"/>
+        <v>3.0567438549174608</v>
       </c>
       <c r="AG30" s="6">
-        <f t="shared" si="76"/>
-        <v>1.7086572664569792</v>
+        <f t="shared" si="72"/>
+        <v>3.5363367238636316</v>
       </c>
       <c r="AH30" s="6">
-        <f t="shared" si="76"/>
-        <v>1.7831540099820806</v>
+        <f t="shared" si="72"/>
+        <v>4.0705764870268739</v>
       </c>
       <c r="AI30" s="6">
-        <f t="shared" si="76"/>
-        <v>1.8604862921687284</v>
+        <f t="shared" si="72"/>
+        <v>4.6657421155373164</v>
       </c>
     </row>
     <row r="32" spans="2:145" x14ac:dyDescent="0.3">
@@ -4571,15 +4565,15 @@
         <v>51</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" ref="J32:L36" si="77">J3/F3-1</f>
+        <f t="shared" ref="J32:L36" si="73">J3/F3-1</f>
         <v>-0.27318156579677955</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="73"/>
         <v>-0.20805369127516771</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="73"/>
         <v>5.4028877503493389E-2</v>
       </c>
       <c r="M32" s="9">
@@ -4591,20 +4585,20 @@
         <v>0.80175706646294875</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" ref="O32:R36" si="78">O3/K3-1</f>
+        <f t="shared" ref="O32:R36" si="74">O3/K3-1</f>
         <v>0.38135593220338992</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.31064958020327005</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="78"/>
-        <v>0.29999999999999982</v>
+        <f t="shared" si="74"/>
+        <v>0.64371257485029942</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="78"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="74"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="T32" s="9"/>
       <c r="U32" s="9">
@@ -4612,60 +4606,60 @@
         <v>0.27940609332819122</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" ref="V32:X32" si="79">V3/U3-1</f>
+        <f t="shared" ref="V32:X32" si="75">V3/U3-1</f>
         <v>0.32735493594574239</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.10730101055978203</v>
       </c>
       <c r="X32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.11279737489745689</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" ref="Y32:AI32" si="80">Y3/X3-1</f>
-        <v>0.20505436785845932</v>
+        <f t="shared" ref="Y32:AI32" si="76">Y3/X3-1</f>
+        <v>0.34430519719867303</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" si="80"/>
-        <v>0.1399999999999999</v>
+        <f t="shared" si="76"/>
+        <v>0.25</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AB32" s="9">
+        <f t="shared" si="76"/>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="AC32" s="9">
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AB32" s="9">
-        <f t="shared" si="80"/>
+      <c r="AD32" s="9">
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AC32" s="9">
-        <f t="shared" si="80"/>
+      <c r="AE32" s="9">
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AD32" s="9">
-        <f t="shared" si="80"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AE32" s="9">
-        <f t="shared" si="80"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
       <c r="AF32" s="9">
-        <f t="shared" si="80"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="76"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="80"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="76"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="80"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="76"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="80"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="76"/>
+        <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.3">
@@ -4673,101 +4667,101 @@
         <v>52</v>
       </c>
       <c r="J33" s="9">
+        <f t="shared" si="73"/>
+        <v>-0.39814814814814814</v>
+      </c>
+      <c r="K33" s="9">
+        <f t="shared" si="73"/>
+        <v>-0.44390243902439019</v>
+      </c>
+      <c r="L33" s="9">
+        <f t="shared" si="73"/>
+        <v>0.7644628099173556</v>
+      </c>
+      <c r="M33" s="9">
+        <f t="shared" ref="M33:N36" si="77">M4/I4-1</f>
+        <v>0.46575342465753433</v>
+      </c>
+      <c r="N33" s="9">
         <f t="shared" si="77"/>
-        <v>-0.39814814814814814</v>
-      </c>
-      <c r="K33" s="9">
-        <f t="shared" si="77"/>
-        <v>-0.44390243902439019</v>
-      </c>
-      <c r="L33" s="9">
-        <f t="shared" si="77"/>
-        <v>0.7644628099173556</v>
-      </c>
-      <c r="M33" s="9">
-        <f t="shared" ref="M33:N36" si="81">M4/I4-1</f>
-        <v>0.46575342465753433</v>
-      </c>
-      <c r="N33" s="9">
-        <f t="shared" si="81"/>
         <v>0.38846153846153841</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>1.9561403508771931</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>-0.12412177985948492</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" si="78"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="74"/>
+        <v>1.0498442367601246</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="78"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="74"/>
+        <v>1.2000000000000002</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9">
-        <f t="shared" ref="U33:X36" si="82">U4/T4-1</f>
+        <f t="shared" ref="U33:X36" si="78">U4/T4-1</f>
         <v>-5.6918547595682156E-2</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>-4.1623309053069768E-2</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>5.4288816503800241E-3</v>
       </c>
       <c r="X33" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.32073434125269995</v>
       </c>
       <c r="Y33" s="9">
-        <f t="shared" ref="Y33:AI33" si="83">Y4/X4-1</f>
-        <v>0.16688470973017178</v>
+        <f t="shared" ref="Y33:AI33" si="79">Y4/X4-1</f>
+        <v>0.76876533115290258</v>
       </c>
       <c r="Z33" s="9">
-        <f t="shared" si="83"/>
-        <v>0.25</v>
+        <f t="shared" si="79"/>
+        <v>0.50000000000000022</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="AB33" s="9">
+        <f t="shared" si="79"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AC33" s="9">
+        <f t="shared" si="79"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AB33" s="9">
-        <f t="shared" si="83"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AC33" s="9">
-        <f t="shared" si="83"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
       <c r="AD33" s="9">
-        <f t="shared" si="83"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="79"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="83"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="79"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="83"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="79"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="79"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="79"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="79"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AL33" t="s">
         <v>65</v>
@@ -4781,100 +4775,100 @@
         <v>53</v>
       </c>
       <c r="J34" s="9">
+        <f t="shared" si="73"/>
+        <v>0.31829573934837097</v>
+      </c>
+      <c r="K34" s="9">
+        <f t="shared" si="73"/>
+        <v>0.38574938574938566</v>
+      </c>
+      <c r="L34" s="9">
+        <f t="shared" si="73"/>
+        <v>0.24113475177304977</v>
+      </c>
+      <c r="M34" s="9">
         <f t="shared" si="77"/>
-        <v>0.31829573934837097</v>
-      </c>
-      <c r="K34" s="9">
+        <v>6.9473684210526354E-2</v>
+      </c>
+      <c r="N34" s="9">
         <f t="shared" si="77"/>
-        <v>0.38574938574938566</v>
-      </c>
-      <c r="L34" s="9">
-        <f t="shared" si="77"/>
-        <v>0.24113475177304977</v>
-      </c>
-      <c r="M34" s="9">
-        <f t="shared" si="81"/>
-        <v>6.9473684210526354E-2</v>
-      </c>
-      <c r="N34" s="9">
-        <f t="shared" si="81"/>
         <v>2.281368821292773E-2</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>-5.1418439716311992E-2</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>3.6190476190476106E-2</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" si="78"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="74"/>
+        <v>0.15354330708661434</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="78"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="74"/>
+        <v>0.19999999999999973</v>
       </c>
       <c r="T34" s="9"/>
       <c r="U34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.31569343065693434</v>
       </c>
       <c r="V34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>4.7156726768377233E-2</v>
       </c>
       <c r="W34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.21258278145695364</v>
       </c>
       <c r="X34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.16602949208083029</v>
       </c>
       <c r="Y34" s="9">
-        <f t="shared" ref="Y34:AI34" si="84">Y5/X5-1</f>
-        <v>5.1147540983607076E-3</v>
+        <f t="shared" ref="Y34:AI34" si="80">Y5/X5-1</f>
+        <v>8.2248243559718937E-2</v>
       </c>
       <c r="Z34" s="9">
-        <f t="shared" si="84"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="80"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AA34" s="9">
-        <f t="shared" si="84"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="80"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AB34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AC34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL34" t="s">
@@ -4889,100 +4883,100 @@
         <v>54</v>
       </c>
       <c r="J35" s="9">
+        <f t="shared" si="73"/>
+        <v>-0.140625</v>
+      </c>
+      <c r="K35" s="9">
+        <f t="shared" si="73"/>
+        <v>-0.31034482758620696</v>
+      </c>
+      <c r="L35" s="9">
+        <f t="shared" si="73"/>
+        <v>-0.28282828282828287</v>
+      </c>
+      <c r="M35" s="9">
         <f t="shared" si="77"/>
-        <v>-0.140625</v>
-      </c>
-      <c r="K35" s="9">
+        <v>-0.46511627906976738</v>
+      </c>
+      <c r="N35" s="9">
         <f t="shared" si="77"/>
-        <v>-0.31034482758620696</v>
-      </c>
-      <c r="L35" s="9">
-        <f t="shared" si="77"/>
-        <v>-0.28282828282828287</v>
-      </c>
-      <c r="M35" s="9">
-        <f t="shared" si="81"/>
-        <v>-0.46511627906976738</v>
-      </c>
-      <c r="N35" s="9">
-        <f t="shared" si="81"/>
         <v>-0.34545454545454546</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="P35" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>-9.8591549295774517E-2</v>
       </c>
       <c r="Q35" s="9">
-        <f t="shared" si="78"/>
-        <v>0.89999999999999991</v>
+        <f t="shared" si="74"/>
+        <v>-0.24637681159420288</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="T35" s="9"/>
       <c r="U35" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>6.708268330733258E-2</v>
       </c>
       <c r="V35" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.10233918128654973</v>
       </c>
       <c r="W35" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>9.2838196286472163E-2</v>
       </c>
       <c r="X35" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>-0.35922330097087385</v>
       </c>
       <c r="Y35" s="9">
-        <f t="shared" ref="Y35:AI35" si="85">Y6/X6-1</f>
-        <v>0.63901515151515142</v>
+        <f t="shared" ref="Y35:AI35" si="81">Y6/X6-1</f>
+        <v>0.33939393939393936</v>
       </c>
       <c r="Z35" s="9">
-        <f t="shared" si="85"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="81"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AA35" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="81"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AB35" s="9">
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AB35" s="9">
-        <f t="shared" si="85"/>
+      <c r="AC35" s="9">
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC35" s="9">
-        <f t="shared" si="85"/>
+      <c r="AD35" s="9">
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AD35" s="9">
-        <f t="shared" si="85"/>
+      <c r="AE35" s="9">
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AE35" s="9">
-        <f t="shared" si="85"/>
+      <c r="AF35" s="9">
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AF35" s="9">
-        <f t="shared" si="85"/>
+      <c r="AG35" s="9">
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AG35" s="9">
-        <f t="shared" si="85"/>
+      <c r="AH35" s="9">
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AH35" s="9">
-        <f t="shared" si="85"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
       <c r="AI35" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL35" t="s">
@@ -4990,7 +4984,7 @@
       </c>
       <c r="AM35" s="4">
         <f>NPV(AM34,Y28:EO28)</f>
-        <v>3446.5738933377929</v>
+        <v>7454.7382975273549</v>
       </c>
     </row>
     <row r="36" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4998,108 +4992,108 @@
         <v>55</v>
       </c>
       <c r="J36" s="10">
+        <f t="shared" si="73"/>
+        <v>-0.22832432432432415</v>
+      </c>
+      <c r="K36" s="10">
+        <f t="shared" si="73"/>
+        <v>-0.14534883720930225</v>
+      </c>
+      <c r="L36" s="10">
+        <f t="shared" si="73"/>
+        <v>0.11528239202657797</v>
+      </c>
+      <c r="M36" s="10">
         <f t="shared" si="77"/>
-        <v>-0.22832432432432415</v>
-      </c>
-      <c r="K36" s="10">
+        <v>-0.17416291854072952</v>
+      </c>
+      <c r="N36" s="10">
         <f t="shared" si="77"/>
-        <v>-0.14534883720930225</v>
-      </c>
-      <c r="L36" s="10">
-        <f t="shared" si="77"/>
-        <v>0.11528239202657797</v>
-      </c>
-      <c r="M36" s="10">
-        <f t="shared" si="81"/>
-        <v>-0.17416291854072952</v>
-      </c>
-      <c r="N36" s="10">
-        <f t="shared" si="81"/>
         <v>0.60381059120201708</v>
       </c>
       <c r="O36" s="10">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.38647959183673475</v>
       </c>
       <c r="P36" s="10">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.19511468573130775</v>
       </c>
       <c r="Q36" s="10">
-        <f t="shared" si="78"/>
-        <v>0.25773373676248057</v>
+        <f t="shared" si="74"/>
+        <v>0.57065052950075623</v>
       </c>
       <c r="R36" s="10">
-        <f t="shared" si="78"/>
-        <v>6.3218029350104787E-2</v>
+        <f t="shared" si="74"/>
+        <v>0.27627533193570919</v>
       </c>
       <c r="T36" s="10"/>
       <c r="U36" s="10">
+        <f t="shared" si="78"/>
+        <v>0.2241249055653487</v>
+      </c>
+      <c r="V36" s="10">
+        <f t="shared" si="78"/>
+        <v>0.23349105122402825</v>
+      </c>
+      <c r="W36" s="10">
+        <f t="shared" si="78"/>
+        <v>0.1118245496997996</v>
+      </c>
+      <c r="X36" s="10">
+        <f t="shared" si="78"/>
+        <v>0.10537763444086101</v>
+      </c>
+      <c r="Y36" s="10">
+        <f t="shared" ref="Y36:AI36" si="82">Y7/X7-1</f>
+        <v>0.34138960510245608</v>
+      </c>
+      <c r="Z36" s="10">
         <f t="shared" si="82"/>
-        <v>0.2241249055653487</v>
-      </c>
-      <c r="V36" s="10">
+        <v>0.2527401944419152</v>
+      </c>
+      <c r="AA36" s="10">
         <f t="shared" si="82"/>
-        <v>0.23349105122402825</v>
-      </c>
-      <c r="W36" s="10">
+        <v>0.17047314047100715</v>
+      </c>
+      <c r="AB36" s="10">
         <f t="shared" si="82"/>
-        <v>0.1118245496997996</v>
-      </c>
-      <c r="X36" s="10">
+        <v>0.1389227200440708</v>
+      </c>
+      <c r="AC36" s="10">
         <f t="shared" si="82"/>
-        <v>0.10537763444086101</v>
-      </c>
-      <c r="Y36" s="10">
-        <f t="shared" ref="Y36:AI36" si="86">Y7/X7-1</f>
-        <v>0.18846994164744224</v>
-      </c>
-      <c r="Z36" s="10">
-        <f t="shared" si="86"/>
-        <v>0.14702617713167676</v>
-      </c>
-      <c r="AA36" s="10">
-        <f t="shared" si="86"/>
-        <v>0.10276981376473726</v>
-      </c>
-      <c r="AB36" s="10">
-        <f t="shared" si="86"/>
-        <v>9.5530148468961018E-2</v>
-      </c>
-      <c r="AC36" s="10">
-        <f t="shared" si="86"/>
-        <v>8.8037528291093903E-2</v>
+        <v>0.11076649084691859</v>
       </c>
       <c r="AD36" s="10">
-        <f t="shared" si="86"/>
-        <v>6.9467233734611389E-2</v>
+        <f t="shared" si="82"/>
+        <v>0.11193782760339865</v>
       </c>
       <c r="AE36" s="10">
-        <f t="shared" si="86"/>
-        <v>4.6080285563213419E-2</v>
+        <f t="shared" si="82"/>
+        <v>0.11404339227887128</v>
       </c>
       <c r="AF36" s="10">
-        <f t="shared" si="86"/>
-        <v>3.7560453854360576E-2</v>
+        <f t="shared" si="82"/>
+        <v>0.1161939300242969</v>
       </c>
       <c r="AG36" s="10">
-        <f t="shared" si="86"/>
-        <v>2.8995837446806227E-2</v>
+        <f t="shared" si="82"/>
+        <v>0.11838934842626525</v>
       </c>
       <c r="AH36" s="10">
-        <f t="shared" si="86"/>
-        <v>2.9031087313679649E-2</v>
+        <f t="shared" si="82"/>
+        <v>0.12062885553814495</v>
       </c>
       <c r="AI36" s="10">
-        <f t="shared" si="86"/>
-        <v>2.906660132548633E-2</v>
+        <f t="shared" si="82"/>
+        <v>0.12291091607126114</v>
       </c>
       <c r="AL36" t="s">
         <v>68</v>
       </c>
       <c r="AM36" s="4">
         <f>Main!D8</f>
-        <v>-771.2</v>
+        <v>-745.59999999999991</v>
       </c>
     </row>
     <row r="37" spans="2:39" x14ac:dyDescent="0.3">
@@ -5107,31 +5101,31 @@
         <v>56</v>
       </c>
       <c r="F37" s="9">
-        <f t="shared" ref="F37:L40" si="87">(F3-F8)/F3</f>
+        <f t="shared" ref="F37:L40" si="83">(F3-F8)/F3</f>
         <v>0.38145474736257629</v>
       </c>
       <c r="G37" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.33092410944759937</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.32370749883558453</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.40065573770491797</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.3411000763941941</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.24511082138200788</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.28722934158197083</v>
       </c>
       <c r="M37" s="9">
@@ -5143,19 +5137,19 @@
         <v>0.46215815136739452</v>
       </c>
       <c r="O37" s="9">
-        <f t="shared" ref="O37:R37" si="88">(O3-O8)/O3</f>
+        <f t="shared" ref="O37:R37" si="84">(O3-O8)/O3</f>
         <v>0.34119867862199155</v>
       </c>
       <c r="P37" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.3300741739716791</v>
       </c>
       <c r="Q37" s="9">
-        <f t="shared" si="88"/>
-        <v>0.35</v>
+        <f t="shared" si="84"/>
+        <v>0.34998698933125161</v>
       </c>
       <c r="R37" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="T37" s="9">
@@ -5167,59 +5161,59 @@
         <v>0.28907309721175584</v>
       </c>
       <c r="V37" s="9">
-        <f t="shared" ref="V37:X37" si="89">(V3-V8)/V3</f>
+        <f t="shared" ref="V37:X37" si="85">(V3-V8)/V3</f>
         <v>0.30032928352446914</v>
       </c>
       <c r="W37" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="85"/>
         <v>0.35387612797374912</v>
       </c>
       <c r="X37" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="85"/>
         <v>0.36795060818282338</v>
       </c>
       <c r="Y37" s="9">
-        <f t="shared" ref="Y37:AI37" si="90">(Y3-Y8)/Y3</f>
-        <v>0.38192834885010235</v>
+        <f t="shared" ref="Y37:AI37" si="86">(Y3-Y8)/Y3</f>
+        <v>0.38346768665515069</v>
       </c>
       <c r="Z37" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.4</v>
       </c>
       <c r="AA37" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.4</v>
       </c>
       <c r="AB37" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.40000000000000008</v>
       </c>
       <c r="AC37" s="9">
-        <f t="shared" si="90"/>
-        <v>0.39999999999999997</v>
+        <f t="shared" si="86"/>
+        <v>0.4</v>
       </c>
       <c r="AD37" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.4</v>
       </c>
       <c r="AE37" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.4</v>
       </c>
       <c r="AF37" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.4</v>
       </c>
       <c r="AG37" s="9">
-        <f t="shared" si="90"/>
-        <v>0.4</v>
+        <f t="shared" si="86"/>
+        <v>0.40000000000000008</v>
       </c>
       <c r="AH37" s="9">
-        <f t="shared" si="90"/>
-        <v>0.4</v>
+        <f t="shared" si="86"/>
+        <v>0.40000000000000008</v>
       </c>
       <c r="AI37" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.4</v>
       </c>
       <c r="AL37" t="s">
@@ -5227,7 +5221,7 @@
       </c>
       <c r="AM37" s="4">
         <f>AM35+AM36</f>
-        <v>2675.3738933377927</v>
+        <v>6709.1382975273555</v>
       </c>
     </row>
     <row r="38" spans="2:39" x14ac:dyDescent="0.3">
@@ -5235,127 +5229,127 @@
         <v>57</v>
       </c>
       <c r="F38" s="9">
+        <f t="shared" si="83"/>
+        <v>-7.175925925925912E-2</v>
+      </c>
+      <c r="G38" s="9">
+        <f t="shared" si="83"/>
+        <v>-0.22439024390243908</v>
+      </c>
+      <c r="H38" s="9">
+        <f t="shared" si="83"/>
+        <v>-0.11157024793388427</v>
+      </c>
+      <c r="I38" s="9">
+        <f t="shared" si="83"/>
+        <v>-0.18264840182648404</v>
+      </c>
+      <c r="J38" s="9">
+        <f t="shared" si="83"/>
+        <v>-7.3076923076923025E-2</v>
+      </c>
+      <c r="K38" s="9">
+        <f t="shared" si="83"/>
+        <v>-0.35087719298245612</v>
+      </c>
+      <c r="L38" s="9">
+        <f t="shared" si="83"/>
+        <v>-3.747072599531602E-2</v>
+      </c>
+      <c r="M38" s="9">
+        <f t="shared" ref="M38:N40" si="87">(M4-M9)/M4</f>
+        <v>-0.11214953271028041</v>
+      </c>
+      <c r="N38" s="9">
         <f t="shared" si="87"/>
-        <v>-7.175925925925912E-2</v>
-      </c>
-      <c r="G38" s="9">
-        <f t="shared" si="87"/>
-        <v>-0.22439024390243908</v>
-      </c>
-      <c r="H38" s="9">
-        <f t="shared" si="87"/>
-        <v>-0.11157024793388427</v>
-      </c>
-      <c r="I38" s="9">
-        <f t="shared" si="87"/>
-        <v>-0.18264840182648404</v>
-      </c>
-      <c r="J38" s="9">
-        <f t="shared" si="87"/>
-        <v>-7.3076923076923025E-2</v>
-      </c>
-      <c r="K38" s="9">
-        <f t="shared" si="87"/>
-        <v>-0.35087719298245612</v>
-      </c>
-      <c r="L38" s="9">
-        <f t="shared" si="87"/>
-        <v>-3.747072599531602E-2</v>
-      </c>
-      <c r="M38" s="9">
-        <f t="shared" ref="M38:N40" si="91">(M4-M9)/M4</f>
-        <v>-0.11214953271028041</v>
-      </c>
-      <c r="N38" s="9">
+        <v>5.5401662049861494E-2</v>
+      </c>
+      <c r="O38" s="9">
+        <f t="shared" ref="O38:R38" si="88">(O4-O9)/O4</f>
+        <v>1.1869436201780582E-2</v>
+      </c>
+      <c r="P38" s="9">
+        <f t="shared" si="88"/>
+        <v>-2.1390374331550915E-2</v>
+      </c>
+      <c r="Q38" s="9">
+        <f t="shared" si="88"/>
+        <v>8.9665653495440714E-2</v>
+      </c>
+      <c r="R38" s="9">
+        <f t="shared" si="88"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="T38" s="9">
+        <f t="shared" ref="T38" si="89">(T4-T9)/T4</f>
+        <v>-0.1432777232580961</v>
+      </c>
+      <c r="U38" s="9">
+        <f t="shared" ref="U38:X40" si="90">(U4-U9)/U4</f>
+        <v>-0.14672216441207087</v>
+      </c>
+      <c r="V38" s="9">
+        <f t="shared" si="90"/>
+        <v>-0.13029315960912052</v>
+      </c>
+      <c r="W38" s="9">
+        <f t="shared" si="90"/>
+        <v>-0.14254859611231122</v>
+      </c>
+      <c r="X38" s="9">
+        <f t="shared" si="90"/>
+        <v>-5.8871627146361308E-2</v>
+      </c>
+      <c r="Y38" s="9">
+        <f t="shared" ref="Y38:AI38" si="91">(Y4-Y9)/Y4</f>
+        <v>6.9482248520709999E-2</v>
+      </c>
+      <c r="Z38" s="9">
         <f t="shared" si="91"/>
-        <v>5.5401662049861494E-2</v>
-      </c>
-      <c r="O38" s="9">
-        <f t="shared" ref="O38:R38" si="92">(O4-O9)/O4</f>
-        <v>1.1869436201780582E-2</v>
-      </c>
-      <c r="P38" s="9">
-        <f t="shared" si="92"/>
-        <v>-2.1390374331550915E-2</v>
-      </c>
-      <c r="Q38" s="9">
-        <f t="shared" si="92"/>
-        <v>0.08</v>
-      </c>
-      <c r="R38" s="9">
-        <f t="shared" si="92"/>
-        <v>0.12000000000000001</v>
-      </c>
-      <c r="T38" s="9">
-        <f t="shared" ref="T38" si="93">(T4-T9)/T4</f>
-        <v>-0.1432777232580961</v>
-      </c>
-      <c r="U38" s="9">
-        <f t="shared" ref="U38:X40" si="94">(U4-U9)/U4</f>
-        <v>-0.14672216441207087</v>
-      </c>
-      <c r="V38" s="9">
-        <f t="shared" si="94"/>
-        <v>-0.13029315960912052</v>
-      </c>
-      <c r="W38" s="9">
-        <f t="shared" si="94"/>
-        <v>-0.14254859611231122</v>
-      </c>
-      <c r="X38" s="9">
-        <f t="shared" si="94"/>
-        <v>-5.8871627146361308E-2</v>
-      </c>
-      <c r="Y38" s="9">
-        <f t="shared" ref="Y38:AI38" si="95">(Y4-Y9)/Y4</f>
-        <v>4.7964403335435488E-2</v>
-      </c>
-      <c r="Z38" s="9">
-        <f t="shared" si="95"/>
-        <v>9.0000000000000052E-2</v>
+        <v>8.9999999999999941E-2</v>
       </c>
       <c r="AA38" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
         <v>0.09</v>
       </c>
       <c r="AB38" s="9">
-        <f t="shared" si="95"/>
-        <v>8.9999999999999927E-2</v>
+        <f t="shared" si="91"/>
+        <v>8.9999999999999955E-2</v>
       </c>
       <c r="AC38" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="AD38" s="9">
+        <f t="shared" si="91"/>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="AE38" s="9">
+        <f t="shared" si="91"/>
         <v>0.09</v>
       </c>
-      <c r="AD38" s="9">
-        <f t="shared" si="95"/>
-        <v>8.9999999999999927E-2</v>
-      </c>
-      <c r="AE38" s="9">
-        <f t="shared" si="95"/>
-        <v>8.9999999999999955E-2</v>
-      </c>
       <c r="AF38" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
         <v>0.09</v>
       </c>
       <c r="AG38" s="9">
-        <f t="shared" si="95"/>
-        <v>8.9999999999999955E-2</v>
+        <f t="shared" si="91"/>
+        <v>0.09</v>
       </c>
       <c r="AH38" s="9">
-        <f t="shared" si="95"/>
-        <v>8.9999999999999955E-2</v>
+        <f t="shared" si="91"/>
+        <v>9.0000000000000024E-2</v>
       </c>
       <c r="AI38" s="9">
-        <f t="shared" si="95"/>
-        <v>8.9999999999999886E-2</v>
+        <f t="shared" si="91"/>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="AL38" t="s">
         <v>70</v>
       </c>
       <c r="AM38" s="7">
         <f>AM37/AI29</f>
-        <v>11.433221766400823</v>
+        <v>28.368449461003618</v>
       </c>
     </row>
     <row r="39" spans="2:39" x14ac:dyDescent="0.3">
@@ -5363,127 +5357,127 @@
         <v>58</v>
       </c>
       <c r="F39" s="9">
+        <f t="shared" si="83"/>
+        <v>-9.7744360902255606E-2</v>
+      </c>
+      <c r="G39" s="9">
+        <f t="shared" si="83"/>
+        <v>-0.25798525798525795</v>
+      </c>
+      <c r="H39" s="9">
+        <f t="shared" si="83"/>
+        <v>-0.3546099290780142</v>
+      </c>
+      <c r="I39" s="9">
+        <f t="shared" si="83"/>
+        <v>-0.20842105263157892</v>
+      </c>
+      <c r="J39" s="9">
+        <f t="shared" si="83"/>
+        <v>-4.7528517110266157E-2</v>
+      </c>
+      <c r="K39" s="9">
+        <f t="shared" si="83"/>
+        <v>-1.7730496453900962E-3</v>
+      </c>
+      <c r="L39" s="9">
+        <f t="shared" si="83"/>
+        <v>1.9047619047619319E-3</v>
+      </c>
+      <c r="M39" s="9">
         <f t="shared" si="87"/>
-        <v>-9.7744360902255606E-2</v>
-      </c>
-      <c r="G39" s="9">
+        <v>-1.1811023622047273E-2</v>
+      </c>
+      <c r="N39" s="9">
         <f t="shared" si="87"/>
-        <v>-0.25798525798525795</v>
-      </c>
-      <c r="H39" s="9">
-        <f t="shared" si="87"/>
-        <v>-0.3546099290780142</v>
-      </c>
-      <c r="I39" s="9">
-        <f t="shared" si="87"/>
-        <v>-0.20842105263157892</v>
-      </c>
-      <c r="J39" s="9">
-        <f t="shared" si="87"/>
-        <v>-4.7528517110266157E-2</v>
-      </c>
-      <c r="K39" s="9">
-        <f t="shared" si="87"/>
-        <v>-1.7730496453900962E-3</v>
-      </c>
-      <c r="L39" s="9">
-        <f t="shared" si="87"/>
-        <v>1.9047619047619319E-3</v>
-      </c>
-      <c r="M39" s="9">
-        <f t="shared" si="91"/>
-        <v>-1.1811023622047273E-2</v>
-      </c>
-      <c r="N39" s="9">
-        <f t="shared" si="91"/>
         <v>-1.6728624535316091E-2</v>
       </c>
       <c r="O39" s="9">
-        <f t="shared" ref="O39:R39" si="96">(O5-O10)/O5</f>
+        <f t="shared" ref="O39:R39" si="92">(O5-O10)/O5</f>
         <v>1.1214953271028064E-2</v>
       </c>
       <c r="P39" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="92"/>
         <v>9.1911764705882359E-2</v>
       </c>
       <c r="Q39" s="9">
-        <f t="shared" si="96"/>
-        <v>5.0000000000000037E-2</v>
+        <f t="shared" si="92"/>
+        <v>0.11604095563139939</v>
       </c>
       <c r="R39" s="9">
-        <f t="shared" si="96"/>
-        <v>3.0000000000000082E-2</v>
+        <f t="shared" si="92"/>
+        <v>9.999999999999995E-2</v>
       </c>
       <c r="T39" s="9">
-        <f t="shared" ref="T39" si="97">(T5-T10)/T5</f>
+        <f t="shared" ref="T39" si="93">(T5-T10)/T5</f>
         <v>-0.20711678832116806</v>
       </c>
       <c r="U39" s="9">
+        <f t="shared" si="90"/>
+        <v>-2.8432732316227623E-2</v>
+      </c>
+      <c r="V39" s="9">
+        <f t="shared" si="90"/>
+        <v>-0.11589403973509933</v>
+      </c>
+      <c r="W39" s="9">
+        <f t="shared" si="90"/>
+        <v>-0.20699071545603498</v>
+      </c>
+      <c r="X39" s="9">
+        <f t="shared" si="90"/>
+        <v>-7.0257611241217799E-3</v>
+      </c>
+      <c r="Y39" s="9">
+        <f t="shared" ref="Y39:AI39" si="94">(Y5-Y10)/Y5</f>
+        <v>8.1606509131827334E-2</v>
+      </c>
+      <c r="Z39" s="9">
         <f t="shared" si="94"/>
-        <v>-2.8432732316227623E-2</v>
-      </c>
-      <c r="V39" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="AA39" s="9">
         <f t="shared" si="94"/>
-        <v>-0.11589403973509933</v>
-      </c>
-      <c r="W39" s="9">
+        <v>0.15000000000000005</v>
+      </c>
+      <c r="AB39" s="9">
         <f t="shared" si="94"/>
-        <v>-0.20699071545603498</v>
-      </c>
-      <c r="X39" s="9">
+        <v>0.17000000000000007</v>
+      </c>
+      <c r="AC39" s="9">
         <f t="shared" si="94"/>
-        <v>-7.0257611241217799E-3</v>
-      </c>
-      <c r="Y39" s="9">
-        <f t="shared" ref="Y39:AI39" si="98">(Y5-Y10)/Y5</f>
-        <v>4.5840851476290086E-2</v>
-      </c>
-      <c r="Z39" s="9">
-        <f t="shared" si="98"/>
-        <v>9.9999999999999992E-2</v>
-      </c>
-      <c r="AA39" s="9">
-        <f t="shared" si="98"/>
-        <v>0.15</v>
-      </c>
-      <c r="AB39" s="9">
-        <f t="shared" si="98"/>
         <v>0.17000000000000004</v>
       </c>
-      <c r="AC39" s="9">
-        <f t="shared" si="98"/>
-        <v>0.1700000000000001</v>
-      </c>
       <c r="AD39" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
+        <v>0.17000000000000004</v>
+      </c>
+      <c r="AE39" s="9">
+        <f t="shared" si="94"/>
         <v>0.17</v>
       </c>
-      <c r="AE39" s="9">
-        <f t="shared" si="98"/>
-        <v>0.17000000000000007</v>
-      </c>
       <c r="AF39" s="9">
-        <f t="shared" si="98"/>
-        <v>0.17000000000000007</v>
+        <f t="shared" si="94"/>
+        <v>0.17000000000000004</v>
       </c>
       <c r="AG39" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.17</v>
       </c>
       <c r="AH39" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
+        <v>0.17</v>
+      </c>
+      <c r="AI39" s="9">
+        <f t="shared" si="94"/>
         <v>0.17000000000000004</v>
-      </c>
-      <c r="AI39" s="9">
-        <f t="shared" si="98"/>
-        <v>0.1700000000000001</v>
       </c>
       <c r="AL39" t="s">
         <v>71</v>
       </c>
       <c r="AM39" s="7">
         <f>Main!D3</f>
-        <v>70.709999999999994</v>
+        <v>132.12</v>
       </c>
     </row>
     <row r="40" spans="2:39" x14ac:dyDescent="0.3">
@@ -5491,127 +5485,127 @@
         <v>59</v>
       </c>
       <c r="F40" s="9">
+        <f t="shared" si="83"/>
+        <v>-3.072916666666667</v>
+      </c>
+      <c r="G40" s="9">
+        <f t="shared" si="83"/>
+        <v>0.26108374384236455</v>
+      </c>
+      <c r="H40" s="9">
+        <f t="shared" si="83"/>
+        <v>0.21717171717171721</v>
+      </c>
+      <c r="I40" s="9">
+        <f t="shared" si="83"/>
+        <v>-4.4031007751937983</v>
+      </c>
+      <c r="J40" s="9">
+        <f t="shared" si="83"/>
+        <v>0.44848484848484849</v>
+      </c>
+      <c r="K40" s="9">
+        <f t="shared" si="83"/>
+        <v>0.31428571428571433</v>
+      </c>
+      <c r="L40" s="9">
+        <f t="shared" si="83"/>
+        <v>0.35211267605633806</v>
+      </c>
+      <c r="M40" s="9">
         <f t="shared" si="87"/>
-        <v>-3.072916666666667</v>
-      </c>
-      <c r="G40" s="9">
+        <v>0.31159420289855078</v>
+      </c>
+      <c r="N40" s="9">
         <f t="shared" si="87"/>
-        <v>0.26108374384236455</v>
-      </c>
-      <c r="H40" s="9">
-        <f t="shared" si="87"/>
-        <v>0.21717171717171721</v>
-      </c>
-      <c r="I40" s="9">
-        <f t="shared" si="87"/>
-        <v>-4.4031007751937983</v>
-      </c>
-      <c r="J40" s="9">
-        <f t="shared" si="87"/>
-        <v>0.44848484848484849</v>
-      </c>
-      <c r="K40" s="9">
-        <f t="shared" si="87"/>
-        <v>0.31428571428571433</v>
-      </c>
-      <c r="L40" s="9">
-        <f t="shared" si="87"/>
-        <v>0.35211267605633806</v>
-      </c>
-      <c r="M40" s="9">
-        <f t="shared" si="91"/>
-        <v>0.31159420289855078</v>
-      </c>
-      <c r="N40" s="9">
-        <f t="shared" si="91"/>
         <v>1.8518518518518615E-2</v>
       </c>
       <c r="O40" s="9">
-        <f t="shared" ref="O40:R40" si="99">(O6-O11)/O6</f>
+        <f t="shared" ref="O40:R40" si="95">(O6-O11)/O6</f>
         <v>0.57037037037037042</v>
       </c>
       <c r="P40" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="95"/>
         <v>0.3984375</v>
       </c>
       <c r="Q40" s="9">
-        <f t="shared" si="99"/>
-        <v>0.50419527078565973</v>
+        <f t="shared" si="95"/>
+        <v>0.44230769230769235</v>
       </c>
       <c r="R40" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="95"/>
         <v>0.31773879142300193</v>
       </c>
       <c r="T40" s="9">
-        <f t="shared" ref="T40" si="100">(T6-T11)/T6</f>
+        <f t="shared" ref="T40" si="96">(T6-T11)/T6</f>
         <v>0.26833073322932915</v>
       </c>
       <c r="U40" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.35087719298245623</v>
       </c>
       <c r="V40" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>-1.1498673740053047</v>
       </c>
       <c r="W40" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>-1.1723300970873785</v>
       </c>
       <c r="X40" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.26325757575757575</v>
       </c>
       <c r="Y40" s="9">
-        <f t="shared" ref="Y40:AI40" si="101">(Y6-Y11)/Y6</f>
-        <v>0.46498728911486015</v>
+        <f t="shared" ref="Y40:AI40" si="97">(Y6-Y11)/Y6</f>
+        <v>0.44711538461538458</v>
       </c>
       <c r="Z40" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
+        <v>0.44</v>
+      </c>
+      <c r="AA40" s="9">
+        <f t="shared" si="97"/>
         <v>0.43999999999999995</v>
       </c>
-      <c r="AA40" s="9">
-        <f t="shared" si="101"/>
+      <c r="AB40" s="9">
+        <f t="shared" si="97"/>
         <v>0.43999999999999995</v>
       </c>
-      <c r="AB40" s="9">
-        <f t="shared" si="101"/>
+      <c r="AC40" s="9">
+        <f t="shared" si="97"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="AD40" s="9">
+        <f t="shared" si="97"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="AE40" s="9">
+        <f t="shared" si="97"/>
         <v>0.43999999999999989</v>
       </c>
-      <c r="AC40" s="9">
-        <f t="shared" si="101"/>
+      <c r="AF40" s="9">
+        <f t="shared" si="97"/>
         <v>0.43999999999999995</v>
       </c>
-      <c r="AD40" s="9">
-        <f t="shared" si="101"/>
-        <v>0.44</v>
-      </c>
-      <c r="AE40" s="9">
-        <f t="shared" si="101"/>
-        <v>0.44</v>
-      </c>
-      <c r="AF40" s="9">
-        <f t="shared" si="101"/>
-        <v>0.43999999999999989</v>
-      </c>
       <c r="AG40" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.43999999999999995</v>
       </c>
       <c r="AH40" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.43999999999999995</v>
       </c>
       <c r="AI40" s="9">
-        <f t="shared" si="101"/>
-        <v>0.44</v>
+        <f t="shared" si="97"/>
+        <v>0.43999999999999995</v>
       </c>
       <c r="AL40" s="1" t="s">
         <v>72</v>
       </c>
       <c r="AM40" s="10">
         <f>AM38/AM39-1</f>
-        <v>-0.83830827653230344</v>
+        <v>-0.7852827016272812</v>
       </c>
     </row>
     <row r="41" spans="2:39" x14ac:dyDescent="0.3">
@@ -5619,31 +5613,31 @@
         <v>50</v>
       </c>
       <c r="F41" s="9">
-        <f t="shared" ref="F41:L41" si="102">F13/F7</f>
+        <f t="shared" ref="F41:L41" si="98">F13/F7</f>
         <v>0.15437837837837823</v>
       </c>
       <c r="G41" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="98"/>
         <v>0.19731104651162795</v>
       </c>
       <c r="H41" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="98"/>
         <v>0.18637873754152831</v>
       </c>
       <c r="I41" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="98"/>
         <v>-1.3243378310844607E-2</v>
       </c>
       <c r="J41" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="98"/>
         <v>0.25861585878397308</v>
       </c>
       <c r="K41" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="98"/>
         <v>0.16113945578231306</v>
       </c>
       <c r="L41" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="98"/>
         <v>0.20405123622281801</v>
       </c>
       <c r="M41" s="9">
@@ -5655,20 +5649,20 @@
         <v>0.38312368972746325</v>
       </c>
       <c r="O41" s="9">
-        <f t="shared" ref="O41:R41" si="103">O13/O7</f>
+        <f t="shared" ref="O41:R41" si="99">O13/O7</f>
         <v>0.27200245323520406</v>
       </c>
       <c r="P41" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="99"/>
         <v>0.26719840478564322</v>
       </c>
       <c r="Q41" s="9">
-        <f t="shared" si="103"/>
-        <v>0.30043759517514618</v>
+        <f t="shared" si="99"/>
+        <v>0.29242920439221731</v>
       </c>
       <c r="R41" s="9">
-        <f t="shared" si="103"/>
-        <v>0.38711559253745564</v>
+        <f t="shared" si="99"/>
+        <v>0.37947874175267604</v>
       </c>
       <c r="T41" s="9">
         <f>T13/T7</f>
@@ -5679,60 +5673,60 @@
         <v>0.20325036000822869</v>
       </c>
       <c r="V41" s="9">
-        <f t="shared" ref="V41:X41" si="104">V13/V7</f>
+        <f t="shared" ref="V41:X41" si="100">V13/V7</f>
         <v>0.12366577718478998</v>
       </c>
       <c r="W41" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.14805370134253365</v>
       </c>
       <c r="X41" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.27446057809743507</v>
       </c>
       <c r="Y41" s="9">
-        <f t="shared" ref="Y41:AI41" si="105">Y13/Y7</f>
-        <v>0.3176466158588282</v>
+        <f t="shared" ref="Y41:AI41" si="101">Y13/Y7</f>
+        <v>0.31610691270347108</v>
       </c>
       <c r="Z41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.33929521786246652</v>
+        <f t="shared" si="101"/>
+        <v>0.33074922064278472</v>
       </c>
       <c r="AA41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.3435168464169096</v>
+        <f t="shared" si="101"/>
+        <v>0.33024320454435968</v>
       </c>
       <c r="AB41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.34555486527276447</v>
+        <f t="shared" si="101"/>
+        <v>0.32685793524514156</v>
       </c>
       <c r="AC41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.34704888430014075</v>
+        <f t="shared" si="101"/>
+        <v>0.32370972605173592</v>
       </c>
       <c r="AD41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.34867372071529767</v>
+        <f t="shared" si="101"/>
+        <v>0.32034856293075403</v>
       </c>
       <c r="AE41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.34941880935900421</v>
+        <f t="shared" si="101"/>
+        <v>0.31665353085110021</v>
       </c>
       <c r="AF41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.35003316908361443</v>
+        <f t="shared" si="101"/>
+        <v>0.31263156305529294</v>
       </c>
       <c r="AG41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.35052293865962769</v>
+        <f t="shared" si="101"/>
+        <v>0.30829191476367956</v>
       </c>
       <c r="AH41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.35101118536219345</v>
+        <f t="shared" si="101"/>
+        <v>0.30364626164892577</v>
       </c>
       <c r="AI41" s="9">
-        <f t="shared" si="105"/>
-        <v>0.35149792177817984</v>
+        <f t="shared" si="101"/>
+        <v>0.29870876006942798</v>
       </c>
       <c r="AL41" t="s">
         <v>73</v>
@@ -5750,15 +5744,15 @@
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
       <c r="J42" s="9">
-        <f t="shared" ref="J42:L42" si="106">J14/F14-1</f>
+        <f t="shared" ref="J42:L42" si="102">J14/F14-1</f>
         <v>-0.12271540469973885</v>
       </c>
       <c r="K42" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>-0.22319474835886222</v>
       </c>
       <c r="L42" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>-9.8795180722891618E-2</v>
       </c>
       <c r="M42" s="9">
@@ -5770,20 +5764,20 @@
         <v>0.17559523809523814</v>
       </c>
       <c r="O42" s="9">
-        <f t="shared" ref="O42:R42" si="107">O14/K14-1</f>
+        <f t="shared" ref="O42:R42" si="103">O14/K14-1</f>
         <v>0.14366197183098595</v>
       </c>
       <c r="P42" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="103"/>
         <v>9.0909090909090828E-2</v>
       </c>
       <c r="Q42" s="9">
-        <f t="shared" si="107"/>
-        <v>0.1570247933884299</v>
+        <f t="shared" si="103"/>
+        <v>0.34159779614325081</v>
       </c>
       <c r="R42" s="9">
-        <f t="shared" si="107"/>
-        <v>0.139240506329114</v>
+        <f t="shared" si="103"/>
+        <v>0.36708860759493667</v>
       </c>
       <c r="T42" s="9"/>
       <c r="U42" s="9">
@@ -5791,59 +5785,59 @@
         <v>0.23684210526315796</v>
       </c>
       <c r="V42" s="9">
-        <f t="shared" ref="V42:X42" si="108">V14/U14-1</f>
+        <f t="shared" ref="V42:X42" si="104">V14/U14-1</f>
         <v>0.45647969052224369</v>
       </c>
       <c r="W42" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="104"/>
         <v>3.5192563081009265E-2</v>
       </c>
       <c r="X42" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="104"/>
         <v>-4.6183450930083469E-2</v>
       </c>
       <c r="Y42" s="9">
-        <f t="shared" ref="Y42:AI42" si="109">Y14/X14-1</f>
-        <v>0.13248150638870215</v>
+        <f t="shared" ref="Y42:AI42" si="105">Y14/X14-1</f>
+        <v>0.23806321452589141</v>
       </c>
       <c r="Z42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AA42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AB42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI42" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5852,31 +5846,31 @@
         <v>61</v>
       </c>
       <c r="F43" s="9">
-        <f t="shared" ref="F43:L43" si="110">F15/F7</f>
+        <f t="shared" ref="F43:L43" si="106">F15/F7</f>
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="G43" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>9.8473837209302334E-2</v>
       </c>
       <c r="H43" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>8.9036544850498348E-2</v>
       </c>
       <c r="I43" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>4.9975012493753128E-2</v>
       </c>
       <c r="J43" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>4.4830484729616135E-2</v>
       </c>
       <c r="K43" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>5.7823129251700675E-2</v>
       </c>
       <c r="L43" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>5.3321417932677986E-2</v>
       </c>
       <c r="M43" s="9">
@@ -5888,20 +5882,20 @@
         <v>3.8085255066387144E-2</v>
       </c>
       <c r="O43" s="9">
-        <f t="shared" ref="O43:R43" si="111">O15/O7</f>
+        <f t="shared" ref="O43:R43" si="107">O15/O7</f>
         <v>6.8383931309414281E-2</v>
       </c>
       <c r="P43" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="107"/>
         <v>6.0069790628115662E-2</v>
       </c>
       <c r="Q43" s="9">
-        <f t="shared" si="111"/>
-        <v>5.5330890755170441E-2</v>
+        <f t="shared" si="107"/>
+        <v>8.0909266037372377E-2</v>
       </c>
       <c r="R43" s="9">
-        <f t="shared" si="111"/>
-        <v>3.9435675483826441E-2</v>
+        <f t="shared" si="107"/>
+        <v>6.8442521970049561E-2</v>
       </c>
       <c r="T43" s="9">
         <f>T15/T7</f>
@@ -5912,60 +5906,60 @@
         <v>8.8973462250565738E-2</v>
       </c>
       <c r="V43" s="9">
-        <f t="shared" ref="V43:X43" si="112">V15/V7</f>
+        <f t="shared" ref="V43:X43" si="108">V15/V7</f>
         <v>7.5800533689126065E-2</v>
       </c>
       <c r="W43" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>6.7426685667141689E-2</v>
       </c>
       <c r="X43" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>4.6139231917492196E-2</v>
       </c>
       <c r="Y43" s="9">
-        <f t="shared" ref="Y43:AI43" si="113">Y15/Y7</f>
-        <v>5.3323681023906021E-2</v>
+        <f t="shared" ref="Y43:AI43" si="109">Y15/Y7</f>
+        <v>7.0007182817890284E-2</v>
       </c>
       <c r="Z43" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v>0.05</v>
       </c>
       <c r="AA43" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v>0.05</v>
       </c>
       <c r="AB43" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
+        <v>5.000000000000001E-2</v>
+      </c>
+      <c r="AC43" s="9">
+        <f t="shared" si="109"/>
         <v>0.05</v>
       </c>
-      <c r="AC43" s="9">
-        <f t="shared" si="113"/>
+      <c r="AD43" s="9">
+        <f t="shared" si="109"/>
         <v>0.05</v>
       </c>
-      <c r="AD43" s="9">
-        <f t="shared" si="113"/>
+      <c r="AE43" s="9">
+        <f t="shared" si="109"/>
         <v>0.05</v>
       </c>
-      <c r="AE43" s="9">
-        <f t="shared" si="113"/>
+      <c r="AF43" s="9">
+        <f t="shared" si="109"/>
         <v>0.05</v>
       </c>
-      <c r="AF43" s="9">
-        <f t="shared" si="113"/>
+      <c r="AG43" s="9">
+        <f t="shared" si="109"/>
         <v>0.05</v>
       </c>
-      <c r="AG43" s="9">
-        <f t="shared" si="113"/>
+      <c r="AH43" s="9">
+        <f t="shared" si="109"/>
         <v>5.000000000000001E-2</v>
       </c>
-      <c r="AH43" s="9">
-        <f t="shared" si="113"/>
-        <v>0.05</v>
-      </c>
       <c r="AI43" s="9">
-        <f t="shared" si="113"/>
-        <v>0.05</v>
+        <f t="shared" si="109"/>
+        <v>5.000000000000001E-2</v>
       </c>
     </row>
     <row r="44" spans="2:39" x14ac:dyDescent="0.3">
@@ -5977,40 +5971,40 @@
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" s="9">
-        <f t="shared" ref="J44" si="114">J16/F16-1</f>
+        <f t="shared" ref="J44" si="110">J16/F16-1</f>
         <v>-0.37447698744769875</v>
       </c>
       <c r="K44" s="9">
-        <f t="shared" ref="K44" si="115">K16/G16-1</f>
+        <f t="shared" ref="K44" si="111">K16/G16-1</f>
         <v>-0.15742793791574283</v>
       </c>
       <c r="L44" s="9">
-        <f t="shared" ref="L44" si="116">L16/H16-1</f>
+        <f t="shared" ref="L44" si="112">L16/H16-1</f>
         <v>-0.14352941176470591</v>
       </c>
       <c r="M44" s="9">
-        <f t="shared" ref="M44:N44" si="117">M16/I16-1</f>
+        <f t="shared" ref="M44:N44" si="113">M16/I16-1</f>
         <v>-0.13824884792626724</v>
       </c>
       <c r="N44" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="113"/>
         <v>0.78260869565217384</v>
       </c>
       <c r="O44" s="9">
-        <f t="shared" ref="O44" si="118">O16/K16-1</f>
+        <f t="shared" ref="O44" si="114">O16/K16-1</f>
         <v>0.18157894736842106</v>
       </c>
       <c r="P44" s="9">
-        <f t="shared" ref="P44" si="119">P16/L16-1</f>
+        <f t="shared" ref="P44" si="115">P16/L16-1</f>
         <v>0.25824175824175821</v>
       </c>
       <c r="Q44" s="9">
-        <f t="shared" ref="Q44" si="120">Q16/M16-1</f>
-        <v>0.25668449197860976</v>
+        <f t="shared" ref="Q44" si="116">Q16/M16-1</f>
+        <v>0.41978609625668462</v>
       </c>
       <c r="R44" s="9">
-        <f t="shared" ref="R44" si="121">R16/N16-1</f>
-        <v>0.12570356472795496</v>
+        <f t="shared" ref="R44" si="117">R16/N16-1</f>
+        <v>0.31332082551594764</v>
       </c>
       <c r="T44" s="9"/>
       <c r="U44" s="9">
@@ -6018,59 +6012,59 @@
         <v>0.14098972922502351</v>
       </c>
       <c r="V44" s="9">
-        <f t="shared" ref="V44:X44" si="122">V16/U16-1</f>
+        <f t="shared" ref="V44:X44" si="118">V16/U16-1</f>
         <v>0.37234042553191471</v>
       </c>
       <c r="W44" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="118"/>
         <v>-4.054859868813343E-2</v>
       </c>
       <c r="X44" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="118"/>
         <v>2.6103169670602888E-2</v>
       </c>
       <c r="Y44" s="9">
-        <f t="shared" ref="Y44:AI44" si="123">Y16/X16-1</f>
-        <v>0.19745608721986652</v>
+        <f t="shared" ref="Y44:AI44" si="119">Y16/X16-1</f>
+        <v>0.29497274379164118</v>
       </c>
       <c r="Z44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AA44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AB44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AC44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI44" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -6079,31 +6073,31 @@
         <v>63</v>
       </c>
       <c r="F45" s="9">
-        <f t="shared" ref="F45:L45" si="124">F18/F7</f>
+        <f t="shared" ref="F45:L45" si="120">F18/F7</f>
         <v>-8.7783783783783931E-2</v>
       </c>
       <c r="G45" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="120"/>
         <v>-0.23110465116279069</v>
       </c>
       <c r="H45" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="120"/>
         <v>-0.18172757475083048</v>
       </c>
       <c r="I45" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="120"/>
         <v>-0.25937031484257872</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="120"/>
         <v>3.5864387783692941E-2</v>
       </c>
       <c r="K45" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="120"/>
         <v>-0.20918367346938757</v>
       </c>
       <c r="L45" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="120"/>
         <v>-6.9109323801012784E-2</v>
       </c>
       <c r="M45" s="9">
@@ -6115,20 +6109,20 @@
         <v>0.18291404612159323</v>
       </c>
       <c r="O45" s="9">
-        <f t="shared" ref="O45:R45" si="125">O18/O7</f>
+        <f t="shared" ref="O45:R45" si="121">O18/O7</f>
         <v>-5.8570990493713476E-2</v>
       </c>
       <c r="P45" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>-8.7238285144565237E-3</v>
       </c>
       <c r="Q45" s="9">
-        <f t="shared" si="125"/>
-        <v>3.100021410649012E-2</v>
+        <f t="shared" si="121"/>
+        <v>1.5411288769023309E-2</v>
       </c>
       <c r="R45" s="9">
-        <f t="shared" si="125"/>
-        <v>0.1751488368118885</v>
+        <f t="shared" si="121"/>
+        <v>0.14129876529690361</v>
       </c>
       <c r="T45" s="9">
         <f>T18/T7</f>
@@ -6139,60 +6133,60 @@
         <v>-0.11777412055132701</v>
       </c>
       <c r="V45" s="9">
-        <f t="shared" ref="V45:X45" si="126">V18/V7</f>
+        <f t="shared" ref="V45:X45" si="122">V18/V7</f>
         <v>-0.21756170780520326</v>
       </c>
       <c r="W45" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>-0.15697892447311179</v>
       </c>
       <c r="X45" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>1.5402361243045028E-2</v>
       </c>
       <c r="Y45" s="9">
-        <f t="shared" ref="Y45:AI45" si="127">Y18/Y7</f>
-        <v>5.5310090907170664E-2</v>
+        <f t="shared" ref="Y45:AI45" si="123">Y18/Y7</f>
+        <v>4.4829079284146284E-2</v>
       </c>
       <c r="Z45" s="9">
-        <f t="shared" si="127"/>
-        <v>8.9689744109432062E-2</v>
+        <f t="shared" si="123"/>
+        <v>0.1047618295817937</v>
       </c>
       <c r="AA45" s="9">
-        <f t="shared" si="127"/>
-        <v>0.10263442388341323</v>
+        <f t="shared" si="123"/>
+        <v>0.12167739317924151</v>
       </c>
       <c r="AB45" s="9">
-        <f t="shared" si="127"/>
-        <v>0.11514949014949574</v>
+        <f t="shared" si="123"/>
+        <v>0.13270886031921075</v>
       </c>
       <c r="AC45" s="9">
-        <f t="shared" si="127"/>
-        <v>0.12626659826188463</v>
+        <f t="shared" si="123"/>
+        <v>0.14004207547244707</v>
       </c>
       <c r="AD45" s="9">
-        <f t="shared" si="127"/>
-        <v>0.135059963909202</v>
+        <f t="shared" si="123"/>
+        <v>0.14717948111134357</v>
       </c>
       <c r="AE45" s="9">
-        <f t="shared" si="127"/>
-        <v>0.13988417875236242</v>
+        <f t="shared" si="123"/>
+        <v>0.15388192399402198</v>
       </c>
       <c r="AF45" s="9">
-        <f t="shared" si="127"/>
-        <v>0.14319862261041594</v>
+        <f t="shared" si="123"/>
+        <v>0.15957864733865226</v>
       </c>
       <c r="AG45" s="9">
-        <f t="shared" si="127"/>
-        <v>0.14505949402646884</v>
+        <f t="shared" si="123"/>
+        <v>0.16430499135558024</v>
       </c>
       <c r="AH45" s="9">
-        <f t="shared" si="127"/>
-        <v>0.14691213482740209</v>
+        <f t="shared" si="123"/>
+        <v>0.16809906071572783</v>
       </c>
       <c r="AI45" s="9">
-        <f t="shared" si="127"/>
-        <v>0.14875656243075708</v>
+        <f t="shared" si="123"/>
+        <v>0.17100166531862374</v>
       </c>
     </row>
     <row r="46" spans="2:39" x14ac:dyDescent="0.3">
@@ -6200,31 +6194,31 @@
         <v>34</v>
       </c>
       <c r="F46" s="9">
-        <f t="shared" ref="F46:L46" si="128">F26/F25</f>
+        <f t="shared" ref="F46:L46" si="124">F26/F25</f>
         <v>7.1005917159763218E-2</v>
       </c>
       <c r="G46" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-4.0268456375838922E-3</v>
       </c>
       <c r="H46" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-2.8943560057887135E-3</v>
       </c>
       <c r="I46" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-3.582089552238806E-3</v>
       </c>
       <c r="J46" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>0.16666666666666627</v>
       </c>
       <c r="K46" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>8.7412587412587471E-3</v>
       </c>
       <c r="L46" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-1.4876033057851241E-2</v>
       </c>
       <c r="M46" s="9">
@@ -6236,19 +6230,19 @@
         <v>3.7950664136622405E-3</v>
       </c>
       <c r="O46" s="9">
-        <f t="shared" ref="O46:R46" si="129">O26/O25</f>
+        <f t="shared" ref="O46:R46" si="125">O26/O25</f>
         <v>-1.7391304347826111E-2</v>
       </c>
       <c r="P46" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="125"/>
         <v>-2.4330900243309032E-2</v>
       </c>
       <c r="Q46" s="9">
-        <f t="shared" si="129"/>
-        <v>0</v>
+        <f t="shared" si="125"/>
+        <v>-1.3333333333333332E-2</v>
       </c>
       <c r="R46" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="T46" s="9">
@@ -6260,59 +6254,59 @@
         <v>-5.2029136316337123E-3</v>
       </c>
       <c r="V46" s="9">
-        <f t="shared" ref="V46:X46" si="130">V26/V25</f>
+        <f t="shared" ref="V46:X46" si="126">V26/V25</f>
         <v>-3.5043007327174285E-3</v>
       </c>
       <c r="W46" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>-6.2030688867123745E-3</v>
       </c>
       <c r="X46" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>-3.3582089552238487E-2</v>
       </c>
       <c r="Y46" s="9">
-        <f t="shared" ref="Y46:AI46" si="131">Y26/Y25</f>
-        <v>3.0851050467250028E-2</v>
+        <f t="shared" ref="Y46:AI46" si="127">Y26/Y25</f>
+        <v>0.14624410722273648</v>
       </c>
       <c r="Z46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
       <c r="AA46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
       <c r="AB46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
       <c r="AC46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
       <c r="AD46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
       <c r="AE46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
       <c r="AF46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
       <c r="AG46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
       <c r="AH46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
       <c r="AI46" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.05</v>
       </c>
     </row>
@@ -6321,31 +6315,31 @@
         <v>35</v>
       </c>
       <c r="F47" s="9">
-        <f t="shared" ref="F47:L47" si="132">F27/F25</f>
+        <f t="shared" ref="F47:L47" si="128">F27/F25</f>
         <v>0</v>
       </c>
       <c r="G47" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="128"/>
         <v>4.5637583892617448E-2</v>
       </c>
       <c r="H47" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="128"/>
         <v>4.3415340086830699E-2</v>
       </c>
       <c r="I47" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="128"/>
         <v>-5.3731343283582094E-3</v>
       </c>
       <c r="J47" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="128"/>
         <v>-8.3333333333333134E-2</v>
       </c>
       <c r="K47" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="128"/>
         <v>-1.7482517482517494E-2</v>
       </c>
       <c r="L47" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="128"/>
         <v>-9.9173553719008271E-3</v>
       </c>
       <c r="M47" s="9">
@@ -6357,19 +6351,19 @@
         <v>3.7950664136622405E-3</v>
       </c>
       <c r="O47" s="9">
-        <f t="shared" ref="O47:R47" si="133">O27/O25</f>
+        <f t="shared" ref="O47:R47" si="129">O27/O25</f>
         <v>-1.7391304347826111E-2</v>
       </c>
       <c r="P47" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>-9.7323600973236134E-3</v>
       </c>
       <c r="Q47" s="9">
-        <f t="shared" si="133"/>
-        <v>0</v>
+        <f t="shared" si="129"/>
+        <v>4.4444444444444444E-3</v>
       </c>
       <c r="R47" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="T47" s="9">
@@ -6381,59 +6375,59 @@
         <v>0.15036420395421426</v>
       </c>
       <c r="V47" s="9">
-        <f t="shared" ref="V47:X47" si="134">V27/V25</f>
+        <f t="shared" ref="V47:X47" si="130">V27/V25</f>
         <v>4.3644472762026154E-2</v>
       </c>
       <c r="W47" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="130"/>
         <v>1.9262161279791058E-2</v>
       </c>
       <c r="X47" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="130"/>
         <v>-7.8358208955223149E-2</v>
       </c>
       <c r="Y47" s="9">
-        <f t="shared" ref="Y47:AI47" si="135">Y27/Y25</f>
-        <v>1.7629171695571447E-2</v>
+        <f t="shared" ref="Y47:AI47" si="131">Y27/Y25</f>
+        <v>6.0218161797597383E-2</v>
       </c>
       <c r="Z47" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>0.02</v>
       </c>
       <c r="AA47" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>0.02</v>
       </c>
       <c r="AB47" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>0.02</v>
       </c>
       <c r="AC47" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>0.02</v>
       </c>
       <c r="AD47" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>0.02</v>
       </c>
       <c r="AE47" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>0.02</v>
       </c>
       <c r="AF47" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>0.02</v>
       </c>
       <c r="AG47" s="9">
-        <f t="shared" si="135"/>
-        <v>2.0000000000000004E-2</v>
+        <f t="shared" si="131"/>
+        <v>0.02</v>
       </c>
       <c r="AH47" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>0.02</v>
       </c>
       <c r="AI47" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>0.02</v>
       </c>
     </row>
@@ -6442,31 +6436,31 @@
         <v>64</v>
       </c>
       <c r="F48" s="9">
-        <f t="shared" ref="F48:L48" si="136">F28/F7</f>
+        <f t="shared" ref="F48:L48" si="132">F28/F7</f>
         <v>-0.10183783783783799</v>
       </c>
       <c r="G48" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>-0.25944767441860461</v>
       </c>
       <c r="H48" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>-0.22026578073089689</v>
       </c>
       <c r="I48" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>-0.42228885557221391</v>
       </c>
       <c r="J48" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>1.2328383300644471E-2</v>
       </c>
       <c r="K48" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>-0.24532312925170049</v>
       </c>
       <c r="L48" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>-0.18468871015787905</v>
       </c>
       <c r="M48" s="9">
@@ -6478,20 +6472,20 @@
         <v>0.18273934311670154</v>
       </c>
       <c r="O48" s="9">
-        <f t="shared" ref="O48:R48" si="137">O28/O7</f>
+        <f t="shared" ref="O48:R48" si="133">O28/O7</f>
         <v>-7.2983747316773886E-2</v>
       </c>
       <c r="P48" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>-0.10593220338983039</v>
       </c>
       <c r="Q48" s="9">
-        <f t="shared" si="137"/>
-        <v>1.8971759594496547E-2</v>
+        <f t="shared" si="133"/>
+        <v>-4.3729531882103635E-2</v>
       </c>
       <c r="R48" s="9">
-        <f t="shared" si="137"/>
-        <v>0.16693307108609132</v>
+        <f t="shared" si="133"/>
+        <v>0.13445451309989864</v>
       </c>
       <c r="T48" s="9">
         <f>T28/T7</f>
@@ -6502,60 +6496,60 @@
         <v>-0.16899814852910935</v>
       </c>
       <c r="V48" s="9">
-        <f t="shared" ref="V48:X48" si="138">V28/V7</f>
+        <f t="shared" ref="V48:X48" si="134">V28/V7</f>
         <v>-0.25125083388925934</v>
       </c>
       <c r="W48" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>-0.22673066826670665</v>
       </c>
       <c r="X48" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>-2.0219839869724695E-2</v>
       </c>
       <c r="Y48" s="9">
-        <f t="shared" ref="Y48:AI48" si="139">Y28/Y7</f>
-        <v>2.4651828905203291E-2</v>
+        <f t="shared" ref="Y48:AI48" si="135">Y28/Y7</f>
+        <v>4.6659989681022956E-3</v>
       </c>
       <c r="Z48" s="9">
-        <f t="shared" si="139"/>
-        <v>7.2268643958378842E-2</v>
+        <f t="shared" si="135"/>
+        <v>8.681867240799658E-2</v>
       </c>
       <c r="AA48" s="9">
-        <f t="shared" si="139"/>
-        <v>8.5143534760654588E-2</v>
+        <f t="shared" si="135"/>
+        <v>0.10391412001853949</v>
       </c>
       <c r="AB48" s="9">
-        <f t="shared" si="139"/>
-        <v>9.7493115535120342E-2</v>
+        <f t="shared" si="135"/>
+        <v>0.11513880755746307</v>
       </c>
       <c r="AC48" s="9">
-        <f t="shared" si="139"/>
-        <v>0.10843208076691603</v>
+        <f t="shared" si="135"/>
+        <v>0.12263533473840643</v>
       </c>
       <c r="AD48" s="9">
-        <f t="shared" si="139"/>
-        <v>0.11702600593468929</v>
+        <f t="shared" si="135"/>
+        <v>0.12990182299260827</v>
       </c>
       <c r="AE48" s="9">
-        <f t="shared" si="139"/>
-        <v>0.12172643150401183</v>
+        <f t="shared" si="135"/>
+        <v>0.13672390635717921</v>
       </c>
       <c r="AF48" s="9">
-        <f t="shared" si="139"/>
-        <v>0.12495045431260481</v>
+        <f t="shared" si="135"/>
+        <v>0.14257223086185267</v>
       </c>
       <c r="AG48" s="9">
-        <f t="shared" si="139"/>
-        <v>0.12675296409569661</v>
+        <f t="shared" si="135"/>
+        <v>0.14748114010144714</v>
       </c>
       <c r="AH48" s="9">
-        <f t="shared" si="139"/>
-        <v>0.12854746765869463</v>
+        <f t="shared" si="135"/>
+        <v>0.15148756810038627</v>
       </c>
       <c r="AI48" s="9">
-        <f t="shared" si="139"/>
-        <v>0.13033398145322853</v>
+        <f t="shared" si="135"/>
+        <v>0.15463097746161467</v>
       </c>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.3">
@@ -6672,16 +6666,19 @@
         <v>597.19999999999993</v>
       </c>
     </row>
-    <row r="65" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
+    <row r="65" spans="2:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="12" t="s">
         <v>91</v>
       </c>
       <c r="P65" s="11">
         <f>P58+P64</f>
         <v>2530.5</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q65" s="11">
+        <v>2638.2</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>92</v>
       </c>
@@ -6689,7 +6686,7 @@
         <v>144.80000000000001</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>93</v>
       </c>
@@ -6697,7 +6694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>94</v>
       </c>
@@ -6705,7 +6702,7 @@
         <v>116.6</v>
       </c>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>84</v>
       </c>
@@ -6713,7 +6710,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>88</v>
       </c>
@@ -6721,7 +6718,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>5</v>
       </c>
@@ -6729,7 +6726,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>95</v>
       </c>
@@ -6737,7 +6734,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>96</v>
       </c>
@@ -6745,7 +6742,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="74" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
         <v>97</v>
       </c>
@@ -6754,7 +6751,7 @@
         <v>387.4</v>
       </c>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>84</v>
       </c>
@@ -6762,7 +6759,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>88</v>
       </c>
@@ -6770,7 +6767,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>5</v>
       </c>
@@ -6778,7 +6775,7 @@
         <v>219.9</v>
       </c>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>95</v>
       </c>
@@ -6786,7 +6783,7 @@
         <v>1126.2</v>
       </c>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>96</v>
       </c>
@@ -6794,7 +6791,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>98</v>
       </c>
@@ -6819,8 +6816,8 @@
         <v>619.4</v>
       </c>
     </row>
-    <row r="83" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="1" t="s">
+    <row r="83" spans="2:16" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="12" t="s">
         <v>101</v>
       </c>
       <c r="P83" s="11">

--- a/Financial Analysis/BE.xlsx
+++ b/Financial Analysis/BE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3C382E-3192-43A2-906C-26F11F31C0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38BE040-353A-49BA-AE3E-81878C73882E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FD927F57-917F-4496-A6AC-5E97F081D2C4}"/>
   </bookViews>
@@ -25,8 +25,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="AD7" authorId="0" shapeId="0" xr:uid="{B50EEE87-8267-44E9-AB65-2A926AB1D898}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+(Q425) guidance of 3.1-3.3b</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="106">
   <si>
     <t>BE</t>
   </si>
@@ -332,6 +366,18 @@
   </si>
   <si>
     <t>L+S/E</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -341,7 +387,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,6 +425,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -442,14 +501,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -466,7 +525,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11269980" y="7620"/>
+          <a:off x="11871960" y="7620"/>
           <a:ext cx="0" cy="9060180"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -492,14 +551,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -516,7 +575,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15521940" y="7620"/>
+          <a:off x="18577560" y="7620"/>
           <a:ext cx="0" cy="9608820"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -865,17 +924,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="7">
-        <v>132.12</v>
+        <v>147.55000000000001</v>
       </c>
       <c r="E3" s="3">
-        <v>45959</v>
+        <v>46076</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45959</v>
+        <v>46076</v>
       </c>
       <c r="G3" s="3">
-        <v>46058</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -883,11 +942,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <f>280.5</f>
+        <v>280.5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -896,7 +955,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>31246.38</v>
+        <v>41387.775000000001</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -904,11 +963,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>595.1+8.5+5.9+23.5</f>
-        <v>633</v>
+        <f>2454.1</f>
+        <v>2454.1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -916,11 +975,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>36.6+1.4+209.8+1128+2.8</f>
-        <v>1378.6</v>
+        <f>51.3+4.2+192.5+2613.7</f>
+        <v>2861.7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s">
         <v>75</v>
@@ -932,7 +991,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>-745.59999999999991</v>
+        <v>-407.59999999999991</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -941,7 +1000,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>31991.98</v>
+        <v>41795.375</v>
       </c>
     </row>
   </sheetData>
@@ -950,16 +1009,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53B87E8-B0FD-46B4-8D96-88D1F839B6F5}">
-  <dimension ref="B2:EO83"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53B87E8-B0FD-46B4-8D96-88D1F839B6F5}">
+  <dimension ref="B2:ES83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.44140625" customWidth="1"/>
-    <col min="39" max="39" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.44140625" customWidth="1"/>
+    <col min="43" max="43" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:39" x14ac:dyDescent="0.3">
       <c r="C2" s="5" t="s">
         <v>38</v>
       </c>
@@ -1008,56 +1067,68 @@
       <c r="R2" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="T2">
+      <c r="S2" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="X2">
         <v>2020</v>
       </c>
-      <c r="U2">
+      <c r="Y2">
         <v>2021</v>
       </c>
-      <c r="V2">
+      <c r="Z2">
         <v>2022</v>
       </c>
-      <c r="W2">
+      <c r="AA2">
         <v>2023</v>
       </c>
-      <c r="X2">
+      <c r="AB2">
         <v>2024</v>
       </c>
-      <c r="Y2">
+      <c r="AC2">
         <v>2025</v>
       </c>
-      <c r="Z2">
+      <c r="AD2">
         <v>2026</v>
       </c>
-      <c r="AA2">
+      <c r="AE2">
         <v>2027</v>
       </c>
-      <c r="AB2">
+      <c r="AF2">
         <v>2028</v>
       </c>
-      <c r="AC2">
+      <c r="AG2">
         <v>2029</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2030</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2031</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2032</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2033</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2034</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -1098,72 +1169,87 @@
         <v>384.3</v>
       </c>
       <c r="R3" s="4">
-        <f>N3*1.2</f>
-        <v>566.04</v>
+        <v>638.5</v>
+      </c>
+      <c r="S3" s="4">
+        <f>O3*1.5</f>
+        <v>317.85000000000002</v>
       </c>
       <c r="T3" s="4">
+        <f>P3*1.5</f>
+        <v>444.90000000000003</v>
+      </c>
+      <c r="U3" s="4">
+        <f>Q3*1.6</f>
+        <v>614.88000000000011</v>
+      </c>
+      <c r="V3" s="4">
+        <f>R3*1.5</f>
+        <v>957.75</v>
+      </c>
+      <c r="X3" s="4">
         <v>518.6</v>
       </c>
-      <c r="U3" s="4">
+      <c r="Y3" s="4">
         <v>663.5</v>
       </c>
-      <c r="V3" s="4">
+      <c r="Z3" s="4">
         <v>880.7</v>
       </c>
-      <c r="W3" s="4">
+      <c r="AA3" s="4">
         <f>SUM(G3:J3)</f>
         <v>975.2</v>
       </c>
-      <c r="X3" s="4">
+      <c r="AB3" s="4">
         <f>SUM(K3:N3)</f>
         <v>1085.2</v>
       </c>
-      <c r="Y3" s="4">
+      <c r="AC3" s="4">
         <f>SUM(O3:R3)</f>
-        <v>1458.84</v>
-      </c>
-      <c r="Z3" s="4">
-        <f>Y3*1.25</f>
-        <v>1823.55</v>
-      </c>
-      <c r="AA3" s="4">
-        <f>Z3*1.15</f>
-        <v>2097.0825</v>
-      </c>
-      <c r="AB3" s="4">
-        <f>AA3*1.12</f>
-        <v>2348.7324000000003</v>
-      </c>
-      <c r="AC3" s="4">
-        <f>AB3*1.1</f>
-        <v>2583.6056400000007</v>
+        <v>1531.3</v>
       </c>
       <c r="AD3" s="4">
-        <f t="shared" ref="AD3:AI3" si="0">AC3*1.1</f>
-        <v>2841.9662040000012</v>
+        <f>SUM(S3:V3)</f>
+        <v>2335.38</v>
       </c>
       <c r="AE3" s="4">
-        <f t="shared" si="0"/>
-        <v>3126.1628244000017</v>
+        <f>AD3*1.3</f>
+        <v>3035.9940000000001</v>
       </c>
       <c r="AF3" s="4">
-        <f t="shared" si="0"/>
-        <v>3438.779106840002</v>
+        <f>AE3*1.15</f>
+        <v>3491.3930999999998</v>
       </c>
       <c r="AG3" s="4">
-        <f t="shared" si="0"/>
-        <v>3782.6570175240026</v>
+        <f>AF3*1.1</f>
+        <v>3840.5324100000003</v>
       </c>
       <c r="AH3" s="4">
-        <f t="shared" si="0"/>
-        <v>4160.9227192764029</v>
+        <f t="shared" ref="AH3:AM3" si="0">AG3*1.1</f>
+        <v>4224.5856510000003</v>
       </c>
       <c r="AI3" s="4">
         <f t="shared" si="0"/>
-        <v>4577.0149912040433</v>
-      </c>
-    </row>
-    <row r="4" spans="2:35" x14ac:dyDescent="0.3">
+        <v>4647.044216100001</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="0"/>
+        <v>5111.7486377100013</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="0"/>
+        <v>5622.9235014810019</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="0"/>
+        <v>6185.2158516291029</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="0"/>
+        <v>6803.7374367920138</v>
+      </c>
+    </row>
+    <row r="4" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -1204,72 +1290,87 @@
         <v>65.8</v>
       </c>
       <c r="R4" s="4">
-        <f>N4*2.2</f>
-        <v>79.420000000000016</v>
+        <v>67.3</v>
+      </c>
+      <c r="S4" s="4">
+        <f>O4*1.9</f>
+        <v>64.03</v>
       </c>
       <c r="T4" s="4">
+        <f>P4*2.2</f>
+        <v>82.28</v>
+      </c>
+      <c r="U4" s="4">
+        <f>Q4*1.5</f>
+        <v>98.699999999999989</v>
+      </c>
+      <c r="V4" s="4">
+        <f>R4*1.55</f>
+        <v>104.315</v>
+      </c>
+      <c r="X4" s="4">
         <v>101.9</v>
       </c>
-      <c r="U4" s="4">
+      <c r="Y4" s="4">
         <v>96.1</v>
       </c>
-      <c r="V4" s="4">
+      <c r="Z4" s="4">
         <v>92.1</v>
       </c>
-      <c r="W4" s="4">
+      <c r="AA4" s="4">
         <f>SUM(G4:J4)</f>
         <v>92.6</v>
       </c>
-      <c r="X4" s="4">
+      <c r="AB4" s="4">
         <f>SUM(K4:N4)</f>
         <v>122.30000000000001</v>
       </c>
-      <c r="Y4" s="4">
-        <f t="shared" ref="Y4:Y6" si="1">SUM(O4:R4)</f>
-        <v>216.32</v>
-      </c>
-      <c r="Z4" s="4">
-        <f>Y4*1.5</f>
-        <v>324.48</v>
-      </c>
-      <c r="AA4" s="4">
-        <f>Z4*1.4</f>
-        <v>454.27199999999999</v>
-      </c>
-      <c r="AB4" s="4">
-        <f>AA4*1.3</f>
-        <v>590.55359999999996</v>
-      </c>
       <c r="AC4" s="4">
-        <f>AB4*1.2</f>
-        <v>708.66431999999998</v>
+        <f t="shared" ref="AC4:AC6" si="1">SUM(O4:R4)</f>
+        <v>204.2</v>
       </c>
       <c r="AD4" s="4">
-        <f t="shared" ref="AD4:AI4" si="2">AC4*1.2</f>
-        <v>850.39718399999992</v>
+        <f t="shared" ref="AD4:AD6" si="2">SUM(S4:V4)</f>
+        <v>349.32499999999999</v>
       </c>
       <c r="AE4" s="4">
-        <f t="shared" si="2"/>
-        <v>1020.4766207999999</v>
+        <f>AD4*1.4</f>
+        <v>489.05499999999995</v>
       </c>
       <c r="AF4" s="4">
-        <f t="shared" si="2"/>
-        <v>1224.5719449599999</v>
+        <f>AE4*1.3</f>
+        <v>635.77149999999995</v>
       </c>
       <c r="AG4" s="4">
-        <f t="shared" si="2"/>
-        <v>1469.4863339519998</v>
+        <f>AF4*1.2</f>
+        <v>762.92579999999987</v>
       </c>
       <c r="AH4" s="4">
-        <f t="shared" si="2"/>
-        <v>1763.3836007423997</v>
+        <f>AG4*1.1</f>
+        <v>839.21837999999991</v>
       </c>
       <c r="AI4" s="4">
-        <f t="shared" si="2"/>
-        <v>2116.0603208908797</v>
-      </c>
-    </row>
-    <row r="5" spans="2:35" x14ac:dyDescent="0.3">
+        <f>AH4*1.05</f>
+        <v>881.1792989999999</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" ref="AJ4:AM4" si="3">AI4*1.05</f>
+        <v>925.23826394999992</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="3"/>
+        <v>971.50017714749993</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="3"/>
+        <v>1020.0751860048749</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="3"/>
+        <v>1071.0789453051186</v>
+      </c>
+    </row>
+    <row r="5" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -1310,72 +1411,87 @@
         <v>58.6</v>
       </c>
       <c r="R5" s="4">
-        <f>N5*1.2</f>
-        <v>64.559999999999988</v>
+        <v>61.7</v>
+      </c>
+      <c r="S5" s="4">
+        <f>O5*1.1</f>
+        <v>58.85</v>
       </c>
       <c r="T5" s="4">
+        <f t="shared" ref="T5:V5" si="4">P5*1.1</f>
+        <v>59.84</v>
+      </c>
+      <c r="U5" s="4">
+        <f t="shared" si="4"/>
+        <v>64.460000000000008</v>
+      </c>
+      <c r="V5" s="4">
+        <f t="shared" si="4"/>
+        <v>67.87</v>
+      </c>
+      <c r="X5" s="4">
         <v>109.6</v>
       </c>
-      <c r="U5" s="4">
+      <c r="Y5" s="4">
         <v>144.19999999999999</v>
       </c>
-      <c r="V5" s="4">
+      <c r="Z5" s="4">
         <v>151</v>
       </c>
-      <c r="W5" s="4">
+      <c r="AA5" s="4">
         <f>SUM(G5:J5)</f>
         <v>183.1</v>
       </c>
-      <c r="X5" s="4">
+      <c r="AB5" s="4">
         <f>SUM(K5:N5)</f>
         <v>213.5</v>
       </c>
-      <c r="Y5" s="4">
+      <c r="AC5" s="4">
         <f t="shared" si="1"/>
-        <v>231.06</v>
-      </c>
-      <c r="Z5" s="4">
-        <f>Y5*1.07</f>
-        <v>247.23420000000002</v>
-      </c>
-      <c r="AA5" s="4">
-        <f>Z5*1.05</f>
-        <v>259.59591</v>
-      </c>
-      <c r="AB5" s="4">
-        <f>AA5*1.04</f>
-        <v>269.97974640000001</v>
-      </c>
-      <c r="AC5" s="4">
-        <f>AB5*1.03</f>
-        <v>278.07913879200004</v>
+        <v>228.2</v>
       </c>
       <c r="AD5" s="4">
-        <f>AC5*1.02</f>
-        <v>283.64072156784005</v>
+        <f t="shared" si="2"/>
+        <v>251.02</v>
       </c>
       <c r="AE5" s="4">
-        <f t="shared" ref="AE5:AI5" si="3">AD5*1.02</f>
-        <v>289.31353599919686</v>
+        <f>AD5*1.05</f>
+        <v>263.57100000000003</v>
       </c>
       <c r="AF5" s="4">
-        <f t="shared" si="3"/>
-        <v>295.09980671918078</v>
+        <f>AE5*1.04</f>
+        <v>274.11384000000004</v>
       </c>
       <c r="AG5" s="4">
-        <f t="shared" si="3"/>
-        <v>301.00180285356441</v>
+        <f>AF5*1.03</f>
+        <v>282.33725520000007</v>
       </c>
       <c r="AH5" s="4">
-        <f t="shared" si="3"/>
-        <v>307.02183891063572</v>
+        <f>AG5*1.02</f>
+        <v>287.98400030400006</v>
       </c>
       <c r="AI5" s="4">
-        <f t="shared" si="3"/>
-        <v>313.16227568884847</v>
-      </c>
-    </row>
-    <row r="6" spans="2:35" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AI5:AM5" si="5">AH5*1.02</f>
+        <v>293.74368031008009</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="5"/>
+        <v>299.61855391628171</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="5"/>
+        <v>305.61092499460733</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="5"/>
+        <v>311.72314349449948</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="5"/>
+        <v>317.95760636438945</v>
+      </c>
+    </row>
+    <row r="6" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>14</v>
       </c>
@@ -1416,193 +1532,224 @@
         <v>10.4</v>
       </c>
       <c r="R6" s="4">
-        <f t="shared" ref="Q6:R6" si="4">N6*1.9</f>
-        <v>20.52</v>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="S6" s="4">
+        <f>O6*1.05</f>
+        <v>28.35</v>
       </c>
       <c r="T6" s="4">
+        <f t="shared" ref="T6:V6" si="6">P6*1.05</f>
+        <v>13.440000000000001</v>
+      </c>
+      <c r="U6" s="4">
+        <f t="shared" si="6"/>
+        <v>10.920000000000002</v>
+      </c>
+      <c r="V6" s="4">
+        <f t="shared" si="6"/>
+        <v>10.709999999999999</v>
+      </c>
+      <c r="X6" s="4">
         <v>64.099999999999994</v>
       </c>
-      <c r="U6" s="4">
+      <c r="Y6" s="4">
         <v>68.400000000000006</v>
       </c>
-      <c r="V6" s="4">
+      <c r="Z6" s="4">
         <v>75.400000000000006</v>
       </c>
-      <c r="W6" s="4">
+      <c r="AA6" s="4">
         <f>SUM(G6:J6)</f>
         <v>82.4</v>
       </c>
-      <c r="X6" s="4">
+      <c r="AB6" s="4">
         <f>SUM(K6:N6)</f>
         <v>52.8</v>
       </c>
-      <c r="Y6" s="4">
+      <c r="AC6" s="4">
         <f t="shared" si="1"/>
-        <v>70.72</v>
-      </c>
-      <c r="Z6" s="4">
-        <f>Y6*1.15</f>
-        <v>81.327999999999989</v>
-      </c>
-      <c r="AA6" s="4">
-        <f>Z6*1.08</f>
-        <v>87.834239999999994</v>
-      </c>
-      <c r="AB6" s="4">
-        <f t="shared" ref="AB6:AI6" si="5">AA6*1.05</f>
-        <v>92.225951999999992</v>
-      </c>
-      <c r="AC6" s="4">
-        <f t="shared" si="5"/>
-        <v>96.837249599999993</v>
+        <v>60.399999999999991</v>
       </c>
       <c r="AD6" s="4">
-        <f t="shared" si="5"/>
-        <v>101.67911208</v>
+        <f t="shared" si="2"/>
+        <v>63.420000000000009</v>
       </c>
       <c r="AE6" s="4">
-        <f t="shared" si="5"/>
-        <v>106.76306768400001</v>
+        <f>AD6*1.08</f>
+        <v>68.493600000000015</v>
       </c>
       <c r="AF6" s="4">
-        <f t="shared" si="5"/>
-        <v>112.1012210682</v>
+        <f t="shared" ref="AF6:AM6" si="7">AE6*1.05</f>
+        <v>71.918280000000024</v>
       </c>
       <c r="AG6" s="4">
-        <f t="shared" si="5"/>
-        <v>117.70628212161002</v>
+        <f t="shared" si="7"/>
+        <v>75.514194000000032</v>
       </c>
       <c r="AH6" s="4">
-        <f t="shared" si="5"/>
-        <v>123.59159622769052</v>
+        <f t="shared" si="7"/>
+        <v>79.289903700000039</v>
       </c>
       <c r="AI6" s="4">
-        <f t="shared" si="5"/>
-        <v>129.77117603907504</v>
-      </c>
-    </row>
-    <row r="7" spans="2:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v>83.254398885000043</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="7"/>
+        <v>87.417118829250043</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="7"/>
+        <v>91.787974770712552</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="7"/>
+        <v>96.377373509248187</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="7"/>
+        <v>101.1962421847106</v>
+      </c>
+    </row>
+    <row r="7" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" ref="F7:O7" si="6">SUM(F3:F6)</f>
+        <f t="shared" ref="F7:O7" si="8">SUM(F3:F6)</f>
         <v>462.49999999999994</v>
       </c>
       <c r="G7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>275.2</v>
       </c>
       <c r="H7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>301</v>
       </c>
       <c r="I7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>400.2</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>356.90000000000003</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>235.20000000000002</v>
       </c>
       <c r="L7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>335.7</v>
       </c>
       <c r="M7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>330.50000000000006</v>
       </c>
       <c r="N7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>572.4</v>
       </c>
       <c r="O7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>326.10000000000002</v>
       </c>
       <c r="P7" s="8">
-        <f t="shared" ref="P7" si="7">SUM(P3:P6)</f>
+        <f t="shared" ref="P7" si="9">SUM(P3:P6)</f>
         <v>401.2</v>
       </c>
       <c r="Q7" s="8">
-        <f t="shared" ref="Q7" si="8">SUM(Q3:Q6)</f>
+        <f t="shared" ref="Q7" si="10">SUM(Q3:Q6)</f>
         <v>519.1</v>
       </c>
       <c r="R7" s="8">
-        <f t="shared" ref="R7" si="9">SUM(R3:R6)</f>
-        <v>730.54</v>
+        <f t="shared" ref="R7:V7" si="11">SUM(R3:R6)</f>
+        <v>777.7</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" si="11"/>
+        <v>469.08000000000004</v>
       </c>
       <c r="T7" s="8">
-        <f>SUM(T3:T6)</f>
-        <v>794.2</v>
+        <f t="shared" si="11"/>
+        <v>600.46000000000015</v>
       </c>
       <c r="U7" s="8">
-        <f>SUM(U3:U6)</f>
-        <v>972.19999999999993</v>
+        <f t="shared" si="11"/>
+        <v>788.96000000000015</v>
       </c>
       <c r="V7" s="8">
-        <f>SUM(V3:V6)</f>
-        <v>1199.2000000000003</v>
-      </c>
-      <c r="W7" s="8">
-        <f>SUM(W3:W6)</f>
-        <v>1333.3</v>
+        <f t="shared" si="11"/>
+        <v>1140.645</v>
       </c>
       <c r="X7" s="8">
         <f>SUM(X3:X6)</f>
+        <v>794.2</v>
+      </c>
+      <c r="Y7" s="8">
+        <f>SUM(Y3:Y6)</f>
+        <v>972.19999999999993</v>
+      </c>
+      <c r="Z7" s="8">
+        <f>SUM(Z3:Z6)</f>
+        <v>1199.2000000000003</v>
+      </c>
+      <c r="AA7" s="8">
+        <f>SUM(AA3:AA6)</f>
+        <v>1333.3</v>
+      </c>
+      <c r="AB7" s="8">
+        <f>SUM(AB3:AB6)</f>
         <v>1473.8</v>
       </c>
-      <c r="Y7" s="8">
-        <f t="shared" ref="Y7:AI7" si="10">SUM(Y3:Y6)</f>
-        <v>1976.9399999999998</v>
-      </c>
-      <c r="Z7" s="8">
-        <f t="shared" si="10"/>
-        <v>2476.5921999999996</v>
-      </c>
-      <c r="AA7" s="8">
-        <f t="shared" si="10"/>
-        <v>2898.7846500000001</v>
-      </c>
-      <c r="AB7" s="8">
-        <f t="shared" si="10"/>
-        <v>3301.4916983999997</v>
-      </c>
       <c r="AC7" s="8">
-        <f t="shared" si="10"/>
-        <v>3667.1863483920006</v>
+        <f t="shared" ref="AC7:AM7" si="12">SUM(AC3:AC6)</f>
+        <v>2024.1000000000001</v>
       </c>
       <c r="AD7" s="8">
-        <f t="shared" si="10"/>
-        <v>4077.683221647841</v>
+        <f t="shared" si="12"/>
+        <v>2999.145</v>
       </c>
       <c r="AE7" s="8">
-        <f t="shared" si="10"/>
-        <v>4542.7160488831978</v>
+        <f t="shared" si="12"/>
+        <v>3857.1135999999997</v>
       </c>
       <c r="AF7" s="8">
-        <f t="shared" si="10"/>
-        <v>5070.5520795873827</v>
+        <f t="shared" si="12"/>
+        <v>4473.1967199999999</v>
       </c>
       <c r="AG7" s="8">
-        <f t="shared" si="10"/>
-        <v>5670.8514364511775</v>
+        <f t="shared" si="12"/>
+        <v>4961.3096592000002</v>
       </c>
       <c r="AH7" s="8">
-        <f t="shared" si="10"/>
-        <v>6354.9197551571287</v>
+        <f t="shared" si="12"/>
+        <v>5431.0779350040002</v>
       </c>
       <c r="AI7" s="8">
-        <f t="shared" si="10"/>
-        <v>7136.008763822846</v>
-      </c>
-    </row>
-    <row r="8" spans="2:35" x14ac:dyDescent="0.3">
+        <f t="shared" si="12"/>
+        <v>5905.2215942950806</v>
+      </c>
+      <c r="AJ7" s="8">
+        <f t="shared" si="12"/>
+        <v>6424.0225744055333</v>
+      </c>
+      <c r="AK7" s="8">
+        <f t="shared" si="12"/>
+        <v>6991.8225783938224</v>
+      </c>
+      <c r="AL7" s="8">
+        <f t="shared" si="12"/>
+        <v>7613.3915546377257</v>
+      </c>
+      <c r="AM7" s="8">
+        <f t="shared" si="12"/>
+        <v>8293.9702306462332</v>
+      </c>
+    </row>
+    <row r="8" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -1643,72 +1790,75 @@
         <v>249.8</v>
       </c>
       <c r="R8" s="4">
-        <f>R3*0.55</f>
-        <v>311.322</v>
-      </c>
-      <c r="T8" s="4">
+        <v>404.7</v>
+      </c>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="X8" s="4">
         <v>332.7</v>
       </c>
-      <c r="U8" s="4">
+      <c r="Y8" s="4">
         <v>471.7</v>
       </c>
-      <c r="V8" s="4">
+      <c r="Z8" s="4">
         <v>616.20000000000005</v>
       </c>
-      <c r="W8" s="4">
+      <c r="AA8" s="4">
         <f>SUM(G8:J8)</f>
         <v>630.09999999999991</v>
       </c>
-      <c r="X8" s="4">
+      <c r="AB8" s="4">
         <f>SUM(K8:N8)</f>
         <v>685.90000000000009</v>
       </c>
-      <c r="Y8" s="4">
-        <f t="shared" ref="Y8:Y11" si="11">SUM(O8:R8)</f>
-        <v>899.42199999999991</v>
-      </c>
-      <c r="Z8" s="4">
-        <f>Z3*0.6</f>
-        <v>1094.1299999999999</v>
-      </c>
-      <c r="AA8" s="4">
-        <f t="shared" ref="AA8:AI8" si="12">AA3*0.6</f>
-        <v>1258.2494999999999</v>
-      </c>
-      <c r="AB8" s="4">
-        <f t="shared" si="12"/>
-        <v>1409.2394400000001</v>
-      </c>
       <c r="AC8" s="4">
-        <f t="shared" si="12"/>
-        <v>1550.1633840000004</v>
+        <f t="shared" ref="AC8:AC11" si="13">SUM(O8:R8)</f>
+        <v>992.8</v>
       </c>
       <c r="AD8" s="4">
-        <f t="shared" si="12"/>
-        <v>1705.1797224000006</v>
+        <f>AD3*0.6</f>
+        <v>1401.2280000000001</v>
       </c>
       <c r="AE8" s="4">
-        <f t="shared" si="12"/>
-        <v>1875.6976946400009</v>
+        <f t="shared" ref="AE8:AM8" si="14">AE3*0.6</f>
+        <v>1821.5964000000001</v>
       </c>
       <c r="AF8" s="4">
-        <f t="shared" si="12"/>
-        <v>2063.2674641040012</v>
+        <f t="shared" si="14"/>
+        <v>2094.8358599999997</v>
       </c>
       <c r="AG8" s="4">
-        <f t="shared" si="12"/>
-        <v>2269.5942105144013</v>
+        <f t="shared" si="14"/>
+        <v>2304.319446</v>
       </c>
       <c r="AH8" s="4">
-        <f t="shared" si="12"/>
-        <v>2496.5536315658414</v>
+        <f t="shared" si="14"/>
+        <v>2534.7513905999999</v>
       </c>
       <c r="AI8" s="4">
-        <f t="shared" si="12"/>
-        <v>2746.2089947224258</v>
-      </c>
-    </row>
-    <row r="9" spans="2:35" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>2788.2265296600003</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="14"/>
+        <v>3067.0491826260009</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="14"/>
+        <v>3373.754100888601</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="14"/>
+        <v>3711.1295109774615</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="14"/>
+        <v>4082.2424620752081</v>
+      </c>
+    </row>
+    <row r="9" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -1749,72 +1899,75 @@
         <v>59.9</v>
       </c>
       <c r="R9" s="4">
-        <f>R4*0.88</f>
-        <v>69.889600000000016</v>
-      </c>
-      <c r="T9" s="4">
+        <v>74.5</v>
+      </c>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="X9" s="4">
         <v>116.5</v>
       </c>
-      <c r="U9" s="4">
+      <c r="Y9" s="4">
         <v>110.2</v>
       </c>
-      <c r="V9" s="4">
+      <c r="Z9" s="4">
         <v>104.1</v>
       </c>
-      <c r="W9" s="4">
+      <c r="AA9" s="4">
         <f>SUM(G9:J9)</f>
         <v>105.80000000000001</v>
       </c>
-      <c r="X9" s="4">
+      <c r="AB9" s="4">
         <f>SUM(K9:N9)</f>
         <v>129.5</v>
       </c>
-      <c r="Y9" s="4">
-        <f t="shared" si="11"/>
-        <v>201.28960000000001</v>
-      </c>
-      <c r="Z9" s="4">
-        <f>Z4*0.91</f>
-        <v>295.27680000000004</v>
-      </c>
-      <c r="AA9" s="4">
-        <f t="shared" ref="AA9:AI9" si="13">AA4*0.91</f>
-        <v>413.38751999999999</v>
-      </c>
-      <c r="AB9" s="4">
-        <f t="shared" si="13"/>
-        <v>537.40377599999999</v>
-      </c>
       <c r="AC9" s="4">
         <f t="shared" si="13"/>
-        <v>644.88453119999997</v>
+        <v>205.9</v>
       </c>
       <c r="AD9" s="4">
-        <f t="shared" si="13"/>
-        <v>773.86143743999992</v>
+        <f>AD4*0.91</f>
+        <v>317.88574999999997</v>
       </c>
       <c r="AE9" s="4">
-        <f t="shared" si="13"/>
-        <v>928.63372492799988</v>
+        <f t="shared" ref="AE9:AM9" si="15">AE4*0.91</f>
+        <v>445.04004999999995</v>
       </c>
       <c r="AF9" s="4">
-        <f t="shared" si="13"/>
-        <v>1114.3604699135999</v>
+        <f t="shared" si="15"/>
+        <v>578.55206499999997</v>
       </c>
       <c r="AG9" s="4">
-        <f t="shared" si="13"/>
-        <v>1337.2325638963198</v>
+        <f t="shared" si="15"/>
+        <v>694.26247799999987</v>
       </c>
       <c r="AH9" s="4">
-        <f t="shared" si="13"/>
-        <v>1604.6790766755837</v>
+        <f t="shared" si="15"/>
+        <v>763.68872579999993</v>
       </c>
       <c r="AI9" s="4">
-        <f t="shared" si="13"/>
-        <v>1925.6148920107005</v>
-      </c>
-    </row>
-    <row r="10" spans="2:35" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v>801.87316208999994</v>
+      </c>
+      <c r="AJ9" s="4">
+        <f t="shared" si="15"/>
+        <v>841.96682019449997</v>
+      </c>
+      <c r="AK9" s="4">
+        <f t="shared" si="15"/>
+        <v>884.06516120422498</v>
+      </c>
+      <c r="AL9" s="4">
+        <f t="shared" si="15"/>
+        <v>928.26841926443626</v>
+      </c>
+      <c r="AM9" s="4">
+        <f t="shared" si="15"/>
+        <v>974.68184022765797</v>
+      </c>
+    </row>
+    <row r="10" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -1855,72 +2008,75 @@
         <v>51.8</v>
       </c>
       <c r="R10" s="4">
-        <f>R5*0.9</f>
-        <v>58.103999999999992</v>
-      </c>
-      <c r="T10" s="4">
+        <v>51.3</v>
+      </c>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="X10" s="4">
         <v>132.30000000000001</v>
       </c>
-      <c r="U10" s="4">
+      <c r="Y10" s="4">
         <v>148.30000000000001</v>
       </c>
-      <c r="V10" s="4">
+      <c r="Z10" s="4">
         <v>168.5</v>
       </c>
-      <c r="W10" s="4">
+      <c r="AA10" s="4">
         <f>SUM(G10:J10)</f>
         <v>221</v>
       </c>
-      <c r="X10" s="4">
+      <c r="AB10" s="4">
         <f>SUM(K10:N10)</f>
         <v>215</v>
       </c>
-      <c r="Y10" s="4">
-        <f t="shared" si="11"/>
-        <v>212.20399999999998</v>
-      </c>
-      <c r="Z10" s="4">
-        <f>Z5*0.9</f>
-        <v>222.51078000000001</v>
-      </c>
-      <c r="AA10" s="4">
-        <f>AA5*0.85</f>
-        <v>220.65652349999999</v>
-      </c>
-      <c r="AB10" s="4">
-        <f>AB5*0.83</f>
-        <v>224.08318951199999</v>
-      </c>
       <c r="AC10" s="4">
-        <f t="shared" ref="AC10:AI10" si="14">AC5*0.83</f>
-        <v>230.80568519736002</v>
+        <f t="shared" si="13"/>
+        <v>205.39999999999998</v>
       </c>
       <c r="AD10" s="4">
-        <f t="shared" si="14"/>
-        <v>235.42179890130723</v>
+        <f>AD5*0.9</f>
+        <v>225.91800000000001</v>
       </c>
       <c r="AE10" s="4">
-        <f t="shared" si="14"/>
-        <v>240.13023487933339</v>
+        <f>AE5*0.85</f>
+        <v>224.03535000000002</v>
       </c>
       <c r="AF10" s="4">
-        <f t="shared" si="14"/>
-        <v>244.93283957692003</v>
+        <f>AF5*0.83</f>
+        <v>227.51448720000002</v>
       </c>
       <c r="AG10" s="4">
-        <f t="shared" si="14"/>
-        <v>249.83149636845846</v>
+        <f t="shared" ref="AG10:AM10" si="16">AG5*0.83</f>
+        <v>234.33992181600004</v>
       </c>
       <c r="AH10" s="4">
-        <f t="shared" si="14"/>
-        <v>254.82812629582764</v>
+        <f t="shared" si="16"/>
+        <v>239.02672025232005</v>
       </c>
       <c r="AI10" s="4">
-        <f t="shared" si="14"/>
-        <v>259.92468882174421</v>
-      </c>
-    </row>
-    <row r="11" spans="2:35" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>243.80725465736646</v>
+      </c>
+      <c r="AJ10" s="4">
+        <f t="shared" si="16"/>
+        <v>248.68339975051381</v>
+      </c>
+      <c r="AK10" s="4">
+        <f t="shared" si="16"/>
+        <v>253.65706774552407</v>
+      </c>
+      <c r="AL10" s="4">
+        <f t="shared" si="16"/>
+        <v>258.73020910043454</v>
+      </c>
+      <c r="AM10" s="4">
+        <f t="shared" si="16"/>
+        <v>263.90481328244323</v>
+      </c>
+    </row>
+    <row r="11" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -1961,313 +2117,325 @@
         <v>5.8</v>
       </c>
       <c r="R11" s="4">
-        <v>14</v>
-      </c>
-      <c r="T11" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="X11" s="4">
         <v>46.9</v>
       </c>
-      <c r="U11" s="4">
+      <c r="Y11" s="4">
         <v>44.4</v>
       </c>
-      <c r="V11" s="4">
+      <c r="Z11" s="4">
         <v>162.1</v>
       </c>
-      <c r="W11" s="4">
+      <c r="AA11" s="4">
         <f>SUM(G11:J11)</f>
         <v>179</v>
       </c>
-      <c r="X11" s="4">
+      <c r="AB11" s="4">
         <f>SUM(K11:N11)</f>
         <v>38.9</v>
       </c>
-      <c r="Y11" s="4">
-        <f t="shared" si="11"/>
-        <v>39.1</v>
-      </c>
-      <c r="Z11" s="4">
-        <f>Z6*0.56</f>
-        <v>45.543679999999995</v>
-      </c>
-      <c r="AA11" s="4">
-        <f t="shared" ref="AA11:AI11" si="15">AA6*0.56</f>
-        <v>49.187174400000004</v>
-      </c>
-      <c r="AB11" s="4">
-        <f t="shared" si="15"/>
-        <v>51.646533120000001</v>
-      </c>
       <c r="AC11" s="4">
-        <f t="shared" si="15"/>
-        <v>54.228859776</v>
+        <f t="shared" si="13"/>
+        <v>32.4</v>
       </c>
       <c r="AD11" s="4">
-        <f t="shared" si="15"/>
-        <v>56.940302764800002</v>
+        <f>AD6*0.56</f>
+        <v>35.515200000000007</v>
       </c>
       <c r="AE11" s="4">
-        <f t="shared" si="15"/>
-        <v>59.787317903040012</v>
+        <f t="shared" ref="AE11:AM11" si="17">AE6*0.56</f>
+        <v>38.35641600000001</v>
       </c>
       <c r="AF11" s="4">
-        <f t="shared" si="15"/>
-        <v>62.77668379819201</v>
+        <f t="shared" si="17"/>
+        <v>40.274236800000018</v>
       </c>
       <c r="AG11" s="4">
-        <f t="shared" si="15"/>
-        <v>65.915517988101612</v>
+        <f t="shared" si="17"/>
+        <v>42.287948640000025</v>
       </c>
       <c r="AH11" s="4">
-        <f t="shared" si="15"/>
-        <v>69.211293887506699</v>
+        <f t="shared" si="17"/>
+        <v>44.402346072000029</v>
       </c>
       <c r="AI11" s="4">
-        <f t="shared" si="15"/>
-        <v>72.671858581882034</v>
-      </c>
-    </row>
-    <row r="12" spans="2:35" x14ac:dyDescent="0.3">
+        <f t="shared" si="17"/>
+        <v>46.622463375600027</v>
+      </c>
+      <c r="AJ11" s="4">
+        <f t="shared" si="17"/>
+        <v>48.95358654438003</v>
+      </c>
+      <c r="AK11" s="4">
+        <f t="shared" si="17"/>
+        <v>51.401265871599037</v>
+      </c>
+      <c r="AL11" s="4">
+        <f t="shared" si="17"/>
+        <v>53.971329165178993</v>
+      </c>
+      <c r="AM11" s="4">
+        <f t="shared" si="17"/>
+        <v>56.669895623437938</v>
+      </c>
+    </row>
+    <row r="12" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="4">
-        <f t="shared" ref="F12:O12" si="16">SUM(F8:F11)</f>
+        <f t="shared" ref="F12:O12" si="18">SUM(F8:F11)</f>
         <v>391.1</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>220.89999999999998</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>244.89999999999998</v>
       </c>
       <c r="I12" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>405.5</v>
       </c>
       <c r="J12" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>264.60000000000002</v>
       </c>
       <c r="K12" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>197.29999999999998</v>
       </c>
       <c r="L12" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>267.2</v>
       </c>
       <c r="M12" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>251.70000000000002</v>
       </c>
       <c r="N12" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>353.1</v>
       </c>
       <c r="O12" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>237.39999999999998</v>
       </c>
       <c r="P12" s="4">
-        <f t="shared" ref="P12" si="17">SUM(P8:P11)</f>
+        <f t="shared" ref="P12" si="19">SUM(P8:P11)</f>
         <v>293.99999999999994</v>
       </c>
       <c r="Q12" s="4">
-        <f t="shared" ref="Q12" si="18">SUM(Q8:Q11)</f>
+        <f t="shared" ref="Q12" si="20">SUM(Q8:Q11)</f>
         <v>367.3</v>
       </c>
       <c r="R12" s="4">
-        <f t="shared" ref="R12" si="19">SUM(R8:R11)</f>
-        <v>453.31560000000002</v>
-      </c>
-      <c r="T12" s="4">
-        <f>SUM(T8:T11)</f>
-        <v>628.4</v>
-      </c>
-      <c r="U12" s="4">
-        <f>SUM(U8:U11)</f>
-        <v>774.6</v>
-      </c>
-      <c r="V12" s="4">
-        <f>SUM(V8:V11)</f>
-        <v>1050.9000000000001</v>
-      </c>
-      <c r="W12" s="4">
-        <f>SUM(W8:W11)</f>
-        <v>1135.8999999999999</v>
-      </c>
+        <f t="shared" ref="R12" si="21">SUM(R8:R11)</f>
+        <v>537.79999999999995</v>
+      </c>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
       <c r="X12" s="4">
         <f>SUM(X8:X11)</f>
+        <v>628.4</v>
+      </c>
+      <c r="Y12" s="4">
+        <f>SUM(Y8:Y11)</f>
+        <v>774.6</v>
+      </c>
+      <c r="Z12" s="4">
+        <f>SUM(Z8:Z11)</f>
+        <v>1050.9000000000001</v>
+      </c>
+      <c r="AA12" s="4">
+        <f>SUM(AA8:AA11)</f>
+        <v>1135.8999999999999</v>
+      </c>
+      <c r="AB12" s="4">
+        <f>SUM(AB8:AB11)</f>
         <v>1069.3000000000002</v>
       </c>
-      <c r="Y12" s="4">
-        <f t="shared" ref="Y12:AI12" si="20">SUM(Y8:Y11)</f>
-        <v>1352.0155999999997</v>
-      </c>
-      <c r="Z12" s="4">
-        <f t="shared" si="20"/>
-        <v>1657.46126</v>
-      </c>
-      <c r="AA12" s="4">
-        <f t="shared" si="20"/>
-        <v>1941.4807178999999</v>
-      </c>
-      <c r="AB12" s="4">
-        <f t="shared" si="20"/>
-        <v>2222.3729386320001</v>
-      </c>
       <c r="AC12" s="4">
-        <f t="shared" si="20"/>
-        <v>2480.0824601733602</v>
+        <f t="shared" ref="AC12:AM12" si="22">SUM(AC8:AC11)</f>
+        <v>1436.5</v>
       </c>
       <c r="AD12" s="4">
-        <f t="shared" si="20"/>
-        <v>2771.4032615061078</v>
+        <f t="shared" si="22"/>
+        <v>1980.5469500000002</v>
       </c>
       <c r="AE12" s="4">
-        <f t="shared" si="20"/>
-        <v>3104.2489723503741</v>
+        <f t="shared" si="22"/>
+        <v>2529.0282160000002</v>
       </c>
       <c r="AF12" s="4">
-        <f t="shared" si="20"/>
-        <v>3485.3374573927131</v>
+        <f t="shared" si="22"/>
+        <v>2941.1766489999995</v>
       </c>
       <c r="AG12" s="4">
-        <f t="shared" si="20"/>
-        <v>3922.5737887672813</v>
+        <f t="shared" si="22"/>
+        <v>3275.2097944560005</v>
       </c>
       <c r="AH12" s="4">
-        <f t="shared" si="20"/>
-        <v>4425.27212842476</v>
+        <f t="shared" si="22"/>
+        <v>3581.8691827243201</v>
       </c>
       <c r="AI12" s="4">
-        <f t="shared" si="20"/>
-        <v>5004.4204341367522</v>
-      </c>
-    </row>
-    <row r="13" spans="2:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>3880.5294097829665</v>
+      </c>
+      <c r="AJ12" s="4">
+        <f t="shared" si="22"/>
+        <v>4206.652989115395</v>
+      </c>
+      <c r="AK12" s="4">
+        <f t="shared" si="22"/>
+        <v>4562.8775957099488</v>
+      </c>
+      <c r="AL12" s="4">
+        <f t="shared" si="22"/>
+        <v>4952.0994685075111</v>
+      </c>
+      <c r="AM12" s="4">
+        <f t="shared" si="22"/>
+        <v>5377.4990112087471</v>
+      </c>
+    </row>
+    <row r="13" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" ref="F13:O13" si="21">F7-F12</f>
+        <f t="shared" ref="F13:O13" si="23">F7-F12</f>
         <v>71.39999999999992</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>54.300000000000011</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>56.100000000000023</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-5.3000000000000114</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>92.300000000000011</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>37.900000000000034</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>68.5</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>78.80000000000004</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>219.29999999999995</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>88.700000000000045</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" ref="P13" si="22">P7-P12</f>
+        <f t="shared" ref="P13" si="24">P7-P12</f>
         <v>107.20000000000005</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" ref="Q13" si="23">Q7-Q12</f>
+        <f t="shared" ref="Q13" si="25">Q7-Q12</f>
         <v>151.80000000000001</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" ref="R13" si="24">R7-R12</f>
-        <v>277.22439999999995</v>
-      </c>
-      <c r="T13" s="8">
-        <f>T7-T12</f>
-        <v>165.80000000000007</v>
-      </c>
-      <c r="U13" s="8">
-        <f>U7-U12</f>
-        <v>197.59999999999991</v>
-      </c>
-      <c r="V13" s="8">
-        <f>V7-V12</f>
-        <v>148.30000000000018</v>
-      </c>
-      <c r="W13" s="8">
-        <f>W7-W12</f>
-        <v>197.40000000000009</v>
-      </c>
+        <f t="shared" ref="R13" si="26">R7-R12</f>
+        <v>239.90000000000009</v>
+      </c>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
       <c r="X13" s="8">
         <f>X7-X12</f>
+        <v>165.80000000000007</v>
+      </c>
+      <c r="Y13" s="8">
+        <f>Y7-Y12</f>
+        <v>197.59999999999991</v>
+      </c>
+      <c r="Z13" s="8">
+        <f>Z7-Z12</f>
+        <v>148.30000000000018</v>
+      </c>
+      <c r="AA13" s="8">
+        <f>AA7-AA12</f>
+        <v>197.40000000000009</v>
+      </c>
+      <c r="AB13" s="8">
+        <f>AB7-AB12</f>
         <v>404.49999999999977</v>
       </c>
-      <c r="Y13" s="8">
-        <f t="shared" ref="Y13:AI13" si="25">Y7-Y12</f>
-        <v>624.92440000000011</v>
-      </c>
-      <c r="Z13" s="8">
-        <f t="shared" si="25"/>
-        <v>819.13093999999955</v>
-      </c>
-      <c r="AA13" s="8">
-        <f t="shared" si="25"/>
-        <v>957.30393210000011</v>
-      </c>
-      <c r="AB13" s="8">
-        <f t="shared" si="25"/>
-        <v>1079.1187597679996</v>
-      </c>
       <c r="AC13" s="8">
-        <f t="shared" si="25"/>
-        <v>1187.1038882186403</v>
+        <f t="shared" ref="AC13:AM13" si="27">AC7-AC12</f>
+        <v>587.60000000000014</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="25"/>
-        <v>1306.2799601417332</v>
+        <f t="shared" si="27"/>
+        <v>1018.5980499999998</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="25"/>
-        <v>1438.4670765328237</v>
+        <f t="shared" si="27"/>
+        <v>1328.0853839999995</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="25"/>
-        <v>1585.2146221946696</v>
+        <f t="shared" si="27"/>
+        <v>1532.0200710000004</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="25"/>
-        <v>1748.2776476838962</v>
+        <f t="shared" si="27"/>
+        <v>1686.0998647439997</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="25"/>
-        <v>1929.6476267323687</v>
+        <f t="shared" si="27"/>
+        <v>1849.2087522796801</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="25"/>
-        <v>2131.5883296860939</v>
-      </c>
-    </row>
-    <row r="14" spans="2:35" x14ac:dyDescent="0.3">
+        <f t="shared" si="27"/>
+        <v>2024.6921845121142</v>
+      </c>
+      <c r="AJ13" s="8">
+        <f t="shared" si="27"/>
+        <v>2217.3695852901383</v>
+      </c>
+      <c r="AK13" s="8">
+        <f t="shared" si="27"/>
+        <v>2428.9449826838736</v>
+      </c>
+      <c r="AL13" s="8">
+        <f t="shared" si="27"/>
+        <v>2661.2920861302146</v>
+      </c>
+      <c r="AM13" s="8">
+        <f t="shared" si="27"/>
+        <v>2916.4712194374861</v>
+      </c>
+    </row>
+    <row r="14" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>22</v>
       </c>
@@ -2308,71 +2476,75 @@
         <v>48.7</v>
       </c>
       <c r="R14" s="4">
-        <v>54</v>
-      </c>
-      <c r="T14" s="4">
+        <v>55.9</v>
+      </c>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="X14" s="4">
         <v>83.6</v>
       </c>
-      <c r="U14" s="4">
+      <c r="Y14" s="4">
         <v>103.4</v>
       </c>
-      <c r="V14" s="4">
+      <c r="Z14" s="4">
         <v>150.6</v>
       </c>
-      <c r="W14" s="4">
+      <c r="AA14" s="4">
         <f>SUM(G14:J14)</f>
         <v>155.9</v>
       </c>
-      <c r="X14" s="4">
+      <c r="AB14" s="4">
         <f>SUM(K14:N14)</f>
         <v>148.69999999999999</v>
       </c>
-      <c r="Y14" s="4">
-        <f t="shared" ref="Y14:Y16" si="26">SUM(O14:R14)</f>
-        <v>184.10000000000002</v>
-      </c>
-      <c r="Z14" s="4">
-        <f>Y14*1.09</f>
-        <v>200.66900000000004</v>
-      </c>
-      <c r="AA14" s="4">
-        <f>Z14*1.06</f>
-        <v>212.70914000000005</v>
-      </c>
-      <c r="AB14" s="4">
-        <f>AA14*1.03</f>
-        <v>219.09041420000005</v>
-      </c>
       <c r="AC14" s="4">
-        <f t="shared" ref="AC14:AD16" si="27">AB14*1.03</f>
-        <v>225.66312662600006</v>
+        <f t="shared" ref="AC14:AC16" si="28">SUM(O14:R14)</f>
+        <v>186.00000000000003</v>
       </c>
       <c r="AD14" s="4">
-        <f t="shared" si="27"/>
-        <v>232.43302042478007</v>
+        <f>AC14*1.3</f>
+        <v>241.80000000000004</v>
       </c>
       <c r="AE14" s="4">
-        <f>AD14*1.02</f>
-        <v>237.08168083327567</v>
+        <f>AD14*1.15</f>
+        <v>278.07000000000005</v>
       </c>
       <c r="AF14" s="4">
-        <f t="shared" ref="AF14:AI14" si="28">AE14*1.02</f>
-        <v>241.82331444994119</v>
+        <f>AE14*1.09</f>
+        <v>303.0963000000001</v>
       </c>
       <c r="AG14" s="4">
-        <f t="shared" si="28"/>
-        <v>246.65978073894001</v>
+        <f>AF14*1.07</f>
+        <v>324.31304100000011</v>
       </c>
       <c r="AH14" s="4">
-        <f t="shared" si="28"/>
-        <v>251.59297635371883</v>
+        <f>AG14*1.05</f>
+        <v>340.52869305000013</v>
       </c>
       <c r="AI14" s="4">
-        <f t="shared" si="28"/>
-        <v>256.62483588079323</v>
-      </c>
-    </row>
-    <row r="15" spans="2:35" x14ac:dyDescent="0.3">
+        <f>AH14*1.04</f>
+        <v>354.14984077200012</v>
+      </c>
+      <c r="AJ14" s="4">
+        <f>AI14*1.03</f>
+        <v>364.77433599516013</v>
+      </c>
+      <c r="AK14" s="4">
+        <f t="shared" ref="AK14:AM14" si="29">AJ14*1.02</f>
+        <v>372.06982271506331</v>
+      </c>
+      <c r="AL14" s="4">
+        <f t="shared" si="29"/>
+        <v>379.51121916936461</v>
+      </c>
+      <c r="AM14" s="4">
+        <f t="shared" si="29"/>
+        <v>387.1014435527519</v>
+      </c>
+    </row>
+    <row r="15" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>23</v>
       </c>
@@ -2413,71 +2585,75 @@
         <v>42</v>
       </c>
       <c r="R15" s="4">
-        <v>50</v>
-      </c>
-      <c r="T15" s="4">
+        <v>41.9</v>
+      </c>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="X15" s="4">
         <v>55.9</v>
       </c>
-      <c r="U15" s="4">
+      <c r="Y15" s="4">
         <v>86.5</v>
       </c>
-      <c r="V15" s="4">
+      <c r="Z15" s="4">
         <v>90.9</v>
       </c>
-      <c r="W15" s="4">
+      <c r="AA15" s="4">
         <f>SUM(G15:J15)</f>
         <v>89.9</v>
       </c>
-      <c r="X15" s="4">
+      <c r="AB15" s="4">
         <f>SUM(K15:N15)</f>
         <v>68</v>
       </c>
-      <c r="Y15" s="4">
-        <f t="shared" si="26"/>
-        <v>138.4</v>
-      </c>
-      <c r="Z15" s="4">
-        <f>Z7*0.05</f>
-        <v>123.82960999999999</v>
-      </c>
-      <c r="AA15" s="4">
-        <f t="shared" ref="AA15:AI15" si="29">AA7*0.05</f>
-        <v>144.9392325</v>
-      </c>
-      <c r="AB15" s="4">
-        <f t="shared" si="29"/>
-        <v>165.07458492000001</v>
-      </c>
       <c r="AC15" s="4">
-        <f t="shared" si="29"/>
-        <v>183.35931741960005</v>
+        <f t="shared" si="28"/>
+        <v>130.30000000000001</v>
       </c>
       <c r="AD15" s="4">
-        <f t="shared" si="29"/>
-        <v>203.88416108239207</v>
+        <f>AD7*0.05</f>
+        <v>149.95725000000002</v>
       </c>
       <c r="AE15" s="4">
-        <f t="shared" si="29"/>
-        <v>227.13580244415991</v>
+        <f t="shared" ref="AE15:AM15" si="30">AE7*0.05</f>
+        <v>192.85568000000001</v>
       </c>
       <c r="AF15" s="4">
-        <f t="shared" si="29"/>
-        <v>253.52760397936913</v>
+        <f t="shared" si="30"/>
+        <v>223.65983600000001</v>
       </c>
       <c r="AG15" s="4">
-        <f t="shared" si="29"/>
-        <v>283.5425718225589</v>
+        <f t="shared" si="30"/>
+        <v>248.06548296000003</v>
       </c>
       <c r="AH15" s="4">
-        <f t="shared" si="29"/>
-        <v>317.74598775785648</v>
+        <f t="shared" si="30"/>
+        <v>271.55389675020001</v>
       </c>
       <c r="AI15" s="4">
-        <f t="shared" si="29"/>
-        <v>356.80043819114235</v>
-      </c>
-    </row>
-    <row r="16" spans="2:35" x14ac:dyDescent="0.3">
+        <f t="shared" si="30"/>
+        <v>295.26107971475403</v>
+      </c>
+      <c r="AJ15" s="4">
+        <f t="shared" si="30"/>
+        <v>321.2011287202767</v>
+      </c>
+      <c r="AK15" s="4">
+        <f t="shared" si="30"/>
+        <v>349.59112891969113</v>
+      </c>
+      <c r="AL15" s="4">
+        <f t="shared" si="30"/>
+        <v>380.66957773188631</v>
+      </c>
+      <c r="AM15" s="4">
+        <f t="shared" si="30"/>
+        <v>414.69851153231167</v>
+      </c>
+    </row>
+    <row r="16" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>24</v>
       </c>
@@ -2518,313 +2694,325 @@
         <v>53.1</v>
       </c>
       <c r="R16" s="4">
-        <v>70</v>
-      </c>
-      <c r="T16" s="4">
+        <v>54.6</v>
+      </c>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="X16" s="4">
         <v>107.1</v>
       </c>
-      <c r="U16" s="4">
+      <c r="Y16" s="4">
         <v>122.2</v>
       </c>
-      <c r="V16" s="4">
+      <c r="Z16" s="4">
         <v>167.7</v>
       </c>
-      <c r="W16" s="4">
+      <c r="AA16" s="4">
         <f>SUM(G16:J16)</f>
         <v>160.9</v>
       </c>
-      <c r="X16" s="4">
+      <c r="AB16" s="4">
         <f>SUM(K16:N16)</f>
         <v>165.10000000000002</v>
       </c>
-      <c r="Y16" s="4">
-        <f t="shared" si="26"/>
-        <v>213.79999999999998</v>
-      </c>
-      <c r="Z16" s="4">
-        <f>Y16*1.1</f>
-        <v>235.18</v>
-      </c>
-      <c r="AA16" s="4">
-        <f>Z16*1.05</f>
-        <v>246.93900000000002</v>
-      </c>
-      <c r="AB16" s="4">
-        <f>AA16*1.04</f>
-        <v>256.81656000000004</v>
-      </c>
       <c r="AC16" s="4">
-        <f t="shared" si="27"/>
-        <v>264.52105680000005</v>
+        <f t="shared" si="28"/>
+        <v>198.39999999999998</v>
       </c>
       <c r="AD16" s="4">
-        <f>AC16*1.02</f>
-        <v>269.81147793600007</v>
+        <f>AC16*1.1</f>
+        <v>218.23999999999998</v>
       </c>
       <c r="AE16" s="4">
-        <f t="shared" ref="AE16:AI16" si="30">AD16*1.02</f>
-        <v>275.20770749472007</v>
+        <f>AD16*1.05</f>
+        <v>229.15199999999999</v>
       </c>
       <c r="AF16" s="4">
-        <f t="shared" si="30"/>
-        <v>280.71186164461449</v>
+        <f>AE16*1.04</f>
+        <v>238.31807999999998</v>
       </c>
       <c r="AG16" s="4">
-        <f t="shared" si="30"/>
-        <v>286.32609887750681</v>
+        <f t="shared" ref="AG16" si="31">AF16*1.03</f>
+        <v>245.46762239999998</v>
       </c>
       <c r="AH16" s="4">
-        <f t="shared" si="30"/>
-        <v>292.05262085505694</v>
+        <f>AG16*1.02</f>
+        <v>250.37697484799997</v>
       </c>
       <c r="AI16" s="4">
-        <f t="shared" si="30"/>
-        <v>297.89367327215808</v>
-      </c>
-    </row>
-    <row r="17" spans="2:145" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AI16:AM16" si="32">AH16*1.02</f>
+        <v>255.38451434495997</v>
+      </c>
+      <c r="AJ16" s="4">
+        <f t="shared" si="32"/>
+        <v>260.49220463185918</v>
+      </c>
+      <c r="AK16" s="4">
+        <f t="shared" si="32"/>
+        <v>265.70204872449636</v>
+      </c>
+      <c r="AL16" s="4">
+        <f t="shared" si="32"/>
+        <v>271.01608969898632</v>
+      </c>
+      <c r="AM16" s="4">
+        <f t="shared" si="32"/>
+        <v>276.43641149296604</v>
+      </c>
+    </row>
+    <row r="17" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" ref="F17:O17" si="31">SUM(F14:F16)</f>
+        <f t="shared" ref="F17:O17" si="33">SUM(F14:F16)</f>
         <v>111.99999999999999</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>117.9</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>110.8</v>
       </c>
       <c r="I17" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>98.5</v>
       </c>
       <c r="J17" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>79.5</v>
       </c>
       <c r="K17" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>87.1</v>
       </c>
       <c r="L17" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>91.699999999999989</v>
       </c>
       <c r="M17" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>88.4</v>
       </c>
       <c r="N17" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>114.6</v>
       </c>
       <c r="O17" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>107.80000000000001</v>
       </c>
       <c r="P17" s="4">
-        <f t="shared" ref="P17" si="32">SUM(P14:P16)</f>
+        <f t="shared" ref="P17" si="34">SUM(P14:P16)</f>
         <v>110.7</v>
       </c>
       <c r="Q17" s="4">
-        <f t="shared" ref="Q17" si="33">SUM(Q14:Q16)</f>
+        <f t="shared" ref="Q17" si="35">SUM(Q14:Q16)</f>
         <v>143.80000000000001</v>
       </c>
       <c r="R17" s="4">
-        <f t="shared" ref="R17" si="34">SUM(R14:R16)</f>
-        <v>174</v>
-      </c>
-      <c r="T17" s="4">
-        <f>SUM(T14:T16)</f>
-        <v>246.6</v>
-      </c>
-      <c r="U17" s="4">
-        <f>SUM(U14:U16)</f>
-        <v>312.10000000000002</v>
-      </c>
-      <c r="V17" s="4">
-        <f>SUM(V14:V16)</f>
-        <v>409.2</v>
-      </c>
-      <c r="W17" s="4">
-        <f>SUM(W14:W16)</f>
-        <v>406.70000000000005</v>
-      </c>
+        <f t="shared" ref="R17" si="36">SUM(R14:R16)</f>
+        <v>152.4</v>
+      </c>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
       <c r="X17" s="4">
         <f>SUM(X14:X16)</f>
+        <v>246.6</v>
+      </c>
+      <c r="Y17" s="4">
+        <f>SUM(Y14:Y16)</f>
+        <v>312.10000000000002</v>
+      </c>
+      <c r="Z17" s="4">
+        <f>SUM(Z14:Z16)</f>
+        <v>409.2</v>
+      </c>
+      <c r="AA17" s="4">
+        <f>SUM(AA14:AA16)</f>
+        <v>406.70000000000005</v>
+      </c>
+      <c r="AB17" s="4">
+        <f>SUM(AB14:AB16)</f>
         <v>381.8</v>
       </c>
-      <c r="Y17" s="4">
-        <f t="shared" ref="Y17:AI17" si="35">SUM(Y14:Y16)</f>
-        <v>536.29999999999995</v>
-      </c>
-      <c r="Z17" s="4">
-        <f t="shared" si="35"/>
-        <v>559.67861000000005</v>
-      </c>
-      <c r="AA17" s="4">
-        <f t="shared" si="35"/>
-        <v>604.58737250000013</v>
-      </c>
-      <c r="AB17" s="4">
-        <f t="shared" si="35"/>
-        <v>640.98155912000016</v>
-      </c>
       <c r="AC17" s="4">
-        <f t="shared" si="35"/>
-        <v>673.54350084560019</v>
+        <f t="shared" ref="AC17:AM17" si="37">SUM(AC14:AC16)</f>
+        <v>514.70000000000005</v>
       </c>
       <c r="AD17" s="4">
-        <f t="shared" si="35"/>
-        <v>706.12865944317218</v>
+        <f t="shared" si="37"/>
+        <v>609.99725000000001</v>
       </c>
       <c r="AE17" s="4">
-        <f t="shared" si="35"/>
-        <v>739.4251907721557</v>
+        <f t="shared" si="37"/>
+        <v>700.0776800000001</v>
       </c>
       <c r="AF17" s="4">
-        <f t="shared" si="35"/>
-        <v>776.06278007392484</v>
+        <f t="shared" si="37"/>
+        <v>765.07421600000009</v>
       </c>
       <c r="AG17" s="4">
-        <f t="shared" si="35"/>
-        <v>816.52845143900572</v>
+        <f t="shared" si="37"/>
+        <v>817.84614636000015</v>
       </c>
       <c r="AH17" s="4">
-        <f t="shared" si="35"/>
-        <v>861.39158496663219</v>
+        <f t="shared" si="37"/>
+        <v>862.45956464820006</v>
       </c>
       <c r="AI17" s="4">
-        <f t="shared" si="35"/>
-        <v>911.31894734409366</v>
-      </c>
-    </row>
-    <row r="18" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="37"/>
+        <v>904.79543483171403</v>
+      </c>
+      <c r="AJ17" s="4">
+        <f t="shared" si="37"/>
+        <v>946.46766934729601</v>
+      </c>
+      <c r="AK17" s="4">
+        <f t="shared" si="37"/>
+        <v>987.36300035925069</v>
+      </c>
+      <c r="AL17" s="4">
+        <f t="shared" si="37"/>
+        <v>1031.1968866002371</v>
+      </c>
+      <c r="AM17" s="4">
+        <f t="shared" si="37"/>
+        <v>1078.2363665780297</v>
+      </c>
+    </row>
+    <row r="18" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="8">
-        <f t="shared" ref="F18:O18" si="36">F13-F17</f>
+        <f t="shared" ref="F18:O18" si="38">F13-F17</f>
         <v>-40.600000000000065</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-63.599999999999994</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-54.699999999999974</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-103.80000000000001</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>12.800000000000011</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-49.19999999999996</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-23.199999999999989</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-9.5999999999999659</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>104.69999999999996</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-19.099999999999966</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" ref="P18" si="37">P13-P17</f>
+        <f t="shared" ref="P18" si="39">P13-P17</f>
         <v>-3.4999999999999574</v>
       </c>
       <c r="Q18" s="8">
-        <f t="shared" ref="Q18" si="38">Q13-Q17</f>
+        <f t="shared" ref="Q18" si="40">Q13-Q17</f>
         <v>8</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" ref="R18" si="39">R13-R17</f>
-        <v>103.22439999999995</v>
-      </c>
-      <c r="T18" s="8">
-        <f>T13-T17</f>
-        <v>-80.799999999999926</v>
-      </c>
-      <c r="U18" s="8">
-        <f>U13-U17</f>
-        <v>-114.50000000000011</v>
-      </c>
-      <c r="V18" s="8">
-        <f>V13-V17</f>
-        <v>-260.89999999999981</v>
-      </c>
-      <c r="W18" s="8">
-        <f>W13-W17</f>
-        <v>-209.29999999999995</v>
-      </c>
+        <f t="shared" ref="R18" si="41">R13-R17</f>
+        <v>87.500000000000085</v>
+      </c>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
       <c r="X18" s="8">
         <f>X13-X17</f>
+        <v>-80.799999999999926</v>
+      </c>
+      <c r="Y18" s="8">
+        <f>Y13-Y17</f>
+        <v>-114.50000000000011</v>
+      </c>
+      <c r="Z18" s="8">
+        <f>Z13-Z17</f>
+        <v>-260.89999999999981</v>
+      </c>
+      <c r="AA18" s="8">
+        <f>AA13-AA17</f>
+        <v>-209.29999999999995</v>
+      </c>
+      <c r="AB18" s="8">
+        <f>AB13-AB17</f>
         <v>22.699999999999761</v>
       </c>
-      <c r="Y18" s="8">
-        <f t="shared" ref="Y18:AI18" si="40">Y13-Y17</f>
-        <v>88.624400000000151</v>
-      </c>
-      <c r="Z18" s="8">
-        <f t="shared" si="40"/>
-        <v>259.45232999999951</v>
-      </c>
-      <c r="AA18" s="8">
-        <f t="shared" si="40"/>
-        <v>352.71655959999998</v>
-      </c>
-      <c r="AB18" s="8">
-        <f t="shared" si="40"/>
-        <v>438.13720064799941</v>
-      </c>
       <c r="AC18" s="8">
-        <f t="shared" si="40"/>
-        <v>513.56038737304016</v>
+        <f t="shared" ref="AC18:AM18" si="42">AC13-AC17</f>
+        <v>72.900000000000091</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="40"/>
-        <v>600.15130069856104</v>
+        <f t="shared" si="42"/>
+        <v>408.60079999999982</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="40"/>
-        <v>699.04188576066804</v>
+        <f t="shared" si="42"/>
+        <v>628.00770399999942</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" si="40"/>
-        <v>809.15184212074473</v>
+        <f t="shared" si="42"/>
+        <v>766.94585500000028</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" si="40"/>
-        <v>931.74919624489053</v>
+        <f t="shared" si="42"/>
+        <v>868.25371838399951</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="40"/>
-        <v>1068.2560417657364</v>
+        <f t="shared" si="42"/>
+        <v>986.74918763148003</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="40"/>
-        <v>1220.2693823420002</v>
-      </c>
-    </row>
-    <row r="19" spans="2:145" x14ac:dyDescent="0.3">
+        <f t="shared" si="42"/>
+        <v>1119.8967496804003</v>
+      </c>
+      <c r="AJ18" s="8">
+        <f t="shared" si="42"/>
+        <v>1270.9019159428422</v>
+      </c>
+      <c r="AK18" s="8">
+        <f t="shared" si="42"/>
+        <v>1441.5819823246229</v>
+      </c>
+      <c r="AL18" s="8">
+        <f t="shared" si="42"/>
+        <v>1630.0951995299774</v>
+      </c>
+      <c r="AM18" s="8">
+        <f t="shared" si="42"/>
+        <v>1838.2348528594564</v>
+      </c>
+    </row>
+    <row r="19" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>27</v>
       </c>
@@ -2865,71 +3053,75 @@
         <v>-5.3</v>
       </c>
       <c r="R19" s="4">
-        <v>-10</v>
-      </c>
-      <c r="T19" s="4">
+        <v>-13.6</v>
+      </c>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="X19" s="4">
         <v>-1.5</v>
       </c>
-      <c r="U19" s="4">
+      <c r="Y19" s="4">
         <v>-0.3</v>
       </c>
-      <c r="V19" s="4">
+      <c r="Z19" s="4">
         <v>-3.9</v>
       </c>
-      <c r="W19" s="4">
+      <c r="AA19" s="4">
         <f>SUM(G19:J19)</f>
         <v>-19.899999999999999</v>
       </c>
-      <c r="X19" s="4">
+      <c r="AB19" s="4">
         <f>SUM(K19:N19)</f>
         <v>-25.299999999999997</v>
       </c>
-      <c r="Y19" s="4">
-        <f t="shared" ref="Y19:Y23" si="41">SUM(O19:R19)</f>
-        <v>-30.5</v>
-      </c>
-      <c r="Z19" s="4">
-        <f t="shared" ref="Z19:AI19" si="42">Y19*1.02</f>
-        <v>-31.11</v>
-      </c>
-      <c r="AA19" s="4">
-        <f t="shared" si="42"/>
-        <v>-31.732199999999999</v>
-      </c>
-      <c r="AB19" s="4">
-        <f t="shared" si="42"/>
-        <v>-32.366844</v>
-      </c>
       <c r="AC19" s="4">
-        <f t="shared" si="42"/>
-        <v>-33.014180879999998</v>
+        <f t="shared" ref="AC19:AC23" si="43">SUM(O19:R19)</f>
+        <v>-34.1</v>
       </c>
       <c r="AD19" s="4">
-        <f t="shared" si="42"/>
-        <v>-33.674464497599999</v>
+        <f t="shared" ref="AD19:AM19" si="44">AC19*1.02</f>
+        <v>-34.782000000000004</v>
       </c>
       <c r="AE19" s="4">
-        <f t="shared" si="42"/>
-        <v>-34.347953787552001</v>
+        <f t="shared" si="44"/>
+        <v>-35.477640000000001</v>
       </c>
       <c r="AF19" s="4">
-        <f t="shared" si="42"/>
-        <v>-35.034912863303042</v>
+        <f t="shared" si="44"/>
+        <v>-36.187192799999998</v>
       </c>
       <c r="AG19" s="4">
-        <f t="shared" si="42"/>
-        <v>-35.735611120569104</v>
+        <f t="shared" si="44"/>
+        <v>-36.910936655999997</v>
       </c>
       <c r="AH19" s="4">
-        <f t="shared" si="42"/>
-        <v>-36.450323342980489</v>
+        <f t="shared" si="44"/>
+        <v>-37.649155389119997</v>
       </c>
       <c r="AI19" s="4">
-        <f t="shared" si="42"/>
-        <v>-37.179329809840098</v>
-      </c>
-    </row>
-    <row r="20" spans="2:145" x14ac:dyDescent="0.3">
+        <f t="shared" si="44"/>
+        <v>-38.402138496902396</v>
+      </c>
+      <c r="AJ19" s="4">
+        <f t="shared" si="44"/>
+        <v>-39.170181266840444</v>
+      </c>
+      <c r="AK19" s="4">
+        <f t="shared" si="44"/>
+        <v>-39.953584892177254</v>
+      </c>
+      <c r="AL19" s="4">
+        <f t="shared" si="44"/>
+        <v>-40.752656590020798</v>
+      </c>
+      <c r="AM19" s="4">
+        <f t="shared" si="44"/>
+        <v>-41.567709721821217</v>
+      </c>
+    </row>
+    <row r="20" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>28</v>
       </c>
@@ -2970,72 +3162,76 @@
         <v>14.4</v>
       </c>
       <c r="R20" s="4">
-        <v>15</v>
-      </c>
-      <c r="T20" s="4">
+        <v>10.6</v>
+      </c>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="X20" s="4">
         <f>76.3+2.5</f>
         <v>78.8</v>
       </c>
-      <c r="U20" s="4">
+      <c r="Y20" s="4">
         <v>69</v>
       </c>
-      <c r="V20" s="4">
+      <c r="Z20" s="4">
         <v>53.5</v>
       </c>
-      <c r="W20" s="4">
+      <c r="AA20" s="4">
         <f>SUM(G20:J20)</f>
         <v>108.3</v>
       </c>
-      <c r="X20" s="4">
+      <c r="AB20" s="4">
         <f>SUM(K20:N20)</f>
         <v>62.7</v>
       </c>
-      <c r="Y20" s="4">
-        <f t="shared" si="41"/>
-        <v>58.2</v>
-      </c>
-      <c r="Z20" s="4">
-        <f t="shared" ref="Z20:AI20" si="43">Y20*1.02</f>
-        <v>59.364000000000004</v>
-      </c>
-      <c r="AA20" s="4">
-        <f t="shared" si="43"/>
-        <v>60.551280000000006</v>
-      </c>
-      <c r="AB20" s="4">
-        <f t="shared" si="43"/>
-        <v>61.762305600000005</v>
-      </c>
       <c r="AC20" s="4">
         <f t="shared" si="43"/>
-        <v>62.997551712000003</v>
+        <v>53.800000000000004</v>
       </c>
       <c r="AD20" s="4">
-        <f t="shared" si="43"/>
-        <v>64.257502746240007</v>
+        <f t="shared" ref="AD20:AM20" si="45">AC20*1.02</f>
+        <v>54.876000000000005</v>
       </c>
       <c r="AE20" s="4">
-        <f t="shared" si="43"/>
-        <v>65.542652801164806</v>
+        <f t="shared" si="45"/>
+        <v>55.973520000000008</v>
       </c>
       <c r="AF20" s="4">
-        <f t="shared" si="43"/>
-        <v>66.853505857188097</v>
+        <f t="shared" si="45"/>
+        <v>57.092990400000012</v>
       </c>
       <c r="AG20" s="4">
-        <f t="shared" si="43"/>
-        <v>68.190575974331864</v>
+        <f t="shared" si="45"/>
+        <v>58.234850208000012</v>
       </c>
       <c r="AH20" s="4">
-        <f t="shared" si="43"/>
-        <v>69.554387493818496</v>
+        <f t="shared" si="45"/>
+        <v>59.399547212160016</v>
       </c>
       <c r="AI20" s="4">
-        <f t="shared" si="43"/>
-        <v>70.945475243694872</v>
-      </c>
-    </row>
-    <row r="21" spans="2:145" x14ac:dyDescent="0.3">
+        <f t="shared" si="45"/>
+        <v>60.58753815640322</v>
+      </c>
+      <c r="AJ20" s="4">
+        <f t="shared" si="45"/>
+        <v>61.799288919531286</v>
+      </c>
+      <c r="AK20" s="4">
+        <f t="shared" si="45"/>
+        <v>63.035274697921913</v>
+      </c>
+      <c r="AL20" s="4">
+        <f t="shared" si="45"/>
+        <v>64.295980191880346</v>
+      </c>
+      <c r="AM20" s="4">
+        <f t="shared" si="45"/>
+        <v>65.581899795717959</v>
+      </c>
+    </row>
+    <row r="21" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>29</v>
       </c>
@@ -3076,40 +3272,32 @@
         <v>20</v>
       </c>
       <c r="R21" s="4">
+        <v>20.8</v>
+      </c>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="X21" s="4">
+        <v>12.9</v>
+      </c>
+      <c r="Y21" s="4">
         <v>0</v>
       </c>
-      <c r="T21" s="4">
-        <v>12.9</v>
-      </c>
-      <c r="U21" s="4">
+      <c r="Z21" s="4">
         <v>0</v>
       </c>
-      <c r="V21" s="4">
-        <v>0</v>
-      </c>
-      <c r="W21" s="4">
+      <c r="AA21" s="4">
         <f>SUM(G21:J21)</f>
         <v>2.7</v>
       </c>
-      <c r="X21" s="4">
+      <c r="AB21" s="4">
         <f>SUM(K21:N21)</f>
         <v>-15.799999999999999</v>
       </c>
-      <c r="Y21" s="4">
-        <f t="shared" si="41"/>
-        <v>15.6</v>
-      </c>
-      <c r="Z21" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="4">
-        <v>0</v>
-      </c>
       <c r="AC21" s="4">
-        <v>0</v>
+        <f t="shared" si="43"/>
+        <v>36.4</v>
       </c>
       <c r="AD21" s="4">
         <v>0</v>
@@ -3129,8 +3317,20 @@
       <c r="AI21" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="AJ21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>30</v>
       </c>
@@ -3167,40 +3367,33 @@
         <v>1.4</v>
       </c>
       <c r="R22" s="4">
+        <f>0.9+66.2</f>
+        <v>67.100000000000009</v>
+      </c>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="X22" s="4">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="Y22" s="4">
         <v>0</v>
       </c>
-      <c r="T22" s="4">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="U22" s="4">
-        <v>0</v>
-      </c>
-      <c r="V22" s="4">
+      <c r="Z22" s="4">
         <v>9</v>
       </c>
-      <c r="W22" s="4">
+      <c r="AA22" s="4">
         <f>SUM(G22:J22)</f>
         <v>4.3</v>
       </c>
-      <c r="X22" s="4">
+      <c r="AB22" s="4">
         <f>SUM(K22:N22)</f>
         <v>27.2</v>
       </c>
-      <c r="Y22" s="4">
-        <f t="shared" si="41"/>
-        <v>33.699999999999996</v>
-      </c>
-      <c r="Z22" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="4">
-        <v>0</v>
-      </c>
       <c r="AC22" s="4">
-        <v>0</v>
+        <f t="shared" si="43"/>
+        <v>100.80000000000001</v>
       </c>
       <c r="AD22" s="4">
         <v>0</v>
@@ -3220,8 +3413,20 @@
       <c r="AI22" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="AJ22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>31</v>
       </c>
@@ -3262,42 +3467,34 @@
         <v>0</v>
       </c>
       <c r="R23" s="4">
-        <v>0</v>
-      </c>
-      <c r="T23" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="X23" s="4">
         <v>-0.5</v>
       </c>
-      <c r="U23" s="4">
+      <c r="Y23" s="4">
         <f>8.1+0.9</f>
         <v>9</v>
       </c>
-      <c r="V23" s="4">
+      <c r="Z23" s="4">
         <f>-5-0.6</f>
         <v>-5.6</v>
       </c>
-      <c r="W23" s="4">
+      <c r="AA23" s="4">
         <f>SUM(G23:J23)</f>
         <v>1.6</v>
       </c>
-      <c r="X23" s="4">
+      <c r="AB23" s="4">
         <f>SUM(K23:N23)</f>
         <v>0.70000000000000007</v>
       </c>
-      <c r="Y23" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="Z23" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="4">
-        <v>0</v>
-      </c>
       <c r="AC23" s="4">
-        <v>0</v>
+        <f t="shared" si="43"/>
+        <v>0.1</v>
       </c>
       <c r="AD23" s="4">
         <v>0</v>
@@ -3317,250 +3514,270 @@
       <c r="AI23" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="AJ23" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" ref="F24:O24" si="44">SUM(F19:F23)</f>
+        <f t="shared" ref="F24:R24" si="46">SUM(F19:F23)</f>
         <v>10.1</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>10.9</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>14.399999999999999</v>
       </c>
       <c r="I24" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>63.7</v>
       </c>
       <c r="J24" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>8</v>
       </c>
       <c r="K24" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>7.9999999999999991</v>
       </c>
       <c r="L24" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>37.300000000000004</v>
       </c>
       <c r="M24" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>4.9000000000000012</v>
       </c>
       <c r="N24" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-0.69999999999999962</v>
       </c>
       <c r="O24" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>3.9000000000000008</v>
       </c>
       <c r="P24" s="4">
-        <f t="shared" ref="P24" si="45">SUM(P19:P23)</f>
+        <f t="shared" si="46"/>
         <v>37.599999999999994</v>
       </c>
       <c r="Q24" s="4">
-        <f t="shared" ref="Q24" si="46">SUM(Q19:Q23)</f>
+        <f t="shared" si="46"/>
         <v>30.5</v>
       </c>
       <c r="R24" s="4">
-        <f t="shared" ref="R24" si="47">SUM(R19:R23)</f>
-        <v>5</v>
-      </c>
-      <c r="T24" s="4">
-        <f t="shared" ref="T24:Y24" si="48">SUM(T19:T23)</f>
+        <f t="shared" si="46"/>
+        <v>85</v>
+      </c>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="X24" s="4">
+        <f t="shared" ref="X24:AM24" si="47">SUM(X19:X23)</f>
         <v>98</v>
       </c>
-      <c r="U24" s="4">
-        <f t="shared" si="48"/>
+      <c r="Y24" s="4">
+        <f t="shared" si="47"/>
         <v>77.7</v>
       </c>
-      <c r="V24" s="4">
-        <f t="shared" si="48"/>
+      <c r="Z24" s="4">
+        <f t="shared" si="47"/>
         <v>53</v>
       </c>
-      <c r="W24" s="4">
-        <f t="shared" si="48"/>
+      <c r="AA24" s="4">
+        <f t="shared" si="47"/>
         <v>97</v>
       </c>
-      <c r="X24" s="4">
-        <f t="shared" si="48"/>
+      <c r="AB24" s="4">
+        <f t="shared" si="47"/>
         <v>49.500000000000014</v>
       </c>
-      <c r="Y24" s="4">
-        <f t="shared" si="48"/>
-        <v>77</v>
-      </c>
-      <c r="Z24" s="4">
-        <f t="shared" ref="Z24:AI24" si="49">SUM(Z19:Z23)</f>
-        <v>28.254000000000005</v>
-      </c>
-      <c r="AA24" s="4">
-        <f t="shared" si="49"/>
-        <v>28.819080000000007</v>
-      </c>
-      <c r="AB24" s="4">
-        <f t="shared" si="49"/>
-        <v>29.395461600000004</v>
-      </c>
       <c r="AC24" s="4">
-        <f t="shared" si="49"/>
-        <v>29.983370832000006</v>
+        <f t="shared" si="47"/>
+        <v>157</v>
       </c>
       <c r="AD24" s="4">
-        <f t="shared" si="49"/>
-        <v>30.583038248640008</v>
+        <f t="shared" si="47"/>
+        <v>20.094000000000001</v>
       </c>
       <c r="AE24" s="4">
-        <f t="shared" si="49"/>
-        <v>31.194699013612805</v>
+        <f t="shared" si="47"/>
+        <v>20.495880000000007</v>
       </c>
       <c r="AF24" s="4">
-        <f t="shared" si="49"/>
-        <v>31.818592993885055</v>
+        <f t="shared" si="47"/>
+        <v>20.905797600000014</v>
       </c>
       <c r="AG24" s="4">
-        <f t="shared" si="49"/>
-        <v>32.45496485376276</v>
+        <f t="shared" si="47"/>
+        <v>21.323913552000015</v>
       </c>
       <c r="AH24" s="4">
-        <f t="shared" si="49"/>
-        <v>33.104064150838006</v>
+        <f t="shared" si="47"/>
+        <v>21.750391823040019</v>
       </c>
       <c r="AI24" s="4">
-        <f t="shared" si="49"/>
-        <v>33.766145433854774</v>
-      </c>
-    </row>
-    <row r="25" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="47"/>
+        <v>22.185399659500824</v>
+      </c>
+      <c r="AJ24" s="4">
+        <f t="shared" si="47"/>
+        <v>22.629107652690841</v>
+      </c>
+      <c r="AK24" s="4">
+        <f t="shared" si="47"/>
+        <v>23.081689805744659</v>
+      </c>
+      <c r="AL24" s="4">
+        <f t="shared" si="47"/>
+        <v>23.543323601859548</v>
+      </c>
+      <c r="AM24" s="4">
+        <f t="shared" si="47"/>
+        <v>24.014190073896742</v>
+      </c>
+    </row>
+    <row r="25" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F25" s="8">
-        <f t="shared" ref="F25:O25" si="50">F18-F24</f>
+        <f t="shared" ref="F25:R25" si="48">F18-F24</f>
         <v>-50.700000000000067</v>
       </c>
       <c r="G25" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-74.5</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-69.099999999999966</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-167.5</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>4.8000000000000114</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-57.19999999999996</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-60.499999999999993</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-14.499999999999968</v>
       </c>
       <c r="N25" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>105.39999999999996</v>
       </c>
       <c r="O25" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-22.999999999999968</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" ref="P25" si="51">P18-P24</f>
+        <f t="shared" si="48"/>
         <v>-41.099999999999952</v>
       </c>
       <c r="Q25" s="8">
-        <f t="shared" ref="Q25" si="52">Q18-Q24</f>
+        <f t="shared" si="48"/>
         <v>-22.5</v>
       </c>
       <c r="R25" s="8">
-        <f t="shared" ref="R25" si="53">R18-R24</f>
-        <v>98.224399999999946</v>
-      </c>
-      <c r="T25" s="8">
-        <f t="shared" ref="T25:Y25" si="54">T18-T24</f>
+        <f t="shared" si="48"/>
+        <v>2.5000000000000853</v>
+      </c>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="X25" s="8">
+        <f t="shared" ref="X25:AM25" si="49">X18-X24</f>
         <v>-178.79999999999993</v>
       </c>
-      <c r="U25" s="8">
-        <f t="shared" si="54"/>
+      <c r="Y25" s="8">
+        <f t="shared" si="49"/>
         <v>-192.2000000000001</v>
       </c>
-      <c r="V25" s="8">
-        <f t="shared" si="54"/>
+      <c r="Z25" s="8">
+        <f t="shared" si="49"/>
         <v>-313.89999999999981</v>
       </c>
-      <c r="W25" s="8">
-        <f t="shared" si="54"/>
+      <c r="AA25" s="8">
+        <f t="shared" si="49"/>
         <v>-306.29999999999995</v>
       </c>
-      <c r="X25" s="8">
-        <f t="shared" si="54"/>
+      <c r="AB25" s="8">
+        <f t="shared" si="49"/>
         <v>-26.800000000000253</v>
       </c>
-      <c r="Y25" s="8">
-        <f t="shared" si="54"/>
-        <v>11.624400000000151</v>
-      </c>
-      <c r="Z25" s="8">
-        <f t="shared" ref="Z25:AI25" si="55">Z18-Z24</f>
-        <v>231.19832999999949</v>
-      </c>
-      <c r="AA25" s="8">
-        <f t="shared" si="55"/>
-        <v>323.8974796</v>
-      </c>
-      <c r="AB25" s="8">
-        <f t="shared" si="55"/>
-        <v>408.74173904799943</v>
-      </c>
       <c r="AC25" s="8">
-        <f t="shared" si="55"/>
-        <v>483.57701654104017</v>
+        <f t="shared" si="49"/>
+        <v>-84.099999999999909</v>
       </c>
       <c r="AD25" s="8">
-        <f t="shared" si="55"/>
-        <v>569.56826244992101</v>
+        <f t="shared" si="49"/>
+        <v>388.50679999999983</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" si="55"/>
-        <v>667.84718674705528</v>
+        <f t="shared" si="49"/>
+        <v>607.51182399999936</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="55"/>
-        <v>777.33324912685964</v>
+        <f t="shared" si="49"/>
+        <v>746.04005740000025</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="55"/>
-        <v>899.29423139112782</v>
+        <f t="shared" si="49"/>
+        <v>846.92980483199949</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="55"/>
-        <v>1035.1519776148984</v>
+        <f t="shared" si="49"/>
+        <v>964.99879580844004</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" si="55"/>
-        <v>1186.5032369081455</v>
-      </c>
-    </row>
-    <row r="26" spans="2:145" x14ac:dyDescent="0.3">
+        <f t="shared" si="49"/>
+        <v>1097.7113500208995</v>
+      </c>
+      <c r="AJ25" s="8">
+        <f t="shared" si="49"/>
+        <v>1248.2728082901513</v>
+      </c>
+      <c r="AK25" s="8">
+        <f t="shared" si="49"/>
+        <v>1418.5002925188783</v>
+      </c>
+      <c r="AL25" s="8">
+        <f t="shared" si="49"/>
+        <v>1606.5518759281179</v>
+      </c>
+      <c r="AM25" s="8">
+        <f t="shared" si="49"/>
+        <v>1814.2206627855596</v>
+      </c>
+    </row>
+    <row r="26" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>34</v>
       </c>
@@ -3601,71 +3818,75 @@
         <v>0.3</v>
       </c>
       <c r="R26" s="4">
-        <v>0</v>
-      </c>
-      <c r="T26" s="4">
+        <v>1</v>
+      </c>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="X26" s="4">
         <v>0.3</v>
       </c>
-      <c r="U26" s="4">
+      <c r="Y26" s="4">
         <v>1</v>
       </c>
-      <c r="V26" s="4">
+      <c r="Z26" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="W26" s="4">
+      <c r="AA26" s="4">
         <f>SUM(G26:J26)</f>
         <v>1.9000000000000001</v>
       </c>
-      <c r="X26" s="4">
+      <c r="AB26" s="4">
         <f>SUM(K26:N26)</f>
         <v>0.9</v>
       </c>
-      <c r="Y26" s="4">
-        <f t="shared" ref="Y26:Y27" si="56">SUM(O26:R26)</f>
-        <v>1.7</v>
-      </c>
-      <c r="Z26" s="4">
-        <f t="shared" ref="Z26:AI26" si="57">Z25*0.05</f>
-        <v>11.559916499999975</v>
-      </c>
-      <c r="AA26" s="4">
-        <f t="shared" si="57"/>
-        <v>16.194873980000001</v>
-      </c>
-      <c r="AB26" s="4">
-        <f t="shared" si="57"/>
-        <v>20.437086952399973</v>
-      </c>
       <c r="AC26" s="4">
-        <f t="shared" si="57"/>
-        <v>24.17885082705201</v>
+        <f t="shared" ref="AC26:AC27" si="50">SUM(O26:R26)</f>
+        <v>2.7</v>
       </c>
       <c r="AD26" s="4">
-        <f t="shared" si="57"/>
-        <v>28.47841312249605</v>
+        <f t="shared" ref="AD26:AM26" si="51">AD25*0.05</f>
+        <v>19.425339999999991</v>
       </c>
       <c r="AE26" s="4">
-        <f t="shared" si="57"/>
-        <v>33.392359337352765</v>
+        <f t="shared" si="51"/>
+        <v>30.37559119999997</v>
       </c>
       <c r="AF26" s="4">
-        <f t="shared" si="57"/>
-        <v>38.866662456342986</v>
+        <f t="shared" si="51"/>
+        <v>37.302002870000017</v>
       </c>
       <c r="AG26" s="4">
-        <f t="shared" si="57"/>
-        <v>44.964711569556393</v>
+        <f t="shared" si="51"/>
+        <v>42.34649024159998</v>
       </c>
       <c r="AH26" s="4">
-        <f t="shared" si="57"/>
-        <v>51.757598880744922</v>
+        <f t="shared" si="51"/>
+        <v>48.249939790422005</v>
       </c>
       <c r="AI26" s="4">
-        <f t="shared" si="57"/>
-        <v>59.32516184540728</v>
-      </c>
-    </row>
-    <row r="27" spans="2:145" x14ac:dyDescent="0.3">
+        <f t="shared" si="51"/>
+        <v>54.885567501044981</v>
+      </c>
+      <c r="AJ26" s="4">
+        <f t="shared" si="51"/>
+        <v>62.413640414507569</v>
+      </c>
+      <c r="AK26" s="4">
+        <f t="shared" si="51"/>
+        <v>70.925014625943916</v>
+      </c>
+      <c r="AL26" s="4">
+        <f t="shared" si="51"/>
+        <v>80.327593796405893</v>
+      </c>
+      <c r="AM26" s="4">
+        <f t="shared" si="51"/>
+        <v>90.711033139277987</v>
+      </c>
+    </row>
+    <row r="27" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>35</v>
       </c>
@@ -3706,633 +3927,641 @@
         <v>-0.1</v>
       </c>
       <c r="R27" s="4">
-        <v>0</v>
-      </c>
-      <c r="T27" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="X27" s="4">
         <v>-21.5</v>
       </c>
-      <c r="U27" s="4">
+      <c r="Y27" s="4">
         <v>-28.9</v>
       </c>
-      <c r="V27" s="4">
+      <c r="Z27" s="4">
         <f>-13.4-0.3</f>
         <v>-13.700000000000001</v>
       </c>
-      <c r="W27" s="4">
+      <c r="AA27" s="4">
         <f>SUM(G27:J27)</f>
         <v>-5.9</v>
       </c>
-      <c r="X27" s="4">
+      <c r="AB27" s="4">
         <f>SUM(K27:N27)</f>
         <v>2.1</v>
       </c>
-      <c r="Y27" s="4">
-        <f t="shared" si="56"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="Z27" s="4">
-        <f t="shared" ref="Z27:AI27" si="58">Z25*0.02</f>
-        <v>4.6239665999999895</v>
-      </c>
-      <c r="AA27" s="4">
-        <f t="shared" si="58"/>
-        <v>6.4779495919999999</v>
-      </c>
-      <c r="AB27" s="4">
-        <f t="shared" si="58"/>
-        <v>8.1748347809599888</v>
-      </c>
       <c r="AC27" s="4">
-        <f t="shared" si="58"/>
-        <v>9.6715403308208039</v>
+        <f t="shared" si="50"/>
+        <v>1</v>
       </c>
       <c r="AD27" s="4">
-        <f t="shared" si="58"/>
-        <v>11.391365248998421</v>
+        <f t="shared" ref="AD27:AM27" si="52">AD25*0.02</f>
+        <v>7.7701359999999964</v>
       </c>
       <c r="AE27" s="4">
-        <f t="shared" si="58"/>
-        <v>13.356943734941106</v>
+        <f t="shared" si="52"/>
+        <v>12.150236479999988</v>
       </c>
       <c r="AF27" s="4">
-        <f t="shared" si="58"/>
-        <v>15.546664982537193</v>
+        <f t="shared" si="52"/>
+        <v>14.920801148000006</v>
       </c>
       <c r="AG27" s="4">
-        <f t="shared" si="58"/>
-        <v>17.985884627822557</v>
+        <f t="shared" si="52"/>
+        <v>16.938596096639991</v>
       </c>
       <c r="AH27" s="4">
-        <f t="shared" si="58"/>
-        <v>20.70303955229797</v>
+        <f t="shared" si="52"/>
+        <v>19.299975916168801</v>
       </c>
       <c r="AI27" s="4">
-        <f t="shared" si="58"/>
-        <v>23.730064738162909</v>
-      </c>
-    </row>
-    <row r="28" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="52"/>
+        <v>21.95422700041799</v>
+      </c>
+      <c r="AJ27" s="4">
+        <f t="shared" si="52"/>
+        <v>24.965456165803026</v>
+      </c>
+      <c r="AK27" s="4">
+        <f t="shared" si="52"/>
+        <v>28.370005850377567</v>
+      </c>
+      <c r="AL27" s="4">
+        <f t="shared" si="52"/>
+        <v>32.131037518562358</v>
+      </c>
+      <c r="AM27" s="4">
+        <f t="shared" si="52"/>
+        <v>36.284413255711193</v>
+      </c>
+    </row>
+    <row r="28" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F28" s="8">
-        <f t="shared" ref="F28:O28" si="59">F25-F26-F27</f>
+        <f t="shared" ref="F28:O28" si="53">F25-F26-F27</f>
         <v>-47.100000000000065</v>
       </c>
       <c r="G28" s="8">
+        <f t="shared" si="53"/>
+        <v>-71.399999999999991</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="53"/>
+        <v>-66.299999999999969</v>
+      </c>
+      <c r="I28" s="8">
+        <f t="shared" si="53"/>
+        <v>-169</v>
+      </c>
+      <c r="J28" s="8">
+        <f t="shared" si="53"/>
+        <v>4.4000000000000119</v>
+      </c>
+      <c r="K28" s="8">
+        <f t="shared" si="53"/>
+        <v>-57.69999999999996</v>
+      </c>
+      <c r="L28" s="8">
+        <f t="shared" si="53"/>
+        <v>-61.999999999999993</v>
+      </c>
+      <c r="M28" s="8">
+        <f t="shared" si="53"/>
+        <v>-14.699999999999967</v>
+      </c>
+      <c r="N28" s="8">
+        <f t="shared" si="53"/>
+        <v>104.59999999999995</v>
+      </c>
+      <c r="O28" s="8">
+        <f t="shared" si="53"/>
+        <v>-23.799999999999965</v>
+      </c>
+      <c r="P28" s="8">
+        <f t="shared" ref="P28" si="54">P25-P26-P27</f>
+        <v>-42.49999999999995</v>
+      </c>
+      <c r="Q28" s="8">
+        <f t="shared" ref="Q28" si="55">Q25-Q26-Q27</f>
+        <v>-22.7</v>
+      </c>
+      <c r="R28" s="8">
+        <f t="shared" ref="R28" si="56">R25-R26-R27</f>
+        <v>1.2000000000000852</v>
+      </c>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="X28" s="8">
+        <f t="shared" ref="X28:AC28" si="57">X25-X26-X27</f>
+        <v>-157.59999999999994</v>
+      </c>
+      <c r="Y28" s="8">
+        <f t="shared" si="57"/>
+        <v>-164.3000000000001</v>
+      </c>
+      <c r="Z28" s="8">
+        <f t="shared" si="57"/>
+        <v>-301.29999999999984</v>
+      </c>
+      <c r="AA28" s="8">
+        <f t="shared" si="57"/>
+        <v>-302.29999999999995</v>
+      </c>
+      <c r="AB28" s="8">
+        <f t="shared" si="57"/>
+        <v>-29.800000000000253</v>
+      </c>
+      <c r="AC28" s="8">
+        <f t="shared" si="57"/>
+        <v>-87.799999999999912</v>
+      </c>
+      <c r="AD28" s="8">
+        <f t="shared" ref="AD28:AM28" si="58">AD25-AD26-AD27</f>
+        <v>361.31132399999984</v>
+      </c>
+      <c r="AE28" s="8">
+        <f t="shared" si="58"/>
+        <v>564.98599631999946</v>
+      </c>
+      <c r="AF28" s="8">
+        <f t="shared" si="58"/>
+        <v>693.81725338200022</v>
+      </c>
+      <c r="AG28" s="8">
+        <f t="shared" si="58"/>
+        <v>787.64471849375946</v>
+      </c>
+      <c r="AH28" s="8">
+        <f t="shared" si="58"/>
+        <v>897.44888010184923</v>
+      </c>
+      <c r="AI28" s="8">
+        <f t="shared" si="58"/>
+        <v>1020.8715555194366</v>
+      </c>
+      <c r="AJ28" s="8">
+        <f t="shared" si="58"/>
+        <v>1160.8937117098405</v>
+      </c>
+      <c r="AK28" s="8">
+        <f t="shared" si="58"/>
+        <v>1319.2052720425568</v>
+      </c>
+      <c r="AL28" s="8">
+        <f t="shared" si="58"/>
+        <v>1494.0932446131496</v>
+      </c>
+      <c r="AM28" s="8">
+        <f t="shared" si="58"/>
+        <v>1687.2252163905705</v>
+      </c>
+      <c r="AN28" s="1">
+        <f>AM28*(1+$AQ$33)</f>
+        <v>1670.3529642266649</v>
+      </c>
+      <c r="AO28" s="1">
+        <f t="shared" ref="AO28:CZ28" si="59">AN28*(1+$AQ$33)</f>
+        <v>1653.6494345843983</v>
+      </c>
+      <c r="AP28" s="1">
         <f t="shared" si="59"/>
-        <v>-71.399999999999991</v>
-      </c>
-      <c r="H28" s="8">
+        <v>1637.1129402385543</v>
+      </c>
+      <c r="AQ28" s="1">
         <f t="shared" si="59"/>
-        <v>-66.299999999999969</v>
-      </c>
-      <c r="I28" s="8">
+        <v>1620.7418108361687</v>
+      </c>
+      <c r="AR28" s="1">
         <f t="shared" si="59"/>
-        <v>-169</v>
-      </c>
-      <c r="J28" s="8">
+        <v>1604.534392727807</v>
+      </c>
+      <c r="AS28" s="1">
         <f t="shared" si="59"/>
-        <v>4.4000000000000119</v>
-      </c>
-      <c r="K28" s="8">
+        <v>1588.489048800529</v>
+      </c>
+      <c r="AT28" s="1">
         <f t="shared" si="59"/>
-        <v>-57.69999999999996</v>
-      </c>
-      <c r="L28" s="8">
+        <v>1572.6041583125236</v>
+      </c>
+      <c r="AU28" s="1">
         <f t="shared" si="59"/>
-        <v>-61.999999999999993</v>
-      </c>
-      <c r="M28" s="8">
+        <v>1556.8781167293985</v>
+      </c>
+      <c r="AV28" s="1">
         <f t="shared" si="59"/>
-        <v>-14.699999999999967</v>
-      </c>
-      <c r="N28" s="8">
+        <v>1541.3093355621045</v>
+      </c>
+      <c r="AW28" s="1">
         <f t="shared" si="59"/>
-        <v>104.59999999999995</v>
-      </c>
-      <c r="O28" s="8">
+        <v>1525.8962422064835</v>
+      </c>
+      <c r="AX28" s="1">
         <f t="shared" si="59"/>
-        <v>-23.799999999999965</v>
-      </c>
-      <c r="P28" s="8">
-        <f t="shared" ref="P28" si="60">P25-P26-P27</f>
-        <v>-42.49999999999995</v>
-      </c>
-      <c r="Q28" s="8">
-        <f t="shared" ref="Q28" si="61">Q25-Q26-Q27</f>
-        <v>-22.7</v>
-      </c>
-      <c r="R28" s="8">
-        <f t="shared" ref="R28" si="62">R25-R26-R27</f>
-        <v>98.224399999999946</v>
-      </c>
-      <c r="T28" s="8">
-        <f t="shared" ref="T28:Y28" si="63">T25-T26-T27</f>
-        <v>-157.59999999999994</v>
-      </c>
-      <c r="U28" s="8">
-        <f t="shared" si="63"/>
-        <v>-164.3000000000001</v>
-      </c>
-      <c r="V28" s="8">
-        <f t="shared" si="63"/>
-        <v>-301.29999999999984</v>
-      </c>
-      <c r="W28" s="8">
-        <f t="shared" si="63"/>
-        <v>-302.29999999999995</v>
-      </c>
-      <c r="X28" s="8">
-        <f t="shared" si="63"/>
-        <v>-29.800000000000253</v>
-      </c>
-      <c r="Y28" s="8">
-        <f t="shared" si="63"/>
-        <v>9.224400000000152</v>
-      </c>
-      <c r="Z28" s="8">
-        <f t="shared" ref="Z28:AI28" si="64">Z25-Z26-Z27</f>
-        <v>215.01444689999951</v>
-      </c>
-      <c r="AA28" s="8">
-        <f t="shared" si="64"/>
-        <v>301.22465602799997</v>
-      </c>
-      <c r="AB28" s="8">
-        <f t="shared" si="64"/>
-        <v>380.12981731463947</v>
-      </c>
-      <c r="AC28" s="8">
-        <f t="shared" si="64"/>
-        <v>449.72662538316735</v>
-      </c>
-      <c r="AD28" s="8">
-        <f t="shared" si="64"/>
-        <v>529.69848407842653</v>
-      </c>
-      <c r="AE28" s="8">
-        <f t="shared" si="64"/>
-        <v>621.09788367476142</v>
-      </c>
-      <c r="AF28" s="8">
-        <f t="shared" si="64"/>
-        <v>722.91992168797947</v>
-      </c>
-      <c r="AG28" s="8">
-        <f t="shared" si="64"/>
-        <v>836.34363519374892</v>
-      </c>
-      <c r="AH28" s="8">
-        <f t="shared" si="64"/>
-        <v>962.6913391818556</v>
-      </c>
-      <c r="AI28" s="8">
-        <f t="shared" si="64"/>
-        <v>1103.4480103245753</v>
-      </c>
-      <c r="AJ28" s="1">
-        <f>AI28*(1+$AM$33)</f>
-        <v>1092.4135302213294</v>
-      </c>
-      <c r="AK28" s="1">
-        <f t="shared" ref="AK28:CV28" si="65">AJ28*(1+$AM$33)</f>
-        <v>1081.4893949191162</v>
-      </c>
-      <c r="AL28" s="1">
-        <f t="shared" si="65"/>
-        <v>1070.674500969925</v>
-      </c>
-      <c r="AM28" s="1">
-        <f t="shared" si="65"/>
-        <v>1059.9677559602258</v>
-      </c>
-      <c r="AN28" s="1">
-        <f t="shared" si="65"/>
-        <v>1049.3680784006235</v>
-      </c>
-      <c r="AO28" s="1">
-        <f t="shared" si="65"/>
-        <v>1038.8743976166172</v>
-      </c>
-      <c r="AP28" s="1">
-        <f t="shared" si="65"/>
-        <v>1028.4856536404511</v>
-      </c>
-      <c r="AQ28" s="1">
-        <f t="shared" si="65"/>
-        <v>1018.2007971040466</v>
-      </c>
-      <c r="AR28" s="1">
-        <f t="shared" si="65"/>
-        <v>1008.0187891330062</v>
-      </c>
-      <c r="AS28" s="1">
-        <f t="shared" si="65"/>
-        <v>997.93860124167611</v>
-      </c>
-      <c r="AT28" s="1">
-        <f t="shared" si="65"/>
-        <v>987.95921522925937</v>
-      </c>
-      <c r="AU28" s="1">
-        <f t="shared" si="65"/>
-        <v>978.07962307696675</v>
-      </c>
-      <c r="AV28" s="1">
-        <f t="shared" si="65"/>
-        <v>968.29882684619713</v>
-      </c>
-      <c r="AW28" s="1">
-        <f t="shared" si="65"/>
-        <v>958.61583857773519</v>
-      </c>
-      <c r="AX28" s="1">
-        <f t="shared" si="65"/>
-        <v>949.02968019195782</v>
+        <v>1510.6372797844188</v>
       </c>
       <c r="AY28" s="1">
-        <f t="shared" si="65"/>
-        <v>939.53938339003821</v>
+        <f t="shared" si="59"/>
+        <v>1495.5309069865746</v>
       </c>
       <c r="AZ28" s="1">
-        <f t="shared" si="65"/>
-        <v>930.14398955613785</v>
+        <f t="shared" si="59"/>
+        <v>1480.5755979167088</v>
       </c>
       <c r="BA28" s="1">
-        <f t="shared" si="65"/>
-        <v>920.84254966057642</v>
+        <f t="shared" si="59"/>
+        <v>1465.7698419375417</v>
       </c>
       <c r="BB28" s="1">
-        <f t="shared" si="65"/>
-        <v>911.63412416397068</v>
+        <f t="shared" si="59"/>
+        <v>1451.1121435181662</v>
       </c>
       <c r="BC28" s="1">
-        <f t="shared" si="65"/>
-        <v>902.51778292233098</v>
+        <f t="shared" si="59"/>
+        <v>1436.6010220829846</v>
       </c>
       <c r="BD28" s="1">
-        <f t="shared" si="65"/>
-        <v>893.49260509310761</v>
+        <f t="shared" si="59"/>
+        <v>1422.2350118621548</v>
       </c>
       <c r="BE28" s="1">
-        <f t="shared" si="65"/>
-        <v>884.55767904217657</v>
+        <f t="shared" si="59"/>
+        <v>1408.0126617435333</v>
       </c>
       <c r="BF28" s="1">
-        <f t="shared" si="65"/>
-        <v>875.7121022517548</v>
+        <f t="shared" si="59"/>
+        <v>1393.9325351260979</v>
       </c>
       <c r="BG28" s="1">
-        <f t="shared" si="65"/>
-        <v>866.95498122923721</v>
+        <f t="shared" si="59"/>
+        <v>1379.9932097748369</v>
       </c>
       <c r="BH28" s="1">
-        <f t="shared" si="65"/>
-        <v>858.28543141694479</v>
+        <f t="shared" si="59"/>
+        <v>1366.1932776770886</v>
       </c>
       <c r="BI28" s="1">
-        <f t="shared" si="65"/>
-        <v>849.70257710277531</v>
+        <f t="shared" si="59"/>
+        <v>1352.5313449003177</v>
       </c>
       <c r="BJ28" s="1">
-        <f t="shared" si="65"/>
-        <v>841.20555133174753</v>
+        <f t="shared" si="59"/>
+        <v>1339.0060314513146</v>
       </c>
       <c r="BK28" s="1">
-        <f t="shared" si="65"/>
-        <v>832.79349581843007</v>
+        <f t="shared" si="59"/>
+        <v>1325.6159711368014</v>
       </c>
       <c r="BL28" s="1">
-        <f t="shared" si="65"/>
-        <v>824.46556086024577</v>
+        <f t="shared" si="59"/>
+        <v>1312.3598114254332</v>
       </c>
       <c r="BM28" s="1">
-        <f t="shared" si="65"/>
-        <v>816.22090525164333</v>
+        <f t="shared" si="59"/>
+        <v>1299.236213311179</v>
       </c>
       <c r="BN28" s="1">
-        <f t="shared" si="65"/>
-        <v>808.05869619912687</v>
+        <f t="shared" si="59"/>
+        <v>1286.2438511780672</v>
       </c>
       <c r="BO28" s="1">
-        <f t="shared" si="65"/>
-        <v>799.97810923713564</v>
+        <f t="shared" si="59"/>
+        <v>1273.3814126662865</v>
       </c>
       <c r="BP28" s="1">
-        <f t="shared" si="65"/>
-        <v>791.9783281447643</v>
+        <f t="shared" si="59"/>
+        <v>1260.6475985396237</v>
       </c>
       <c r="BQ28" s="1">
-        <f t="shared" si="65"/>
-        <v>784.05854486331668</v>
+        <f t="shared" si="59"/>
+        <v>1248.0411225542275</v>
       </c>
       <c r="BR28" s="1">
-        <f t="shared" si="65"/>
-        <v>776.21795941468349</v>
+        <f t="shared" si="59"/>
+        <v>1235.5607113286853</v>
       </c>
       <c r="BS28" s="1">
-        <f t="shared" si="65"/>
-        <v>768.45577982053669</v>
+        <f t="shared" si="59"/>
+        <v>1223.2051042153985</v>
       </c>
       <c r="BT28" s="1">
-        <f t="shared" si="65"/>
-        <v>760.77122202233136</v>
+        <f t="shared" si="59"/>
+        <v>1210.9730531732446</v>
       </c>
       <c r="BU28" s="1">
-        <f t="shared" si="65"/>
-        <v>753.16350980210802</v>
+        <f t="shared" si="59"/>
+        <v>1198.863322641512</v>
       </c>
       <c r="BV28" s="1">
-        <f t="shared" si="65"/>
-        <v>745.63187470408695</v>
+        <f t="shared" si="59"/>
+        <v>1186.8746894150968</v>
       </c>
       <c r="BW28" s="1">
-        <f t="shared" si="65"/>
-        <v>738.17555595704607</v>
+        <f t="shared" si="59"/>
+        <v>1175.0059425209458</v>
       </c>
       <c r="BX28" s="1">
-        <f t="shared" si="65"/>
-        <v>730.79380039747559</v>
+        <f t="shared" si="59"/>
+        <v>1163.2558830957364</v>
       </c>
       <c r="BY28" s="1">
-        <f t="shared" si="65"/>
-        <v>723.48586239350084</v>
+        <f t="shared" si="59"/>
+        <v>1151.6233242647791</v>
       </c>
       <c r="BZ28" s="1">
-        <f t="shared" si="65"/>
-        <v>716.25100376956584</v>
+        <f t="shared" si="59"/>
+        <v>1140.1070910221313</v>
       </c>
       <c r="CA28" s="1">
-        <f t="shared" si="65"/>
-        <v>709.08849373187013</v>
+        <f t="shared" si="59"/>
+        <v>1128.70602011191</v>
       </c>
       <c r="CB28" s="1">
-        <f t="shared" si="65"/>
-        <v>701.99760879455141</v>
+        <f t="shared" si="59"/>
+        <v>1117.4189599107908</v>
       </c>
       <c r="CC28" s="1">
-        <f t="shared" si="65"/>
-        <v>694.97763270660585</v>
+        <f t="shared" si="59"/>
+        <v>1106.2447703116829</v>
       </c>
       <c r="CD28" s="1">
-        <f t="shared" si="65"/>
-        <v>688.0278563795398</v>
+        <f t="shared" si="59"/>
+        <v>1095.1823226085662</v>
       </c>
       <c r="CE28" s="1">
-        <f t="shared" si="65"/>
-        <v>681.1475778157444</v>
+        <f t="shared" si="59"/>
+        <v>1084.2304993824805</v>
       </c>
       <c r="CF28" s="1">
-        <f t="shared" si="65"/>
-        <v>674.3361020375869</v>
+        <f t="shared" si="59"/>
+        <v>1073.3881943886556</v>
       </c>
       <c r="CG28" s="1">
-        <f t="shared" si="65"/>
-        <v>667.59274101721098</v>
+        <f t="shared" si="59"/>
+        <v>1062.6543124447689</v>
       </c>
       <c r="CH28" s="1">
-        <f t="shared" si="65"/>
-        <v>660.91681360703888</v>
+        <f t="shared" si="59"/>
+        <v>1052.0277693203213</v>
       </c>
       <c r="CI28" s="1">
-        <f t="shared" si="65"/>
-        <v>654.30764547096851</v>
+        <f t="shared" si="59"/>
+        <v>1041.507491627118</v>
       </c>
       <c r="CJ28" s="1">
-        <f t="shared" si="65"/>
-        <v>647.76456901625886</v>
+        <f t="shared" si="59"/>
+        <v>1031.0924167108469</v>
       </c>
       <c r="CK28" s="1">
-        <f t="shared" si="65"/>
-        <v>641.28692332609626</v>
+        <f t="shared" si="59"/>
+        <v>1020.7814925437384</v>
       </c>
       <c r="CL28" s="1">
-        <f t="shared" si="65"/>
-        <v>634.87405409283531</v>
+        <f t="shared" si="59"/>
+        <v>1010.573677618301</v>
       </c>
       <c r="CM28" s="1">
-        <f t="shared" si="65"/>
-        <v>628.52531355190695</v>
+        <f t="shared" si="59"/>
+        <v>1000.467940842118</v>
       </c>
       <c r="CN28" s="1">
-        <f t="shared" si="65"/>
-        <v>622.24006041638791</v>
+        <f t="shared" si="59"/>
+        <v>990.46326143369674</v>
       </c>
       <c r="CO28" s="1">
-        <f t="shared" si="65"/>
-        <v>616.017659812224</v>
+        <f t="shared" si="59"/>
+        <v>980.5586288193598</v>
       </c>
       <c r="CP28" s="1">
-        <f t="shared" si="65"/>
-        <v>609.85748321410176</v>
+        <f t="shared" si="59"/>
+        <v>970.75304253116622</v>
       </c>
       <c r="CQ28" s="1">
-        <f t="shared" si="65"/>
-        <v>603.75890838196074</v>
+        <f t="shared" si="59"/>
+        <v>961.04551210585453</v>
       </c>
       <c r="CR28" s="1">
-        <f t="shared" si="65"/>
-        <v>597.72131929814111</v>
+        <f t="shared" si="59"/>
+        <v>951.43505698479601</v>
       </c>
       <c r="CS28" s="1">
-        <f t="shared" si="65"/>
-        <v>591.74410610515974</v>
+        <f t="shared" si="59"/>
+        <v>941.92070641494809</v>
       </c>
       <c r="CT28" s="1">
-        <f t="shared" si="65"/>
-        <v>585.82666504410815</v>
+        <f t="shared" si="59"/>
+        <v>932.50149935079855</v>
       </c>
       <c r="CU28" s="1">
-        <f t="shared" si="65"/>
-        <v>579.96839839366703</v>
+        <f t="shared" si="59"/>
+        <v>923.17648435729052</v>
       </c>
       <c r="CV28" s="1">
-        <f t="shared" si="65"/>
-        <v>574.16871440973034</v>
+        <f t="shared" si="59"/>
+        <v>913.94471951371759</v>
       </c>
       <c r="CW28" s="1">
-        <f t="shared" ref="CW28:EO28" si="66">CV28*(1+$AM$33)</f>
-        <v>568.427027265633</v>
+        <f t="shared" si="59"/>
+        <v>904.80527231858036</v>
       </c>
       <c r="CX28" s="1">
-        <f t="shared" si="66"/>
-        <v>562.74275699297664</v>
+        <f t="shared" si="59"/>
+        <v>895.75721959539453</v>
       </c>
       <c r="CY28" s="1">
-        <f t="shared" si="66"/>
-        <v>557.11532942304689</v>
+        <f t="shared" si="59"/>
+        <v>886.79964739944057</v>
       </c>
       <c r="CZ28" s="1">
-        <f t="shared" si="66"/>
-        <v>551.54417612881639</v>
+        <f t="shared" si="59"/>
+        <v>877.93165092544621</v>
       </c>
       <c r="DA28" s="1">
-        <f t="shared" si="66"/>
-        <v>546.02873436752827</v>
+        <f t="shared" ref="DA28:ES28" si="60">CZ28*(1+$AQ$33)</f>
+        <v>869.15233441619171</v>
       </c>
       <c r="DB28" s="1">
-        <f t="shared" si="66"/>
-        <v>540.56844702385297</v>
+        <f t="shared" si="60"/>
+        <v>860.46081107202974</v>
       </c>
       <c r="DC28" s="1">
-        <f t="shared" si="66"/>
-        <v>535.16276255361447</v>
+        <f t="shared" si="60"/>
+        <v>851.85620296130946</v>
       </c>
       <c r="DD28" s="1">
-        <f t="shared" si="66"/>
-        <v>529.81113492807833</v>
+        <f t="shared" si="60"/>
+        <v>843.33764093169634</v>
       </c>
       <c r="DE28" s="1">
-        <f t="shared" si="66"/>
-        <v>524.51302357879752</v>
+        <f t="shared" si="60"/>
+        <v>834.90426452237932</v>
       </c>
       <c r="DF28" s="1">
-        <f t="shared" si="66"/>
-        <v>519.26789334300952</v>
+        <f t="shared" si="60"/>
+        <v>826.55522187715553</v>
       </c>
       <c r="DG28" s="1">
-        <f t="shared" si="66"/>
-        <v>514.07521440957942</v>
+        <f t="shared" si="60"/>
+        <v>818.28966965838401</v>
       </c>
       <c r="DH28" s="1">
-        <f t="shared" si="66"/>
-        <v>508.9344622654836</v>
+        <f t="shared" si="60"/>
+        <v>810.10677296180017</v>
       </c>
       <c r="DI28" s="1">
-        <f t="shared" si="66"/>
-        <v>503.84511764282877</v>
+        <f t="shared" si="60"/>
+        <v>802.00570523218221</v>
       </c>
       <c r="DJ28" s="1">
-        <f t="shared" si="66"/>
-        <v>498.80666646640049</v>
+        <f t="shared" si="60"/>
+        <v>793.98564817986039</v>
       </c>
       <c r="DK28" s="1">
-        <f t="shared" si="66"/>
-        <v>493.81859980173647</v>
+        <f t="shared" si="60"/>
+        <v>786.04579169806175</v>
       </c>
       <c r="DL28" s="1">
-        <f t="shared" si="66"/>
-        <v>488.88041380371908</v>
+        <f t="shared" si="60"/>
+        <v>778.18533378108111</v>
       </c>
       <c r="DM28" s="1">
-        <f t="shared" si="66"/>
-        <v>483.99160966568189</v>
+        <f t="shared" si="60"/>
+        <v>770.40348044327027</v>
       </c>
       <c r="DN28" s="1">
-        <f t="shared" si="66"/>
-        <v>479.15169356902504</v>
+        <f t="shared" si="60"/>
+        <v>762.69944563883757</v>
       </c>
       <c r="DO28" s="1">
-        <f t="shared" si="66"/>
-        <v>474.36017663333479</v>
+        <f t="shared" si="60"/>
+        <v>755.07245118244919</v>
       </c>
       <c r="DP28" s="1">
-        <f t="shared" si="66"/>
-        <v>469.61657486700142</v>
+        <f t="shared" si="60"/>
+        <v>747.52172667062473</v>
       </c>
       <c r="DQ28" s="1">
-        <f t="shared" si="66"/>
-        <v>464.92040911833141</v>
+        <f t="shared" si="60"/>
+        <v>740.04650940391844</v>
       </c>
       <c r="DR28" s="1">
-        <f t="shared" si="66"/>
-        <v>460.27120502714808</v>
+        <f t="shared" si="60"/>
+        <v>732.64604430987924</v>
       </c>
       <c r="DS28" s="1">
-        <f t="shared" si="66"/>
-        <v>455.66849297687662</v>
+        <f t="shared" si="60"/>
+        <v>725.31958386678048</v>
       </c>
       <c r="DT28" s="1">
-        <f t="shared" si="66"/>
-        <v>451.11180804710784</v>
+        <f t="shared" si="60"/>
+        <v>718.06638802811267</v>
       </c>
       <c r="DU28" s="1">
-        <f t="shared" si="66"/>
-        <v>446.60068996663676</v>
+        <f t="shared" si="60"/>
+        <v>710.88572414783152</v>
       </c>
       <c r="DV28" s="1">
-        <f t="shared" si="66"/>
-        <v>442.13468306697041</v>
+        <f t="shared" si="60"/>
+        <v>703.77686690635323</v>
       </c>
       <c r="DW28" s="1">
-        <f t="shared" si="66"/>
-        <v>437.71333623630068</v>
+        <f t="shared" si="60"/>
+        <v>696.73909823728968</v>
       </c>
       <c r="DX28" s="1">
-        <f t="shared" si="66"/>
-        <v>433.33620287393768</v>
+        <f t="shared" si="60"/>
+        <v>689.77170725491681</v>
       </c>
       <c r="DY28" s="1">
-        <f t="shared" si="66"/>
-        <v>429.00284084519831</v>
+        <f t="shared" si="60"/>
+        <v>682.87399018236761</v>
       </c>
       <c r="DZ28" s="1">
-        <f t="shared" si="66"/>
-        <v>424.71281243674633</v>
+        <f t="shared" si="60"/>
+        <v>676.04525028054388</v>
       </c>
       <c r="EA28" s="1">
-        <f t="shared" si="66"/>
-        <v>420.46568431237887</v>
+        <f t="shared" si="60"/>
+        <v>669.28479777773839</v>
       </c>
       <c r="EB28" s="1">
-        <f t="shared" si="66"/>
-        <v>416.26102746925505</v>
+        <f t="shared" si="60"/>
+        <v>662.59194979996096</v>
       </c>
       <c r="EC28" s="1">
-        <f t="shared" si="66"/>
-        <v>412.0984171945625</v>
+        <f t="shared" si="60"/>
+        <v>655.96603030196138</v>
       </c>
       <c r="ED28" s="1">
-        <f t="shared" si="66"/>
-        <v>407.97743302261688</v>
+        <f t="shared" si="60"/>
+        <v>649.40636999894173</v>
       </c>
       <c r="EE28" s="1">
-        <f t="shared" si="66"/>
-        <v>403.89765869239068</v>
+        <f t="shared" si="60"/>
+        <v>642.91230629895233</v>
       </c>
       <c r="EF28" s="1">
-        <f t="shared" si="66"/>
-        <v>399.85868210546676</v>
+        <f t="shared" si="60"/>
+        <v>636.48318323596277</v>
       </c>
       <c r="EG28" s="1">
-        <f t="shared" si="66"/>
-        <v>395.86009528441207</v>
+        <f t="shared" si="60"/>
+        <v>630.11835140360313</v>
       </c>
       <c r="EH28" s="1">
-        <f t="shared" si="66"/>
-        <v>391.90149433156796</v>
+        <f t="shared" si="60"/>
+        <v>623.81716788956714</v>
       </c>
       <c r="EI28" s="1">
-        <f t="shared" si="66"/>
-        <v>387.98247938825227</v>
+        <f t="shared" si="60"/>
+        <v>617.57899621067145</v>
       </c>
       <c r="EJ28" s="1">
-        <f t="shared" si="66"/>
-        <v>384.10265459436977</v>
+        <f t="shared" si="60"/>
+        <v>611.40320624856474</v>
       </c>
       <c r="EK28" s="1">
-        <f t="shared" si="66"/>
-        <v>380.26162804842608</v>
+        <f t="shared" si="60"/>
+        <v>605.28917418607909</v>
       </c>
       <c r="EL28" s="1">
-        <f t="shared" si="66"/>
-        <v>376.45901176794183</v>
+        <f t="shared" si="60"/>
+        <v>599.23628244421832</v>
       </c>
       <c r="EM28" s="1">
-        <f t="shared" si="66"/>
-        <v>372.69442165026243</v>
+        <f t="shared" si="60"/>
+        <v>593.24391961977608</v>
       </c>
       <c r="EN28" s="1">
-        <f t="shared" si="66"/>
-        <v>368.96747743375983</v>
+        <f t="shared" si="60"/>
+        <v>587.31148042357836</v>
       </c>
       <c r="EO28" s="1">
-        <f t="shared" si="66"/>
-        <v>365.27780265942221</v>
-      </c>
-    </row>
-    <row r="29" spans="2:145" x14ac:dyDescent="0.3">
+        <f t="shared" si="60"/>
+        <v>581.43836561934256</v>
+      </c>
+      <c r="EP28" s="1">
+        <f t="shared" si="60"/>
+        <v>575.62398196314916</v>
+      </c>
+      <c r="EQ28" s="1">
+        <f t="shared" si="60"/>
+        <v>569.86774214351772</v>
+      </c>
+      <c r="ER28" s="1">
+        <f t="shared" si="60"/>
+        <v>564.16906472208257</v>
+      </c>
+      <c r="ES28" s="1">
+        <f t="shared" si="60"/>
+        <v>558.52737407486177</v>
+      </c>
+    </row>
+    <row r="29" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>2</v>
       </c>
@@ -4376,1366 +4605,1414 @@
         <v>236.5</v>
       </c>
       <c r="R29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
-      </c>
-      <c r="T29" s="4">
-        <v>228.6</v>
-      </c>
-      <c r="U29" s="4">
-        <v>228.6</v>
-      </c>
-      <c r="V29" s="4">
-        <v>228.6</v>
-      </c>
-      <c r="W29" s="4">
-        <v>228.6</v>
-      </c>
+        <f>280.5</f>
+        <v>280.5</v>
+      </c>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
       <c r="X29" s="4">
         <v>228.6</v>
       </c>
       <c r="Y29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <v>228.6</v>
       </c>
       <c r="Z29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <v>228.6</v>
       </c>
       <c r="AA29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <v>228.6</v>
       </c>
       <c r="AB29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <v>228.6</v>
       </c>
       <c r="AC29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <f t="shared" ref="AC29:AM29" si="61">280.5</f>
+        <v>280.5</v>
       </c>
       <c r="AD29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <f t="shared" si="61"/>
+        <v>280.5</v>
       </c>
       <c r="AE29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <f t="shared" si="61"/>
+        <v>280.5</v>
       </c>
       <c r="AF29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <f t="shared" si="61"/>
+        <v>280.5</v>
       </c>
       <c r="AG29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <f t="shared" si="61"/>
+        <v>280.5</v>
       </c>
       <c r="AH29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
+        <f t="shared" si="61"/>
+        <v>280.5</v>
       </c>
       <c r="AI29" s="4">
-        <f>236.5</f>
-        <v>236.5</v>
-      </c>
-    </row>
-    <row r="30" spans="2:145" x14ac:dyDescent="0.3">
+        <f t="shared" si="61"/>
+        <v>280.5</v>
+      </c>
+      <c r="AJ29" s="4">
+        <f t="shared" si="61"/>
+        <v>280.5</v>
+      </c>
+      <c r="AK29" s="4">
+        <f t="shared" si="61"/>
+        <v>280.5</v>
+      </c>
+      <c r="AL29" s="4">
+        <f t="shared" si="61"/>
+        <v>280.5</v>
+      </c>
+      <c r="AM29" s="4">
+        <f t="shared" si="61"/>
+        <v>280.5</v>
+      </c>
+    </row>
+    <row r="30" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="F30" s="6">
-        <f t="shared" ref="F30:O30" si="67">F28/F29</f>
+        <f t="shared" ref="F30:O30" si="62">F28/F29</f>
         <v>-0.20603674540682443</v>
       </c>
       <c r="G30" s="6">
+        <f t="shared" si="62"/>
+        <v>-0.31233595800524933</v>
+      </c>
+      <c r="H30" s="6">
+        <f t="shared" si="62"/>
+        <v>-0.29002624671916</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="62"/>
+        <v>-0.73928258967629046</v>
+      </c>
+      <c r="J30" s="6">
+        <f t="shared" si="62"/>
+        <v>1.9247594050743711E-2</v>
+      </c>
+      <c r="K30" s="6">
+        <f t="shared" si="62"/>
+        <v>-0.2524059492563428</v>
+      </c>
+      <c r="L30" s="6">
+        <f t="shared" si="62"/>
+        <v>-0.27121609798775148</v>
+      </c>
+      <c r="M30" s="6">
+        <f t="shared" si="62"/>
+        <v>-6.4304461942257071E-2</v>
+      </c>
+      <c r="N30" s="6">
+        <f t="shared" si="62"/>
+        <v>0.45736773065150832</v>
+      </c>
+      <c r="O30" s="6">
+        <f t="shared" si="62"/>
+        <v>-0.10249784668389306</v>
+      </c>
+      <c r="P30" s="6">
+        <f t="shared" ref="P30" si="63">P28/P29</f>
+        <v>-0.18162393162393142</v>
+      </c>
+      <c r="Q30" s="6">
+        <f t="shared" ref="Q30" si="64">Q28/Q29</f>
+        <v>-9.5983086680761096E-2</v>
+      </c>
+      <c r="R30" s="6">
+        <f t="shared" ref="R30" si="65">R28/R29</f>
+        <v>4.2780748663104641E-3</v>
+      </c>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="6"/>
+      <c r="X30" s="6">
+        <f t="shared" ref="X30:AC30" si="66">X28/X29</f>
+        <v>-0.68941382327209078</v>
+      </c>
+      <c r="Y30" s="6">
+        <f t="shared" si="66"/>
+        <v>-0.71872265966754201</v>
+      </c>
+      <c r="Z30" s="6">
+        <f t="shared" si="66"/>
+        <v>-1.3180227471566048</v>
+      </c>
+      <c r="AA30" s="6">
+        <f t="shared" si="66"/>
+        <v>-1.322397200349956</v>
+      </c>
+      <c r="AB30" s="6">
+        <f t="shared" si="66"/>
+        <v>-0.13035870516185588</v>
+      </c>
+      <c r="AC30" s="6">
+        <f t="shared" si="66"/>
+        <v>-0.31301247771835977</v>
+      </c>
+      <c r="AD30" s="6">
+        <f t="shared" ref="AD30:AM30" si="67">AD28/AD29</f>
+        <v>1.2880974117647053</v>
+      </c>
+      <c r="AE30" s="6">
         <f t="shared" si="67"/>
-        <v>-0.31233595800524933</v>
-      </c>
-      <c r="H30" s="6">
+        <v>2.0142103255614954</v>
+      </c>
+      <c r="AF30" s="6">
         <f t="shared" si="67"/>
-        <v>-0.29002624671916</v>
-      </c>
-      <c r="I30" s="6">
+        <v>2.4735017945882363</v>
+      </c>
+      <c r="AG30" s="6">
         <f t="shared" si="67"/>
-        <v>-0.73928258967629046</v>
-      </c>
-      <c r="J30" s="6">
+        <v>2.8080025614750781</v>
+      </c>
+      <c r="AH30" s="6">
         <f t="shared" si="67"/>
-        <v>1.9247594050743711E-2</v>
-      </c>
-      <c r="K30" s="6">
+        <v>3.1994612481349347</v>
+      </c>
+      <c r="AI30" s="6">
         <f t="shared" si="67"/>
-        <v>-0.2524059492563428</v>
-      </c>
-      <c r="L30" s="6">
+        <v>3.6394707861655493</v>
+      </c>
+      <c r="AJ30" s="6">
         <f t="shared" si="67"/>
-        <v>-0.27121609798775148</v>
-      </c>
-      <c r="M30" s="6">
+        <v>4.1386585087694847</v>
+      </c>
+      <c r="AK30" s="6">
         <f t="shared" si="67"/>
-        <v>-6.4304461942257071E-2</v>
-      </c>
-      <c r="N30" s="6">
+        <v>4.7030490981909336</v>
+      </c>
+      <c r="AL30" s="6">
         <f t="shared" si="67"/>
-        <v>0.45736773065150832</v>
-      </c>
-      <c r="O30" s="6">
+        <v>5.3265356314194285</v>
+      </c>
+      <c r="AM30" s="6">
         <f t="shared" si="67"/>
-        <v>-0.10249784668389306</v>
-      </c>
-      <c r="P30" s="6">
-        <f t="shared" ref="P30" si="68">P28/P29</f>
-        <v>-0.18162393162393142</v>
-      </c>
-      <c r="Q30" s="6">
-        <f t="shared" ref="Q30" si="69">Q28/Q29</f>
-        <v>-9.5983086680761096E-2</v>
-      </c>
-      <c r="R30" s="6">
-        <f t="shared" ref="R30" si="70">R28/R29</f>
-        <v>0.41532515856236762</v>
-      </c>
-      <c r="T30" s="6">
-        <f t="shared" ref="T30:Y30" si="71">T28/T29</f>
-        <v>-0.68941382327209078</v>
-      </c>
-      <c r="U30" s="6">
-        <f t="shared" si="71"/>
-        <v>-0.71872265966754201</v>
-      </c>
-      <c r="V30" s="6">
-        <f t="shared" si="71"/>
-        <v>-1.3180227471566048</v>
-      </c>
-      <c r="W30" s="6">
-        <f t="shared" si="71"/>
-        <v>-1.322397200349956</v>
-      </c>
-      <c r="X30" s="6">
-        <f t="shared" si="71"/>
-        <v>-0.13035870516185588</v>
-      </c>
-      <c r="Y30" s="6">
-        <f t="shared" si="71"/>
-        <v>3.9003805496829393E-2</v>
-      </c>
-      <c r="Z30" s="6">
-        <f t="shared" ref="Z30:AI30" si="72">Z28/Z29</f>
-        <v>0.90915199534883517</v>
-      </c>
-      <c r="AA30" s="6">
-        <f t="shared" si="72"/>
-        <v>1.2736771925073995</v>
-      </c>
-      <c r="AB30" s="6">
-        <f t="shared" si="72"/>
-        <v>1.6073142381168688</v>
-      </c>
-      <c r="AC30" s="6">
-        <f t="shared" si="72"/>
-        <v>1.9015924963347457</v>
-      </c>
-      <c r="AD30" s="6">
-        <f t="shared" si="72"/>
-        <v>2.2397398903950383</v>
-      </c>
-      <c r="AE30" s="6">
-        <f t="shared" si="72"/>
-        <v>2.6262066962992026</v>
-      </c>
-      <c r="AF30" s="6">
-        <f t="shared" si="72"/>
-        <v>3.0567438549174608</v>
-      </c>
-      <c r="AG30" s="6">
-        <f t="shared" si="72"/>
-        <v>3.5363367238636316</v>
-      </c>
-      <c r="AH30" s="6">
-        <f t="shared" si="72"/>
-        <v>4.0705764870268739</v>
-      </c>
-      <c r="AI30" s="6">
-        <f t="shared" si="72"/>
-        <v>4.6657421155373164</v>
-      </c>
-    </row>
-    <row r="32" spans="2:145" x14ac:dyDescent="0.3">
+        <v>6.015063160037684</v>
+      </c>
+    </row>
+    <row r="32" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>51</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" ref="J32:L36" si="73">J3/F3-1</f>
+        <f t="shared" ref="J32:R36" si="68">J3/F3-1</f>
         <v>-0.27318156579677955</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>-0.20805369127516771</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>5.4028877503493389E-2</v>
       </c>
       <c r="M32" s="9">
-        <f>M3/I3-1</f>
+        <f t="shared" si="68"/>
         <v>-0.23344262295081963</v>
       </c>
       <c r="N32" s="9">
-        <f>N3/J3-1</f>
+        <f t="shared" si="68"/>
         <v>0.80175706646294875</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" ref="O32:R36" si="74">O3/K3-1</f>
+        <f t="shared" si="68"/>
         <v>0.38135593220338992</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.31064958020327005</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.64371257485029942</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="74"/>
-        <v>0.19999999999999996</v>
-      </c>
+        <f t="shared" si="68"/>
+        <v>0.35361458554165792</v>
+      </c>
+      <c r="S32" s="9"/>
       <c r="T32" s="9"/>
-      <c r="U32" s="9">
-        <f>U3/T3-1</f>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9">
+        <f t="shared" ref="Y32:AM32" si="69">Y3/X3-1</f>
         <v>0.27940609332819122</v>
       </c>
-      <c r="V32" s="9">
-        <f t="shared" ref="V32:X32" si="75">V3/U3-1</f>
+      <c r="Z32" s="9">
+        <f t="shared" si="69"/>
         <v>0.32735493594574239</v>
       </c>
-      <c r="W32" s="9">
-        <f t="shared" si="75"/>
+      <c r="AA32" s="9">
+        <f t="shared" si="69"/>
         <v>0.10730101055978203</v>
       </c>
-      <c r="X32" s="9">
-        <f t="shared" si="75"/>
+      <c r="AB32" s="9">
+        <f t="shared" si="69"/>
         <v>0.11279737489745689</v>
       </c>
-      <c r="Y32" s="9">
-        <f t="shared" ref="Y32:AI32" si="76">Y3/X3-1</f>
-        <v>0.34430519719867303</v>
-      </c>
-      <c r="Z32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.25</v>
-      </c>
-      <c r="AA32" s="9">
-        <f t="shared" si="76"/>
+      <c r="AC32" s="9">
+        <f t="shared" si="69"/>
+        <v>0.41107629929966816</v>
+      </c>
+      <c r="AD32" s="9">
+        <f t="shared" si="69"/>
+        <v>0.52509632338535894</v>
+      </c>
+      <c r="AE32" s="9">
+        <f t="shared" si="69"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AF32" s="9">
+        <f t="shared" si="69"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AB32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="AC32" s="9">
-        <f t="shared" si="76"/>
+      <c r="AG32" s="9">
+        <f t="shared" si="69"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AD32" s="9">
-        <f t="shared" si="76"/>
+      <c r="AH32" s="9">
+        <f t="shared" si="69"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AE32" s="9">
-        <f t="shared" si="76"/>
+      <c r="AI32" s="9">
+        <f t="shared" si="69"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AF32" s="9">
-        <f t="shared" si="76"/>
+      <c r="AJ32" s="9">
+        <f t="shared" si="69"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AG32" s="9">
-        <f t="shared" si="76"/>
+      <c r="AK32" s="9">
+        <f t="shared" si="69"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AH32" s="9">
-        <f t="shared" si="76"/>
+      <c r="AL32" s="9">
+        <f t="shared" si="69"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AI32" s="9">
-        <f t="shared" si="76"/>
+      <c r="AM32" s="9">
+        <f t="shared" si="69"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>52</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>-0.39814814814814814</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>-0.44390243902439019</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>0.7644628099173556</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" ref="M33:N36" si="77">M4/I4-1</f>
+        <f t="shared" si="68"/>
         <v>0.46575342465753433</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="68"/>
         <v>0.38846153846153841</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>1.9561403508771931</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>-0.12412177985948492</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>1.0498442367601246</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="74"/>
-        <v>1.2000000000000002</v>
-      </c>
+        <f t="shared" si="68"/>
+        <v>0.86426592797783908</v>
+      </c>
+      <c r="S33" s="9"/>
       <c r="T33" s="9"/>
-      <c r="U33" s="9">
-        <f t="shared" ref="U33:X36" si="78">U4/T4-1</f>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9">
+        <f t="shared" ref="Y33:AM33" si="70">Y4/X4-1</f>
         <v>-5.6918547595682156E-2</v>
       </c>
-      <c r="V33" s="9">
-        <f t="shared" si="78"/>
+      <c r="Z33" s="9">
+        <f t="shared" si="70"/>
         <v>-4.1623309053069768E-2</v>
       </c>
-      <c r="W33" s="9">
-        <f t="shared" si="78"/>
+      <c r="AA33" s="9">
+        <f t="shared" si="70"/>
         <v>5.4288816503800241E-3</v>
       </c>
-      <c r="X33" s="9">
-        <f t="shared" si="78"/>
+      <c r="AB33" s="9">
+        <f t="shared" si="70"/>
         <v>0.32073434125269995</v>
       </c>
-      <c r="Y33" s="9">
-        <f t="shared" ref="Y33:AI33" si="79">Y4/X4-1</f>
-        <v>0.76876533115290258</v>
-      </c>
-      <c r="Z33" s="9">
-        <f t="shared" si="79"/>
-        <v>0.50000000000000022</v>
-      </c>
-      <c r="AA33" s="9">
-        <f t="shared" si="79"/>
+      <c r="AC33" s="9">
+        <f t="shared" si="70"/>
+        <v>0.66966475878986076</v>
+      </c>
+      <c r="AD33" s="9">
+        <f t="shared" si="70"/>
+        <v>0.71070029382957878</v>
+      </c>
+      <c r="AE33" s="9">
+        <f t="shared" si="70"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="AB33" s="9">
-        <f t="shared" si="79"/>
+      <c r="AF33" s="9">
+        <f t="shared" si="70"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AC33" s="9">
-        <f t="shared" si="79"/>
+      <c r="AG33" s="9">
+        <f t="shared" si="70"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AD33" s="9">
-        <f t="shared" si="79"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AE33" s="9">
-        <f t="shared" si="79"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AF33" s="9">
-        <f t="shared" si="79"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AG33" s="9">
-        <f t="shared" si="79"/>
-        <v>0.19999999999999996</v>
-      </c>
       <c r="AH33" s="9">
-        <f t="shared" si="79"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="70"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="79"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AL33" t="s">
+        <f t="shared" si="70"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AJ33" s="9">
+        <f t="shared" si="70"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AK33" s="9">
+        <f t="shared" si="70"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AL33" s="9">
+        <f t="shared" si="70"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AM33" s="9">
+        <f t="shared" si="70"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AP33" t="s">
         <v>65</v>
       </c>
-      <c r="AM33" s="9">
+      <c r="AQ33" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>53</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>0.31829573934837097</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>0.38574938574938566</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>0.24113475177304977</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="68"/>
         <v>6.9473684210526354E-2</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="68"/>
         <v>2.281368821292773E-2</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>-5.1418439716311992E-2</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>3.6190476190476106E-2</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.15354330708661434</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="74"/>
-        <v>0.19999999999999973</v>
-      </c>
+        <f t="shared" si="68"/>
+        <v>0.14684014869888484</v>
+      </c>
+      <c r="S34" s="9"/>
       <c r="T34" s="9"/>
-      <c r="U34" s="9">
-        <f t="shared" si="78"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9">
+        <f t="shared" ref="Y34:AM34" si="71">Y5/X5-1</f>
         <v>0.31569343065693434</v>
       </c>
-      <c r="V34" s="9">
-        <f t="shared" si="78"/>
+      <c r="Z34" s="9">
+        <f t="shared" si="71"/>
         <v>4.7156726768377233E-2</v>
       </c>
-      <c r="W34" s="9">
-        <f t="shared" si="78"/>
+      <c r="AA34" s="9">
+        <f t="shared" si="71"/>
         <v>0.21258278145695364</v>
       </c>
-      <c r="X34" s="9">
-        <f t="shared" si="78"/>
+      <c r="AB34" s="9">
+        <f t="shared" si="71"/>
         <v>0.16602949208083029</v>
       </c>
-      <c r="Y34" s="9">
-        <f t="shared" ref="Y34:AI34" si="80">Y5/X5-1</f>
-        <v>8.2248243559718937E-2</v>
-      </c>
-      <c r="Z34" s="9">
-        <f t="shared" si="80"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="AA34" s="9">
-        <f t="shared" si="80"/>
+      <c r="AC34" s="9">
+        <f t="shared" si="71"/>
+        <v>6.8852459016393475E-2</v>
+      </c>
+      <c r="AD34" s="9">
+        <f t="shared" si="71"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AE34" s="9">
+        <f t="shared" si="71"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AB34" s="9">
-        <f t="shared" si="80"/>
+      <c r="AF34" s="9">
+        <f t="shared" si="71"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AC34" s="9">
-        <f t="shared" si="80"/>
+      <c r="AG34" s="9">
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD34" s="9">
-        <f t="shared" si="80"/>
+      <c r="AH34" s="9">
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE34" s="9">
-        <f t="shared" si="80"/>
+      <c r="AI34" s="9">
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF34" s="9">
-        <f t="shared" si="80"/>
+      <c r="AJ34" s="9">
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG34" s="9">
-        <f t="shared" si="80"/>
+      <c r="AK34" s="9">
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH34" s="9">
-        <f t="shared" si="80"/>
+      <c r="AL34" s="9">
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI34" s="9">
-        <f t="shared" si="80"/>
+      <c r="AM34" s="9">
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL34" t="s">
+      <c r="AP34" t="s">
         <v>66</v>
       </c>
-      <c r="AM34" s="9">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="AQ34" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="35" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>54</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>-0.140625</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>-0.31034482758620696</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>-0.28282828282828287</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="68"/>
         <v>-0.46511627906976738</v>
       </c>
       <c r="N35" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="68"/>
         <v>-0.34545454545454546</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="P35" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>-9.8591549295774517E-2</v>
       </c>
       <c r="Q35" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>-0.24637681159420288</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="74"/>
-        <v>0.89999999999999991</v>
-      </c>
+        <f t="shared" si="68"/>
+        <v>-5.5555555555555691E-2</v>
+      </c>
+      <c r="S35" s="9"/>
       <c r="T35" s="9"/>
-      <c r="U35" s="9">
-        <f t="shared" si="78"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9">
+        <f t="shared" ref="Y35:AM35" si="72">Y6/X6-1</f>
         <v>6.708268330733258E-2</v>
       </c>
-      <c r="V35" s="9">
-        <f t="shared" si="78"/>
+      <c r="Z35" s="9">
+        <f t="shared" si="72"/>
         <v>0.10233918128654973</v>
       </c>
-      <c r="W35" s="9">
-        <f t="shared" si="78"/>
+      <c r="AA35" s="9">
+        <f t="shared" si="72"/>
         <v>9.2838196286472163E-2</v>
       </c>
-      <c r="X35" s="9">
-        <f t="shared" si="78"/>
+      <c r="AB35" s="9">
+        <f t="shared" si="72"/>
         <v>-0.35922330097087385</v>
       </c>
-      <c r="Y35" s="9">
-        <f t="shared" ref="Y35:AI35" si="81">Y6/X6-1</f>
-        <v>0.33939393939393936</v>
-      </c>
-      <c r="Z35" s="9">
-        <f t="shared" si="81"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AA35" s="9">
-        <f t="shared" si="81"/>
+      <c r="AC35" s="9">
+        <f t="shared" si="72"/>
+        <v>0.14393939393939381</v>
+      </c>
+      <c r="AD35" s="9">
+        <f t="shared" si="72"/>
+        <v>5.0000000000000266E-2</v>
+      </c>
+      <c r="AE35" s="9">
+        <f t="shared" si="72"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AB35" s="9">
-        <f t="shared" si="81"/>
+      <c r="AF35" s="9">
+        <f t="shared" si="72"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC35" s="9">
-        <f t="shared" si="81"/>
+      <c r="AG35" s="9">
+        <f t="shared" si="72"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AD35" s="9">
-        <f t="shared" si="81"/>
+      <c r="AH35" s="9">
+        <f t="shared" si="72"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AE35" s="9">
-        <f t="shared" si="81"/>
+      <c r="AI35" s="9">
+        <f t="shared" si="72"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AF35" s="9">
-        <f t="shared" si="81"/>
+      <c r="AJ35" s="9">
+        <f t="shared" si="72"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AG35" s="9">
-        <f t="shared" si="81"/>
+      <c r="AK35" s="9">
+        <f t="shared" si="72"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AH35" s="9">
-        <f t="shared" si="81"/>
+      <c r="AL35" s="9">
+        <f t="shared" si="72"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AI35" s="9">
-        <f t="shared" si="81"/>
+      <c r="AM35" s="9">
+        <f t="shared" si="72"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AL35" t="s">
+      <c r="AP35" t="s">
         <v>67</v>
       </c>
-      <c r="AM35" s="4">
-        <f>NPV(AM34,Y28:EO28)</f>
-        <v>7454.7382975273549</v>
-      </c>
-    </row>
-    <row r="36" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AQ35" s="4">
+        <f>NPV(AQ34,AD28:ES28)</f>
+        <v>14717.815783211758</v>
+      </c>
+    </row>
+    <row r="36" spans="2:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>55</v>
       </c>
       <c r="J36" s="10">
+        <f t="shared" si="68"/>
+        <v>-0.22832432432432415</v>
+      </c>
+      <c r="K36" s="10">
+        <f t="shared" si="68"/>
+        <v>-0.14534883720930225</v>
+      </c>
+      <c r="L36" s="10">
+        <f t="shared" si="68"/>
+        <v>0.11528239202657797</v>
+      </c>
+      <c r="M36" s="10">
+        <f t="shared" si="68"/>
+        <v>-0.17416291854072952</v>
+      </c>
+      <c r="N36" s="10">
+        <f t="shared" si="68"/>
+        <v>0.60381059120201708</v>
+      </c>
+      <c r="O36" s="10">
+        <f t="shared" si="68"/>
+        <v>0.38647959183673475</v>
+      </c>
+      <c r="P36" s="10">
+        <f t="shared" si="68"/>
+        <v>0.19511468573130775</v>
+      </c>
+      <c r="Q36" s="10">
+        <f t="shared" si="68"/>
+        <v>0.57065052950075623</v>
+      </c>
+      <c r="R36" s="10">
+        <f t="shared" si="68"/>
+        <v>0.35866526904262774</v>
+      </c>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10"/>
+      <c r="V36" s="10"/>
+      <c r="X36" s="10"/>
+      <c r="Y36" s="10">
+        <f t="shared" ref="Y36:AM36" si="73">Y7/X7-1</f>
+        <v>0.2241249055653487</v>
+      </c>
+      <c r="Z36" s="10">
         <f t="shared" si="73"/>
-        <v>-0.22832432432432415</v>
-      </c>
-      <c r="K36" s="10">
+        <v>0.23349105122402825</v>
+      </c>
+      <c r="AA36" s="10">
         <f t="shared" si="73"/>
-        <v>-0.14534883720930225</v>
-      </c>
-      <c r="L36" s="10">
+        <v>0.1118245496997996</v>
+      </c>
+      <c r="AB36" s="10">
         <f t="shared" si="73"/>
-        <v>0.11528239202657797</v>
-      </c>
-      <c r="M36" s="10">
-        <f t="shared" si="77"/>
-        <v>-0.17416291854072952</v>
-      </c>
-      <c r="N36" s="10">
-        <f t="shared" si="77"/>
-        <v>0.60381059120201708</v>
-      </c>
-      <c r="O36" s="10">
-        <f t="shared" si="74"/>
-        <v>0.38647959183673475</v>
-      </c>
-      <c r="P36" s="10">
-        <f t="shared" si="74"/>
-        <v>0.19511468573130775</v>
-      </c>
-      <c r="Q36" s="10">
-        <f t="shared" si="74"/>
-        <v>0.57065052950075623</v>
-      </c>
-      <c r="R36" s="10">
-        <f t="shared" si="74"/>
-        <v>0.27627533193570919</v>
-      </c>
-      <c r="T36" s="10"/>
-      <c r="U36" s="10">
-        <f t="shared" si="78"/>
-        <v>0.2241249055653487</v>
-      </c>
-      <c r="V36" s="10">
-        <f t="shared" si="78"/>
-        <v>0.23349105122402825</v>
-      </c>
-      <c r="W36" s="10">
-        <f t="shared" si="78"/>
-        <v>0.1118245496997996</v>
-      </c>
-      <c r="X36" s="10">
-        <f t="shared" si="78"/>
         <v>0.10537763444086101</v>
       </c>
-      <c r="Y36" s="10">
-        <f t="shared" ref="Y36:AI36" si="82">Y7/X7-1</f>
-        <v>0.34138960510245608</v>
-      </c>
-      <c r="Z36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.2527401944419152</v>
-      </c>
-      <c r="AA36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.17047314047100715</v>
-      </c>
-      <c r="AB36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.1389227200440708</v>
-      </c>
       <c r="AC36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.11076649084691859</v>
+        <f t="shared" si="73"/>
+        <v>0.37338851947347007</v>
       </c>
       <c r="AD36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.11193782760339865</v>
+        <f t="shared" si="73"/>
+        <v>0.48171780050392754</v>
       </c>
       <c r="AE36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.11404339227887128</v>
+        <f t="shared" si="73"/>
+        <v>0.2860710635864554</v>
       </c>
       <c r="AF36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.1161939300242969</v>
+        <f t="shared" si="73"/>
+        <v>0.15972646488814846</v>
       </c>
       <c r="AG36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.11838934842626525</v>
+        <f t="shared" si="73"/>
+        <v>0.10911948875791899</v>
       </c>
       <c r="AH36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.12062885553814495</v>
+        <f t="shared" si="73"/>
+        <v>9.4686344548739365E-2</v>
       </c>
       <c r="AI36" s="10">
-        <f t="shared" si="82"/>
-        <v>0.12291091607126114</v>
-      </c>
-      <c r="AL36" t="s">
+        <f t="shared" si="73"/>
+        <v>8.730194354884202E-2</v>
+      </c>
+      <c r="AJ36" s="10">
+        <f t="shared" si="73"/>
+        <v>8.7854616770292937E-2</v>
+      </c>
+      <c r="AK36" s="10">
+        <f t="shared" si="73"/>
+        <v>8.8386987656380089E-2</v>
+      </c>
+      <c r="AL36" s="10">
+        <f t="shared" si="73"/>
+        <v>8.8899420612399416E-2</v>
+      </c>
+      <c r="AM36" s="10">
+        <f t="shared" si="73"/>
+        <v>8.9392312364905191E-2</v>
+      </c>
+      <c r="AP36" t="s">
         <v>68</v>
       </c>
-      <c r="AM36" s="4">
+      <c r="AQ36" s="4">
         <f>Main!D8</f>
-        <v>-745.59999999999991</v>
-      </c>
-    </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.3">
+        <v>-407.59999999999991</v>
+      </c>
+    </row>
+    <row r="37" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>56</v>
       </c>
       <c r="F37" s="9">
-        <f t="shared" ref="F37:L40" si="83">(F3-F8)/F3</f>
+        <f t="shared" ref="F37:R37" si="74">(F3-F8)/F3</f>
         <v>0.38145474736257629</v>
       </c>
       <c r="G37" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="74"/>
         <v>0.33092410944759937</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="74"/>
         <v>0.32370749883558453</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="74"/>
         <v>0.40065573770491797</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="74"/>
         <v>0.3411000763941941</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="74"/>
         <v>0.24511082138200788</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="74"/>
         <v>0.28722934158197083</v>
       </c>
       <c r="M37" s="9">
-        <f>(M3-M8)/M3</f>
+        <f t="shared" si="74"/>
         <v>0.33661248930710014</v>
       </c>
       <c r="N37" s="9">
-        <f>(N3-N8)/N3</f>
+        <f t="shared" si="74"/>
         <v>0.46215815136739452</v>
       </c>
       <c r="O37" s="9">
-        <f t="shared" ref="O37:R37" si="84">(O3-O8)/O3</f>
+        <f t="shared" si="74"/>
         <v>0.34119867862199155</v>
       </c>
       <c r="P37" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="74"/>
         <v>0.3300741739716791</v>
       </c>
       <c r="Q37" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="74"/>
         <v>0.34998698933125161</v>
       </c>
       <c r="R37" s="9">
-        <f t="shared" si="84"/>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="T37" s="9">
-        <f>(T3-T8)/T3</f>
+        <f t="shared" si="74"/>
+        <v>0.36617071260767425</v>
+      </c>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="X37" s="9">
+        <f t="shared" ref="X37:AM37" si="75">(X3-X8)/X3</f>
         <v>0.35846509834168921</v>
       </c>
-      <c r="U37" s="9">
-        <f>(U3-U8)/U3</f>
+      <c r="Y37" s="9">
+        <f t="shared" si="75"/>
         <v>0.28907309721175584</v>
       </c>
-      <c r="V37" s="9">
-        <f t="shared" ref="V37:X37" si="85">(V3-V8)/V3</f>
+      <c r="Z37" s="9">
+        <f t="shared" si="75"/>
         <v>0.30032928352446914</v>
       </c>
-      <c r="W37" s="9">
-        <f t="shared" si="85"/>
+      <c r="AA37" s="9">
+        <f t="shared" si="75"/>
         <v>0.35387612797374912</v>
       </c>
-      <c r="X37" s="9">
-        <f t="shared" si="85"/>
+      <c r="AB37" s="9">
+        <f t="shared" si="75"/>
         <v>0.36795060818282338</v>
       </c>
-      <c r="Y37" s="9">
-        <f t="shared" ref="Y37:AI37" si="86">(Y3-Y8)/Y3</f>
-        <v>0.38346768665515069</v>
-      </c>
-      <c r="Z37" s="9">
-        <f t="shared" si="86"/>
+      <c r="AC37" s="9">
+        <f t="shared" si="75"/>
+        <v>0.35166198654737807</v>
+      </c>
+      <c r="AD37" s="9">
+        <f t="shared" si="75"/>
         <v>0.4</v>
       </c>
-      <c r="AA37" s="9">
-        <f t="shared" si="86"/>
+      <c r="AE37" s="9">
+        <f t="shared" si="75"/>
+        <v>0.39999999999999997</v>
+      </c>
+      <c r="AF37" s="9">
+        <f t="shared" si="75"/>
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="AG37" s="9">
+        <f t="shared" si="75"/>
         <v>0.4</v>
       </c>
-      <c r="AB37" s="9">
-        <f t="shared" si="86"/>
+      <c r="AH37" s="9">
+        <f t="shared" si="75"/>
         <v>0.40000000000000008</v>
       </c>
-      <c r="AC37" s="9">
-        <f t="shared" si="86"/>
+      <c r="AI37" s="9">
+        <f t="shared" si="75"/>
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="AJ37" s="9">
+        <f t="shared" si="75"/>
+        <v>0.39999999999999997</v>
+      </c>
+      <c r="AK37" s="9">
+        <f t="shared" si="75"/>
         <v>0.4</v>
       </c>
-      <c r="AD37" s="9">
-        <f t="shared" si="86"/>
+      <c r="AL37" s="9">
+        <f t="shared" si="75"/>
         <v>0.4</v>
       </c>
-      <c r="AE37" s="9">
-        <f t="shared" si="86"/>
+      <c r="AM37" s="9">
+        <f t="shared" si="75"/>
         <v>0.4</v>
       </c>
-      <c r="AF37" s="9">
-        <f t="shared" si="86"/>
-        <v>0.4</v>
-      </c>
-      <c r="AG37" s="9">
-        <f t="shared" si="86"/>
-        <v>0.40000000000000008</v>
-      </c>
-      <c r="AH37" s="9">
-        <f t="shared" si="86"/>
-        <v>0.40000000000000008</v>
-      </c>
-      <c r="AI37" s="9">
-        <f t="shared" si="86"/>
-        <v>0.4</v>
-      </c>
-      <c r="AL37" t="s">
+      <c r="AP37" t="s">
         <v>69</v>
       </c>
-      <c r="AM37" s="4">
-        <f>AM35+AM36</f>
-        <v>6709.1382975273555</v>
-      </c>
-    </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="AQ37" s="4">
+        <f>AQ35+AQ36</f>
+        <v>14310.215783211757</v>
+      </c>
+    </row>
+    <row r="38" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>57</v>
       </c>
       <c r="F38" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" ref="F38:R38" si="76">(F4-F9)/F4</f>
         <v>-7.175925925925912E-2</v>
       </c>
       <c r="G38" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>-0.22439024390243908</v>
       </c>
       <c r="H38" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>-0.11157024793388427</v>
       </c>
       <c r="I38" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>-0.18264840182648404</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>-7.3076923076923025E-2</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>-0.35087719298245612</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>-3.747072599531602E-2</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" ref="M38:N40" si="87">(M4-M9)/M4</f>
+        <f t="shared" si="76"/>
         <v>-0.11214953271028041</v>
       </c>
       <c r="N38" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="76"/>
         <v>5.5401662049861494E-2</v>
       </c>
       <c r="O38" s="9">
-        <f t="shared" ref="O38:R38" si="88">(O4-O9)/O4</f>
+        <f t="shared" si="76"/>
         <v>1.1869436201780582E-2</v>
       </c>
       <c r="P38" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="76"/>
         <v>-2.1390374331550915E-2</v>
       </c>
       <c r="Q38" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="76"/>
         <v>8.9665653495440714E-2</v>
       </c>
       <c r="R38" s="9">
-        <f t="shared" si="88"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="T38" s="9">
-        <f t="shared" ref="T38" si="89">(T4-T9)/T4</f>
+        <f t="shared" si="76"/>
+        <v>-0.10698365527488861</v>
+      </c>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="X38" s="9">
+        <f t="shared" ref="X38:AM38" si="77">(X4-X9)/X4</f>
         <v>-0.1432777232580961</v>
       </c>
-      <c r="U38" s="9">
-        <f t="shared" ref="U38:X40" si="90">(U4-U9)/U4</f>
+      <c r="Y38" s="9">
+        <f t="shared" si="77"/>
         <v>-0.14672216441207087</v>
       </c>
-      <c r="V38" s="9">
-        <f t="shared" si="90"/>
+      <c r="Z38" s="9">
+        <f t="shared" si="77"/>
         <v>-0.13029315960912052</v>
       </c>
-      <c r="W38" s="9">
-        <f t="shared" si="90"/>
+      <c r="AA38" s="9">
+        <f t="shared" si="77"/>
         <v>-0.14254859611231122</v>
       </c>
-      <c r="X38" s="9">
-        <f t="shared" si="90"/>
+      <c r="AB38" s="9">
+        <f t="shared" si="77"/>
         <v>-5.8871627146361308E-2</v>
       </c>
-      <c r="Y38" s="9">
-        <f t="shared" ref="Y38:AI38" si="91">(Y4-Y9)/Y4</f>
-        <v>6.9482248520709999E-2</v>
-      </c>
-      <c r="Z38" s="9">
-        <f t="shared" si="91"/>
-        <v>8.9999999999999941E-2</v>
-      </c>
-      <c r="AA38" s="9">
-        <f t="shared" si="91"/>
-        <v>0.09</v>
-      </c>
-      <c r="AB38" s="9">
-        <f t="shared" si="91"/>
+      <c r="AC38" s="9">
+        <f t="shared" si="77"/>
+        <v>-8.3251714005877428E-3</v>
+      </c>
+      <c r="AD38" s="9">
+        <f t="shared" si="77"/>
+        <v>9.0000000000000052E-2</v>
+      </c>
+      <c r="AE38" s="9">
+        <f t="shared" si="77"/>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="AF38" s="9">
+        <f t="shared" si="77"/>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="AG38" s="9">
+        <f t="shared" si="77"/>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="AH38" s="9">
+        <f t="shared" si="77"/>
+        <v>8.9999999999999983E-2</v>
+      </c>
+      <c r="AI38" s="9">
+        <f t="shared" si="77"/>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="AJ38" s="9">
+        <f t="shared" si="77"/>
         <v>8.9999999999999955E-2</v>
       </c>
-      <c r="AC38" s="9">
-        <f t="shared" si="91"/>
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="AD38" s="9">
-        <f t="shared" si="91"/>
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="AE38" s="9">
-        <f t="shared" si="91"/>
-        <v>0.09</v>
-      </c>
-      <c r="AF38" s="9">
-        <f t="shared" si="91"/>
-        <v>0.09</v>
-      </c>
-      <c r="AG38" s="9">
-        <f t="shared" si="91"/>
-        <v>0.09</v>
-      </c>
-      <c r="AH38" s="9">
-        <f t="shared" si="91"/>
-        <v>9.0000000000000024E-2</v>
-      </c>
-      <c r="AI38" s="9">
-        <f t="shared" si="91"/>
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="AL38" t="s">
+      <c r="AK38" s="9">
+        <f t="shared" si="77"/>
+        <v>8.9999999999999955E-2</v>
+      </c>
+      <c r="AL38" s="9">
+        <f t="shared" si="77"/>
+        <v>8.9999999999999913E-2</v>
+      </c>
+      <c r="AM38" s="9">
+        <f t="shared" si="77"/>
+        <v>8.9999999999999983E-2</v>
+      </c>
+      <c r="AP38" t="s">
         <v>70</v>
       </c>
-      <c r="AM38" s="7">
-        <f>AM37/AI29</f>
-        <v>28.368449461003618</v>
-      </c>
-    </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="AQ38" s="7">
+        <f>AQ37/AM29</f>
+        <v>51.016812061360987</v>
+      </c>
+    </row>
+    <row r="39" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>58</v>
       </c>
       <c r="F39" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" ref="F39:R39" si="78">(F5-F10)/F5</f>
         <v>-9.7744360902255606E-2</v>
       </c>
       <c r="G39" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>-0.25798525798525795</v>
       </c>
       <c r="H39" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>-0.3546099290780142</v>
       </c>
       <c r="I39" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>-0.20842105263157892</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>-4.7528517110266157E-2</v>
       </c>
       <c r="K39" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>-1.7730496453900962E-3</v>
       </c>
       <c r="L39" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>1.9047619047619319E-3</v>
       </c>
       <c r="M39" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="78"/>
         <v>-1.1811023622047273E-2</v>
       </c>
       <c r="N39" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="78"/>
         <v>-1.6728624535316091E-2</v>
       </c>
       <c r="O39" s="9">
-        <f t="shared" ref="O39:R39" si="92">(O5-O10)/O5</f>
+        <f t="shared" si="78"/>
         <v>1.1214953271028064E-2</v>
       </c>
       <c r="P39" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="78"/>
         <v>9.1911764705882359E-2</v>
       </c>
       <c r="Q39" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="78"/>
         <v>0.11604095563139939</v>
       </c>
       <c r="R39" s="9">
-        <f t="shared" si="92"/>
-        <v>9.999999999999995E-2</v>
-      </c>
-      <c r="T39" s="9">
-        <f t="shared" ref="T39" si="93">(T5-T10)/T5</f>
+        <f t="shared" si="78"/>
+        <v>0.16855753646677479</v>
+      </c>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="X39" s="9">
+        <f t="shared" ref="X39:AM39" si="79">(X5-X10)/X5</f>
         <v>-0.20711678832116806</v>
       </c>
-      <c r="U39" s="9">
-        <f t="shared" si="90"/>
+      <c r="Y39" s="9">
+        <f t="shared" si="79"/>
         <v>-2.8432732316227623E-2</v>
       </c>
-      <c r="V39" s="9">
-        <f t="shared" si="90"/>
+      <c r="Z39" s="9">
+        <f t="shared" si="79"/>
         <v>-0.11589403973509933</v>
       </c>
-      <c r="W39" s="9">
-        <f t="shared" si="90"/>
+      <c r="AA39" s="9">
+        <f t="shared" si="79"/>
         <v>-0.20699071545603498</v>
       </c>
-      <c r="X39" s="9">
-        <f t="shared" si="90"/>
+      <c r="AB39" s="9">
+        <f t="shared" si="79"/>
         <v>-7.0257611241217799E-3</v>
       </c>
-      <c r="Y39" s="9">
-        <f t="shared" ref="Y39:AI39" si="94">(Y5-Y10)/Y5</f>
-        <v>8.1606509131827334E-2</v>
-      </c>
-      <c r="Z39" s="9">
-        <f t="shared" si="94"/>
+      <c r="AC39" s="9">
+        <f t="shared" si="79"/>
+        <v>9.9912357581069297E-2</v>
+      </c>
+      <c r="AD39" s="9">
+        <f t="shared" si="79"/>
         <v>0.1</v>
       </c>
-      <c r="AA39" s="9">
-        <f t="shared" si="94"/>
-        <v>0.15000000000000005</v>
-      </c>
-      <c r="AB39" s="9">
-        <f t="shared" si="94"/>
+      <c r="AE39" s="9">
+        <f t="shared" si="79"/>
+        <v>0.15</v>
+      </c>
+      <c r="AF39" s="9">
+        <f t="shared" si="79"/>
+        <v>0.17000000000000004</v>
+      </c>
+      <c r="AG39" s="9">
+        <f t="shared" si="79"/>
         <v>0.17000000000000007</v>
       </c>
-      <c r="AC39" s="9">
-        <f t="shared" si="94"/>
+      <c r="AH39" s="9">
+        <f t="shared" si="79"/>
+        <v>0.17</v>
+      </c>
+      <c r="AI39" s="9">
+        <f t="shared" si="79"/>
+        <v>0.17000000000000007</v>
+      </c>
+      <c r="AJ39" s="9">
+        <f t="shared" si="79"/>
+        <v>0.17</v>
+      </c>
+      <c r="AK39" s="9">
+        <f t="shared" si="79"/>
         <v>0.17000000000000004</v>
       </c>
-      <c r="AD39" s="9">
-        <f t="shared" si="94"/>
+      <c r="AL39" s="9">
+        <f t="shared" si="79"/>
+        <v>0.17000000000000012</v>
+      </c>
+      <c r="AM39" s="9">
+        <f t="shared" si="79"/>
         <v>0.17000000000000004</v>
       </c>
-      <c r="AE39" s="9">
-        <f t="shared" si="94"/>
-        <v>0.17</v>
-      </c>
-      <c r="AF39" s="9">
-        <f t="shared" si="94"/>
-        <v>0.17000000000000004</v>
-      </c>
-      <c r="AG39" s="9">
-        <f t="shared" si="94"/>
-        <v>0.17</v>
-      </c>
-      <c r="AH39" s="9">
-        <f t="shared" si="94"/>
-        <v>0.17</v>
-      </c>
-      <c r="AI39" s="9">
-        <f t="shared" si="94"/>
-        <v>0.17000000000000004</v>
-      </c>
-      <c r="AL39" t="s">
+      <c r="AP39" t="s">
         <v>71</v>
       </c>
-      <c r="AM39" s="7">
+      <c r="AQ39" s="7">
         <f>Main!D3</f>
-        <v>132.12</v>
-      </c>
-    </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.3">
+        <v>147.55000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>59</v>
       </c>
       <c r="F40" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" ref="F40:R40" si="80">(F6-F11)/F6</f>
         <v>-3.072916666666667</v>
       </c>
       <c r="G40" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.26108374384236455</v>
       </c>
       <c r="H40" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.21717171717171721</v>
       </c>
       <c r="I40" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>-4.4031007751937983</v>
       </c>
       <c r="J40" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.44848484848484849</v>
       </c>
       <c r="K40" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.31428571428571433</v>
       </c>
       <c r="L40" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.35211267605633806</v>
       </c>
       <c r="M40" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="80"/>
         <v>0.31159420289855078</v>
       </c>
       <c r="N40" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="80"/>
         <v>1.8518518518518615E-2</v>
       </c>
       <c r="O40" s="9">
-        <f t="shared" ref="O40:R40" si="95">(O6-O11)/O6</f>
+        <f t="shared" si="80"/>
         <v>0.57037037037037042</v>
       </c>
       <c r="P40" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="80"/>
         <v>0.3984375</v>
       </c>
       <c r="Q40" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="80"/>
         <v>0.44230769230769235</v>
       </c>
       <c r="R40" s="9">
-        <f t="shared" si="95"/>
-        <v>0.31773879142300193</v>
-      </c>
-      <c r="T40" s="9">
-        <f t="shared" ref="T40" si="96">(T6-T11)/T6</f>
+        <f t="shared" si="80"/>
+        <v>0.28431372549019607</v>
+      </c>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="X40" s="9">
+        <f t="shared" ref="X40:AM40" si="81">(X6-X11)/X6</f>
         <v>0.26833073322932915</v>
       </c>
-      <c r="U40" s="9">
-        <f t="shared" si="90"/>
+      <c r="Y40" s="9">
+        <f t="shared" si="81"/>
         <v>0.35087719298245623</v>
       </c>
-      <c r="V40" s="9">
-        <f t="shared" si="90"/>
+      <c r="Z40" s="9">
+        <f t="shared" si="81"/>
         <v>-1.1498673740053047</v>
       </c>
-      <c r="W40" s="9">
-        <f t="shared" si="90"/>
+      <c r="AA40" s="9">
+        <f t="shared" si="81"/>
         <v>-1.1723300970873785</v>
       </c>
-      <c r="X40" s="9">
-        <f t="shared" si="90"/>
+      <c r="AB40" s="9">
+        <f t="shared" si="81"/>
         <v>0.26325757575757575</v>
       </c>
-      <c r="Y40" s="9">
-        <f t="shared" ref="Y40:AI40" si="97">(Y6-Y11)/Y6</f>
-        <v>0.44711538461538458</v>
-      </c>
-      <c r="Z40" s="9">
-        <f t="shared" si="97"/>
+      <c r="AC40" s="9">
+        <f t="shared" si="81"/>
+        <v>0.46357615894039728</v>
+      </c>
+      <c r="AD40" s="9">
+        <f t="shared" si="81"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="AE40" s="9">
+        <f t="shared" si="81"/>
         <v>0.44</v>
       </c>
-      <c r="AA40" s="9">
-        <f t="shared" si="97"/>
+      <c r="AF40" s="9">
+        <f t="shared" si="81"/>
         <v>0.43999999999999995</v>
       </c>
-      <c r="AB40" s="9">
-        <f t="shared" si="97"/>
+      <c r="AG40" s="9">
+        <f t="shared" si="81"/>
+        <v>0.43999999999999989</v>
+      </c>
+      <c r="AH40" s="9">
+        <f t="shared" si="81"/>
+        <v>0.43999999999999989</v>
+      </c>
+      <c r="AI40" s="9">
+        <f t="shared" si="81"/>
         <v>0.43999999999999995</v>
       </c>
-      <c r="AC40" s="9">
-        <f t="shared" si="97"/>
+      <c r="AJ40" s="9">
+        <f t="shared" si="81"/>
         <v>0.43999999999999995</v>
       </c>
-      <c r="AD40" s="9">
-        <f t="shared" si="97"/>
+      <c r="AK40" s="9">
+        <f t="shared" si="81"/>
+        <v>0.43999999999999989</v>
+      </c>
+      <c r="AL40" s="9">
+        <f t="shared" si="81"/>
+        <v>0.43999999999999989</v>
+      </c>
+      <c r="AM40" s="9">
+        <f t="shared" si="81"/>
         <v>0.43999999999999995</v>
       </c>
-      <c r="AE40" s="9">
-        <f t="shared" si="97"/>
-        <v>0.43999999999999989</v>
-      </c>
-      <c r="AF40" s="9">
-        <f t="shared" si="97"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="AG40" s="9">
-        <f t="shared" si="97"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="AH40" s="9">
-        <f t="shared" si="97"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="AI40" s="9">
-        <f t="shared" si="97"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="AL40" s="1" t="s">
+      <c r="AP40" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AM40" s="10">
-        <f>AM38/AM39-1</f>
-        <v>-0.7852827016272812</v>
-      </c>
-    </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="AQ40" s="10">
+        <f>AQ38/AQ39-1</f>
+        <v>-0.65424051466376831</v>
+      </c>
+    </row>
+    <row r="41" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>50</v>
       </c>
       <c r="F41" s="9">
-        <f t="shared" ref="F41:L41" si="98">F13/F7</f>
+        <f t="shared" ref="F41:R41" si="82">F13/F7</f>
         <v>0.15437837837837823</v>
       </c>
       <c r="G41" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="82"/>
         <v>0.19731104651162795</v>
       </c>
       <c r="H41" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="82"/>
         <v>0.18637873754152831</v>
       </c>
       <c r="I41" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="82"/>
         <v>-1.3243378310844607E-2</v>
       </c>
       <c r="J41" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="82"/>
         <v>0.25861585878397308</v>
       </c>
       <c r="K41" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="82"/>
         <v>0.16113945578231306</v>
       </c>
       <c r="L41" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="82"/>
         <v>0.20405123622281801</v>
       </c>
       <c r="M41" s="9">
-        <f>M13/M7</f>
+        <f t="shared" si="82"/>
         <v>0.23842662632375197</v>
       </c>
       <c r="N41" s="9">
-        <f>N13/N7</f>
+        <f t="shared" si="82"/>
         <v>0.38312368972746325</v>
       </c>
       <c r="O41" s="9">
-        <f t="shared" ref="O41:R41" si="99">O13/O7</f>
+        <f t="shared" si="82"/>
         <v>0.27200245323520406</v>
       </c>
       <c r="P41" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="82"/>
         <v>0.26719840478564322</v>
       </c>
       <c r="Q41" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="82"/>
         <v>0.29242920439221731</v>
       </c>
       <c r="R41" s="9">
-        <f t="shared" si="99"/>
-        <v>0.37947874175267604</v>
-      </c>
-      <c r="T41" s="9">
-        <f>T13/T7</f>
+        <f t="shared" si="82"/>
+        <v>0.30847370451330858</v>
+      </c>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="X41" s="9">
+        <f t="shared" ref="X41:AM41" si="83">X13/X7</f>
         <v>0.2087635356333418</v>
       </c>
-      <c r="U41" s="9">
-        <f>U13/U7</f>
+      <c r="Y41" s="9">
+        <f t="shared" si="83"/>
         <v>0.20325036000822869</v>
       </c>
-      <c r="V41" s="9">
-        <f t="shared" ref="V41:X41" si="100">V13/V7</f>
+      <c r="Z41" s="9">
+        <f t="shared" si="83"/>
         <v>0.12366577718478998</v>
       </c>
-      <c r="W41" s="9">
-        <f t="shared" si="100"/>
+      <c r="AA41" s="9">
+        <f t="shared" si="83"/>
         <v>0.14805370134253365</v>
       </c>
-      <c r="X41" s="9">
-        <f t="shared" si="100"/>
+      <c r="AB41" s="9">
+        <f t="shared" si="83"/>
         <v>0.27446057809743507</v>
       </c>
-      <c r="Y41" s="9">
-        <f t="shared" ref="Y41:AI41" si="101">Y13/Y7</f>
-        <v>0.31610691270347108</v>
-      </c>
-      <c r="Z41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.33074922064278472</v>
-      </c>
-      <c r="AA41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.33024320454435968</v>
-      </c>
-      <c r="AB41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.32685793524514156</v>
-      </c>
       <c r="AC41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.32370972605173592</v>
+        <f t="shared" si="83"/>
+        <v>0.29030186255619789</v>
       </c>
       <c r="AD41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.32034856293075403</v>
+        <f t="shared" si="83"/>
+        <v>0.33962947773448759</v>
       </c>
       <c r="AE41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.31665353085110021</v>
+        <f t="shared" si="83"/>
+        <v>0.34432104462777546</v>
       </c>
       <c r="AF41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.31263156305529294</v>
+        <f t="shared" si="83"/>
+        <v>0.34248886577024951</v>
       </c>
       <c r="AG41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.30829191476367956</v>
+        <f t="shared" si="83"/>
+        <v>0.33984975350558533</v>
       </c>
       <c r="AH41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.30364626164892577</v>
+        <f t="shared" si="83"/>
+        <v>0.34048650643756928</v>
       </c>
       <c r="AI41" s="9">
-        <f t="shared" si="101"/>
-        <v>0.29870876006942798</v>
-      </c>
-      <c r="AL41" t="s">
+        <f t="shared" si="83"/>
+        <v>0.34286472610411939</v>
+      </c>
+      <c r="AJ41" s="9">
+        <f t="shared" si="83"/>
+        <v>0.3451683987108855</v>
+      </c>
+      <c r="AK41" s="9">
+        <f t="shared" si="83"/>
+        <v>0.34739797176630538</v>
+      </c>
+      <c r="AL41" s="9">
+        <f t="shared" si="83"/>
+        <v>0.34955408073148142</v>
+      </c>
+      <c r="AM41" s="9">
+        <f t="shared" si="83"/>
+        <v>0.35163753164450967</v>
+      </c>
+      <c r="AP41" t="s">
         <v>73</v>
       </c>
-      <c r="AM41" s="5" t="s">
+      <c r="AQ41" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>60</v>
       </c>
@@ -5744,225 +6021,233 @@
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
       <c r="J42" s="9">
-        <f t="shared" ref="J42:L42" si="102">J14/F14-1</f>
+        <f t="shared" ref="J42:R42" si="84">J14/F14-1</f>
         <v>-0.12271540469973885</v>
       </c>
       <c r="K42" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="84"/>
         <v>-0.22319474835886222</v>
       </c>
       <c r="L42" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="84"/>
         <v>-9.8795180722891618E-2</v>
       </c>
       <c r="M42" s="9">
-        <f>M14/I14-1</f>
+        <f t="shared" si="84"/>
         <v>3.4188034188034067E-2</v>
       </c>
       <c r="N42" s="9">
-        <f>N14/J14-1</f>
+        <f t="shared" si="84"/>
         <v>0.17559523809523814</v>
       </c>
       <c r="O42" s="9">
-        <f t="shared" ref="O42:R42" si="103">O14/K14-1</f>
+        <f t="shared" si="84"/>
         <v>0.14366197183098595</v>
       </c>
       <c r="P42" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="84"/>
         <v>9.0909090909090828E-2</v>
       </c>
       <c r="Q42" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="84"/>
         <v>0.34159779614325081</v>
       </c>
       <c r="R42" s="9">
-        <f t="shared" si="103"/>
-        <v>0.36708860759493667</v>
-      </c>
+        <f t="shared" si="84"/>
+        <v>0.41518987341772151</v>
+      </c>
+      <c r="S42" s="9"/>
       <c r="T42" s="9"/>
-      <c r="U42" s="9">
-        <f>U14/T14-1</f>
+      <c r="U42" s="9"/>
+      <c r="V42" s="9"/>
+      <c r="X42" s="9"/>
+      <c r="Y42" s="9">
+        <f t="shared" ref="Y42:AM42" si="85">Y14/X14-1</f>
         <v>0.23684210526315796</v>
       </c>
-      <c r="V42" s="9">
-        <f t="shared" ref="V42:X42" si="104">V14/U14-1</f>
+      <c r="Z42" s="9">
+        <f t="shared" si="85"/>
         <v>0.45647969052224369</v>
       </c>
-      <c r="W42" s="9">
-        <f t="shared" si="104"/>
+      <c r="AA42" s="9">
+        <f t="shared" si="85"/>
         <v>3.5192563081009265E-2</v>
       </c>
-      <c r="X42" s="9">
-        <f t="shared" si="104"/>
+      <c r="AB42" s="9">
+        <f t="shared" si="85"/>
         <v>-4.6183450930083469E-2</v>
       </c>
-      <c r="Y42" s="9">
-        <f t="shared" ref="Y42:AI42" si="105">Y14/X14-1</f>
-        <v>0.23806321452589141</v>
-      </c>
-      <c r="Z42" s="9">
-        <f t="shared" si="105"/>
+      <c r="AC42" s="9">
+        <f t="shared" si="85"/>
+        <v>0.25084061869536001</v>
+      </c>
+      <c r="AD42" s="9">
+        <f t="shared" si="85"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AE42" s="9">
+        <f t="shared" si="85"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AF42" s="9">
+        <f t="shared" si="85"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AA42" s="9">
-        <f t="shared" si="105"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="AB42" s="9">
-        <f t="shared" si="105"/>
+      <c r="AG42" s="9">
+        <f t="shared" si="85"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AH42" s="9">
+        <f t="shared" si="85"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AI42" s="9">
+        <f t="shared" si="85"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AJ42" s="9">
+        <f t="shared" si="85"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AC42" s="9">
-        <f t="shared" si="105"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AD42" s="9">
-        <f t="shared" si="105"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AE42" s="9">
-        <f t="shared" si="105"/>
+      <c r="AK42" s="9">
+        <f t="shared" si="85"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF42" s="9">
-        <f t="shared" si="105"/>
+      <c r="AL42" s="9">
+        <f t="shared" si="85"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG42" s="9">
-        <f t="shared" si="105"/>
+      <c r="AM42" s="9">
+        <f t="shared" si="85"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH42" s="9">
-        <f t="shared" si="105"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AI42" s="9">
-        <f t="shared" si="105"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>61</v>
       </c>
       <c r="F43" s="9">
-        <f t="shared" ref="F43:L43" si="106">F15/F7</f>
+        <f t="shared" ref="F43:R43" si="86">F15/F7</f>
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="G43" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v>9.8473837209302334E-2</v>
       </c>
       <c r="H43" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v>8.9036544850498348E-2</v>
       </c>
       <c r="I43" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v>4.9975012493753128E-2</v>
       </c>
       <c r="J43" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v>4.4830484729616135E-2</v>
       </c>
       <c r="K43" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v>5.7823129251700675E-2</v>
       </c>
       <c r="L43" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v>5.3321417932677986E-2</v>
       </c>
       <c r="M43" s="9">
-        <f>M15/M7</f>
+        <f t="shared" si="86"/>
         <v>4.4478063540090762E-2</v>
       </c>
       <c r="N43" s="9">
-        <f>N15/N7</f>
+        <f t="shared" si="86"/>
         <v>3.8085255066387144E-2</v>
       </c>
       <c r="O43" s="9">
-        <f t="shared" ref="O43:R43" si="107">O15/O7</f>
+        <f t="shared" si="86"/>
         <v>6.8383931309414281E-2</v>
       </c>
       <c r="P43" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="86"/>
         <v>6.0069790628115662E-2</v>
       </c>
       <c r="Q43" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="86"/>
         <v>8.0909266037372377E-2</v>
       </c>
       <c r="R43" s="9">
-        <f t="shared" si="107"/>
-        <v>6.8442521970049561E-2</v>
-      </c>
-      <c r="T43" s="9">
-        <f>T15/T7</f>
+        <f t="shared" si="86"/>
+        <v>5.3876816253053871E-2</v>
+      </c>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="X43" s="9">
+        <f t="shared" ref="X43:AM43" si="87">X15/X7</f>
         <v>7.0385293376983127E-2</v>
       </c>
-      <c r="U43" s="9">
-        <f>U15/U7</f>
+      <c r="Y43" s="9">
+        <f t="shared" si="87"/>
         <v>8.8973462250565738E-2</v>
       </c>
-      <c r="V43" s="9">
-        <f t="shared" ref="V43:X43" si="108">V15/V7</f>
+      <c r="Z43" s="9">
+        <f t="shared" si="87"/>
         <v>7.5800533689126065E-2</v>
       </c>
-      <c r="W43" s="9">
-        <f t="shared" si="108"/>
+      <c r="AA43" s="9">
+        <f t="shared" si="87"/>
         <v>6.7426685667141689E-2</v>
       </c>
-      <c r="X43" s="9">
-        <f t="shared" si="108"/>
+      <c r="AB43" s="9">
+        <f t="shared" si="87"/>
         <v>4.6139231917492196E-2</v>
       </c>
-      <c r="Y43" s="9">
-        <f t="shared" ref="Y43:AI43" si="109">Y15/Y7</f>
-        <v>7.0007182817890284E-2</v>
-      </c>
-      <c r="Z43" s="9">
-        <f t="shared" si="109"/>
+      <c r="AC43" s="9">
+        <f t="shared" si="87"/>
+        <v>6.4374289807815815E-2</v>
+      </c>
+      <c r="AD43" s="9">
+        <f t="shared" si="87"/>
         <v>0.05</v>
       </c>
-      <c r="AA43" s="9">
-        <f t="shared" si="109"/>
+      <c r="AE43" s="9">
+        <f t="shared" si="87"/>
         <v>0.05</v>
       </c>
-      <c r="AB43" s="9">
-        <f t="shared" si="109"/>
-        <v>5.000000000000001E-2</v>
-      </c>
-      <c r="AC43" s="9">
-        <f t="shared" si="109"/>
+      <c r="AF43" s="9">
+        <f t="shared" si="87"/>
         <v>0.05</v>
       </c>
-      <c r="AD43" s="9">
-        <f t="shared" si="109"/>
+      <c r="AG43" s="9">
+        <f t="shared" si="87"/>
         <v>0.05</v>
       </c>
-      <c r="AE43" s="9">
-        <f t="shared" si="109"/>
+      <c r="AH43" s="9">
+        <f t="shared" si="87"/>
         <v>0.05</v>
       </c>
-      <c r="AF43" s="9">
-        <f t="shared" si="109"/>
+      <c r="AI43" s="9">
+        <f t="shared" si="87"/>
         <v>0.05</v>
       </c>
-      <c r="AG43" s="9">
-        <f t="shared" si="109"/>
+      <c r="AJ43" s="9">
+        <f t="shared" si="87"/>
         <v>0.05</v>
       </c>
-      <c r="AH43" s="9">
-        <f t="shared" si="109"/>
-        <v>5.000000000000001E-2</v>
-      </c>
-      <c r="AI43" s="9">
-        <f t="shared" si="109"/>
-        <v>5.000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="AK43" s="9">
+        <f t="shared" si="87"/>
+        <v>0.05</v>
+      </c>
+      <c r="AL43" s="9">
+        <f t="shared" si="87"/>
+        <v>0.05</v>
+      </c>
+      <c r="AM43" s="9">
+        <f t="shared" si="87"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="44" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>62</v>
       </c>
@@ -5971,254 +6256,262 @@
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" s="9">
-        <f t="shared" ref="J44" si="110">J16/F16-1</f>
+        <f t="shared" ref="J44:R44" si="88">J16/F16-1</f>
         <v>-0.37447698744769875</v>
       </c>
       <c r="K44" s="9">
-        <f t="shared" ref="K44" si="111">K16/G16-1</f>
+        <f t="shared" si="88"/>
         <v>-0.15742793791574283</v>
       </c>
       <c r="L44" s="9">
-        <f t="shared" ref="L44" si="112">L16/H16-1</f>
+        <f t="shared" si="88"/>
         <v>-0.14352941176470591</v>
       </c>
       <c r="M44" s="9">
-        <f t="shared" ref="M44:N44" si="113">M16/I16-1</f>
+        <f t="shared" si="88"/>
         <v>-0.13824884792626724</v>
       </c>
       <c r="N44" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="88"/>
         <v>0.78260869565217384</v>
       </c>
       <c r="O44" s="9">
-        <f t="shared" ref="O44" si="114">O16/K16-1</f>
+        <f t="shared" si="88"/>
         <v>0.18157894736842106</v>
       </c>
       <c r="P44" s="9">
-        <f t="shared" ref="P44" si="115">P16/L16-1</f>
+        <f t="shared" si="88"/>
         <v>0.25824175824175821</v>
       </c>
       <c r="Q44" s="9">
-        <f t="shared" ref="Q44" si="116">Q16/M16-1</f>
+        <f t="shared" si="88"/>
         <v>0.41978609625668462</v>
       </c>
       <c r="R44" s="9">
-        <f t="shared" ref="R44" si="117">R16/N16-1</f>
-        <v>0.31332082551594764</v>
-      </c>
+        <f t="shared" si="88"/>
+        <v>2.4390243902439046E-2</v>
+      </c>
+      <c r="S44" s="9"/>
       <c r="T44" s="9"/>
-      <c r="U44" s="9">
-        <f>U16/T16-1</f>
+      <c r="U44" s="9"/>
+      <c r="V44" s="9"/>
+      <c r="X44" s="9"/>
+      <c r="Y44" s="9">
+        <f t="shared" ref="Y44:AM44" si="89">Y16/X16-1</f>
         <v>0.14098972922502351</v>
       </c>
-      <c r="V44" s="9">
-        <f t="shared" ref="V44:X44" si="118">V16/U16-1</f>
+      <c r="Z44" s="9">
+        <f t="shared" si="89"/>
         <v>0.37234042553191471</v>
       </c>
-      <c r="W44" s="9">
-        <f t="shared" si="118"/>
+      <c r="AA44" s="9">
+        <f t="shared" si="89"/>
         <v>-4.054859868813343E-2</v>
       </c>
-      <c r="X44" s="9">
-        <f t="shared" si="118"/>
+      <c r="AB44" s="9">
+        <f t="shared" si="89"/>
         <v>2.6103169670602888E-2</v>
       </c>
-      <c r="Y44" s="9">
-        <f t="shared" ref="Y44:AI44" si="119">Y16/X16-1</f>
-        <v>0.29497274379164118</v>
-      </c>
-      <c r="Z44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AC44" s="9">
+        <f t="shared" si="89"/>
+        <v>0.20169594185342188</v>
+      </c>
+      <c r="AD44" s="9">
+        <f t="shared" si="89"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AA44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AE44" s="9">
+        <f t="shared" si="89"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AB44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AF44" s="9">
+        <f t="shared" si="89"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AC44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AG44" s="9">
+        <f t="shared" si="89"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AH44" s="9">
+        <f t="shared" si="89"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AI44" s="9">
+        <f t="shared" si="89"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AJ44" s="9">
+        <f t="shared" si="89"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AK44" s="9">
+        <f t="shared" si="89"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AL44" s="9">
+        <f t="shared" si="89"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI44" s="9">
-        <f t="shared" si="119"/>
+      <c r="AM44" s="9">
+        <f t="shared" si="89"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>63</v>
       </c>
       <c r="F45" s="9">
-        <f t="shared" ref="F45:L45" si="120">F18/F7</f>
+        <f t="shared" ref="F45:R45" si="90">F18/F7</f>
         <v>-8.7783783783783931E-2</v>
       </c>
       <c r="G45" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="90"/>
         <v>-0.23110465116279069</v>
       </c>
       <c r="H45" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="90"/>
         <v>-0.18172757475083048</v>
       </c>
       <c r="I45" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="90"/>
         <v>-0.25937031484257872</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="90"/>
         <v>3.5864387783692941E-2</v>
       </c>
       <c r="K45" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="90"/>
         <v>-0.20918367346938757</v>
       </c>
       <c r="L45" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="90"/>
         <v>-6.9109323801012784E-2</v>
       </c>
       <c r="M45" s="9">
-        <f>M18/M7</f>
+        <f t="shared" si="90"/>
         <v>-2.9046898638426518E-2</v>
       </c>
       <c r="N45" s="9">
-        <f>N18/N7</f>
+        <f t="shared" si="90"/>
         <v>0.18291404612159323</v>
       </c>
       <c r="O45" s="9">
-        <f t="shared" ref="O45:R45" si="121">O18/O7</f>
+        <f t="shared" si="90"/>
         <v>-5.8570990493713476E-2</v>
       </c>
       <c r="P45" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="90"/>
         <v>-8.7238285144565237E-3</v>
       </c>
       <c r="Q45" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="90"/>
         <v>1.5411288769023309E-2</v>
       </c>
       <c r="R45" s="9">
-        <f t="shared" si="121"/>
-        <v>0.14129876529690361</v>
-      </c>
-      <c r="T45" s="9">
-        <f>T18/T7</f>
+        <f t="shared" si="90"/>
+        <v>0.11251125112511261</v>
+      </c>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="X45" s="9">
+        <f t="shared" ref="X45:AM45" si="91">X18/X7</f>
         <v>-0.10173759758247283</v>
       </c>
-      <c r="U45" s="9">
-        <f>U18/U7</f>
+      <c r="Y45" s="9">
+        <f t="shared" si="91"/>
         <v>-0.11777412055132701</v>
       </c>
-      <c r="V45" s="9">
-        <f t="shared" ref="V45:X45" si="122">V18/V7</f>
+      <c r="Z45" s="9">
+        <f t="shared" si="91"/>
         <v>-0.21756170780520326</v>
       </c>
-      <c r="W45" s="9">
-        <f t="shared" si="122"/>
+      <c r="AA45" s="9">
+        <f t="shared" si="91"/>
         <v>-0.15697892447311179</v>
       </c>
-      <c r="X45" s="9">
-        <f t="shared" si="122"/>
+      <c r="AB45" s="9">
+        <f t="shared" si="91"/>
         <v>1.5402361243045028E-2</v>
       </c>
-      <c r="Y45" s="9">
-        <f t="shared" ref="Y45:AI45" si="123">Y18/Y7</f>
-        <v>4.4829079284146284E-2</v>
-      </c>
-      <c r="Z45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.1047618295817937</v>
-      </c>
-      <c r="AA45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.12167739317924151</v>
-      </c>
-      <c r="AB45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.13270886031921075</v>
-      </c>
       <c r="AC45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.14004207547244707</v>
+        <f t="shared" si="91"/>
+        <v>3.6016007114273052E-2</v>
       </c>
       <c r="AD45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.14717948111134357</v>
+        <f t="shared" si="91"/>
+        <v>0.13623909480868709</v>
       </c>
       <c r="AE45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.15388192399402198</v>
+        <f t="shared" si="91"/>
+        <v>0.16281804715318715</v>
       </c>
       <c r="AF45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.15957864733865226</v>
+        <f t="shared" si="91"/>
+        <v>0.17145363886433332</v>
       </c>
       <c r="AG45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.16430499135558024</v>
+        <f t="shared" si="91"/>
+        <v>0.1750049438607312</v>
       </c>
       <c r="AH45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.16809906071572783</v>
+        <f t="shared" si="91"/>
+        <v>0.18168569838995566</v>
       </c>
       <c r="AI45" s="9">
-        <f t="shared" si="123"/>
-        <v>0.17100166531862374</v>
-      </c>
-    </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.3">
+        <f t="shared" si="91"/>
+        <v>0.18964516941452469</v>
+      </c>
+      <c r="AJ45" s="9">
+        <f t="shared" si="91"/>
+        <v>0.19783584214139363</v>
+      </c>
+      <c r="AK45" s="9">
+        <f t="shared" si="91"/>
+        <v>0.20618114463879694</v>
+      </c>
+      <c r="AL45" s="9">
+        <f t="shared" si="91"/>
+        <v>0.21410894052033866</v>
+      </c>
+      <c r="AM45" s="9">
+        <f t="shared" si="91"/>
+        <v>0.22163509172810575</v>
+      </c>
+    </row>
+    <row r="46" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>34</v>
       </c>
       <c r="F46" s="9">
-        <f t="shared" ref="F46:L46" si="124">F26/F25</f>
+        <f t="shared" ref="F46:L46" si="92">F26/F25</f>
         <v>7.1005917159763218E-2</v>
       </c>
       <c r="G46" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="92"/>
         <v>-4.0268456375838922E-3</v>
       </c>
       <c r="H46" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="92"/>
         <v>-2.8943560057887135E-3</v>
       </c>
       <c r="I46" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="92"/>
         <v>-3.582089552238806E-3</v>
       </c>
       <c r="J46" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="92"/>
         <v>0.16666666666666627</v>
       </c>
       <c r="K46" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="92"/>
         <v>8.7412587412587471E-3</v>
       </c>
       <c r="L46" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="92"/>
         <v>-1.4876033057851241E-2</v>
       </c>
       <c r="M46" s="9">
@@ -6230,116 +6523,120 @@
         <v>3.7950664136622405E-3</v>
       </c>
       <c r="O46" s="9">
-        <f t="shared" ref="O46:R46" si="125">O26/O25</f>
+        <f t="shared" ref="O46:R46" si="93">O26/O25</f>
         <v>-1.7391304347826111E-2</v>
       </c>
       <c r="P46" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="93"/>
         <v>-2.4330900243309032E-2</v>
       </c>
       <c r="Q46" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="93"/>
         <v>-1.3333333333333332E-2</v>
       </c>
       <c r="R46" s="9">
-        <f t="shared" si="125"/>
-        <v>0</v>
-      </c>
-      <c r="T46" s="9">
-        <f>T26/T25</f>
+        <f t="shared" si="93"/>
+        <v>0.39999999999998637</v>
+      </c>
+      <c r="S46" s="9"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="X46" s="9">
+        <f>X26/X25</f>
         <v>-1.6778523489932892E-3</v>
       </c>
-      <c r="U46" s="9">
-        <f>U26/U25</f>
+      <c r="Y46" s="9">
+        <f>Y26/Y25</f>
         <v>-5.2029136316337123E-3</v>
       </c>
-      <c r="V46" s="9">
-        <f t="shared" ref="V46:X46" si="126">V26/V25</f>
+      <c r="Z46" s="9">
+        <f t="shared" ref="Z46:AB46" si="94">Z26/Z25</f>
         <v>-3.5043007327174285E-3</v>
       </c>
-      <c r="W46" s="9">
-        <f t="shared" si="126"/>
+      <c r="AA46" s="9">
+        <f t="shared" si="94"/>
         <v>-6.2030688867123745E-3</v>
       </c>
-      <c r="X46" s="9">
-        <f t="shared" si="126"/>
+      <c r="AB46" s="9">
+        <f t="shared" si="94"/>
         <v>-3.3582089552238487E-2</v>
       </c>
-      <c r="Y46" s="9">
-        <f t="shared" ref="Y46:AI46" si="127">Y26/Y25</f>
-        <v>0.14624410722273648</v>
-      </c>
-      <c r="Z46" s="9">
-        <f t="shared" si="127"/>
+      <c r="AC46" s="9">
+        <f t="shared" ref="AC46:AM46" si="95">AC26/AC25</f>
+        <v>-3.2104637336504198E-2</v>
+      </c>
+      <c r="AD46" s="9">
+        <f t="shared" si="95"/>
         <v>0.05</v>
       </c>
-      <c r="AA46" s="9">
-        <f t="shared" si="127"/>
+      <c r="AE46" s="9">
+        <f t="shared" si="95"/>
         <v>0.05</v>
       </c>
-      <c r="AB46" s="9">
-        <f t="shared" si="127"/>
+      <c r="AF46" s="9">
+        <f t="shared" si="95"/>
         <v>0.05</v>
       </c>
-      <c r="AC46" s="9">
-        <f t="shared" si="127"/>
+      <c r="AG46" s="9">
+        <f t="shared" si="95"/>
+        <v>5.000000000000001E-2</v>
+      </c>
+      <c r="AH46" s="9">
+        <f t="shared" si="95"/>
         <v>0.05</v>
       </c>
-      <c r="AD46" s="9">
-        <f t="shared" si="127"/>
+      <c r="AI46" s="9">
+        <f t="shared" si="95"/>
         <v>0.05</v>
       </c>
-      <c r="AE46" s="9">
-        <f t="shared" si="127"/>
+      <c r="AJ46" s="9">
+        <f t="shared" si="95"/>
         <v>0.05</v>
       </c>
-      <c r="AF46" s="9">
-        <f t="shared" si="127"/>
+      <c r="AK46" s="9">
+        <f t="shared" si="95"/>
         <v>0.05</v>
       </c>
-      <c r="AG46" s="9">
-        <f t="shared" si="127"/>
+      <c r="AL46" s="9">
+        <f t="shared" si="95"/>
         <v>0.05</v>
       </c>
-      <c r="AH46" s="9">
-        <f t="shared" si="127"/>
+      <c r="AM46" s="9">
+        <f t="shared" si="95"/>
         <v>0.05</v>
       </c>
-      <c r="AI46" s="9">
-        <f t="shared" si="127"/>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>35</v>
       </c>
       <c r="F47" s="9">
-        <f t="shared" ref="F47:L47" si="128">F27/F25</f>
+        <f t="shared" ref="F47:L47" si="96">F27/F25</f>
         <v>0</v>
       </c>
       <c r="G47" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="96"/>
         <v>4.5637583892617448E-2</v>
       </c>
       <c r="H47" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="96"/>
         <v>4.3415340086830699E-2</v>
       </c>
       <c r="I47" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="96"/>
         <v>-5.3731343283582094E-3</v>
       </c>
       <c r="J47" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="96"/>
         <v>-8.3333333333333134E-2</v>
       </c>
       <c r="K47" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="96"/>
         <v>-1.7482517482517494E-2</v>
       </c>
       <c r="L47" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="96"/>
         <v>-9.9173553719008271E-3</v>
       </c>
       <c r="M47" s="9">
@@ -6351,205 +6648,213 @@
         <v>3.7950664136622405E-3</v>
       </c>
       <c r="O47" s="9">
-        <f t="shared" ref="O47:R47" si="129">O27/O25</f>
+        <f t="shared" ref="O47:R47" si="97">O27/O25</f>
         <v>-1.7391304347826111E-2</v>
       </c>
       <c r="P47" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="97"/>
         <v>-9.7323600973236134E-3</v>
       </c>
       <c r="Q47" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="97"/>
         <v>4.4444444444444444E-3</v>
       </c>
       <c r="R47" s="9">
-        <f t="shared" si="129"/>
-        <v>0</v>
-      </c>
-      <c r="T47" s="9">
-        <f>T27/T25</f>
+        <f t="shared" si="97"/>
+        <v>0.1199999999999959</v>
+      </c>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="X47" s="9">
+        <f>X27/X25</f>
         <v>0.12024608501118574</v>
       </c>
-      <c r="U47" s="9">
-        <f>U27/U25</f>
+      <c r="Y47" s="9">
+        <f>Y27/Y25</f>
         <v>0.15036420395421426</v>
       </c>
-      <c r="V47" s="9">
-        <f t="shared" ref="V47:X47" si="130">V27/V25</f>
+      <c r="Z47" s="9">
+        <f t="shared" ref="Z47:AB47" si="98">Z27/Z25</f>
         <v>4.3644472762026154E-2</v>
       </c>
-      <c r="W47" s="9">
-        <f t="shared" si="130"/>
+      <c r="AA47" s="9">
+        <f t="shared" si="98"/>
         <v>1.9262161279791058E-2</v>
       </c>
-      <c r="X47" s="9">
-        <f t="shared" si="130"/>
+      <c r="AB47" s="9">
+        <f t="shared" si="98"/>
         <v>-7.8358208955223149E-2</v>
       </c>
-      <c r="Y47" s="9">
-        <f t="shared" ref="Y47:AI47" si="131">Y27/Y25</f>
-        <v>6.0218161797597383E-2</v>
-      </c>
-      <c r="Z47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AC47" s="9">
+        <f t="shared" ref="AC47:AM47" si="99">AC27/AC25</f>
+        <v>-1.189060642092748E-2</v>
+      </c>
+      <c r="AD47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
-      <c r="AA47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AE47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
-      <c r="AB47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AF47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
-      <c r="AC47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AG47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
-      <c r="AD47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AH47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
-      <c r="AE47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AI47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
-      <c r="AF47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AJ47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
-      <c r="AG47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AK47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
-      <c r="AH47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AL47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
-      <c r="AI47" s="9">
-        <f t="shared" si="131"/>
+      <c r="AM47" s="9">
+        <f t="shared" si="99"/>
         <v>0.02</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>64</v>
       </c>
       <c r="F48" s="9">
-        <f t="shared" ref="F48:L48" si="132">F28/F7</f>
+        <f t="shared" ref="F48:R48" si="100">F28/F7</f>
         <v>-0.10183783783783799</v>
       </c>
       <c r="G48" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="100"/>
         <v>-0.25944767441860461</v>
       </c>
       <c r="H48" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="100"/>
         <v>-0.22026578073089689</v>
       </c>
       <c r="I48" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="100"/>
         <v>-0.42228885557221391</v>
       </c>
       <c r="J48" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="100"/>
         <v>1.2328383300644471E-2</v>
       </c>
       <c r="K48" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="100"/>
         <v>-0.24532312925170049</v>
       </c>
       <c r="L48" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="100"/>
         <v>-0.18468871015787905</v>
       </c>
       <c r="M48" s="9">
-        <f>M28/M7</f>
+        <f t="shared" si="100"/>
         <v>-4.4478063540090665E-2</v>
       </c>
       <c r="N48" s="9">
-        <f>N28/N7</f>
+        <f t="shared" si="100"/>
         <v>0.18273934311670154</v>
       </c>
       <c r="O48" s="9">
-        <f t="shared" ref="O48:R48" si="133">O28/O7</f>
+        <f t="shared" si="100"/>
         <v>-7.2983747316773886E-2</v>
       </c>
       <c r="P48" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="100"/>
         <v>-0.10593220338983039</v>
       </c>
       <c r="Q48" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="100"/>
         <v>-4.3729531882103635E-2</v>
       </c>
       <c r="R48" s="9">
-        <f t="shared" si="133"/>
-        <v>0.13445451309989864</v>
-      </c>
-      <c r="T48" s="9">
-        <f>T28/T7</f>
+        <f t="shared" si="100"/>
+        <v>1.5430114440016525E-3</v>
+      </c>
+      <c r="S48" s="9"/>
+      <c r="T48" s="9"/>
+      <c r="U48" s="9"/>
+      <c r="V48" s="9"/>
+      <c r="X48" s="9">
+        <f t="shared" ref="X48:AM48" si="101">X28/X7</f>
         <v>-0.19843868043314017</v>
       </c>
-      <c r="U48" s="9">
-        <f>U28/U7</f>
+      <c r="Y48" s="9">
+        <f t="shared" si="101"/>
         <v>-0.16899814852910935</v>
       </c>
-      <c r="V48" s="9">
-        <f t="shared" ref="V48:X48" si="134">V28/V7</f>
+      <c r="Z48" s="9">
+        <f t="shared" si="101"/>
         <v>-0.25125083388925934</v>
       </c>
-      <c r="W48" s="9">
-        <f t="shared" si="134"/>
+      <c r="AA48" s="9">
+        <f t="shared" si="101"/>
         <v>-0.22673066826670665</v>
       </c>
-      <c r="X48" s="9">
-        <f t="shared" si="134"/>
+      <c r="AB48" s="9">
+        <f t="shared" si="101"/>
         <v>-2.0219839869724695E-2</v>
       </c>
-      <c r="Y48" s="9">
-        <f t="shared" ref="Y48:AI48" si="135">Y28/Y7</f>
-        <v>4.6659989681022956E-3</v>
-      </c>
-      <c r="Z48" s="9">
-        <f t="shared" si="135"/>
-        <v>8.681867240799658E-2</v>
-      </c>
-      <c r="AA48" s="9">
-        <f t="shared" si="135"/>
-        <v>0.10391412001853949</v>
-      </c>
-      <c r="AB48" s="9">
-        <f t="shared" si="135"/>
-        <v>0.11513880755746307</v>
-      </c>
       <c r="AC48" s="9">
-        <f t="shared" si="135"/>
-        <v>0.12263533473840643</v>
+        <f t="shared" si="101"/>
+        <v>-4.3377303492910385E-2</v>
       </c>
       <c r="AD48" s="9">
-        <f t="shared" si="135"/>
-        <v>0.12990182299260827</v>
+        <f t="shared" si="101"/>
+        <v>0.12047144236107285</v>
       </c>
       <c r="AE48" s="9">
-        <f t="shared" si="135"/>
-        <v>0.13672390635717921</v>
+        <f t="shared" si="101"/>
+        <v>0.14647896196782992</v>
       </c>
       <c r="AF48" s="9">
-        <f t="shared" si="135"/>
-        <v>0.14257223086185267</v>
+        <f t="shared" si="101"/>
+        <v>0.15510546412588808</v>
       </c>
       <c r="AG48" s="9">
-        <f t="shared" si="135"/>
-        <v>0.14748114010144714</v>
+        <f t="shared" si="101"/>
+        <v>0.15875741943121635</v>
       </c>
       <c r="AH48" s="9">
-        <f t="shared" si="135"/>
-        <v>0.15148756810038627</v>
+        <f t="shared" si="101"/>
+        <v>0.1652432336346483</v>
       </c>
       <c r="AI48" s="9">
-        <f t="shared" si="135"/>
-        <v>0.15463097746161467</v>
+        <f t="shared" si="101"/>
+        <v>0.17287607911372549</v>
+      </c>
+      <c r="AJ48" s="9">
+        <f t="shared" si="101"/>
+        <v>0.18071133752472335</v>
+      </c>
+      <c r="AK48" s="9">
+        <f t="shared" si="101"/>
+        <v>0.18867831059088569</v>
+      </c>
+      <c r="AL48" s="9">
+        <f t="shared" si="101"/>
+        <v>0.19624542280411378</v>
+      </c>
+      <c r="AM48" s="9">
+        <f t="shared" si="101"/>
+        <v>0.20342793251852662</v>
       </c>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.3">
@@ -6666,7 +6971,7 @@
         <v>597.19999999999993</v>
       </c>
     </row>
-    <row r="65" spans="2:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B65" s="12" t="s">
         <v>91</v>
       </c>
@@ -6677,8 +6982,12 @@
       <c r="Q65" s="11">
         <v>2638.2</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R65" s="11">
+        <f>4396.7</f>
+        <v>4396.7</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>92</v>
       </c>
@@ -6686,7 +6995,7 @@
         <v>144.80000000000001</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>93</v>
       </c>
@@ -6694,7 +7003,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>94</v>
       </c>
@@ -6702,7 +7011,7 @@
         <v>116.6</v>
       </c>
     </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>84</v>
       </c>
@@ -6710,7 +7019,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>88</v>
       </c>
@@ -6718,7 +7027,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>5</v>
       </c>
@@ -6726,7 +7035,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>95</v>
       </c>
@@ -6734,7 +7043,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>96</v>
       </c>
@@ -6742,7 +7051,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="74" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
         <v>97</v>
       </c>
@@ -6751,7 +7060,7 @@
         <v>387.4</v>
       </c>
     </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>84</v>
       </c>
@@ -6759,7 +7068,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>88</v>
       </c>
@@ -6767,7 +7076,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>5</v>
       </c>
@@ -6775,7 +7084,7 @@
         <v>219.9</v>
       </c>
     </row>
-    <row r="78" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>95</v>
       </c>
@@ -6783,7 +7092,7 @@
         <v>1126.2</v>
       </c>
     </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>96</v>
       </c>
@@ -6791,7 +7100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>98</v>
       </c>
@@ -6829,5 +7138,6 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>